--- a/수요예측_일정.xlsx
+++ b/수요예측_일정.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체 이력" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'수요예측 일정'!$A$1:$K$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체 이력'!$A$1:$K$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'수요예측 일정'!$A$1:$K$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체 이력'!$A$1:$K$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -539,169 +539,169 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>인터엑스</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5700, 6648</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2026년 11월 18일(수) ~ 2026년 12월 4일(금)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026년 12월 8일(화)</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>유캐스트</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>2026년 10월 28일(수) ~ 2026년 11월 06일(금)</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>2026년 11월 17일(화)</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>옵토닉스</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>2026년 10월 14일(수) ~ 2026년 10월 23일(금)</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>2026년 10월 29일(목)</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>이노보테라퓨틱스</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-02</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>2026년 11월 16일(월) ~ 2026년 12월 01일(화)</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2026년 12월 04일(금)</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -710,169 +710,169 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>이노보테라퓨틱스</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>2026년 11월 16일(월) ~ 2026년 12월 01일(화)</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026년 12월 04일(금)</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>2026-11-19</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>2026-11-25</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>NH투자증권 02-2229-6315, 6829</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>2026년 11월 17일(화) ~ 2026년 11월 25일(수)</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>2026년 11월 26일(목)</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>이에스티</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>2026년 10월 14일(수) ~ 2026년 10월 20일(화)</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>2026년 10월 21일(수)</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>에스에프씨</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 28일(수) ~ 2026년 11월 12일(목)</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 17일(화)</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -886,7 +886,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>씨아이에스케미칼</t>
+          <t>에스에프씨</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
+          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>2026년 11월 23일(월) ~ 2026년 12월 04일(금)</t>
+          <t>2026년 10월 28일(수) ~ 2026년 11월 12일(목)</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026년 12월 08일(화)</t>
+          <t>2026년 11월 17일(화)</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
@@ -938,12 +938,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>제이앤티지</t>
+          <t>씨아이에스케미칼</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -973,17 +973,17 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
+          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>2026년 11월 03일(화) ~ 2026년 11월 09일(월)</t>
+          <t>2026년 11월 23일(월) ~ 2026년 12월 04일(금)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026년 11월 11일(수)</t>
+          <t>2026년 12월 08일(화)</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -1000,107 +1000,107 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>제이앤티지</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>2026년 11월 03일(화) ~ 2026년 11월 09일(월)</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2026년 11월 11일(수)</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>씨앤엠</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>2026년 10월 26일(월) ~ 2026년 11월 6일(금)</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>2026년 11월 11일(수)</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>넥스아이</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>2026년 10월 23일(금)</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>2026년 10월 30일(금)</t>
-        </is>
-      </c>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1129,12 +1129,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1144,17 +1144,17 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
+          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>2026년 10월 29일(목) ~ 2026년 11월 05일(목)</t>
+          <t>2026년 10월 23일(금)</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>2026년 11월 09일(월)</t>
+          <t>2026년 10월 30일(금)</t>
         </is>
       </c>
       <c r="K12" s="8" t="inlineStr">
@@ -1166,169 +1166,169 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>하나에어로다이내믹스</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>2026년 10월 29일(목) ~ 2026년 11월 05일(목)</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>2026년 11월 09일(월)</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>바로팜</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>2026년 10월 12일(월) ~ 2026년 10월 21일(수)</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>2026년 10월 30일(금)</t>
         </is>
       </c>
-      <c r="K13" s="8" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>엠비디</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>2026년 10월 26일(월) ~ 2026년 11월 03일(화)</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>2026년 11월 10일(화)</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>래블업</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>NH투자증권 02-768-7462, 7467</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>2026년 10월 6일(화) ~ 2026년 10월 16일(금)</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>2026년 10월 21일(수)</t>
-        </is>
-      </c>
-      <c r="K15" s="8" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1337,112 +1337,112 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>래블업</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>NH투자증권 02-768-7462, 7467</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>2026년 10월 6일(화) ~ 2026년 10월 16일(금)</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>2026년 10월 21일(수)</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>에이엘로봇</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>정정-변경(수요예측)</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>2026년 10월 28일(수) ~ 2026년 11월 03일(화)</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>2026년 11월 04일(수)</t>
         </is>
       </c>
-      <c r="K16" s="8" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>아델</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>2026년 11월 2일(월) ~ 2026년 11월 17일(화)</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 20일(금)</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K17" s="8" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SimwonAmericaCorp.</t>
+          <t>아델</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1466,15 +1466,39 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>수요예측 항목 없음(원문 확인)</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr"/>
-      <c r="I18" s="3" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>2026년 11월 2일(월) ~ 2026년 11월 17일(화)</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2026년 11월 20일(금)</t>
+        </is>
+      </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
           <t>열기</t>
@@ -1484,54 +1508,30 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>다비오</t>
+          <t>SimwonAmericaCorp.</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 19일(월) ~ 2026년 10월 28일(수)</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 9일(월)</t>
-        </is>
-      </c>
+          <t>수요예측 항목 없음(원문 확인)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="4" t="inlineStr">
         <is>
           <t>열기</t>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>엔키화이트햇</t>
+          <t>다비오</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1561,26 +1561,34 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
+          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>2026년 10월 30일(금) ~ 2026년 11월 05일(목)</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr"/>
+          <t>2026년 10월 19일(월) ~ 2026년 10월 28일(수)</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2026년 11월 9일(월)</t>
+        </is>
+      </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
           <t>열기</t>
@@ -1595,164 +1603,156 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
+          <t>엔키화이트햇</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>2026년 10월 30일(금) ~ 2026년 11월 05일(목)</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>영광와이케이엠씨</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>2026년 10월 27일(화) ~ 2026년 11월 02일(월)</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>2026년 11월 03일(화)</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>영광</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>2026년 10월 6일(화) ~ 2026년 10월 16일(금)</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>2026년 10월 21일(수)</t>
         </is>
       </c>
-      <c r="K22" s="8" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>인텔리빅스</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 12일(월) ~ 2026년 10월 16일(금)</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>2026년 10월 20일(화)</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
+      <c r="K23" s="8" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1761,17 +1761,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>제논</t>
+          <t>인텔리빅스</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1796,17 +1796,17 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-8023, 7653, 7850</t>
+          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>2026년 10월 12일(월) ~ 2026년 10월 23일(금)</t>
+          <t>2026년 10월 12일(월) ~ 2026년 10월 16일(금)</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026년 11월 03일(화)</t>
+          <t>2026년 10월 20일(화)</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -1818,12 +1818,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>케이엠에프</t>
+          <t>제논</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
+          <t>삼성증권 02-2020-8023, 7653, 7850</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>2026년 10월 19일(월) ~ 2026년 11월 13일(금)</t>
+          <t>2026년 10월 12일(월) ~ 2026년 10월 23일(금)</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026년 11월 23일(월)</t>
+          <t>2026년 11월 03일(화)</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -1875,17 +1875,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>디티에스</t>
+          <t>케이엠에프</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1910,17 +1910,17 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>2026년 10월 01일(목) ~ 2026년 10월 08일(목)</t>
+          <t>2026년 10월 19일(월) ~ 2026년 11월 13일(금)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026년 10월 12일(월)</t>
+          <t>2026년 11월 23일(월)</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
@@ -1932,12 +1932,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>엠에스바이오</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1967,17 +1967,17 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
+          <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>2026년 09월 11일(금) ~ 2026년 10월 02일(금)</t>
+          <t>2026년 10월 01일(목) ~ 2026년 10월 08일(목)</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2026년 10월 07일(수)</t>
+          <t>2026년 10월 12일(월)</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
@@ -1989,32 +1989,32 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>엠에스바이오</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>크리에이츠</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2024,17 +2024,17 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-7414, 7375, 7651</t>
+          <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>2026년 09월 28일(월) ~ 2026년 10월 16일(금)</t>
+          <t>2026년 09월 11일(금) ~ 2026년 10월 02일(금)</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>2026년 10월 19일(월)</t>
+          <t>2026년 10월 07일(수)</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
@@ -2046,58 +2046,115 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>크리에이츠</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-7414, 7375, 7651</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>2026년 09월 28일(월) ~ 2026년 10월 16일(금)</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>2026년 10월 19일(월)</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>티앤이코리아</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>2026년 9월 8일(화) ~ 2026년 10월 13일(화)</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="4" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="4" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K29"/>
+  <autoFilter ref="A1:K30"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -2127,6 +2184,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2138,7 +2196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2214,169 +2272,169 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>인터엑스</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5700, 6648</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2026년 11월 18일(수) ~ 2026년 12월 4일(금)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026년 12월 8일(화)</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>유캐스트</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>2026년 10월 28일(수) ~ 2026년 11월 06일(금)</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>2026년 11월 17일(화)</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>옵토닉스</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>2026년 10월 14일(수) ~ 2026년 10월 23일(금)</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>2026년 10월 29일(목)</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>이노보테라퓨틱스</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-02</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>2026년 11월 16일(월) ~ 2026년 12월 01일(화)</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2026년 12월 04일(금)</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2385,169 +2443,169 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>이노보테라퓨틱스</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>2026년 11월 16일(월) ~ 2026년 12월 01일(화)</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026년 12월 04일(금)</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>2026-11-19</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>2026-11-25</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>NH투자증권 02-2229-6315, 6829</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>2026년 11월 17일(화) ~ 2026년 11월 25일(수)</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>2026년 11월 26일(목)</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>이에스티</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>2026년 10월 14일(수) ~ 2026년 10월 20일(화)</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>2026년 10월 21일(수)</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>에스에프씨</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 28일(수) ~ 2026년 11월 12일(목)</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 17일(화)</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2561,7 +2619,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>씨아이에스케미칼</t>
+          <t>에스에프씨</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -2576,12 +2634,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2591,17 +2649,17 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
+          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>2026년 11월 23일(월) ~ 2026년 12월 04일(금)</t>
+          <t>2026년 10월 28일(수) ~ 2026년 11월 12일(목)</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026년 12월 08일(화)</t>
+          <t>2026년 11월 17일(화)</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
@@ -2613,12 +2671,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>제이앤티지</t>
+          <t>씨아이에스케미칼</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -2633,12 +2691,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2648,17 +2706,17 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
+          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>2026년 11월 03일(화) ~ 2026년 11월 09일(월)</t>
+          <t>2026년 11월 23일(월) ~ 2026년 12월 04일(금)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026년 11월 11일(수)</t>
+          <t>2026년 12월 08일(화)</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -2675,107 +2733,107 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>제이앤티지</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>2026년 11월 03일(화) ~ 2026년 11월 09일(월)</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2026년 11월 11일(수)</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>씨앤엠</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>2026년 10월 26일(월) ~ 2026년 11월 6일(금)</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>2026년 11월 11일(수)</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>넥스아이</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>2026년 10월 23일(금)</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>2026년 10월 30일(금)</t>
-        </is>
-      </c>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2789,7 +2847,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -2804,12 +2862,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -2819,17 +2877,17 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
+          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>2026년 10월 29일(목) ~ 2026년 11월 05일(목)</t>
+          <t>2026년 10월 23일(금)</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>2026년 11월 09일(월)</t>
+          <t>2026년 10월 30일(금)</t>
         </is>
       </c>
       <c r="K12" s="8" t="inlineStr">
@@ -2841,169 +2899,169 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>하나에어로다이내믹스</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>2026년 10월 29일(목) ~ 2026년 11월 05일(목)</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>2026년 11월 09일(월)</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>바로팜</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>2026년 10월 12일(월) ~ 2026년 10월 21일(수)</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>2026년 10월 30일(금)</t>
         </is>
       </c>
-      <c r="K13" s="8" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>엠비디</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>2026년 10월 26일(월) ~ 2026년 11월 03일(화)</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>2026년 11월 10일(화)</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>래블업</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>NH투자증권 02-768-7462, 7467</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>2026년 10월 6일(화) ~ 2026년 10월 16일(금)</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>2026년 10월 21일(수)</t>
-        </is>
-      </c>
-      <c r="K15" s="8" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3012,32 +3070,32 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>래블업</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>이에스티</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -3047,12 +3105,12 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+          <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>2026년 10월 14일(수) ~ 2026년 10월 20일(화)</t>
+          <t>2026년 10월 6일(화) ~ 2026년 10월 16일(금)</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -3069,112 +3127,112 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>이에스티</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>2026년 10월 14일(수) ~ 2026년 10월 20일(화)</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>2026년 10월 21일(수)</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>에이엘로봇</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>정정-변경(수요예측)</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>2026년 10월 28일(수) ~ 2026년 11월 03일(화)</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>2026년 11월 04일(수)</t>
         </is>
       </c>
-      <c r="K17" s="8" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>아델</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>2026년 11월 2일(월) ~ 2026년 11월 17일(화)</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 20일(금)</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="K18" s="8" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3188,7 +3246,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SimwonAmericaCorp.</t>
+          <t>아델</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -3198,15 +3256,39 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>수요예측 항목 없음(원문 확인)</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>2026년 11월 2일(월) ~ 2026년 11월 17일(화)</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2026년 11월 20일(금)</t>
+        </is>
+      </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
           <t>열기</t>
@@ -3216,54 +3298,30 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>다비오</t>
+          <t>SimwonAmericaCorp.</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 19일(월) ~ 2026년 10월 28일(수)</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 9일(월)</t>
-        </is>
-      </c>
+          <t>수요예측 항목 없음(원문 확인)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="4" t="inlineStr">
         <is>
           <t>열기</t>
@@ -3278,12 +3336,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>엔키화이트햇</t>
+          <t>다비오</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3293,26 +3351,34 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
+          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>2026년 10월 30일(금) ~ 2026년 11월 05일(목)</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr"/>
+          <t>2026년 10월 19일(월) ~ 2026년 10월 28일(수)</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>2026년 11월 9일(월)</t>
+        </is>
+      </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
           <t>열기</t>
@@ -3327,164 +3393,156 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
+          <t>엔키화이트햇</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>2026년 10월 30일(금) ~ 2026년 11월 05일(목)</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>영광와이케이엠씨</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>2026년 10월 27일(화) ~ 2026년 11월 02일(월)</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>2026년 11월 03일(화)</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>영광</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>2026년 10월 6일(화) ~ 2026년 10월 16일(금)</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>2026년 10월 21일(수)</t>
         </is>
       </c>
-      <c r="K23" s="8" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>인텔리빅스</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 12일(월) ~ 2026년 10월 16일(금)</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>2026년 10월 20일(화)</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="K24" s="8" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3493,169 +3551,169 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>인텔리빅스</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>2026년 10월 12일(월) ~ 2026년 10월 16일(금)</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2026년 10월 20일(화)</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>제논</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-8023, 7653, 7850</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>2026년 10월 12일(월) ~ 2026년 10월 23일(금)</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>2026년 11월 03일(화)</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>래블업</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>2026년 10월 6일(화) ~ 2026년 10월 16일(금)</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>2026년 10월 21일(수)</t>
         </is>
       </c>
-      <c r="K26" s="8" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>케이엠에프</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-20</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 19일(월) ~ 2026년 11월 13일(금)</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 23일(월)</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
+      <c r="K27" s="8" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3664,17 +3722,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>바로팜</t>
+          <t>케이엠에프</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3684,12 +3742,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3699,17 +3757,17 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>2026년 10월 12일(월) ~ 2026년 10월 21일(수)</t>
+          <t>2026년 10월 19일(월) ~ 2026년 11월 13일(금)</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>2026년 10월 30일(금)</t>
+          <t>2026년 11월 23일(월)</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
@@ -3726,7 +3784,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>디티에스</t>
+          <t>바로팜</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -3741,12 +3799,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3756,17 +3814,17 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
+          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>2026년 10월 01일(목) ~ 2026년 10월 08일(목)</t>
+          <t>2026년 10월 12일(월) ~ 2026년 10월 21일(수)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2026년 10월 12일(월)</t>
+          <t>2026년 10월 30일(금)</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
@@ -3778,12 +3836,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>엠에스바이오</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -3798,12 +3856,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3813,17 +3871,17 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
+          <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>2026년 09월 11일(금) ~ 2026년 10월 02일(금)</t>
+          <t>2026년 10월 01일(목) ~ 2026년 10월 08일(목)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026년 10월 07일(수)</t>
+          <t>2026년 10월 12일(월)</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
@@ -3840,12 +3898,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>옵토닉스</t>
+          <t>엠에스바이오</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -3855,12 +3913,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3870,17 +3928,17 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>한국투자증권 02-3276-5958, 6269</t>
+          <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>2026년 10월 14일(수) ~ 2026년 10월 23일(금)</t>
+          <t>2026년 09월 11일(금) ~ 2026년 10월 02일(금)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026년 10월 29일(목)</t>
+          <t>2026년 10월 07일(수)</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
@@ -3892,12 +3950,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>넥스아이</t>
+          <t>옵토닉스</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -3912,12 +3970,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,17 +3985,17 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
+          <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>2026년 10월 14일(수)</t>
+          <t>2026년 10월 14일(수) ~ 2026년 10월 23일(금)</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>2026년 10월 30일(금)</t>
+          <t>2026년 10월 29일(목)</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
@@ -3954,12 +4012,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -3969,12 +4027,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -3984,17 +4042,17 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-7414, 7375, 7651</t>
+          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>2026년 09월 28일(월) ~ 2026년 10월 16일(금)</t>
+          <t>2026년 10월 14일(수)</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2026년 10월 19일(월)</t>
+          <t>2026년 10월 30일(금)</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
@@ -4006,12 +4064,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>티앤이코리아</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -4026,12 +4084,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4041,15 +4099,19 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
+          <t>삼성증권 02-2020-7414, 7375, 7651</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>2026년 9월 8일(화) ~ 2026년 10월 13일(화)</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr"/>
+          <t>2026년 09월 28일(월) ~ 2026년 10월 16일(금)</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>2026년 10월 19일(월)</t>
+        </is>
+      </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
           <t>열기</t>
@@ -4059,17 +4121,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>티앤이코리아</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4079,12 +4141,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4094,19 +4156,15 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
+          <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>2026년 10월 29일(목) ~ 2026년 11월 05일(목)</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 09일(월)</t>
-        </is>
-      </c>
+          <t>2026년 9월 8일(화) ~ 2026년 10월 13일(화)</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="4" t="inlineStr">
         <is>
           <t>열기</t>
@@ -4121,12 +4179,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>래블업</t>
+          <t>하나에어로다이내믹스</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4136,12 +4194,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4151,17 +4209,17 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>NH투자증권 02-768-7462, 7467</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>2026년 10월 6일(화) ~ 2026년 10월 16일(금)</t>
+          <t>2026년 10월 29일(목) ~ 2026년 11월 05일(목)</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2026년 10월 21일(수)</t>
+          <t>2026년 11월 09일(월)</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
@@ -4178,12 +4236,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>영광</t>
+          <t>래블업</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4208,7 +4266,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+          <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -4235,7 +4293,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>이에스티</t>
+          <t>영광</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -4250,12 +4308,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4265,12 +4323,12 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>2026년 10월 14일(수) ~ 2026년 10월 20일(화)</t>
+          <t>2026년 10월 6일(화) ~ 2026년 10월 16일(금)</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4292,57 +4350,114 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
+          <t>이에스티</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>2026년 10월 14일(수) ~ 2026년 10월 20일(화)</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>2026년 10월 21일(수)</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>에이엘로봇</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
+      <c r="I40" s="3" t="inlineStr">
         <is>
           <t>2026년 10월 15일(목) ~ 2026년 10월 21일(수)</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>2026년 10월 22일(목)</t>
         </is>
       </c>
-      <c r="K39" s="4" t="inlineStr">
+      <c r="K40" s="4" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K39"/>
+  <autoFilter ref="A1:K40"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -4382,6 +4497,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/수요예측_일정.xlsx
+++ b/수요예측_일정.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체 이력" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'수요예측 일정'!$A$1:$K$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체 이력'!$A$1:$K$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'수요예측 일정'!$A$1:$L$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체 이력'!$A$1:$L$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="4">
     <font>
       <name val="Calibri"/>
@@ -72,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -82,6 +84,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -93,6 +101,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -463,20 +477,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="48" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -492,45 +507,50 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>업종</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>보고서명</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>수요예측 시작</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>수요예측 종료</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>마감시각</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>공모가 밴드</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>기관 최대 참여수량(주)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>최대 참여금액(밴드 상단, 억원)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>국내기관 문의처</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>기업IR 기간</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>공모가 확정공고</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>DART</t>
         </is>
@@ -549,45 +569,46 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
+          <t>응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>2026-11-30</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>2026-12-04</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>10,000 ~ 13,000원</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>2250000</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5700, 6648</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2026년 11월 18일(수) ~ 2026년 12월 4일(금)</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>2026년 12월 8일(화)</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -606,102 +627,104 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>기타 무선 통신장비 제조업</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>19,000 ~ 23,000원</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>600000</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>138</v>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 28일(수) ~ 2026년 11월 06일(금)</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 17일(화)</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>옵토닉스</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>광학렌즈 및 광학요소 제조업</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>10,000 ~ 12,000원</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>1572490</v>
+      </c>
+      <c r="J4" s="11" t="n">
+        <v>188.7</v>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>2026년 10월 14일(수) ~ 2026년 10월 23일(금)</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>2026년 10월 29일(목)</t>
-        </is>
-      </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -720,45 +743,46 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>의학 및 약학 연구개발업</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>2026-11-26</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>2026-12-02</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>20,000 ~ 24,000원</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>396</v>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>2026년 11월 16일(월) ~ 2026년 12월 01일(화)</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2026년 12월 04일(금)</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="L5" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -777,102 +801,104 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
+          <t>기타 엔지니어링 서비스업</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>2026-11-19</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2026-11-25</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>11,200 ~ 13,600원</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>1575000</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>214.2</v>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>NH투자증권 02-2229-6315, 6829</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>2026년 11월 17일(화) ~ 2026년 11월 25일(수)</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 26일(목)</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="L6" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>이에스티</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>그 외 기타 전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>10,600 ~ 12,400원</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>204.6</v>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>2026년 10월 14일(수) ~ 2026년 10월 20일(화)</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>2026년 10월 21일(수)</t>
-        </is>
-      </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="L7" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -891,45 +917,46 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
+          <t>그 외 기타 분류 안된 화학제품 제조업</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>31,600 ~ 36,100원</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>1353.8</v>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 28일(수) ~ 2026년 11월 12일(목)</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 17일(화)</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="L8" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -948,45 +975,46 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
+          <t>알루미늄 제련, 정련 및 합금 제조업</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>2026-11-30</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>2026-12-04</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>5,400 ~ 6,800원</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>204</v>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>2026년 11월 23일(월) ~ 2026년 12월 04일(금)</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2026년 12월 08일(화)</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="L9" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1005,45 +1033,46 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>그 외 자동차용 신품 부품 제조업</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>26,400 ~ 31,900원</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>3182000</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>1015.1</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>2026년 11월 03일(화) ~ 2026년 11월 09일(월)</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 11일(수)</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="L10" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1062,216 +1091,220 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
+          <t>전동기 및 발전기 제조업</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>10,000 ~ 13,000원</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>2059500</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>267.7</v>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 26일(월) ~ 2026년 11월 6일(금)</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 11일(수)</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="L11" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>넥스아이</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>의학 및 약학 연구개발업</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>10,500 ~ 13,000원</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="J12" s="11" t="n">
+        <v>487.5</v>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-6384, 5198</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>2026년 10월 23일(금)</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>2026년 10월 30일(금)</t>
-        </is>
-      </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="L12" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>하나에어로다이내믹스</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>항공기용 부품 제조업</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>4,700 ~ 5,700원</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>188.1</v>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
         <is>
           <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>2026년 10월 29일(목) ~ 2026년 11월 05일(목)</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>2026년 11월 09일(월)</t>
-        </is>
-      </c>
-      <c r="K13" s="8" t="inlineStr">
+      <c r="L13" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>바로팜</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>전자상거래 소매 중개업</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>16,400 ~ 20,200원</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="n">
+        <v>1335000</v>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>269.7</v>
+      </c>
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>2026년 10월 12일(월) ~ 2026년 10월 21일(수)</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>2026년 10월 30일(금)</t>
-        </is>
-      </c>
-      <c r="K14" s="8" t="inlineStr">
+      <c r="L14" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1290,159 +1323,162 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
+          <t>물질 검사, 측정 및 분석기구 제조업</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>9,600 ~ 11,700원</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>175.5</v>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 26일(월) ~ 2026년 11월 03일(화)</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 10일(화)</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="L15" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>래블업</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>시스템 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>19,000 ~ 22,000원</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>1635000</v>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>359.7</v>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
         <is>
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>2026년 10월 6일(화) ~ 2026년 10월 16일(금)</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>2026년 10월 21일(수)</t>
-        </is>
-      </c>
-      <c r="K16" s="8" t="inlineStr">
+      <c r="L16" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>에이엘로봇</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>기타 기계 및 장비 제조업</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>정정-변경(수요예측)</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>15,700 ~ 17,600원</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>316.8</v>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>2026년 10월 28일(수) ~ 2026년 11월 03일(화)</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>2026년 11월 04일(수)</t>
-        </is>
-      </c>
-      <c r="K17" s="8" t="inlineStr">
+      <c r="L17" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1461,45 +1497,46 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
+          <t>의학 및 약학 연구개발업</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>2026-11-12</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>2026-11-18</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>18,000 ~ 25,000원</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>1627500</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>406.9</v>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>2026년 11월 2일(월) ~ 2026년 11월 17일(화)</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 20일(금)</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="L18" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1518,21 +1555,26 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
+          <t>자동차 신품 부품 제조업</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>수요예측 항목 없음(원문 확인)</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1551,45 +1593,46 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
+          <t>응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>12,300 ~ 16,600원</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>750000</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 19일(월) ~ 2026년 10월 28일(수)</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 9일(월)</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="L20" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1608,37 +1651,46 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
+          <t>응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>13,000 ~ 16,500원</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>1258000</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>207.6</v>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 30일(금) ~ 2026년 11월 05일(목)</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="L21" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1657,102 +1709,104 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
+          <t>그 외 기타 금속가공업</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>9,400 ~ 11,000원</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>1694840</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>186.4</v>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 27일(화) ~ 2026년 11월 02일(월)</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 03일(화)</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="L22" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>영광</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>수상 금속 골조 구조재 제조업</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>14,000 ~ 17,000원</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="n">
+        <v>1695000</v>
+      </c>
+      <c r="J23" s="11" t="n">
+        <v>288.1</v>
+      </c>
+      <c r="K23" s="8" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>2026년 10월 6일(화) ~ 2026년 10월 16일(금)</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>2026년 10월 21일(수)</t>
-        </is>
-      </c>
-      <c r="K23" s="8" t="inlineStr">
+      <c r="L23" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1771,45 +1825,46 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
+          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>7,600 ~ 9,000원</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>1875000</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>168.8</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
         <is>
           <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 12일(월) ~ 2026년 10월 16일(금)</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>2026년 10월 20일(화)</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="L24" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1828,45 +1883,46 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
+          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>9,700 ~ 12,200원</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>1550000</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>189.1</v>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-8023, 7653, 7850</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 12일(월) ~ 2026년 10월 23일(금)</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 03일(화)</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="L25" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1885,45 +1941,46 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
+          <t>기타 식품 제조업</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>2026-11-16</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>15,000 ~ 17,800원</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>267</v>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 19일(월) ~ 2026년 11월 13일(금)</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 23일(월)</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
+      <c r="L26" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1942,45 +1999,46 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
+          <t>특수 목적용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>17,000 ~ 18,500원</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>1671687</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>309.3</v>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 01일(목) ~ 2026년 10월 08일(목)</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>2026년 10월 12일(월)</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
+      <c r="L27" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1999,45 +2057,46 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
+          <t>그 외 기타 의료용 기기 제조업</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>6,800 ~ 7,800원</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>2840000</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>221.5</v>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
         <is>
           <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>2026년 09월 11일(금) ~ 2026년 10월 02일(금)</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>2026년 10월 07일(수)</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
+      <c r="L28" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2056,45 +2115,46 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
+          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>15,000 ~ 18,000원</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>1050000</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>189</v>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-7414, 7375, 7651</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>2026년 09월 28일(월) ~ 2026년 10월 16일(금)</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>2026년 10월 19일(월)</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
+      <c r="L29" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2113,78 +2173,83 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
+          <t>산업용 송풍기 및 배기장치 제조업</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>12,600 ~ 15,300원</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>275.4</v>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
         <is>
           <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>2026년 9월 8일(화) ~ 2026년 10월 13일(화)</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="4" t="inlineStr">
+      <c r="L30" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K30"/>
+  <autoFilter ref="A1:L30"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2196,20 +2261,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="48" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2225,45 +2291,50 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>업종</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>보고서명</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>수요예측 시작</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>수요예측 종료</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>마감시각</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>공모가 밴드</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>기관 최대 참여수량(주)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>최대 참여금액(밴드 상단, 억원)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>국내기관 문의처</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>기업IR 기간</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>공모가 확정공고</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>DART</t>
         </is>
@@ -2282,45 +2353,46 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
+          <t>응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>2026-11-30</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>2026-12-04</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>10,000 ~ 13,000원</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>2250000</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5700, 6648</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2026년 11월 18일(수) ~ 2026년 12월 4일(금)</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>2026년 12월 8일(화)</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2339,102 +2411,104 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>기타 무선 통신장비 제조업</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>19,000 ~ 23,000원</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>600000</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>138</v>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 28일(수) ~ 2026년 11월 06일(금)</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 17일(화)</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>옵토닉스</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>광학렌즈 및 광학요소 제조업</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>10,000 ~ 12,000원</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>1572490</v>
+      </c>
+      <c r="J4" s="11" t="n">
+        <v>188.7</v>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>2026년 10월 14일(수) ~ 2026년 10월 23일(금)</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>2026년 10월 29일(목)</t>
-        </is>
-      </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2453,45 +2527,46 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>의학 및 약학 연구개발업</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>2026-11-26</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>2026-12-02</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>20,000 ~ 24,000원</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>396</v>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>2026년 11월 16일(월) ~ 2026년 12월 01일(화)</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2026년 12월 04일(금)</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="L5" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2510,102 +2585,104 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
+          <t>기타 엔지니어링 서비스업</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>2026-11-19</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2026-11-25</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>11,200 ~ 13,600원</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>1575000</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>214.2</v>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>NH투자증권 02-2229-6315, 6829</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>2026년 11월 17일(화) ~ 2026년 11월 25일(수)</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 26일(목)</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="L6" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>이에스티</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>그 외 기타 전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>10,600 ~ 12,400원</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>204.6</v>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>2026년 10월 14일(수) ~ 2026년 10월 20일(화)</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>2026년 10월 21일(수)</t>
-        </is>
-      </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="L7" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2624,45 +2701,46 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
+          <t>그 외 기타 분류 안된 화학제품 제조업</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>31,600 ~ 36,100원</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>1353.8</v>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 28일(수) ~ 2026년 11월 12일(목)</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 17일(화)</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="L8" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2681,45 +2759,46 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
+          <t>알루미늄 제련, 정련 및 합금 제조업</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>2026-11-30</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>2026-12-04</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>5,400 ~ 6,800원</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>204</v>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>2026년 11월 23일(월) ~ 2026년 12월 04일(금)</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2026년 12월 08일(화)</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="L9" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2738,45 +2817,46 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>그 외 자동차용 신품 부품 제조업</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>26,400 ~ 31,900원</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>3182000</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>1015.1</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>2026년 11월 03일(화) ~ 2026년 11월 09일(월)</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 11일(수)</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="L10" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2795,216 +2875,220 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
+          <t>전동기 및 발전기 제조업</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>10,000 ~ 13,000원</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>2059500</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>267.7</v>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 26일(월) ~ 2026년 11월 6일(금)</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 11일(수)</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="L11" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>넥스아이</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>의학 및 약학 연구개발업</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>10,500 ~ 13,000원</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="J12" s="11" t="n">
+        <v>487.5</v>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-6384, 5198</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>2026년 10월 23일(금)</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>2026년 10월 30일(금)</t>
-        </is>
-      </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="L12" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>하나에어로다이내믹스</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>항공기용 부품 제조업</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>4,700 ~ 5,700원</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>188.1</v>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
         <is>
           <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>2026년 10월 29일(목) ~ 2026년 11월 05일(목)</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>2026년 11월 09일(월)</t>
-        </is>
-      </c>
-      <c r="K13" s="8" t="inlineStr">
+      <c r="L13" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>바로팜</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>전자상거래 소매 중개업</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>16,400 ~ 20,200원</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="n">
+        <v>1335000</v>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>269.7</v>
+      </c>
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>2026년 10월 12일(월) ~ 2026년 10월 21일(수)</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>2026년 10월 30일(금)</t>
-        </is>
-      </c>
-      <c r="K14" s="8" t="inlineStr">
+      <c r="L14" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3023,216 +3107,220 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
+          <t>물질 검사, 측정 및 분석기구 제조업</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>9,600 ~ 11,700원</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>175.5</v>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 26일(월) ~ 2026년 11월 03일(화)</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 10일(화)</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="L15" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>래블업</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>시스템 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>19,000 ~ 22,000원</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>1635000</v>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>359.7</v>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
         <is>
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>2026년 10월 6일(화) ~ 2026년 10월 16일(금)</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>2026년 10월 21일(수)</t>
-        </is>
-      </c>
-      <c r="K16" s="8" t="inlineStr">
+      <c r="L16" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>이에스티</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>그 외 기타 전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>10,600 ~ 12,400원</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>204.6</v>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>2026년 10월 14일(수) ~ 2026년 10월 20일(화)</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>2026년 10월 21일(수)</t>
-        </is>
-      </c>
-      <c r="K17" s="8" t="inlineStr">
+      <c r="L17" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>에이엘로봇</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>기타 기계 및 장비 제조업</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>정정-변경(수요예측)</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>15,700 ~ 17,600원</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="J18" s="11" t="n">
+        <v>316.8</v>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>2026년 10월 28일(수) ~ 2026년 11월 03일(화)</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>2026년 11월 04일(수)</t>
-        </is>
-      </c>
-      <c r="K18" s="8" t="inlineStr">
+      <c r="L18" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3251,45 +3339,46 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
+          <t>의학 및 약학 연구개발업</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>2026-11-12</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>2026-11-18</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>18,000 ~ 25,000원</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>1627500</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>406.9</v>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>2026년 11월 2일(월) ~ 2026년 11월 17일(화)</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 20일(금)</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="L19" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3308,21 +3397,26 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
+          <t>자동차 신품 부품 제조업</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>수요예측 항목 없음(원문 확인)</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="4" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3341,45 +3435,46 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
+          <t>응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>12,300 ~ 16,600원</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>750000</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 19일(월) ~ 2026년 10월 28일(수)</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 9일(월)</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="L21" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3398,37 +3493,46 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
+          <t>응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>13,000 ~ 16,500원</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>1258000</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>207.6</v>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 30일(금) ~ 2026년 11월 05일(목)</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="L22" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3447,102 +3551,104 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
+          <t>그 외 기타 금속가공업</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>9,400 ~ 11,000원</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>1694840</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>186.4</v>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 27일(화) ~ 2026년 11월 02일(월)</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 03일(화)</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
+      <c r="L23" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>영광</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>수상 금속 골조 구조재 제조업</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>14,000 ~ 17,000원</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="n">
+        <v>1695000</v>
+      </c>
+      <c r="J24" s="11" t="n">
+        <v>288.1</v>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>2026년 10월 6일(화) ~ 2026년 10월 16일(금)</t>
-        </is>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>2026년 10월 21일(수)</t>
-        </is>
-      </c>
-      <c r="K24" s="8" t="inlineStr">
+      <c r="L24" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3561,45 +3667,46 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
+          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>7,600 ~ 9,000원</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>1875000</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>168.8</v>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 12일(월) ~ 2026년 10월 16일(금)</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2026년 10월 20일(화)</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="L25" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3618,102 +3725,104 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
+          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>9,700 ~ 12,200원</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>1550000</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>189.1</v>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-8023, 7653, 7850</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 12일(월) ~ 2026년 10월 23일(금)</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 03일(화)</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
+      <c r="L26" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>래블업</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>시스템 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>19,000 ~ 22,000원</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="n">
+        <v>1635000</v>
+      </c>
+      <c r="J27" s="11" t="n">
+        <v>359.7</v>
+      </c>
+      <c r="K27" s="8" t="inlineStr">
         <is>
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>2026년 10월 6일(화) ~ 2026년 10월 16일(금)</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>2026년 10월 21일(수)</t>
-        </is>
-      </c>
-      <c r="K27" s="8" t="inlineStr">
+      <c r="L27" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3732,45 +3841,46 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
+          <t>기타 식품 제조업</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>2026-11-16</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>15,000 ~ 17,800원</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>267</v>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
         <is>
           <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 19일(월) ~ 2026년 11월 13일(금)</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 23일(월)</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
+      <c r="L28" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3789,45 +3899,46 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
+          <t>전자상거래 소매 중개업</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>16,400 ~ 20,200원</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>1335000</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>269.7</v>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
         <is>
           <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 12일(월) ~ 2026년 10월 21일(수)</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>2026년 10월 30일(금)</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
+      <c r="L29" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3846,45 +3957,46 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
+          <t>특수 목적용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>17,000 ~ 18,500원</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>1671687</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>309.3</v>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 01일(목) ~ 2026년 10월 08일(목)</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>2026년 10월 12일(월)</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
+      <c r="L30" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3903,45 +4015,46 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
+          <t>그 외 기타 의료용 기기 제조업</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>6,800 ~ 7,800원</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>2840000</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>221.5</v>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>2026년 09월 11일(금) ~ 2026년 10월 02일(금)</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>2026년 10월 07일(수)</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
+      <c r="L31" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3960,45 +4073,46 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
+          <t>광학렌즈 및 광학요소 제조업</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>10,000 ~ 12,000원</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>1572490</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>188.7</v>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
         <is>
           <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 14일(수) ~ 2026년 10월 23일(금)</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>2026년 10월 29일(목)</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
+      <c r="L32" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4017,45 +4131,46 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
+          <t>의학 및 약학 연구개발업</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>10,500 ~ 13,000원</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>487.5</v>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-6384, 5198</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 14일(수)</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>2026년 10월 30일(금)</t>
-        </is>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
+      <c r="L33" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4074,45 +4189,46 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
+          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>15,000 ~ 18,000원</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>1050000</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>189</v>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-7414, 7375, 7651</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>2026년 09월 28일(월) ~ 2026년 10월 16일(금)</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>2026년 10월 19일(월)</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
+      <c r="L34" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4131,41 +4247,46 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
+          <t>산업용 송풍기 및 배기장치 제조업</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>12,600 ~ 15,300원</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>275.4</v>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
         <is>
           <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>2026년 9월 8일(화) ~ 2026년 10월 13일(화)</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="4" t="inlineStr">
+      <c r="L35" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4184,45 +4305,46 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
+          <t>항공기용 부품 제조업</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>4,700 ~ 5,700원</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>188.1</v>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
         <is>
           <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 29일(목) ~ 2026년 11월 05일(목)</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>2026년 11월 09일(월)</t>
-        </is>
-      </c>
-      <c r="K36" s="4" t="inlineStr">
+      <c r="L36" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4241,45 +4363,46 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
+          <t>시스템 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>19,000 ~ 22,000원</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>1635000</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>359.7</v>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
         <is>
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 6일(화) ~ 2026년 10월 16일(금)</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>2026년 10월 21일(수)</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
+      <c r="L37" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4298,45 +4421,46 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
+          <t>수상 금속 골조 구조재 제조업</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>14,000 ~ 17,000원</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>1695000</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>288.1</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 6일(화) ~ 2026년 10월 16일(금)</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>2026년 10월 21일(수)</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr">
+      <c r="L38" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4355,45 +4479,46 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
+          <t>그 외 기타 전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>10,600 ~ 12,400원</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>204.6</v>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 14일(수) ~ 2026년 10월 20일(화)</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>2026년 10월 21일(수)</t>
-        </is>
-      </c>
-      <c r="K39" s="4" t="inlineStr">
+      <c r="L39" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4412,92 +4537,93 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
+          <t>기타 기계 및 장비 제조업</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>15,700 ~ 17,600원</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>316.8</v>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>2026년 10월 15일(목) ~ 2026년 10월 21일(수)</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>2026년 10월 22일(목)</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr">
+      <c r="L40" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K40"/>
+  <autoFilter ref="A1:L40"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/수요예측_일정.xlsx
+++ b/수요예측_일정.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'수요예측 일정'!$A$1:$L$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체 이력'!$A$1:$L$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체 이력'!$A$1:$L$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -79,21 +79,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -110,6 +95,21 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -559,169 +559,169 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>제논</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>9,700 ~ 12,200원</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>1550000</v>
+      </c>
+      <c r="J2" s="6" t="n">
+        <v>189.1</v>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-8023, 7653, 7850</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>인터엑스</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>2026-11-30</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>2026-12-04</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>10,000 ~ 13,000원</t>
         </is>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I3" s="10" t="n">
         <v>2250000</v>
       </c>
-      <c r="J2" s="5" t="n">
+      <c r="J3" s="11" t="n">
         <v>292.5</v>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5700, 6648</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>유캐스트</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>기타 무선 통신장비 제조업</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>19,000 ~ 23,000원</t>
         </is>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I4" s="10" t="n">
         <v>600000</v>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="J4" s="11" t="n">
         <v>138</v>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K4" s="9" t="inlineStr">
         <is>
           <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
-        </is>
-      </c>
-      <c r="L3" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>옵토닉스</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>광학렌즈 및 광학요소 제조업</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>10,000 ~ 12,000원</t>
-        </is>
-      </c>
-      <c r="I4" s="10" t="n">
-        <v>1572490</v>
-      </c>
-      <c r="J4" s="11" t="n">
-        <v>188.7</v>
-      </c>
-      <c r="K4" s="8" t="inlineStr">
-        <is>
-          <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
       <c r="L4" s="12" t="inlineStr">
@@ -738,164 +738,164 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>옵토닉스</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>광학렌즈 및 광학요소 제조업</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10,000 ~ 12,000원</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>1572490</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>188.7</v>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>한국투자증권 02-3276-5958, 6269</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
           <t>이노보테라퓨틱스</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>2026-11-26</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>2026-12-02</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>20,000 ~ 24,000원</t>
         </is>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I6" s="10" t="n">
         <v>1650000</v>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="J6" s="11" t="n">
         <v>396</v>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>기타 엔지니어링 서비스업</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>2026-11-19</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>2026-11-25</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>11,200 ~ 13,600원</t>
         </is>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I7" s="10" t="n">
         <v>1575000</v>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="J7" s="11" t="n">
         <v>214.2</v>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K7" s="9" t="inlineStr">
         <is>
           <t>NH투자증권 02-2229-6315, 6829</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>이에스티</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>그 외 기타 전자부품 제조업</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>10,600 ~ 12,400원</t>
-        </is>
-      </c>
-      <c r="I7" s="10" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="J7" s="11" t="n">
-        <v>204.6</v>
-      </c>
-      <c r="K7" s="8" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
       <c r="L7" s="12" t="inlineStr">
@@ -907,404 +907,404 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>이에스티</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>그 외 기타 전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>10,600 ~ 12,400원</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>204.6</v>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>에스에프씨</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>그 외 기타 분류 안된 화학제품 제조업</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>31,600 ~ 36,100원</t>
         </is>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="I9" s="10" t="n">
         <v>3750000</v>
       </c>
-      <c r="J8" s="5" t="n">
+      <c r="J9" s="11" t="n">
         <v>1353.8</v>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K9" s="9" t="inlineStr">
         <is>
           <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
         </is>
       </c>
-      <c r="L8" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>씨아이에스케미칼</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>알루미늄 제련, 정련 및 합금 제조업</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>2026-11-30</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>2026-12-04</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>5,400 ~ 6,800원</t>
         </is>
       </c>
-      <c r="I9" s="4" t="n">
+      <c r="I10" s="10" t="n">
         <v>3000000</v>
       </c>
-      <c r="J9" s="5" t="n">
+      <c r="J10" s="11" t="n">
         <v>204</v>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K10" s="9" t="inlineStr">
         <is>
           <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
-      <c r="L9" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="L10" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>제이앤티지</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>그 외 자동차용 신품 부품 제조업</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>26,400 ~ 31,900원</t>
         </is>
       </c>
-      <c r="I10" s="4" t="n">
+      <c r="I11" s="10" t="n">
         <v>3182000</v>
       </c>
-      <c r="J10" s="5" t="n">
+      <c r="J11" s="11" t="n">
         <v>1015.1</v>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="K11" s="9" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
         </is>
       </c>
-      <c r="L10" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="L11" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>씨앤엠</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>전동기 및 발전기 제조업</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>10,000 ~ 13,000원</t>
         </is>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="I12" s="10" t="n">
         <v>2059500</v>
       </c>
-      <c r="J11" s="5" t="n">
+      <c r="J12" s="11" t="n">
         <v>267.7</v>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K12" s="9" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L11" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="L12" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>넥스아이</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>10,500 ~ 13,000원</t>
         </is>
       </c>
-      <c r="I12" s="10" t="n">
+      <c r="I13" s="5" t="n">
         <v>3750000</v>
       </c>
-      <c r="J12" s="11" t="n">
+      <c r="J13" s="6" t="n">
         <v>487.5</v>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-6384, 5198</t>
         </is>
       </c>
-      <c r="L12" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>하나에어로다이내믹스</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>항공기용 부품 제조업</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>4,700 ~ 5,700원</t>
         </is>
       </c>
-      <c r="I13" s="10" t="n">
+      <c r="I14" s="5" t="n">
         <v>3300000</v>
       </c>
-      <c r="J13" s="11" t="n">
+      <c r="J14" s="6" t="n">
         <v>188.1</v>
       </c>
-      <c r="K13" s="8" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
         </is>
       </c>
-      <c r="L13" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>바로팜</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>전자상거래 소매 중개업</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>16,400 ~ 20,200원</t>
-        </is>
-      </c>
-      <c r="I14" s="10" t="n">
-        <v>1335000</v>
-      </c>
-      <c r="J14" s="11" t="n">
-        <v>269.7</v>
-      </c>
-      <c r="K14" s="8" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
-        </is>
-      </c>
-      <c r="L14" s="12" t="inlineStr">
+      <c r="L14" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1318,167 +1318,167 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>바로팜</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>전자상거래 소매 중개업</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>16,400 ~ 20,200원</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>1335000</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>269.7</v>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
           <t>엠비디</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>물질 검사, 측정 및 분석기구 제조업</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>9,600 ~ 11,700원</t>
         </is>
       </c>
-      <c r="I15" s="4" t="n">
+      <c r="I16" s="10" t="n">
         <v>1500000</v>
       </c>
-      <c r="J15" s="5" t="n">
+      <c r="J16" s="11" t="n">
         <v>175.5</v>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K16" s="9" t="inlineStr">
         <is>
           <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
         </is>
       </c>
-      <c r="L15" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="L16" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>래블업</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>시스템 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>19,000 ~ 22,000원</t>
         </is>
       </c>
-      <c r="I16" s="10" t="n">
+      <c r="I17" s="5" t="n">
         <v>1635000</v>
       </c>
-      <c r="J16" s="11" t="n">
+      <c r="J17" s="6" t="n">
         <v>359.7</v>
       </c>
-      <c r="K16" s="8" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="L16" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>에이엘로봇</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>기타 기계 및 장비 제조업</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>정정-변경(수요예측)</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>15,700 ~ 17,600원</t>
-        </is>
-      </c>
-      <c r="I17" s="10" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="J17" s="11" t="n">
-        <v>316.8</v>
-      </c>
-      <c r="K17" s="8" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
-        </is>
-      </c>
-      <c r="L17" s="12" t="inlineStr">
+      <c r="L17" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1492,318 +1492,318 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
+          <t>에이엘로봇</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>기타 기계 및 장비 제조업</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경(수요예측)</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>15,700 ~ 17,600원</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>316.8</v>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
           <t>아델</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>2026-11-12</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>2026-11-18</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>18,000 ~ 25,000원</t>
         </is>
       </c>
-      <c r="I18" s="4" t="n">
+      <c r="I19" s="10" t="n">
         <v>1627500</v>
       </c>
-      <c r="J18" s="5" t="n">
+      <c r="J19" s="11" t="n">
         <v>406.9</v>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K19" s="9" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L18" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="L19" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>SimwonAmericaCorp.</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>수요예측 항목 없음(원문 확인)</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="4" t="inlineStr"/>
-      <c r="J19" s="5" t="inlineStr"/>
-      <c r="K19" s="3" t="inlineStr"/>
-      <c r="L19" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr"/>
+      <c r="G20" s="8" t="inlineStr"/>
+      <c r="H20" s="8" t="inlineStr"/>
+      <c r="I20" s="10" t="inlineStr"/>
+      <c r="J20" s="11" t="inlineStr"/>
+      <c r="K20" s="9" t="inlineStr"/>
+      <c r="L20" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>다비오</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>12,300 ~ 16,600원</t>
         </is>
       </c>
-      <c r="I20" s="4" t="n">
+      <c r="I21" s="10" t="n">
         <v>750000</v>
       </c>
-      <c r="J20" s="5" t="n">
+      <c r="J21" s="11" t="n">
         <v>124.5</v>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K21" s="9" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
         </is>
       </c>
-      <c r="L20" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="L21" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>엔키화이트햇</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>13,000 ~ 16,500원</t>
         </is>
       </c>
-      <c r="I21" s="4" t="n">
+      <c r="I22" s="10" t="n">
         <v>1258000</v>
       </c>
-      <c r="J21" s="5" t="n">
+      <c r="J22" s="11" t="n">
         <v>207.6</v>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="K22" s="9" t="inlineStr">
         <is>
           <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
         </is>
       </c>
-      <c r="L21" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="L22" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>영광와이케이엠씨</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>그 외 기타 금속가공업</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>9,400 ~ 11,000원</t>
         </is>
       </c>
-      <c r="I22" s="4" t="n">
+      <c r="I23" s="10" t="n">
         <v>1694840</v>
       </c>
-      <c r="J22" s="5" t="n">
+      <c r="J23" s="11" t="n">
         <v>186.4</v>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="K23" s="9" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
-        </is>
-      </c>
-      <c r="L22" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>영광</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>수상 금속 골조 구조재 제조업</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>14,000 ~ 17,000원</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="n">
-        <v>1695000</v>
-      </c>
-      <c r="J23" s="11" t="n">
-        <v>288.1</v>
-      </c>
-      <c r="K23" s="8" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr">
@@ -1820,399 +1820,399 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
+          <t>영광</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>수상 금속 골조 구조재 제조업</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>14,000 ~ 17,000원</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>1695000</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>288.1</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
           <t>인텔리빅스</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>7,600 ~ 9,000원</t>
         </is>
       </c>
-      <c r="I24" s="4" t="n">
+      <c r="I25" s="10" t="n">
         <v>1875000</v>
       </c>
-      <c r="J24" s="5" t="n">
+      <c r="J25" s="11" t="n">
         <v>168.8</v>
       </c>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="K25" s="9" t="inlineStr">
         <is>
           <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L24" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="L25" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>케이엠에프</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>기타 식품 제조업</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>15,000 ~ 17,800원</t>
+        </is>
+      </c>
+      <c r="I26" s="10" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="J26" s="11" t="n">
+        <v>267</v>
+      </c>
+      <c r="K26" s="9" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
+        </is>
+      </c>
+      <c r="L26" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>디티에스</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>특수 목적용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>17,000 ~ 18,500원</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="n">
+        <v>1671687</v>
+      </c>
+      <c r="J27" s="11" t="n">
+        <v>309.3</v>
+      </c>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
+        </is>
+      </c>
+      <c r="L27" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>엠에스바이오</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>그 외 기타 의료용 기기 제조업</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>6,800 ~ 7,800원</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="n">
+        <v>2840000</v>
+      </c>
+      <c r="J28" s="11" t="n">
+        <v>221.5</v>
+      </c>
+      <c r="K28" s="9" t="inlineStr">
+        <is>
+          <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
+        </is>
+      </c>
+      <c r="L28" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>크리에이츠</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>15,000 ~ 18,000원</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="n">
+        <v>1050000</v>
+      </c>
+      <c r="J29" s="11" t="n">
+        <v>189</v>
+      </c>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-7414, 7375, 7651</t>
+        </is>
+      </c>
+      <c r="L29" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>티앤이코리아</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>산업용 송풍기 및 배기장치 제조업</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>제논</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>9,700 ~ 12,200원</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="n">
-        <v>1550000</v>
-      </c>
-      <c r="J25" s="5" t="n">
-        <v>189.1</v>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>삼성증권 02-2020-8023, 7653, 7850</t>
-        </is>
-      </c>
-      <c r="L25" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>케이엠에프</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>기타 식품 제조업</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-20</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>15,000 ~ 17,800원</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="J26" s="5" t="n">
-        <v>267</v>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
-        </is>
-      </c>
-      <c r="L26" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>디티에스</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>특수 목적용 기계 제조업</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>17,000 ~ 18,500원</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>1671687</v>
-      </c>
-      <c r="J27" s="5" t="n">
-        <v>309.3</v>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
-        </is>
-      </c>
-      <c r="L27" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>엠에스바이오</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>그 외 기타 의료용 기기 제조업</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>6,800 ~ 7,800원</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="n">
-        <v>2840000</v>
-      </c>
-      <c r="J28" s="5" t="n">
-        <v>221.5</v>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
-        </is>
-      </c>
-      <c r="L28" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>크리에이츠</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>15,000 ~ 18,000원</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="n">
-        <v>1050000</v>
-      </c>
-      <c r="J29" s="5" t="n">
-        <v>189</v>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>삼성증권 02-2020-7414, 7375, 7651</t>
-        </is>
-      </c>
-      <c r="L29" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>티앤이코리아</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>산업용 송풍기 및 배기장치 제조업</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>12,600 ~ 15,300원</t>
         </is>
       </c>
-      <c r="I30" s="4" t="n">
+      <c r="I30" s="10" t="n">
         <v>1800000</v>
       </c>
-      <c r="J30" s="5" t="n">
+      <c r="J30" s="11" t="n">
         <v>275.4</v>
       </c>
-      <c r="K30" s="3" t="inlineStr">
+      <c r="K30" s="9" t="inlineStr">
         <is>
           <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
         </is>
       </c>
-      <c r="L30" s="6" t="inlineStr">
+      <c r="L30" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2261,7 +2261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2343,169 +2343,169 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>제논</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>9,700 ~ 12,200원</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>1550000</v>
+      </c>
+      <c r="J2" s="6" t="n">
+        <v>189.1</v>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-8023, 7653, 7850</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>인터엑스</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>2026-11-30</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>2026-12-04</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>10,000 ~ 13,000원</t>
         </is>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I3" s="10" t="n">
         <v>2250000</v>
       </c>
-      <c r="J2" s="5" t="n">
+      <c r="J3" s="11" t="n">
         <v>292.5</v>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5700, 6648</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>유캐스트</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>기타 무선 통신장비 제조업</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>19,000 ~ 23,000원</t>
         </is>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I4" s="10" t="n">
         <v>600000</v>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="J4" s="11" t="n">
         <v>138</v>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K4" s="9" t="inlineStr">
         <is>
           <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
-        </is>
-      </c>
-      <c r="L3" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>옵토닉스</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>광학렌즈 및 광학요소 제조업</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>10,000 ~ 12,000원</t>
-        </is>
-      </c>
-      <c r="I4" s="10" t="n">
-        <v>1572490</v>
-      </c>
-      <c r="J4" s="11" t="n">
-        <v>188.7</v>
-      </c>
-      <c r="K4" s="8" t="inlineStr">
-        <is>
-          <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
       <c r="L4" s="12" t="inlineStr">
@@ -2522,164 +2522,164 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>옵토닉스</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>광학렌즈 및 광학요소 제조업</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10,000 ~ 12,000원</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>1572490</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>188.7</v>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>한국투자증권 02-3276-5958, 6269</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
           <t>이노보테라퓨틱스</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>2026-11-26</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>2026-12-02</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>20,000 ~ 24,000원</t>
         </is>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I6" s="10" t="n">
         <v>1650000</v>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="J6" s="11" t="n">
         <v>396</v>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>기타 엔지니어링 서비스업</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>2026-11-19</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>2026-11-25</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>11,200 ~ 13,600원</t>
         </is>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I7" s="10" t="n">
         <v>1575000</v>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="J7" s="11" t="n">
         <v>214.2</v>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K7" s="9" t="inlineStr">
         <is>
           <t>NH투자증권 02-2229-6315, 6829</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>이에스티</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>그 외 기타 전자부품 제조업</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>10,600 ~ 12,400원</t>
-        </is>
-      </c>
-      <c r="I7" s="10" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="J7" s="11" t="n">
-        <v>204.6</v>
-      </c>
-      <c r="K7" s="8" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
       <c r="L7" s="12" t="inlineStr">
@@ -2691,404 +2691,404 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>이에스티</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>그 외 기타 전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>10,600 ~ 12,400원</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>204.6</v>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>에스에프씨</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>그 외 기타 분류 안된 화학제품 제조업</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>31,600 ~ 36,100원</t>
         </is>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="I9" s="10" t="n">
         <v>3750000</v>
       </c>
-      <c r="J8" s="5" t="n">
+      <c r="J9" s="11" t="n">
         <v>1353.8</v>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K9" s="9" t="inlineStr">
         <is>
           <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
         </is>
       </c>
-      <c r="L8" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>씨아이에스케미칼</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>알루미늄 제련, 정련 및 합금 제조업</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>2026-11-30</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>2026-12-04</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>5,400 ~ 6,800원</t>
         </is>
       </c>
-      <c r="I9" s="4" t="n">
+      <c r="I10" s="10" t="n">
         <v>3000000</v>
       </c>
-      <c r="J9" s="5" t="n">
+      <c r="J10" s="11" t="n">
         <v>204</v>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K10" s="9" t="inlineStr">
         <is>
           <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
-      <c r="L9" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="L10" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>제이앤티지</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>그 외 자동차용 신품 부품 제조업</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>26,400 ~ 31,900원</t>
         </is>
       </c>
-      <c r="I10" s="4" t="n">
+      <c r="I11" s="10" t="n">
         <v>3182000</v>
       </c>
-      <c r="J10" s="5" t="n">
+      <c r="J11" s="11" t="n">
         <v>1015.1</v>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="K11" s="9" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
         </is>
       </c>
-      <c r="L10" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="L11" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>씨앤엠</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>전동기 및 발전기 제조업</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>10,000 ~ 13,000원</t>
         </is>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="I12" s="10" t="n">
         <v>2059500</v>
       </c>
-      <c r="J11" s="5" t="n">
+      <c r="J12" s="11" t="n">
         <v>267.7</v>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K12" s="9" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L11" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="L12" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>넥스아이</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>10,500 ~ 13,000원</t>
         </is>
       </c>
-      <c r="I12" s="10" t="n">
+      <c r="I13" s="5" t="n">
         <v>3750000</v>
       </c>
-      <c r="J12" s="11" t="n">
+      <c r="J13" s="6" t="n">
         <v>487.5</v>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-6384, 5198</t>
         </is>
       </c>
-      <c r="L12" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>하나에어로다이내믹스</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>항공기용 부품 제조업</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>4,700 ~ 5,700원</t>
         </is>
       </c>
-      <c r="I13" s="10" t="n">
+      <c r="I14" s="5" t="n">
         <v>3300000</v>
       </c>
-      <c r="J13" s="11" t="n">
+      <c r="J14" s="6" t="n">
         <v>188.1</v>
       </c>
-      <c r="K13" s="8" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
         </is>
       </c>
-      <c r="L13" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>바로팜</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>전자상거래 소매 중개업</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>16,400 ~ 20,200원</t>
-        </is>
-      </c>
-      <c r="I14" s="10" t="n">
-        <v>1335000</v>
-      </c>
-      <c r="J14" s="11" t="n">
-        <v>269.7</v>
-      </c>
-      <c r="K14" s="8" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
-        </is>
-      </c>
-      <c r="L14" s="12" t="inlineStr">
+      <c r="L14" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3102,225 +3102,225 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>바로팜</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>전자상거래 소매 중개업</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>16,400 ~ 20,200원</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>1335000</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>269.7</v>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
           <t>엠비디</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>물질 검사, 측정 및 분석기구 제조업</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>9,600 ~ 11,700원</t>
         </is>
       </c>
-      <c r="I15" s="4" t="n">
+      <c r="I16" s="10" t="n">
         <v>1500000</v>
       </c>
-      <c r="J15" s="5" t="n">
+      <c r="J16" s="11" t="n">
         <v>175.5</v>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K16" s="9" t="inlineStr">
         <is>
           <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
         </is>
       </c>
-      <c r="L15" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="L16" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>래블업</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>시스템 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>19,000 ~ 22,000원</t>
         </is>
       </c>
-      <c r="I16" s="10" t="n">
+      <c r="I17" s="5" t="n">
         <v>1635000</v>
       </c>
-      <c r="J16" s="11" t="n">
+      <c r="J17" s="6" t="n">
         <v>359.7</v>
       </c>
-      <c r="K16" s="8" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="L16" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>이에스티</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>그 외 기타 전자부품 제조업</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>10,600 ~ 12,400원</t>
         </is>
       </c>
-      <c r="I17" s="10" t="n">
+      <c r="I18" s="5" t="n">
         <v>1650000</v>
       </c>
-      <c r="J17" s="11" t="n">
+      <c r="J18" s="6" t="n">
         <v>204.6</v>
       </c>
-      <c r="K17" s="8" t="inlineStr">
+      <c r="K18" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="L17" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>에이엘로봇</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>기타 기계 및 장비 제조업</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>정정-변경(수요예측)</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>15,700 ~ 17,600원</t>
-        </is>
-      </c>
-      <c r="I18" s="10" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="J18" s="11" t="n">
-        <v>316.8</v>
-      </c>
-      <c r="K18" s="8" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
-        </is>
-      </c>
-      <c r="L18" s="12" t="inlineStr">
+      <c r="L18" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3334,318 +3334,318 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
+          <t>에이엘로봇</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>기타 기계 및 장비 제조업</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경(수요예측)</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>15,700 ~ 17,600원</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>316.8</v>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
           <t>아델</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>2026-11-12</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>2026-11-18</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>18,000 ~ 25,000원</t>
         </is>
       </c>
-      <c r="I19" s="4" t="n">
+      <c r="I20" s="10" t="n">
         <v>1627500</v>
       </c>
-      <c r="J19" s="5" t="n">
+      <c r="J20" s="11" t="n">
         <v>406.9</v>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="K20" s="9" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L19" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="L20" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>SimwonAmericaCorp.</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>수요예측 항목 없음(원문 확인)</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="4" t="inlineStr"/>
-      <c r="J20" s="5" t="inlineStr"/>
-      <c r="K20" s="3" t="inlineStr"/>
-      <c r="L20" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr"/>
+      <c r="G21" s="8" t="inlineStr"/>
+      <c r="H21" s="8" t="inlineStr"/>
+      <c r="I21" s="10" t="inlineStr"/>
+      <c r="J21" s="11" t="inlineStr"/>
+      <c r="K21" s="9" t="inlineStr"/>
+      <c r="L21" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>다비오</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>12,300 ~ 16,600원</t>
         </is>
       </c>
-      <c r="I21" s="4" t="n">
+      <c r="I22" s="10" t="n">
         <v>750000</v>
       </c>
-      <c r="J21" s="5" t="n">
+      <c r="J22" s="11" t="n">
         <v>124.5</v>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="K22" s="9" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
         </is>
       </c>
-      <c r="L21" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="L22" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>엔키화이트햇</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>13,000 ~ 16,500원</t>
         </is>
       </c>
-      <c r="I22" s="4" t="n">
+      <c r="I23" s="10" t="n">
         <v>1258000</v>
       </c>
-      <c r="J22" s="5" t="n">
+      <c r="J23" s="11" t="n">
         <v>207.6</v>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="K23" s="9" t="inlineStr">
         <is>
           <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
         </is>
       </c>
-      <c r="L22" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="L23" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>영광와이케이엠씨</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>그 외 기타 금속가공업</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>9,400 ~ 11,000원</t>
         </is>
       </c>
-      <c r="I23" s="4" t="n">
+      <c r="I24" s="10" t="n">
         <v>1694840</v>
       </c>
-      <c r="J23" s="5" t="n">
+      <c r="J24" s="11" t="n">
         <v>186.4</v>
       </c>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="K24" s="9" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
-        </is>
-      </c>
-      <c r="L23" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>영광</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>수상 금속 골조 구조재 제조업</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>14,000 ~ 17,000원</t>
-        </is>
-      </c>
-      <c r="I24" s="10" t="n">
-        <v>1695000</v>
-      </c>
-      <c r="J24" s="11" t="n">
-        <v>288.1</v>
-      </c>
-      <c r="K24" s="8" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
       <c r="L24" s="12" t="inlineStr">
@@ -3662,164 +3662,164 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
+          <t>영광</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>수상 금속 골조 구조재 제조업</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>14,000 ~ 17,000원</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>1695000</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>288.1</v>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
           <t>인텔리빅스</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>7,600 ~ 9,000원</t>
         </is>
       </c>
-      <c r="I25" s="4" t="n">
+      <c r="I26" s="10" t="n">
         <v>1875000</v>
       </c>
-      <c r="J25" s="5" t="n">
+      <c r="J26" s="11" t="n">
         <v>168.8</v>
       </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="K26" s="9" t="inlineStr">
         <is>
           <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L25" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="L26" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>제논</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>9,700 ~ 12,200원</t>
         </is>
       </c>
-      <c r="I26" s="4" t="n">
+      <c r="I27" s="10" t="n">
         <v>1550000</v>
       </c>
-      <c r="J26" s="5" t="n">
+      <c r="J27" s="11" t="n">
         <v>189.1</v>
       </c>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="K27" s="9" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-8023, 7653, 7850</t>
-        </is>
-      </c>
-      <c r="L26" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>래블업</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>시스템 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>19,000 ~ 22,000원</t>
-        </is>
-      </c>
-      <c r="I27" s="10" t="n">
-        <v>1635000</v>
-      </c>
-      <c r="J27" s="11" t="n">
-        <v>359.7</v>
-      </c>
-      <c r="K27" s="8" t="inlineStr">
-        <is>
-          <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
@@ -3831,759 +3831,817 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>래블업</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>시스템 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>19,000 ~ 22,000원</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>1635000</v>
+      </c>
+      <c r="J28" s="6" t="n">
+        <v>359.7</v>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>NH투자증권 02-768-7462, 7467</t>
+        </is>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>케이엠에프</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>기타 식품 제조업</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
         <is>
           <t>2026-11-16</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>15,000 ~ 17,800원</t>
         </is>
       </c>
-      <c r="I28" s="4" t="n">
+      <c r="I29" s="10" t="n">
         <v>1500000</v>
       </c>
-      <c r="J28" s="5" t="n">
+      <c r="J29" s="11" t="n">
         <v>267</v>
       </c>
-      <c r="K28" s="3" t="inlineStr">
+      <c r="K29" s="9" t="inlineStr">
         <is>
           <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
         </is>
       </c>
-      <c r="L28" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="L29" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>바로팜</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>전자상거래 소매 중개업</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="8" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>16,400 ~ 20,200원</t>
         </is>
       </c>
-      <c r="I29" s="4" t="n">
+      <c r="I30" s="10" t="n">
         <v>1335000</v>
       </c>
-      <c r="J29" s="5" t="n">
+      <c r="J30" s="11" t="n">
         <v>269.7</v>
       </c>
-      <c r="K29" s="3" t="inlineStr">
+      <c r="K30" s="9" t="inlineStr">
         <is>
           <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L29" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="L30" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>디티에스</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>17,000 ~ 18,500원</t>
         </is>
       </c>
-      <c r="I30" s="4" t="n">
+      <c r="I31" s="10" t="n">
         <v>1671687</v>
       </c>
-      <c r="J30" s="5" t="n">
+      <c r="J31" s="11" t="n">
         <v>309.3</v>
       </c>
-      <c r="K30" s="3" t="inlineStr">
+      <c r="K31" s="9" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
         </is>
       </c>
-      <c r="L30" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="L31" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>엠에스바이오</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>그 외 기타 의료용 기기 제조업</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="8" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G32" s="8" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>6,800 ~ 7,800원</t>
         </is>
       </c>
-      <c r="I31" s="4" t="n">
+      <c r="I32" s="10" t="n">
         <v>2840000</v>
       </c>
-      <c r="J31" s="5" t="n">
+      <c r="J32" s="11" t="n">
         <v>221.5</v>
       </c>
-      <c r="K31" s="3" t="inlineStr">
+      <c r="K32" s="9" t="inlineStr">
         <is>
           <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
-      <c r="L31" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="L32" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>옵토닉스</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>광학렌즈 및 광학요소 제조업</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="8" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>10,000 ~ 12,000원</t>
         </is>
       </c>
-      <c r="I32" s="4" t="n">
+      <c r="I33" s="10" t="n">
         <v>1572490</v>
       </c>
-      <c r="J32" s="5" t="n">
+      <c r="J33" s="11" t="n">
         <v>188.7</v>
       </c>
-      <c r="K32" s="3" t="inlineStr">
+      <c r="K33" s="9" t="inlineStr">
         <is>
           <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
-      <c r="L32" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="L33" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>넥스아이</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>10,500 ~ 13,000원</t>
         </is>
       </c>
-      <c r="I33" s="4" t="n">
+      <c r="I34" s="10" t="n">
         <v>3750000</v>
       </c>
-      <c r="J33" s="5" t="n">
+      <c r="J34" s="11" t="n">
         <v>487.5</v>
       </c>
-      <c r="K33" s="3" t="inlineStr">
+      <c r="K34" s="9" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-6384, 5198</t>
         </is>
       </c>
-      <c r="L33" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="L34" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>크리에이츠</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="8" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G35" s="8" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H35" s="8" t="inlineStr">
         <is>
           <t>15,000 ~ 18,000원</t>
         </is>
       </c>
-      <c r="I34" s="4" t="n">
+      <c r="I35" s="10" t="n">
         <v>1050000</v>
       </c>
-      <c r="J34" s="5" t="n">
+      <c r="J35" s="11" t="n">
         <v>189</v>
       </c>
-      <c r="K34" s="3" t="inlineStr">
+      <c r="K35" s="9" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-7414, 7375, 7651</t>
         </is>
       </c>
-      <c r="L34" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="L35" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>티앤이코리아</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>산업용 송풍기 및 배기장치 제조업</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D36" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G36" s="8" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H36" s="8" t="inlineStr">
         <is>
           <t>12,600 ~ 15,300원</t>
         </is>
       </c>
-      <c r="I35" s="4" t="n">
+      <c r="I36" s="10" t="n">
         <v>1800000</v>
       </c>
-      <c r="J35" s="5" t="n">
+      <c r="J36" s="11" t="n">
         <v>275.4</v>
       </c>
-      <c r="K35" s="3" t="inlineStr">
+      <c r="K36" s="9" t="inlineStr">
         <is>
           <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
         </is>
       </c>
-      <c r="L35" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="L36" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>하나에어로다이내믹스</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>항공기용 부품 제조업</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D37" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="8" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G37" s="8" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H37" s="8" t="inlineStr">
         <is>
           <t>4,700 ~ 5,700원</t>
         </is>
       </c>
-      <c r="I36" s="4" t="n">
+      <c r="I37" s="10" t="n">
         <v>3300000</v>
       </c>
-      <c r="J36" s="5" t="n">
+      <c r="J37" s="11" t="n">
         <v>188.1</v>
       </c>
-      <c r="K36" s="3" t="inlineStr">
+      <c r="K37" s="9" t="inlineStr">
         <is>
           <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
         </is>
       </c>
-      <c r="L36" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="L37" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>래블업</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>시스템 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="8" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G38" s="8" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H38" s="8" t="inlineStr">
         <is>
           <t>19,000 ~ 22,000원</t>
         </is>
       </c>
-      <c r="I37" s="4" t="n">
+      <c r="I38" s="10" t="n">
         <v>1635000</v>
       </c>
-      <c r="J37" s="5" t="n">
+      <c r="J38" s="11" t="n">
         <v>359.7</v>
       </c>
-      <c r="K37" s="3" t="inlineStr">
+      <c r="K38" s="9" t="inlineStr">
         <is>
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="L37" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="L38" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>영광</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
         <is>
           <t>수상 금속 골조 구조재 제조업</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D39" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="8" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G39" s="8" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H39" s="8" t="inlineStr">
         <is>
           <t>14,000 ~ 17,000원</t>
         </is>
       </c>
-      <c r="I38" s="4" t="n">
+      <c r="I39" s="10" t="n">
         <v>1695000</v>
       </c>
-      <c r="J38" s="5" t="n">
+      <c r="J39" s="11" t="n">
         <v>288.1</v>
       </c>
-      <c r="K38" s="3" t="inlineStr">
+      <c r="K39" s="9" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L38" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="L39" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>이에스티</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t>그 외 기타 전자부품 제조업</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D40" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="8" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G40" s="8" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H40" s="8" t="inlineStr">
         <is>
           <t>10,600 ~ 12,400원</t>
         </is>
       </c>
-      <c r="I39" s="4" t="n">
+      <c r="I40" s="10" t="n">
         <v>1650000</v>
       </c>
-      <c r="J39" s="5" t="n">
+      <c r="J40" s="11" t="n">
         <v>204.6</v>
       </c>
-      <c r="K39" s="3" t="inlineStr">
+      <c r="K40" s="9" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="L39" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="L40" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>에이엘로봇</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C41" s="9" t="inlineStr">
         <is>
           <t>기타 기계 및 장비 제조업</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D41" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="8" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G41" s="8" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" s="8" t="inlineStr">
         <is>
           <t>15,700 ~ 17,600원</t>
         </is>
       </c>
-      <c r="I40" s="4" t="n">
+      <c r="I41" s="10" t="n">
         <v>1800000</v>
       </c>
-      <c r="J40" s="5" t="n">
+      <c r="J41" s="11" t="n">
         <v>316.8</v>
       </c>
-      <c r="K40" s="3" t="inlineStr">
+      <c r="K41" s="9" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="L40" s="6" t="inlineStr">
+      <c r="L41" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L40"/>
+  <autoFilter ref="A1:L41"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -4624,6 +4682,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/수요예측_일정.xlsx
+++ b/수요예측_일정.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'수요예측 일정'!$A$1:$L$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체 이력'!$A$1:$L$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체 이력'!$A$1:$L$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -559,7 +559,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -579,17 +579,17 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>정정-변경없음</t>
+          <t>정정-변경(수요예측)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2343,7 +2343,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -2363,17 +2363,17 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>정정-변경없음</t>
+          <t>정정-변경(수요예측)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -2399,58 +2399,58 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>인터엑스</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-04</t>
-        </is>
-      </c>
-      <c r="H3" s="8" t="inlineStr">
-        <is>
-          <t>10,000 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I3" s="10" t="n">
-        <v>2250000</v>
-      </c>
-      <c r="J3" s="11" t="n">
-        <v>292.5</v>
-      </c>
-      <c r="K3" s="9" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5700, 6648</t>
-        </is>
-      </c>
-      <c r="L3" s="12" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>제논</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>9,700 ~ 12,200원</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>1550000</v>
+      </c>
+      <c r="J3" s="6" t="n">
+        <v>189.1</v>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-8023, 7653, 7850</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2459,172 +2459,172 @@
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>인터엑스</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>10,000 ~ 13,000원</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>2250000</v>
+      </c>
+      <c r="J4" s="11" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5700, 6648</t>
+        </is>
+      </c>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>유캐스트</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>기타 무선 통신장비 제조업</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>19,000 ~ 23,000원</t>
         </is>
       </c>
-      <c r="I4" s="10" t="n">
+      <c r="I5" s="10" t="n">
         <v>600000</v>
       </c>
-      <c r="J4" s="11" t="n">
+      <c r="J5" s="11" t="n">
         <v>138</v>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K5" s="9" t="inlineStr">
         <is>
           <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
         </is>
       </c>
-      <c r="L4" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>옵토닉스</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>광학렌즈 및 광학요소 제조업</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>10,000 ~ 12,000원</t>
         </is>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I6" s="5" t="n">
         <v>1572490</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="J6" s="6" t="n">
         <v>188.7</v>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>이노보테라퓨틱스</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-02</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>20,000 ~ 24,000원</t>
-        </is>
-      </c>
-      <c r="I6" s="10" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="J6" s="11" t="n">
-        <v>396</v>
-      </c>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
-        </is>
-      </c>
-      <c r="L6" s="12" t="inlineStr">
+      <c r="L6" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2633,172 +2633,172 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>이노보테라퓨틱스</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>의학 및 약학 연구개발업</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>20,000 ~ 24,000원</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>396</v>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+        </is>
+      </c>
+      <c r="L7" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>기타 엔지니어링 서비스업</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>2026-11-19</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>2026-11-25</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>11,200 ~ 13,600원</t>
         </is>
       </c>
-      <c r="I7" s="10" t="n">
+      <c r="I8" s="10" t="n">
         <v>1575000</v>
       </c>
-      <c r="J7" s="11" t="n">
+      <c r="J8" s="11" t="n">
         <v>214.2</v>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="K8" s="9" t="inlineStr">
         <is>
           <t>NH투자증권 02-2229-6315, 6829</t>
         </is>
       </c>
-      <c r="L7" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="L8" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>이에스티</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>그 외 기타 전자부품 제조업</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>10,600 ~ 12,400원</t>
         </is>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="I9" s="5" t="n">
         <v>1650000</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J9" s="6" t="n">
         <v>204.6</v>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>에스에프씨</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>그 외 기타 분류 안된 화학제품 제조업</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>31,600 ~ 36,100원</t>
-        </is>
-      </c>
-      <c r="I9" s="10" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J9" s="11" t="n">
-        <v>1353.8</v>
-      </c>
-      <c r="K9" s="9" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
-        </is>
-      </c>
-      <c r="L9" s="12" t="inlineStr">
+      <c r="L9" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2812,12 +2812,12 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>씨아이에스케미칼</t>
+          <t>에스에프씨</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>알루미늄 제련, 정련 및 합금 제조업</t>
+          <t>그 외 기타 분류 안된 화학제품 제조업</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -2832,28 +2832,28 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>5,400 ~ 6,800원</t>
+          <t>31,600 ~ 36,100원</t>
         </is>
       </c>
       <c r="I10" s="10" t="n">
-        <v>3000000</v>
+        <v>3750000</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>204</v>
+        <v>1353.8</v>
       </c>
       <c r="K10" s="9" t="inlineStr">
         <is>
-          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
+          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
         </is>
       </c>
       <c r="L10" s="12" t="inlineStr">
@@ -2865,17 +2865,17 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>제이앤티지</t>
+          <t>씨아이에스케미칼</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>그 외 자동차용 신품 부품 제조업</t>
+          <t>알루미늄 제련, 정련 및 합금 제조업</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -2890,28 +2890,28 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>26,400 ~ 31,900원</t>
+          <t>5,400 ~ 6,800원</t>
         </is>
       </c>
       <c r="I11" s="10" t="n">
-        <v>3182000</v>
+        <v>3000000</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>1015.1</v>
+        <v>204</v>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
+          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
       <c r="L11" s="12" t="inlineStr">
@@ -2928,109 +2928,109 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
+          <t>제이앤티지</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>그 외 자동차용 신품 부품 제조업</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>26,400 ~ 31,900원</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>3182000</v>
+      </c>
+      <c r="J12" s="11" t="n">
+        <v>1015.1</v>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
+        </is>
+      </c>
+      <c r="L12" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
           <t>씨앤엠</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>전동기 및 발전기 제조업</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>10,000 ~ 13,000원</t>
         </is>
       </c>
-      <c r="I12" s="10" t="n">
+      <c r="I13" s="10" t="n">
         <v>2059500</v>
       </c>
-      <c r="J12" s="11" t="n">
+      <c r="J13" s="11" t="n">
         <v>267.7</v>
       </c>
-      <c r="K12" s="9" t="inlineStr">
+      <c r="K13" s="9" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L12" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>넥스아이</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,500 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J13" s="6" t="n">
-        <v>487.5</v>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
+      <c r="L13" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3044,12 +3044,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>항공기용 부품 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -3064,28 +3064,28 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,700 ~ 5,700원</t>
+          <t>10,500 ~ 13,000원</t>
         </is>
       </c>
       <c r="I14" s="5" t="n">
-        <v>3300000</v>
+        <v>3750000</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>188.1</v>
+        <v>487.5</v>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
+          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
@@ -3097,172 +3097,172 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>하나에어로다이내믹스</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>항공기용 부품 제조업</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>4,700 ~ 5,700원</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>188.1</v>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>바로팜</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>전자상거래 소매 중개업</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>16,400 ~ 20,200원</t>
         </is>
       </c>
-      <c r="I15" s="5" t="n">
+      <c r="I16" s="5" t="n">
         <v>1335000</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="J16" s="6" t="n">
         <v>269.7</v>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L15" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>엠비디</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>물질 검사, 측정 및 분석기구 제조업</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>9,600 ~ 11,700원</t>
         </is>
       </c>
-      <c r="I16" s="10" t="n">
+      <c r="I17" s="10" t="n">
         <v>1500000</v>
       </c>
-      <c r="J16" s="11" t="n">
+      <c r="J17" s="11" t="n">
         <v>175.5</v>
       </c>
-      <c r="K16" s="9" t="inlineStr">
+      <c r="K17" s="9" t="inlineStr">
         <is>
           <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
         </is>
       </c>
-      <c r="L16" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>래블업</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>시스템 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>19,000 ~ 22,000원</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>1635000</v>
-      </c>
-      <c r="J17" s="6" t="n">
-        <v>359.7</v>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>NH투자증권 02-768-7462, 7467</t>
-        </is>
-      </c>
-      <c r="L17" s="7" t="inlineStr">
+      <c r="L17" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3271,53 +3271,53 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>래블업</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>시스템 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>이에스티</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>그 외 기타 전자부품 제조업</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,600 ~ 12,400원</t>
+          <t>19,000 ~ 22,000원</t>
         </is>
       </c>
       <c r="I18" s="5" t="n">
-        <v>1650000</v>
+        <v>1635000</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>204.6</v>
+        <v>359.7</v>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+          <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr">
@@ -3329,114 +3329,114 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>이에스티</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>그 외 기타 전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>10,600 ~ 12,400원</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>204.6</v>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>에이엘로봇</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>기타 기계 및 장비 제조업</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>정정-변경(수요예측)</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>15,700 ~ 17,600원</t>
         </is>
       </c>
-      <c r="I19" s="5" t="n">
+      <c r="I20" s="5" t="n">
         <v>1800000</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="J20" s="6" t="n">
         <v>316.8</v>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="L19" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>아델</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>18,000 ~ 25,000원</t>
-        </is>
-      </c>
-      <c r="I20" s="10" t="n">
-        <v>1627500</v>
-      </c>
-      <c r="J20" s="11" t="n">
-        <v>406.9</v>
-      </c>
-      <c r="K20" s="9" t="inlineStr">
-        <is>
-          <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
-        </is>
-      </c>
-      <c r="L20" s="12" t="inlineStr">
+      <c r="L20" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3450,12 +3450,12 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>SimwonAmericaCorp.</t>
+          <t>아델</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>자동차 신품 부품 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
@@ -3465,15 +3465,35 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>수요예측 항목 없음(원문 확인)</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr"/>
-      <c r="G21" s="8" t="inlineStr"/>
-      <c r="H21" s="8" t="inlineStr"/>
-      <c r="I21" s="10" t="inlineStr"/>
-      <c r="J21" s="11" t="inlineStr"/>
-      <c r="K21" s="9" t="inlineStr"/>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>18,000 ~ 25,000원</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="n">
+        <v>1627500</v>
+      </c>
+      <c r="J21" s="11" t="n">
+        <v>406.9</v>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -3483,55 +3503,35 @@
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>다비오</t>
+          <t>SimwonAmericaCorp.</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
+          <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>12,300 ~ 16,600원</t>
-        </is>
-      </c>
-      <c r="I22" s="10" t="n">
-        <v>750000</v>
-      </c>
-      <c r="J22" s="11" t="n">
-        <v>124.5</v>
-      </c>
-      <c r="K22" s="9" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
-        </is>
-      </c>
+          <t>수요예측 항목 없음(원문 확인)</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr"/>
+      <c r="G22" s="8" t="inlineStr"/>
+      <c r="H22" s="8" t="inlineStr"/>
+      <c r="I22" s="10" t="inlineStr"/>
+      <c r="J22" s="11" t="inlineStr"/>
+      <c r="K22" s="9" t="inlineStr"/>
       <c r="L22" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>엔키화이트햇</t>
+          <t>다비오</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -3566,28 +3566,28 @@
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>13,000 ~ 16,500원</t>
+          <t>12,300 ~ 16,600원</t>
         </is>
       </c>
       <c r="I23" s="10" t="n">
-        <v>1258000</v>
+        <v>750000</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>207.6</v>
+        <v>124.5</v>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
+          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr">
@@ -3604,167 +3604,167 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
+          <t>엔키화이트햇</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>13,000 ~ 16,500원</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="n">
+        <v>1258000</v>
+      </c>
+      <c r="J24" s="11" t="n">
+        <v>207.6</v>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
+        </is>
+      </c>
+      <c r="L24" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
           <t>영광와이케이엠씨</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>그 외 기타 금속가공업</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>9,400 ~ 11,000원</t>
         </is>
       </c>
-      <c r="I24" s="10" t="n">
+      <c r="I25" s="10" t="n">
         <v>1694840</v>
       </c>
-      <c r="J24" s="11" t="n">
+      <c r="J25" s="11" t="n">
         <v>186.4</v>
       </c>
-      <c r="K24" s="9" t="inlineStr">
+      <c r="K25" s="9" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
         </is>
       </c>
-      <c r="L24" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="L25" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>영광</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>수상 금속 골조 구조재 제조업</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>14,000 ~ 17,000원</t>
         </is>
       </c>
-      <c r="I25" s="5" t="n">
+      <c r="I26" s="5" t="n">
         <v>1695000</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="J26" s="6" t="n">
         <v>288.1</v>
       </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L25" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>인텔리빅스</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>7,600 ~ 9,000원</t>
-        </is>
-      </c>
-      <c r="I26" s="10" t="n">
-        <v>1875000</v>
-      </c>
-      <c r="J26" s="11" t="n">
-        <v>168.8</v>
-      </c>
-      <c r="K26" s="9" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
-        </is>
-      </c>
-      <c r="L26" s="12" t="inlineStr">
+      <c r="L26" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3773,172 +3773,172 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>인텔리빅스</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>7,600 ~ 9,000원</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="n">
+        <v>1875000</v>
+      </c>
+      <c r="J27" s="11" t="n">
+        <v>168.8</v>
+      </c>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
+      <c r="L27" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>제논</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>9,700 ~ 12,200원</t>
         </is>
       </c>
-      <c r="I27" s="10" t="n">
+      <c r="I28" s="10" t="n">
         <v>1550000</v>
       </c>
-      <c r="J27" s="11" t="n">
+      <c r="J28" s="11" t="n">
         <v>189.1</v>
       </c>
-      <c r="K27" s="9" t="inlineStr">
+      <c r="K28" s="9" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-8023, 7653, 7850</t>
         </is>
       </c>
-      <c r="L27" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="L28" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>래블업</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>시스템 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>19,000 ~ 22,000원</t>
         </is>
       </c>
-      <c r="I28" s="5" t="n">
+      <c r="I29" s="5" t="n">
         <v>1635000</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="J29" s="6" t="n">
         <v>359.7</v>
       </c>
-      <c r="K28" s="3" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr">
         <is>
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="L28" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>케이엠에프</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>기타 식품 제조업</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-20</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t>15,000 ~ 17,800원</t>
-        </is>
-      </c>
-      <c r="I29" s="10" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="J29" s="11" t="n">
-        <v>267</v>
-      </c>
-      <c r="K29" s="9" t="inlineStr">
-        <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
-        </is>
-      </c>
-      <c r="L29" s="12" t="inlineStr">
+      <c r="L29" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3947,22 +3947,22 @@
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>바로팜</t>
+          <t>케이엠에프</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>전자상거래 소매 중개업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
@@ -3972,28 +3972,28 @@
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>16,400 ~ 20,200원</t>
+          <t>15,000 ~ 17,800원</t>
         </is>
       </c>
       <c r="I30" s="10" t="n">
-        <v>1335000</v>
+        <v>1500000</v>
       </c>
       <c r="J30" s="11" t="n">
-        <v>269.7</v>
+        <v>267</v>
       </c>
       <c r="K30" s="9" t="inlineStr">
         <is>
-          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
         </is>
       </c>
       <c r="L30" s="12" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>디티에스</t>
+          <t>바로팜</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>전자상거래 소매 중개업</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
@@ -4030,28 +4030,28 @@
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>17,000 ~ 18,500원</t>
+          <t>16,400 ~ 20,200원</t>
         </is>
       </c>
       <c r="I31" s="10" t="n">
-        <v>1671687</v>
+        <v>1335000</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>309.3</v>
+        <v>269.7</v>
       </c>
       <c r="K31" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
+          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
@@ -4063,17 +4063,17 @@
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>엠에스바이오</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>그 외 기타 의료용 기기 제조업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
@@ -4088,28 +4088,28 @@
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>6,800 ~ 7,800원</t>
+          <t>17,000 ~ 18,500원</t>
         </is>
       </c>
       <c r="I32" s="10" t="n">
-        <v>2840000</v>
+        <v>1671687</v>
       </c>
       <c r="J32" s="11" t="n">
-        <v>221.5</v>
+        <v>309.3</v>
       </c>
       <c r="K32" s="9" t="inlineStr">
         <is>
-          <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
+          <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
         </is>
       </c>
       <c r="L32" s="12" t="inlineStr">
@@ -4126,17 +4126,17 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>옵토닉스</t>
+          <t>엠에스바이오</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>광학렌즈 및 광학요소 제조업</t>
+          <t>그 외 기타 의료용 기기 제조업</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -4146,28 +4146,28 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>10,000 ~ 12,000원</t>
+          <t>6,800 ~ 7,800원</t>
         </is>
       </c>
       <c r="I33" s="10" t="n">
-        <v>1572490</v>
+        <v>2840000</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>188.7</v>
+        <v>221.5</v>
       </c>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>한국투자증권 02-3276-5958, 6269</t>
+          <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
       <c r="L33" s="12" t="inlineStr">
@@ -4179,17 +4179,17 @@
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>넥스아이</t>
+          <t>옵토닉스</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>의학 및 약학 연구개발업</t>
+          <t>광학렌즈 및 광학요소 제조업</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
@@ -4204,28 +4204,28 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>10,500 ~ 13,000원</t>
+          <t>10,000 ~ 12,000원</t>
         </is>
       </c>
       <c r="I34" s="10" t="n">
-        <v>3750000</v>
+        <v>1572490</v>
       </c>
       <c r="J34" s="11" t="n">
-        <v>487.5</v>
+        <v>188.7</v>
       </c>
       <c r="K34" s="9" t="inlineStr">
         <is>
-          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
+          <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
       <c r="L34" s="12" t="inlineStr">
@@ -4242,17 +4242,17 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -4262,28 +4262,28 @@
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>15,000 ~ 18,000원</t>
+          <t>10,500 ~ 13,000원</t>
         </is>
       </c>
       <c r="I35" s="10" t="n">
-        <v>1050000</v>
+        <v>3750000</v>
       </c>
       <c r="J35" s="11" t="n">
-        <v>189</v>
+        <v>487.5</v>
       </c>
       <c r="K35" s="9" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-7414, 7375, 7651</t>
+          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
         </is>
       </c>
       <c r="L35" s="12" t="inlineStr">
@@ -4295,17 +4295,17 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>티앤이코리아</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>산업용 송풍기 및 배기장치 제조업</t>
+          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
@@ -4320,28 +4320,28 @@
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>12,600 ~ 15,300원</t>
+          <t>15,000 ~ 18,000원</t>
         </is>
       </c>
       <c r="I36" s="10" t="n">
-        <v>1800000</v>
+        <v>1050000</v>
       </c>
       <c r="J36" s="11" t="n">
-        <v>275.4</v>
+        <v>189</v>
       </c>
       <c r="K36" s="9" t="inlineStr">
         <is>
-          <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
+          <t>삼성증권 02-2020-7414, 7375, 7651</t>
         </is>
       </c>
       <c r="L36" s="12" t="inlineStr">
@@ -4353,22 +4353,22 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>티앤이코리아</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>항공기용 부품 제조업</t>
+          <t>산업용 송풍기 및 배기장치 제조업</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -4378,28 +4378,28 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>4,700 ~ 5,700원</t>
+          <t>12,600 ~ 15,300원</t>
         </is>
       </c>
       <c r="I37" s="10" t="n">
-        <v>3300000</v>
+        <v>1800000</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>188.1</v>
+        <v>275.4</v>
       </c>
       <c r="K37" s="9" t="inlineStr">
         <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
+          <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
         </is>
       </c>
       <c r="L37" s="12" t="inlineStr">
@@ -4416,17 +4416,17 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>래블업</t>
+          <t>하나에어로다이내믹스</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>시스템 소프트웨어 개발 및 공급업</t>
+          <t>항공기용 부품 제조업</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
@@ -4436,28 +4436,28 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>19,000 ~ 22,000원</t>
+          <t>4,700 ~ 5,700원</t>
         </is>
       </c>
       <c r="I38" s="10" t="n">
-        <v>1635000</v>
+        <v>3300000</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>359.7</v>
+        <v>188.1</v>
       </c>
       <c r="K38" s="9" t="inlineStr">
         <is>
-          <t>NH투자증권 02-768-7462, 7467</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
         </is>
       </c>
       <c r="L38" s="12" t="inlineStr">
@@ -4474,17 +4474,17 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>영광</t>
+          <t>래블업</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>수상 금속 골조 구조재 제조업</t>
+          <t>시스템 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -4504,18 +4504,18 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>14,000 ~ 17,000원</t>
+          <t>19,000 ~ 22,000원</t>
         </is>
       </c>
       <c r="I39" s="10" t="n">
-        <v>1695000</v>
+        <v>1635000</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>288.1</v>
+        <v>359.7</v>
       </c>
       <c r="K39" s="9" t="inlineStr">
         <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+          <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
       <c r="L39" s="12" t="inlineStr">
@@ -4532,12 +4532,12 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>이에스티</t>
+          <t>영광</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>그 외 기타 전자부품 제조업</t>
+          <t>수상 금속 골조 구조재 제조업</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
@@ -4552,28 +4552,28 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>10,600 ~ 12,400원</t>
+          <t>14,000 ~ 17,000원</t>
         </is>
       </c>
       <c r="I40" s="10" t="n">
-        <v>1650000</v>
+        <v>1695000</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>204.6</v>
+        <v>288.1</v>
       </c>
       <c r="K40" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
       <c r="L40" s="12" t="inlineStr">
@@ -4590,58 +4590,116 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
+          <t>이에스티</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>그 외 기타 전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>10,600 ~ 12,400원</t>
+        </is>
+      </c>
+      <c r="I41" s="10" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J41" s="11" t="n">
+        <v>204.6</v>
+      </c>
+      <c r="K41" s="9" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+        </is>
+      </c>
+      <c r="L41" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
           <t>에이엘로봇</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>기타 기계 및 장비 제조업</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="D42" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="E42" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
+      <c r="F42" s="8" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G41" s="8" t="inlineStr">
+      <c r="G42" s="8" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="H41" s="8" t="inlineStr">
+      <c r="H42" s="8" t="inlineStr">
         <is>
           <t>15,700 ~ 17,600원</t>
         </is>
       </c>
-      <c r="I41" s="10" t="n">
+      <c r="I42" s="10" t="n">
         <v>1800000</v>
       </c>
-      <c r="J41" s="11" t="n">
+      <c r="J42" s="11" t="n">
         <v>316.8</v>
       </c>
-      <c r="K41" s="9" t="inlineStr">
+      <c r="K42" s="9" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="L41" s="12" t="inlineStr">
+      <c r="L42" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L41"/>
+  <autoFilter ref="A1:L42"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -4683,6 +4741,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/수요예측_일정.xlsx
+++ b/수요예측_일정.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체 이력" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'수요예측 일정'!$A$1:$L$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체 이력'!$A$1:$L$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'수요예측 일정'!$A$1:$L$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체 이력'!$A$1:$L$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -615,58 +615,58 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>동원파츠</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>반도체 제조용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>인터엑스</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-04</t>
-        </is>
-      </c>
-      <c r="H3" s="8" t="inlineStr">
-        <is>
-          <t>10,000 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I3" s="10" t="n">
-        <v>2250000</v>
-      </c>
-      <c r="J3" s="11" t="n">
-        <v>292.5</v>
-      </c>
-      <c r="K3" s="9" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5700, 6648</t>
-        </is>
-      </c>
-      <c r="L3" s="12" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>23,000 ~ 26,500원</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>1522500</v>
+      </c>
+      <c r="J3" s="6" t="n">
+        <v>403.5</v>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-6975, 8217, 7651</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -675,172 +675,172 @@
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>인터엑스</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>10,000 ~ 13,000원</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>2250000</v>
+      </c>
+      <c r="J4" s="11" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5700, 6648</t>
+        </is>
+      </c>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>유캐스트</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>기타 무선 통신장비 제조업</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>19,000 ~ 23,000원</t>
         </is>
       </c>
-      <c r="I4" s="10" t="n">
+      <c r="I5" s="10" t="n">
         <v>600000</v>
       </c>
-      <c r="J4" s="11" t="n">
+      <c r="J5" s="11" t="n">
         <v>138</v>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K5" s="9" t="inlineStr">
         <is>
           <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
         </is>
       </c>
-      <c r="L4" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>옵토닉스</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>광학렌즈 및 광학요소 제조업</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>10,000 ~ 12,000원</t>
         </is>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I6" s="5" t="n">
         <v>1572490</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="J6" s="6" t="n">
         <v>188.7</v>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>이노보테라퓨틱스</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-02</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>20,000 ~ 24,000원</t>
-        </is>
-      </c>
-      <c r="I6" s="10" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="J6" s="11" t="n">
-        <v>396</v>
-      </c>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
-        </is>
-      </c>
-      <c r="L6" s="12" t="inlineStr">
+      <c r="L6" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -849,172 +849,172 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>이노보테라퓨틱스</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>의학 및 약학 연구개발업</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>20,000 ~ 24,000원</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>396</v>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+        </is>
+      </c>
+      <c r="L7" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>기타 엔지니어링 서비스업</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>2026-11-19</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>2026-11-25</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>11,200 ~ 13,600원</t>
         </is>
       </c>
-      <c r="I7" s="10" t="n">
+      <c r="I8" s="10" t="n">
         <v>1575000</v>
       </c>
-      <c r="J7" s="11" t="n">
+      <c r="J8" s="11" t="n">
         <v>214.2</v>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="K8" s="9" t="inlineStr">
         <is>
           <t>NH투자증권 02-2229-6315, 6829</t>
         </is>
       </c>
-      <c r="L7" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="L8" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>이에스티</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>그 외 기타 전자부품 제조업</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>10,600 ~ 12,400원</t>
         </is>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="I9" s="5" t="n">
         <v>1650000</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J9" s="6" t="n">
         <v>204.6</v>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>에스에프씨</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>그 외 기타 분류 안된 화학제품 제조업</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>31,600 ~ 36,100원</t>
-        </is>
-      </c>
-      <c r="I9" s="10" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J9" s="11" t="n">
-        <v>1353.8</v>
-      </c>
-      <c r="K9" s="9" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
-        </is>
-      </c>
-      <c r="L9" s="12" t="inlineStr">
+      <c r="L9" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>씨아이에스케미칼</t>
+          <t>에스에프씨</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>알루미늄 제련, 정련 및 합금 제조업</t>
+          <t>그 외 기타 분류 안된 화학제품 제조업</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -1048,28 +1048,28 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>5,400 ~ 6,800원</t>
+          <t>31,600 ~ 36,100원</t>
         </is>
       </c>
       <c r="I10" s="10" t="n">
-        <v>3000000</v>
+        <v>3750000</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>204</v>
+        <v>1353.8</v>
       </c>
       <c r="K10" s="9" t="inlineStr">
         <is>
-          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
+          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
         </is>
       </c>
       <c r="L10" s="12" t="inlineStr">
@@ -1081,17 +1081,17 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>제이앤티지</t>
+          <t>씨아이에스케미칼</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>그 외 자동차용 신품 부품 제조업</t>
+          <t>알루미늄 제련, 정련 및 합금 제조업</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -1106,28 +1106,28 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>26,400 ~ 31,900원</t>
+          <t>5,400 ~ 6,800원</t>
         </is>
       </c>
       <c r="I11" s="10" t="n">
-        <v>3182000</v>
+        <v>3000000</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>1015.1</v>
+        <v>204</v>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
+          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
       <c r="L11" s="12" t="inlineStr">
@@ -1144,109 +1144,109 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
+          <t>제이앤티지</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>그 외 자동차용 신품 부품 제조업</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>26,400 ~ 31,900원</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>3182000</v>
+      </c>
+      <c r="J12" s="11" t="n">
+        <v>1015.1</v>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
+        </is>
+      </c>
+      <c r="L12" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
           <t>씨앤엠</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>전동기 및 발전기 제조업</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>10,000 ~ 13,000원</t>
         </is>
       </c>
-      <c r="I12" s="10" t="n">
+      <c r="I13" s="10" t="n">
         <v>2059500</v>
       </c>
-      <c r="J12" s="11" t="n">
+      <c r="J13" s="11" t="n">
         <v>267.7</v>
       </c>
-      <c r="K12" s="9" t="inlineStr">
+      <c r="K13" s="9" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L12" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>넥스아이</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,500 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J13" s="6" t="n">
-        <v>487.5</v>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
+      <c r="L13" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>항공기용 부품 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1280,28 +1280,28 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,700 ~ 5,700원</t>
+          <t>10,500 ~ 13,000원</t>
         </is>
       </c>
       <c r="I14" s="5" t="n">
-        <v>3300000</v>
+        <v>3750000</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>188.1</v>
+        <v>487.5</v>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
+          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
@@ -1313,172 +1313,172 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>하나에어로다이내믹스</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>항공기용 부품 제조업</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>4,700 ~ 5,700원</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>188.1</v>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>바로팜</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>전자상거래 소매 중개업</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>16,400 ~ 20,200원</t>
         </is>
       </c>
-      <c r="I15" s="5" t="n">
+      <c r="I16" s="5" t="n">
         <v>1335000</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="J16" s="6" t="n">
         <v>269.7</v>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L15" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>엠비디</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>물질 검사, 측정 및 분석기구 제조업</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>9,600 ~ 11,700원</t>
         </is>
       </c>
-      <c r="I16" s="10" t="n">
+      <c r="I17" s="10" t="n">
         <v>1500000</v>
       </c>
-      <c r="J16" s="11" t="n">
+      <c r="J17" s="11" t="n">
         <v>175.5</v>
       </c>
-      <c r="K16" s="9" t="inlineStr">
+      <c r="K17" s="9" t="inlineStr">
         <is>
           <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
         </is>
       </c>
-      <c r="L16" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>래블업</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>시스템 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>19,000 ~ 22,000원</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>1635000</v>
-      </c>
-      <c r="J17" s="6" t="n">
-        <v>359.7</v>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>NH투자증권 02-768-7462, 7467</t>
-        </is>
-      </c>
-      <c r="L17" s="7" t="inlineStr">
+      <c r="L17" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1487,114 +1487,114 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>래블업</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>시스템 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>19,000 ~ 22,000원</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>1635000</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>359.7</v>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>NH투자증권 02-768-7462, 7467</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>에이엘로봇</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>기타 기계 및 장비 제조업</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>정정-변경(수요예측)</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>15,700 ~ 17,600원</t>
         </is>
       </c>
-      <c r="I18" s="5" t="n">
+      <c r="I19" s="5" t="n">
         <v>1800000</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="J19" s="6" t="n">
         <v>316.8</v>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="L18" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>아델</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>18,000 ~ 25,000원</t>
-        </is>
-      </c>
-      <c r="I19" s="10" t="n">
-        <v>1627500</v>
-      </c>
-      <c r="J19" s="11" t="n">
-        <v>406.9</v>
-      </c>
-      <c r="K19" s="9" t="inlineStr">
-        <is>
-          <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
-        </is>
-      </c>
-      <c r="L19" s="12" t="inlineStr">
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1608,12 +1608,12 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>SimwonAmericaCorp.</t>
+          <t>아델</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>자동차 신품 부품 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
@@ -1623,15 +1623,35 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>수요예측 항목 없음(원문 확인)</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr"/>
-      <c r="G20" s="8" t="inlineStr"/>
-      <c r="H20" s="8" t="inlineStr"/>
-      <c r="I20" s="10" t="inlineStr"/>
-      <c r="J20" s="11" t="inlineStr"/>
-      <c r="K20" s="9" t="inlineStr"/>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>18,000 ~ 25,000원</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="n">
+        <v>1627500</v>
+      </c>
+      <c r="J20" s="11" t="n">
+        <v>406.9</v>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
       <c r="L20" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -1641,55 +1661,35 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>다비오</t>
+          <t>SimwonAmericaCorp.</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
+          <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>12,300 ~ 16,600원</t>
-        </is>
-      </c>
-      <c r="I21" s="10" t="n">
-        <v>750000</v>
-      </c>
-      <c r="J21" s="11" t="n">
-        <v>124.5</v>
-      </c>
-      <c r="K21" s="9" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
-        </is>
-      </c>
+          <t>수요예측 항목 없음(원문 확인)</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr"/>
+      <c r="G21" s="8" t="inlineStr"/>
+      <c r="H21" s="8" t="inlineStr"/>
+      <c r="I21" s="10" t="inlineStr"/>
+      <c r="J21" s="11" t="inlineStr"/>
+      <c r="K21" s="9" t="inlineStr"/>
       <c r="L21" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>엔키화이트햇</t>
+          <t>다비오</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
@@ -1724,28 +1724,28 @@
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>13,000 ~ 16,500원</t>
+          <t>12,300 ~ 16,600원</t>
         </is>
       </c>
       <c r="I22" s="10" t="n">
-        <v>1258000</v>
+        <v>750000</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>207.6</v>
+        <v>124.5</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
+          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
         </is>
       </c>
       <c r="L22" s="12" t="inlineStr">
@@ -1762,167 +1762,167 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
+          <t>엔키화이트햇</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>13,000 ~ 16,500원</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="n">
+        <v>1258000</v>
+      </c>
+      <c r="J23" s="11" t="n">
+        <v>207.6</v>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
+        </is>
+      </c>
+      <c r="L23" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
           <t>영광와이케이엠씨</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>그 외 기타 금속가공업</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>9,400 ~ 11,000원</t>
         </is>
       </c>
-      <c r="I23" s="10" t="n">
+      <c r="I24" s="10" t="n">
         <v>1694840</v>
       </c>
-      <c r="J23" s="11" t="n">
+      <c r="J24" s="11" t="n">
         <v>186.4</v>
       </c>
-      <c r="K23" s="9" t="inlineStr">
+      <c r="K24" s="9" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
         </is>
       </c>
-      <c r="L23" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="L24" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>영광</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>수상 금속 골조 구조재 제조업</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>14,000 ~ 17,000원</t>
         </is>
       </c>
-      <c r="I24" s="5" t="n">
+      <c r="I25" s="5" t="n">
         <v>1695000</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="J25" s="6" t="n">
         <v>288.1</v>
       </c>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L24" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>인텔리빅스</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>7,600 ~ 9,000원</t>
-        </is>
-      </c>
-      <c r="I25" s="10" t="n">
-        <v>1875000</v>
-      </c>
-      <c r="J25" s="11" t="n">
-        <v>168.8</v>
-      </c>
-      <c r="K25" s="9" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
-        </is>
-      </c>
-      <c r="L25" s="12" t="inlineStr">
+      <c r="L25" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1931,22 +1931,22 @@
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>케이엠에프</t>
+          <t>인텔리빅스</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
@@ -1956,28 +1956,28 @@
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>15,000 ~ 17,800원</t>
+          <t>7,600 ~ 9,000원</t>
         </is>
       </c>
       <c r="I26" s="10" t="n">
-        <v>1500000</v>
+        <v>1875000</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>267</v>
+        <v>168.8</v>
       </c>
       <c r="K26" s="9" t="inlineStr">
         <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
+          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
       <c r="L26" s="12" t="inlineStr">
@@ -1989,22 +1989,22 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>디티에스</t>
+          <t>케이엠에프</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -2014,28 +2014,28 @@
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>17,000 ~ 18,500원</t>
+          <t>15,000 ~ 17,800원</t>
         </is>
       </c>
       <c r="I27" s="10" t="n">
-        <v>1671687</v>
+        <v>1500000</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>309.3</v>
+        <v>267</v>
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
@@ -2047,17 +2047,17 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>엠에스바이오</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>그 외 기타 의료용 기기 제조업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
@@ -2072,28 +2072,28 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>6,800 ~ 7,800원</t>
+          <t>17,000 ~ 18,500원</t>
         </is>
       </c>
       <c r="I28" s="10" t="n">
-        <v>2840000</v>
+        <v>1671687</v>
       </c>
       <c r="J28" s="11" t="n">
-        <v>221.5</v>
+        <v>309.3</v>
       </c>
       <c r="K28" s="9" t="inlineStr">
         <is>
-          <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
+          <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
         </is>
       </c>
       <c r="L28" s="12" t="inlineStr">
@@ -2105,53 +2105,53 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>엠에스바이오</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>그 외 기타 의료용 기기 제조업</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>크리에이츠</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>15,000 ~ 18,000원</t>
+          <t>6,800 ~ 7,800원</t>
         </is>
       </c>
       <c r="I29" s="10" t="n">
-        <v>1050000</v>
+        <v>2840000</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>189</v>
+        <v>221.5</v>
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-7414, 7375, 7651</t>
+          <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
@@ -2163,63 +2163,121 @@
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>크리에이츠</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>15,000 ~ 18,000원</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="n">
+        <v>1050000</v>
+      </c>
+      <c r="J30" s="11" t="n">
+        <v>189</v>
+      </c>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-7414, 7375, 7651</t>
+        </is>
+      </c>
+      <c r="L30" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>티앤이코리아</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>산업용 송풍기 및 배기장치 제조업</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>12,600 ~ 15,300원</t>
         </is>
       </c>
-      <c r="I30" s="10" t="n">
+      <c r="I31" s="10" t="n">
         <v>1800000</v>
       </c>
-      <c r="J30" s="11" t="n">
+      <c r="J31" s="11" t="n">
         <v>275.4</v>
       </c>
-      <c r="K30" s="9" t="inlineStr">
+      <c r="K31" s="9" t="inlineStr">
         <is>
           <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
         </is>
       </c>
-      <c r="L30" s="12" t="inlineStr">
+      <c r="L31" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L30"/>
+  <autoFilter ref="A1:L31"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -2250,6 +2308,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2261,7 +2320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2457,58 +2516,58 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>동원파츠</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>반도체 제조용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>인터엑스</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-04</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>10,000 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I4" s="10" t="n">
-        <v>2250000</v>
-      </c>
-      <c r="J4" s="11" t="n">
-        <v>292.5</v>
-      </c>
-      <c r="K4" s="9" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5700, 6648</t>
-        </is>
-      </c>
-      <c r="L4" s="12" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>23,000 ~ 26,500원</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>1522500</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>403.5</v>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-6975, 8217, 7651</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2517,172 +2576,172 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>인터엑스</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>10,000 ~ 13,000원</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="n">
+        <v>2250000</v>
+      </c>
+      <c r="J5" s="11" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5700, 6648</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>유캐스트</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>기타 무선 통신장비 제조업</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>19,000 ~ 23,000원</t>
         </is>
       </c>
-      <c r="I5" s="10" t="n">
+      <c r="I6" s="10" t="n">
         <v>600000</v>
       </c>
-      <c r="J5" s="11" t="n">
+      <c r="J6" s="11" t="n">
         <v>138</v>
       </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
         </is>
       </c>
-      <c r="L5" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>옵토닉스</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>광학렌즈 및 광학요소 제조업</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>10,000 ~ 12,000원</t>
         </is>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="I7" s="5" t="n">
         <v>1572490</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="J7" s="6" t="n">
         <v>188.7</v>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>이노보테라퓨틱스</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-02</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>20,000 ~ 24,000원</t>
-        </is>
-      </c>
-      <c r="I7" s="10" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="J7" s="11" t="n">
-        <v>396</v>
-      </c>
-      <c r="K7" s="9" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
-        </is>
-      </c>
-      <c r="L7" s="12" t="inlineStr">
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2691,172 +2750,172 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>이노보테라퓨틱스</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>의학 및 약학 연구개발업</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>20,000 ~ 24,000원</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J8" s="11" t="n">
+        <v>396</v>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+        </is>
+      </c>
+      <c r="L8" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>기타 엔지니어링 서비스업</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>2026-11-19</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>2026-11-25</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>11,200 ~ 13,600원</t>
         </is>
       </c>
-      <c r="I8" s="10" t="n">
+      <c r="I9" s="10" t="n">
         <v>1575000</v>
       </c>
-      <c r="J8" s="11" t="n">
+      <c r="J9" s="11" t="n">
         <v>214.2</v>
       </c>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="K9" s="9" t="inlineStr">
         <is>
           <t>NH투자증권 02-2229-6315, 6829</t>
         </is>
       </c>
-      <c r="L8" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>이에스티</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>그 외 기타 전자부품 제조업</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>10,600 ~ 12,400원</t>
         </is>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="I10" s="5" t="n">
         <v>1650000</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J10" s="6" t="n">
         <v>204.6</v>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="L9" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>에스에프씨</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>그 외 기타 분류 안된 화학제품 제조업</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>31,600 ~ 36,100원</t>
-        </is>
-      </c>
-      <c r="I10" s="10" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J10" s="11" t="n">
-        <v>1353.8</v>
-      </c>
-      <c r="K10" s="9" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
-        </is>
-      </c>
-      <c r="L10" s="12" t="inlineStr">
+      <c r="L10" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2870,12 +2929,12 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>씨아이에스케미칼</t>
+          <t>에스에프씨</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>알루미늄 제련, 정련 및 합금 제조업</t>
+          <t>그 외 기타 분류 안된 화학제품 제조업</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -2890,28 +2949,28 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>5,400 ~ 6,800원</t>
+          <t>31,600 ~ 36,100원</t>
         </is>
       </c>
       <c r="I11" s="10" t="n">
-        <v>3000000</v>
+        <v>3750000</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>204</v>
+        <v>1353.8</v>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
+          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
         </is>
       </c>
       <c r="L11" s="12" t="inlineStr">
@@ -2923,17 +2982,17 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>제이앤티지</t>
+          <t>씨아이에스케미칼</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>그 외 자동차용 신품 부품 제조업</t>
+          <t>알루미늄 제련, 정련 및 합금 제조업</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
@@ -2948,28 +3007,28 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>26,400 ~ 31,900원</t>
+          <t>5,400 ~ 6,800원</t>
         </is>
       </c>
       <c r="I12" s="10" t="n">
-        <v>3182000</v>
+        <v>3000000</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>1015.1</v>
+        <v>204</v>
       </c>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
+          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
       <c r="L12" s="12" t="inlineStr">
@@ -2986,109 +3045,109 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
+          <t>제이앤티지</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>그 외 자동차용 신품 부품 제조업</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>26,400 ~ 31,900원</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>3182000</v>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>1015.1</v>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
+        </is>
+      </c>
+      <c r="L13" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
           <t>씨앤엠</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>전동기 및 발전기 제조업</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>10,000 ~ 13,000원</t>
         </is>
       </c>
-      <c r="I13" s="10" t="n">
+      <c r="I14" s="10" t="n">
         <v>2059500</v>
       </c>
-      <c r="J13" s="11" t="n">
+      <c r="J14" s="11" t="n">
         <v>267.7</v>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K14" s="9" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L13" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>넥스아이</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>10,500 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J14" s="6" t="n">
-        <v>487.5</v>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
-        </is>
-      </c>
-      <c r="L14" s="7" t="inlineStr">
+      <c r="L14" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3102,12 +3161,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>항공기용 부품 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -3122,28 +3181,28 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,700 ~ 5,700원</t>
+          <t>10,500 ~ 13,000원</t>
         </is>
       </c>
       <c r="I15" s="5" t="n">
-        <v>3300000</v>
+        <v>3750000</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>188.1</v>
+        <v>487.5</v>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
+          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -3155,172 +3214,172 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>하나에어로다이내믹스</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>항공기용 부품 제조업</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,700 ~ 5,700원</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>188.1</v>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>바로팜</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>전자상거래 소매 중개업</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>16,400 ~ 20,200원</t>
         </is>
       </c>
-      <c r="I16" s="5" t="n">
+      <c r="I17" s="5" t="n">
         <v>1335000</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="J17" s="6" t="n">
         <v>269.7</v>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>엠비디</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>물질 검사, 측정 및 분석기구 제조업</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>9,600 ~ 11,700원</t>
         </is>
       </c>
-      <c r="I17" s="10" t="n">
+      <c r="I18" s="10" t="n">
         <v>1500000</v>
       </c>
-      <c r="J17" s="11" t="n">
+      <c r="J18" s="11" t="n">
         <v>175.5</v>
       </c>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="K18" s="9" t="inlineStr">
         <is>
           <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
         </is>
       </c>
-      <c r="L17" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>래블업</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>시스템 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>19,000 ~ 22,000원</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>1635000</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>359.7</v>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>NH투자증권 02-768-7462, 7467</t>
-        </is>
-      </c>
-      <c r="L18" s="7" t="inlineStr">
+      <c r="L18" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3329,53 +3388,53 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>래블업</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>시스템 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>이에스티</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>그 외 기타 전자부품 제조업</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,600 ~ 12,400원</t>
+          <t>19,000 ~ 22,000원</t>
         </is>
       </c>
       <c r="I19" s="5" t="n">
-        <v>1650000</v>
+        <v>1635000</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>204.6</v>
+        <v>359.7</v>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+          <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
@@ -3387,114 +3446,114 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>이에스티</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>그 외 기타 전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>10,600 ~ 12,400원</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>204.6</v>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>에이엘로봇</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>기타 기계 및 장비 제조업</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>정정-변경(수요예측)</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>15,700 ~ 17,600원</t>
         </is>
       </c>
-      <c r="I20" s="5" t="n">
+      <c r="I21" s="5" t="n">
         <v>1800000</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="J21" s="6" t="n">
         <v>316.8</v>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="L20" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>아델</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>18,000 ~ 25,000원</t>
-        </is>
-      </c>
-      <c r="I21" s="10" t="n">
-        <v>1627500</v>
-      </c>
-      <c r="J21" s="11" t="n">
-        <v>406.9</v>
-      </c>
-      <c r="K21" s="9" t="inlineStr">
-        <is>
-          <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
-        </is>
-      </c>
-      <c r="L21" s="12" t="inlineStr">
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3508,12 +3567,12 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>SimwonAmericaCorp.</t>
+          <t>아델</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>자동차 신품 부품 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
@@ -3523,15 +3582,35 @@
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>수요예측 항목 없음(원문 확인)</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr"/>
-      <c r="G22" s="8" t="inlineStr"/>
-      <c r="H22" s="8" t="inlineStr"/>
-      <c r="I22" s="10" t="inlineStr"/>
-      <c r="J22" s="11" t="inlineStr"/>
-      <c r="K22" s="9" t="inlineStr"/>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>18,000 ~ 25,000원</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="n">
+        <v>1627500</v>
+      </c>
+      <c r="J22" s="11" t="n">
+        <v>406.9</v>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
       <c r="L22" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -3541,55 +3620,35 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>다비오</t>
+          <t>SimwonAmericaCorp.</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
+          <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>12,300 ~ 16,600원</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="n">
-        <v>750000</v>
-      </c>
-      <c r="J23" s="11" t="n">
-        <v>124.5</v>
-      </c>
-      <c r="K23" s="9" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
-        </is>
-      </c>
+          <t>수요예측 항목 없음(원문 확인)</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr"/>
+      <c r="G23" s="8" t="inlineStr"/>
+      <c r="H23" s="8" t="inlineStr"/>
+      <c r="I23" s="10" t="inlineStr"/>
+      <c r="J23" s="11" t="inlineStr"/>
+      <c r="K23" s="9" t="inlineStr"/>
       <c r="L23" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -3604,7 +3663,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>엔키화이트햇</t>
+          <t>다비오</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -3614,7 +3673,7 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
@@ -3624,28 +3683,28 @@
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>13,000 ~ 16,500원</t>
+          <t>12,300 ~ 16,600원</t>
         </is>
       </c>
       <c r="I24" s="10" t="n">
-        <v>1258000</v>
+        <v>750000</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>207.6</v>
+        <v>124.5</v>
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
-          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
+          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
         </is>
       </c>
       <c r="L24" s="12" t="inlineStr">
@@ -3662,167 +3721,167 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
+          <t>엔키화이트햇</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>13,000 ~ 16,500원</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="n">
+        <v>1258000</v>
+      </c>
+      <c r="J25" s="11" t="n">
+        <v>207.6</v>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
+        </is>
+      </c>
+      <c r="L25" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
           <t>영광와이케이엠씨</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>그 외 기타 금속가공업</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>9,400 ~ 11,000원</t>
         </is>
       </c>
-      <c r="I25" s="10" t="n">
+      <c r="I26" s="10" t="n">
         <v>1694840</v>
       </c>
-      <c r="J25" s="11" t="n">
+      <c r="J26" s="11" t="n">
         <v>186.4</v>
       </c>
-      <c r="K25" s="9" t="inlineStr">
+      <c r="K26" s="9" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
         </is>
       </c>
-      <c r="L25" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="L26" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>영광</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>수상 금속 골조 구조재 제조업</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>14,000 ~ 17,000원</t>
         </is>
       </c>
-      <c r="I26" s="5" t="n">
+      <c r="I27" s="5" t="n">
         <v>1695000</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="J27" s="6" t="n">
         <v>288.1</v>
       </c>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L26" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>인텔리빅스</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>7,600 ~ 9,000원</t>
-        </is>
-      </c>
-      <c r="I27" s="10" t="n">
-        <v>1875000</v>
-      </c>
-      <c r="J27" s="11" t="n">
-        <v>168.8</v>
-      </c>
-      <c r="K27" s="9" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
-        </is>
-      </c>
-      <c r="L27" s="12" t="inlineStr">
+      <c r="L27" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3831,172 +3890,172 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>인텔리빅스</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>7,600 ~ 9,000원</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="n">
+        <v>1875000</v>
+      </c>
+      <c r="J28" s="11" t="n">
+        <v>168.8</v>
+      </c>
+      <c r="K28" s="9" t="inlineStr">
+        <is>
+          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
+      <c r="L28" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>제논</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>9,700 ~ 12,200원</t>
         </is>
       </c>
-      <c r="I28" s="10" t="n">
+      <c r="I29" s="10" t="n">
         <v>1550000</v>
       </c>
-      <c r="J28" s="11" t="n">
+      <c r="J29" s="11" t="n">
         <v>189.1</v>
       </c>
-      <c r="K28" s="9" t="inlineStr">
+      <c r="K29" s="9" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-8023, 7653, 7850</t>
         </is>
       </c>
-      <c r="L28" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="L29" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>래블업</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>시스템 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>19,000 ~ 22,000원</t>
         </is>
       </c>
-      <c r="I29" s="5" t="n">
+      <c r="I30" s="5" t="n">
         <v>1635000</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="J30" s="6" t="n">
         <v>359.7</v>
       </c>
-      <c r="K29" s="3" t="inlineStr">
+      <c r="K30" s="3" t="inlineStr">
         <is>
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="L29" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>케이엠에프</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>기타 식품 제조업</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-20</t>
-        </is>
-      </c>
-      <c r="H30" s="8" t="inlineStr">
-        <is>
-          <t>15,000 ~ 17,800원</t>
-        </is>
-      </c>
-      <c r="I30" s="10" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="J30" s="11" t="n">
-        <v>267</v>
-      </c>
-      <c r="K30" s="9" t="inlineStr">
-        <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
-        </is>
-      </c>
-      <c r="L30" s="12" t="inlineStr">
+      <c r="L30" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4005,22 +4064,22 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>바로팜</t>
+          <t>케이엠에프</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>전자상거래 소매 중개업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -4030,28 +4089,28 @@
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>16,400 ~ 20,200원</t>
+          <t>15,000 ~ 17,800원</t>
         </is>
       </c>
       <c r="I31" s="10" t="n">
-        <v>1335000</v>
+        <v>1500000</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>269.7</v>
+        <v>267</v>
       </c>
       <c r="K31" s="9" t="inlineStr">
         <is>
-          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
@@ -4068,12 +4127,12 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>디티에스</t>
+          <t>바로팜</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>전자상거래 소매 중개업</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
@@ -4088,28 +4147,28 @@
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>17,000 ~ 18,500원</t>
+          <t>16,400 ~ 20,200원</t>
         </is>
       </c>
       <c r="I32" s="10" t="n">
-        <v>1671687</v>
+        <v>1335000</v>
       </c>
       <c r="J32" s="11" t="n">
-        <v>309.3</v>
+        <v>269.7</v>
       </c>
       <c r="K32" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
+          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
       <c r="L32" s="12" t="inlineStr">
@@ -4121,22 +4180,22 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>엠에스바이오</t>
+          <t>동원파츠</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>그 외 기타 의료용 기기 제조업</t>
+          <t>반도체 제조용 기계 제조업</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -4146,28 +4205,28 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>6,800 ~ 7,800원</t>
+          <t>23,000 ~ 26,500원</t>
         </is>
       </c>
       <c r="I33" s="10" t="n">
-        <v>2840000</v>
+        <v>1522500</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>221.5</v>
+        <v>403.5</v>
       </c>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
+          <t>삼성증권 02-2020-6975, 8217, 7651</t>
         </is>
       </c>
       <c r="L33" s="12" t="inlineStr">
@@ -4179,22 +4238,22 @@
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>옵토닉스</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>광학렌즈 및 광학요소 제조업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
@@ -4204,28 +4263,28 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>10,000 ~ 12,000원</t>
+          <t>17,000 ~ 18,500원</t>
         </is>
       </c>
       <c r="I34" s="10" t="n">
-        <v>1572490</v>
+        <v>1671687</v>
       </c>
       <c r="J34" s="11" t="n">
-        <v>188.7</v>
+        <v>309.3</v>
       </c>
       <c r="K34" s="9" t="inlineStr">
         <is>
-          <t>한국투자증권 02-3276-5958, 6269</t>
+          <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
         </is>
       </c>
       <c r="L34" s="12" t="inlineStr">
@@ -4237,53 +4296,53 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>엠에스바이오</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>그 외 기타 의료용 기기 제조업</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>넥스아이</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>10,500 ~ 13,000원</t>
+          <t>6,800 ~ 7,800원</t>
         </is>
       </c>
       <c r="I35" s="10" t="n">
-        <v>3750000</v>
+        <v>2840000</v>
       </c>
       <c r="J35" s="11" t="n">
-        <v>487.5</v>
+        <v>221.5</v>
       </c>
       <c r="K35" s="9" t="inlineStr">
         <is>
-          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
+          <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
       <c r="L35" s="12" t="inlineStr">
@@ -4295,22 +4354,22 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>옵토닉스</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
+          <t>광학렌즈 및 광학요소 제조업</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
@@ -4320,28 +4379,28 @@
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>15,000 ~ 18,000원</t>
+          <t>10,000 ~ 12,000원</t>
         </is>
       </c>
       <c r="I36" s="10" t="n">
-        <v>1050000</v>
+        <v>1572490</v>
       </c>
       <c r="J36" s="11" t="n">
-        <v>189</v>
+        <v>188.7</v>
       </c>
       <c r="K36" s="9" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-7414, 7375, 7651</t>
+          <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
       <c r="L36" s="12" t="inlineStr">
@@ -4353,22 +4412,22 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>티앤이코리아</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>산업용 송풍기 및 배기장치 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -4378,28 +4437,28 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>12,600 ~ 15,300원</t>
+          <t>10,500 ~ 13,000원</t>
         </is>
       </c>
       <c r="I37" s="10" t="n">
-        <v>1800000</v>
+        <v>3750000</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>275.4</v>
+        <v>487.5</v>
       </c>
       <c r="K37" s="9" t="inlineStr">
         <is>
-          <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
+          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
         </is>
       </c>
       <c r="L37" s="12" t="inlineStr">
@@ -4411,22 +4470,22 @@
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>항공기용 부품 제조업</t>
+          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
@@ -4436,28 +4495,28 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>4,700 ~ 5,700원</t>
+          <t>15,000 ~ 18,000원</t>
         </is>
       </c>
       <c r="I38" s="10" t="n">
-        <v>3300000</v>
+        <v>1050000</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>188.1</v>
+        <v>189</v>
       </c>
       <c r="K38" s="9" t="inlineStr">
         <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
+          <t>삼성증권 02-2020-7414, 7375, 7651</t>
         </is>
       </c>
       <c r="L38" s="12" t="inlineStr">
@@ -4469,17 +4528,17 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>래블업</t>
+          <t>티앤이코리아</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>시스템 소프트웨어 개발 및 공급업</t>
+          <t>산업용 송풍기 및 배기장치 제조업</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
@@ -4494,28 +4553,28 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>19,000 ~ 22,000원</t>
+          <t>12,600 ~ 15,300원</t>
         </is>
       </c>
       <c r="I39" s="10" t="n">
-        <v>1635000</v>
+        <v>1800000</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>359.7</v>
+        <v>275.4</v>
       </c>
       <c r="K39" s="9" t="inlineStr">
         <is>
-          <t>NH투자증권 02-768-7462, 7467</t>
+          <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
         </is>
       </c>
       <c r="L39" s="12" t="inlineStr">
@@ -4532,12 +4591,12 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>영광</t>
+          <t>하나에어로다이내믹스</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>수상 금속 골조 구조재 제조업</t>
+          <t>항공기용 부품 제조업</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
@@ -4552,28 +4611,28 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>14,000 ~ 17,000원</t>
+          <t>4,700 ~ 5,700원</t>
         </is>
       </c>
       <c r="I40" s="10" t="n">
-        <v>1695000</v>
+        <v>3300000</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>288.1</v>
+        <v>188.1</v>
       </c>
       <c r="K40" s="9" t="inlineStr">
         <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
         </is>
       </c>
       <c r="L40" s="12" t="inlineStr">
@@ -4590,17 +4649,17 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>이에스티</t>
+          <t>래블업</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>그 외 기타 전자부품 제조업</t>
+          <t>시스템 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -4610,28 +4669,28 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>10,600 ~ 12,400원</t>
+          <t>19,000 ~ 22,000원</t>
         </is>
       </c>
       <c r="I41" s="10" t="n">
-        <v>1650000</v>
+        <v>1635000</v>
       </c>
       <c r="J41" s="11" t="n">
-        <v>204.6</v>
+        <v>359.7</v>
       </c>
       <c r="K41" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+          <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
       <c r="L41" s="12" t="inlineStr">
@@ -4648,58 +4707,174 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
+          <t>영광</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>수상 금속 골조 구조재 제조업</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>14,000 ~ 17,000원</t>
+        </is>
+      </c>
+      <c r="I42" s="10" t="n">
+        <v>1695000</v>
+      </c>
+      <c r="J42" s="11" t="n">
+        <v>288.1</v>
+      </c>
+      <c r="K42" s="9" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+        </is>
+      </c>
+      <c r="L42" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>이에스티</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>그 외 기타 전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>10,600 ~ 12,400원</t>
+        </is>
+      </c>
+      <c r="I43" s="10" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J43" s="11" t="n">
+        <v>204.6</v>
+      </c>
+      <c r="K43" s="9" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+        </is>
+      </c>
+      <c r="L43" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
           <t>에이엘로봇</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C44" s="9" t="inlineStr">
         <is>
           <t>기타 기계 및 장비 제조업</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr">
+      <c r="D44" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
+      <c r="E44" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
+      <c r="F44" s="8" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G42" s="8" t="inlineStr">
+      <c r="G44" s="8" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="H42" s="8" t="inlineStr">
+      <c r="H44" s="8" t="inlineStr">
         <is>
           <t>15,700 ~ 17,600원</t>
         </is>
       </c>
-      <c r="I42" s="10" t="n">
+      <c r="I44" s="10" t="n">
         <v>1800000</v>
       </c>
-      <c r="J42" s="11" t="n">
+      <c r="J44" s="11" t="n">
         <v>316.8</v>
       </c>
-      <c r="K42" s="9" t="inlineStr">
+      <c r="K44" s="9" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="L42" s="12" t="inlineStr">
+      <c r="L44" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L42"/>
+  <autoFilter ref="A1:L44"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -4742,6 +4917,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/수요예측_일정.xlsx
+++ b/수요예측_일정.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'수요예측 일정'!$A$1:$L$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체 이력'!$A$1:$L$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체 이력'!$A$1:$L$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -559,17 +559,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>제논</t>
+          <t>케이엠에프</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -579,7 +579,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>정정-변경(수요예측)</t>
+          <t>정정-변경없음</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -594,18 +594,18 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>9,700 ~ 12,200원</t>
+          <t>15,000 ~ 17,800원</t>
         </is>
       </c>
       <c r="I2" s="5" t="n">
-        <v>1550000</v>
+        <v>1500000</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>189.1</v>
+        <v>267</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-8023, 7653, 7850</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
         </is>
       </c>
       <c r="L2" s="7" t="inlineStr">
@@ -617,114 +617,114 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>제논</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경(수요예측)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>9,700 ~ 12,200원</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>1550000</v>
+      </c>
+      <c r="J3" s="6" t="n">
+        <v>189.1</v>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-8023, 7653, 7850</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>동원파츠</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>반도체 제조용 기계 제조업</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>23,000 ~ 26,500원</t>
         </is>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="I4" s="5" t="n">
         <v>1522500</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="J4" s="6" t="n">
         <v>403.5</v>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-6975, 8217, 7651</t>
         </is>
       </c>
-      <c r="L3" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>인터엑스</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-04</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>10,000 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I4" s="10" t="n">
-        <v>2250000</v>
-      </c>
-      <c r="J4" s="11" t="n">
-        <v>292.5</v>
-      </c>
-      <c r="K4" s="9" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5700, 6648</t>
-        </is>
-      </c>
-      <c r="L4" s="12" t="inlineStr">
+      <c r="L4" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -733,172 +733,172 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>인터엑스</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>10,000 ~ 13,000원</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="n">
+        <v>2250000</v>
+      </c>
+      <c r="J5" s="11" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5700, 6648</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>유캐스트</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>기타 무선 통신장비 제조업</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>19,000 ~ 23,000원</t>
         </is>
       </c>
-      <c r="I5" s="10" t="n">
+      <c r="I6" s="10" t="n">
         <v>600000</v>
       </c>
-      <c r="J5" s="11" t="n">
+      <c r="J6" s="11" t="n">
         <v>138</v>
       </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
         </is>
       </c>
-      <c r="L5" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>옵토닉스</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>광학렌즈 및 광학요소 제조업</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>10,000 ~ 12,000원</t>
         </is>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="I7" s="5" t="n">
         <v>1572490</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="J7" s="6" t="n">
         <v>188.7</v>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>이노보테라퓨틱스</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-02</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>20,000 ~ 24,000원</t>
-        </is>
-      </c>
-      <c r="I7" s="10" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="J7" s="11" t="n">
-        <v>396</v>
-      </c>
-      <c r="K7" s="9" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
-        </is>
-      </c>
-      <c r="L7" s="12" t="inlineStr">
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -907,172 +907,172 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>이노보테라퓨틱스</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>의학 및 약학 연구개발업</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>20,000 ~ 24,000원</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J8" s="11" t="n">
+        <v>396</v>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+        </is>
+      </c>
+      <c r="L8" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>기타 엔지니어링 서비스업</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>2026-11-19</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>2026-11-25</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>11,200 ~ 13,600원</t>
         </is>
       </c>
-      <c r="I8" s="10" t="n">
+      <c r="I9" s="10" t="n">
         <v>1575000</v>
       </c>
-      <c r="J8" s="11" t="n">
+      <c r="J9" s="11" t="n">
         <v>214.2</v>
       </c>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="K9" s="9" t="inlineStr">
         <is>
           <t>NH투자증권 02-2229-6315, 6829</t>
         </is>
       </c>
-      <c r="L8" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>이에스티</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>그 외 기타 전자부품 제조업</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>10,600 ~ 12,400원</t>
         </is>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="I10" s="5" t="n">
         <v>1650000</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J10" s="6" t="n">
         <v>204.6</v>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="L9" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>에스에프씨</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>그 외 기타 분류 안된 화학제품 제조업</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>31,600 ~ 36,100원</t>
-        </is>
-      </c>
-      <c r="I10" s="10" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J10" s="11" t="n">
-        <v>1353.8</v>
-      </c>
-      <c r="K10" s="9" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
-        </is>
-      </c>
-      <c r="L10" s="12" t="inlineStr">
+      <c r="L10" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>씨아이에스케미칼</t>
+          <t>에스에프씨</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>알루미늄 제련, 정련 및 합금 제조업</t>
+          <t>그 외 기타 분류 안된 화학제품 제조업</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -1106,28 +1106,28 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>5,400 ~ 6,800원</t>
+          <t>31,600 ~ 36,100원</t>
         </is>
       </c>
       <c r="I11" s="10" t="n">
-        <v>3000000</v>
+        <v>3750000</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>204</v>
+        <v>1353.8</v>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
+          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
         </is>
       </c>
       <c r="L11" s="12" t="inlineStr">
@@ -1139,17 +1139,17 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>제이앤티지</t>
+          <t>씨아이에스케미칼</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>그 외 자동차용 신품 부품 제조업</t>
+          <t>알루미늄 제련, 정련 및 합금 제조업</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
@@ -1164,28 +1164,28 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>26,400 ~ 31,900원</t>
+          <t>5,400 ~ 6,800원</t>
         </is>
       </c>
       <c r="I12" s="10" t="n">
-        <v>3182000</v>
+        <v>3000000</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>1015.1</v>
+        <v>204</v>
       </c>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
+          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
       <c r="L12" s="12" t="inlineStr">
@@ -1202,109 +1202,109 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
+          <t>제이앤티지</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>그 외 자동차용 신품 부품 제조업</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>26,400 ~ 31,900원</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>3182000</v>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>1015.1</v>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
+        </is>
+      </c>
+      <c r="L13" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
           <t>씨앤엠</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>전동기 및 발전기 제조업</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>10,000 ~ 13,000원</t>
         </is>
       </c>
-      <c r="I13" s="10" t="n">
+      <c r="I14" s="10" t="n">
         <v>2059500</v>
       </c>
-      <c r="J13" s="11" t="n">
+      <c r="J14" s="11" t="n">
         <v>267.7</v>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K14" s="9" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L13" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>넥스아이</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>10,500 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J14" s="6" t="n">
-        <v>487.5</v>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
-        </is>
-      </c>
-      <c r="L14" s="7" t="inlineStr">
+      <c r="L14" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>항공기용 부품 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1338,28 +1338,28 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,700 ~ 5,700원</t>
+          <t>10,500 ~ 13,000원</t>
         </is>
       </c>
       <c r="I15" s="5" t="n">
-        <v>3300000</v>
+        <v>3750000</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>188.1</v>
+        <v>487.5</v>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
+          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -1371,172 +1371,172 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>하나에어로다이내믹스</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>항공기용 부품 제조업</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,700 ~ 5,700원</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>188.1</v>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>바로팜</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>전자상거래 소매 중개업</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>16,400 ~ 20,200원</t>
         </is>
       </c>
-      <c r="I16" s="5" t="n">
+      <c r="I17" s="5" t="n">
         <v>1335000</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="J17" s="6" t="n">
         <v>269.7</v>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>엠비디</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>물질 검사, 측정 및 분석기구 제조업</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>9,600 ~ 11,700원</t>
         </is>
       </c>
-      <c r="I17" s="10" t="n">
+      <c r="I18" s="10" t="n">
         <v>1500000</v>
       </c>
-      <c r="J17" s="11" t="n">
+      <c r="J18" s="11" t="n">
         <v>175.5</v>
       </c>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="K18" s="9" t="inlineStr">
         <is>
           <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
         </is>
       </c>
-      <c r="L17" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>래블업</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>시스템 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>19,000 ~ 22,000원</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>1635000</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>359.7</v>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>NH투자증권 02-768-7462, 7467</t>
-        </is>
-      </c>
-      <c r="L18" s="7" t="inlineStr">
+      <c r="L18" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1545,114 +1545,114 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>래블업</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>시스템 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>19,000 ~ 22,000원</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>1635000</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>359.7</v>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>NH투자증권 02-768-7462, 7467</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>에이엘로봇</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>기타 기계 및 장비 제조업</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>정정-변경(수요예측)</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>15,700 ~ 17,600원</t>
         </is>
       </c>
-      <c r="I19" s="5" t="n">
+      <c r="I20" s="5" t="n">
         <v>1800000</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="J20" s="6" t="n">
         <v>316.8</v>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="L19" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>아델</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>18,000 ~ 25,000원</t>
-        </is>
-      </c>
-      <c r="I20" s="10" t="n">
-        <v>1627500</v>
-      </c>
-      <c r="J20" s="11" t="n">
-        <v>406.9</v>
-      </c>
-      <c r="K20" s="9" t="inlineStr">
-        <is>
-          <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
-        </is>
-      </c>
-      <c r="L20" s="12" t="inlineStr">
+      <c r="L20" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1666,12 +1666,12 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>SimwonAmericaCorp.</t>
+          <t>아델</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>자동차 신품 부품 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
@@ -1681,15 +1681,35 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>수요예측 항목 없음(원문 확인)</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr"/>
-      <c r="G21" s="8" t="inlineStr"/>
-      <c r="H21" s="8" t="inlineStr"/>
-      <c r="I21" s="10" t="inlineStr"/>
-      <c r="J21" s="11" t="inlineStr"/>
-      <c r="K21" s="9" t="inlineStr"/>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>18,000 ~ 25,000원</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="n">
+        <v>1627500</v>
+      </c>
+      <c r="J21" s="11" t="n">
+        <v>406.9</v>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -1699,55 +1719,35 @@
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>다비오</t>
+          <t>SimwonAmericaCorp.</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
+          <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>12,300 ~ 16,600원</t>
-        </is>
-      </c>
-      <c r="I22" s="10" t="n">
-        <v>750000</v>
-      </c>
-      <c r="J22" s="11" t="n">
-        <v>124.5</v>
-      </c>
-      <c r="K22" s="9" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
-        </is>
-      </c>
+          <t>수요예측 항목 없음(원문 확인)</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr"/>
+      <c r="G22" s="8" t="inlineStr"/>
+      <c r="H22" s="8" t="inlineStr"/>
+      <c r="I22" s="10" t="inlineStr"/>
+      <c r="J22" s="11" t="inlineStr"/>
+      <c r="K22" s="9" t="inlineStr"/>
       <c r="L22" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>엔키화이트햇</t>
+          <t>다비오</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -1782,28 +1782,28 @@
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>13,000 ~ 16,500원</t>
+          <t>12,300 ~ 16,600원</t>
         </is>
       </c>
       <c r="I23" s="10" t="n">
-        <v>1258000</v>
+        <v>750000</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>207.6</v>
+        <v>124.5</v>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
+          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr">
@@ -1820,167 +1820,167 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
+          <t>엔키화이트햇</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>13,000 ~ 16,500원</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="n">
+        <v>1258000</v>
+      </c>
+      <c r="J24" s="11" t="n">
+        <v>207.6</v>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
+        </is>
+      </c>
+      <c r="L24" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
           <t>영광와이케이엠씨</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>그 외 기타 금속가공업</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>9,400 ~ 11,000원</t>
         </is>
       </c>
-      <c r="I24" s="10" t="n">
+      <c r="I25" s="10" t="n">
         <v>1694840</v>
       </c>
-      <c r="J24" s="11" t="n">
+      <c r="J25" s="11" t="n">
         <v>186.4</v>
       </c>
-      <c r="K24" s="9" t="inlineStr">
+      <c r="K25" s="9" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
         </is>
       </c>
-      <c r="L24" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="L25" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>영광</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>수상 금속 골조 구조재 제조업</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>14,000 ~ 17,000원</t>
         </is>
       </c>
-      <c r="I25" s="5" t="n">
+      <c r="I26" s="5" t="n">
         <v>1695000</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="J26" s="6" t="n">
         <v>288.1</v>
       </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L25" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>인텔리빅스</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>7,600 ~ 9,000원</t>
-        </is>
-      </c>
-      <c r="I26" s="10" t="n">
-        <v>1875000</v>
-      </c>
-      <c r="J26" s="11" t="n">
-        <v>168.8</v>
-      </c>
-      <c r="K26" s="9" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
-        </is>
-      </c>
-      <c r="L26" s="12" t="inlineStr">
+      <c r="L26" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1989,22 +1989,22 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>케이엠에프</t>
+          <t>인텔리빅스</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -2014,28 +2014,28 @@
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>15,000 ~ 17,800원</t>
+          <t>7,600 ~ 9,000원</t>
         </is>
       </c>
       <c r="I27" s="10" t="n">
-        <v>1500000</v>
+        <v>1875000</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>267</v>
+        <v>168.8</v>
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
+          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
@@ -2320,7 +2320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2402,17 +2402,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>제논</t>
+          <t>케이엠에프</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>정정-변경(수요예측)</t>
+          <t>정정-변경없음</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -2437,18 +2437,18 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>9,700 ~ 12,200원</t>
+          <t>15,000 ~ 17,800원</t>
         </is>
       </c>
       <c r="I2" s="5" t="n">
-        <v>1550000</v>
+        <v>1500000</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>189.1</v>
+        <v>267</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-8023, 7653, 7850</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
         </is>
       </c>
       <c r="L2" s="7" t="inlineStr">
@@ -2460,7 +2460,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -2480,17 +2480,17 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>정정-변경없음</t>
+          <t>정정-변경(수요예측)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -2523,109 +2523,109 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>제논</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9,700 ~ 12,200원</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>1550000</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>189.1</v>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-8023, 7653, 7850</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>동원파츠</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>반도체 제조용 기계 제조업</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>23,000 ~ 26,500원</t>
         </is>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="I5" s="5" t="n">
         <v>1522500</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="J5" s="6" t="n">
         <v>403.5</v>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-6975, 8217, 7651</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>인터엑스</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-04</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>10,000 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I5" s="10" t="n">
-        <v>2250000</v>
-      </c>
-      <c r="J5" s="11" t="n">
-        <v>292.5</v>
-      </c>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5700, 6648</t>
-        </is>
-      </c>
-      <c r="L5" s="12" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2634,172 +2634,172 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>인터엑스</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>10,000 ~ 13,000원</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>2250000</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5700, 6648</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>유캐스트</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>기타 무선 통신장비 제조업</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>19,000 ~ 23,000원</t>
         </is>
       </c>
-      <c r="I6" s="10" t="n">
+      <c r="I7" s="10" t="n">
         <v>600000</v>
       </c>
-      <c r="J6" s="11" t="n">
+      <c r="J7" s="11" t="n">
         <v>138</v>
       </c>
-      <c r="K6" s="9" t="inlineStr">
+      <c r="K7" s="9" t="inlineStr">
         <is>
           <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
         </is>
       </c>
-      <c r="L6" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="L7" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>옵토닉스</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>광학렌즈 및 광학요소 제조업</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>10,000 ~ 12,000원</t>
         </is>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="I8" s="5" t="n">
         <v>1572490</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J8" s="6" t="n">
         <v>188.7</v>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>이노보테라퓨틱스</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-02</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>20,000 ~ 24,000원</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="J8" s="11" t="n">
-        <v>396</v>
-      </c>
-      <c r="K8" s="9" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
-        </is>
-      </c>
-      <c r="L8" s="12" t="inlineStr">
+      <c r="L8" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2808,172 +2808,172 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>이노보테라퓨틱스</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>의학 및 약학 연구개발업</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>20,000 ~ 24,000원</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>396</v>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+        </is>
+      </c>
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>기타 엔지니어링 서비스업</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>2026-11-19</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>2026-11-25</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>11,200 ~ 13,600원</t>
         </is>
       </c>
-      <c r="I9" s="10" t="n">
+      <c r="I10" s="10" t="n">
         <v>1575000</v>
       </c>
-      <c r="J9" s="11" t="n">
+      <c r="J10" s="11" t="n">
         <v>214.2</v>
       </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="K10" s="9" t="inlineStr">
         <is>
           <t>NH투자증권 02-2229-6315, 6829</t>
         </is>
       </c>
-      <c r="L9" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="L10" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>이에스티</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>그 외 기타 전자부품 제조업</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>10,600 ~ 12,400원</t>
         </is>
       </c>
-      <c r="I10" s="5" t="n">
+      <c r="I11" s="5" t="n">
         <v>1650000</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J11" s="6" t="n">
         <v>204.6</v>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="L10" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>에스에프씨</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>그 외 기타 분류 안된 화학제품 제조업</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>31,600 ~ 36,100원</t>
-        </is>
-      </c>
-      <c r="I11" s="10" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J11" s="11" t="n">
-        <v>1353.8</v>
-      </c>
-      <c r="K11" s="9" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
-        </is>
-      </c>
-      <c r="L11" s="12" t="inlineStr">
+      <c r="L11" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2987,12 +2987,12 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>씨아이에스케미칼</t>
+          <t>에스에프씨</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>알루미늄 제련, 정련 및 합금 제조업</t>
+          <t>그 외 기타 분류 안된 화학제품 제조업</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
@@ -3007,28 +3007,28 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>5,400 ~ 6,800원</t>
+          <t>31,600 ~ 36,100원</t>
         </is>
       </c>
       <c r="I12" s="10" t="n">
-        <v>3000000</v>
+        <v>3750000</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>204</v>
+        <v>1353.8</v>
       </c>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
+          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
         </is>
       </c>
       <c r="L12" s="12" t="inlineStr">
@@ -3040,17 +3040,17 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>제이앤티지</t>
+          <t>씨아이에스케미칼</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>그 외 자동차용 신품 부품 제조업</t>
+          <t>알루미늄 제련, 정련 및 합금 제조업</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -3065,28 +3065,28 @@
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>26,400 ~ 31,900원</t>
+          <t>5,400 ~ 6,800원</t>
         </is>
       </c>
       <c r="I13" s="10" t="n">
-        <v>3182000</v>
+        <v>3000000</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>1015.1</v>
+        <v>204</v>
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
+          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
       <c r="L13" s="12" t="inlineStr">
@@ -3103,109 +3103,109 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
+          <t>제이앤티지</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>그 외 자동차용 신품 부품 제조업</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>26,400 ~ 31,900원</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="n">
+        <v>3182000</v>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>1015.1</v>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
+        </is>
+      </c>
+      <c r="L14" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
           <t>씨앤엠</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>전동기 및 발전기 제조업</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>10,000 ~ 13,000원</t>
         </is>
       </c>
-      <c r="I14" s="10" t="n">
+      <c r="I15" s="10" t="n">
         <v>2059500</v>
       </c>
-      <c r="J14" s="11" t="n">
+      <c r="J15" s="11" t="n">
         <v>267.7</v>
       </c>
-      <c r="K14" s="9" t="inlineStr">
+      <c r="K15" s="9" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L14" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>넥스아이</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>10,500 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J15" s="6" t="n">
-        <v>487.5</v>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
-        </is>
-      </c>
-      <c r="L15" s="7" t="inlineStr">
+      <c r="L15" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3219,12 +3219,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>항공기용 부품 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -3239,28 +3239,28 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,700 ~ 5,700원</t>
+          <t>10,500 ~ 13,000원</t>
         </is>
       </c>
       <c r="I16" s="5" t="n">
-        <v>3300000</v>
+        <v>3750000</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>188.1</v>
+        <v>487.5</v>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
+          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
@@ -3272,172 +3272,172 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>하나에어로다이내믹스</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>항공기용 부품 제조업</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>4,700 ~ 5,700원</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>188.1</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>바로팜</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>전자상거래 소매 중개업</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>16,400 ~ 20,200원</t>
         </is>
       </c>
-      <c r="I17" s="5" t="n">
+      <c r="I18" s="5" t="n">
         <v>1335000</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="J18" s="6" t="n">
         <v>269.7</v>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="K18" s="3" t="inlineStr">
         <is>
           <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L17" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>엠비디</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>물질 검사, 측정 및 분석기구 제조업</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>9,600 ~ 11,700원</t>
         </is>
       </c>
-      <c r="I18" s="10" t="n">
+      <c r="I19" s="10" t="n">
         <v>1500000</v>
       </c>
-      <c r="J18" s="11" t="n">
+      <c r="J19" s="11" t="n">
         <v>175.5</v>
       </c>
-      <c r="K18" s="9" t="inlineStr">
+      <c r="K19" s="9" t="inlineStr">
         <is>
           <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
         </is>
       </c>
-      <c r="L18" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>래블업</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>시스템 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>19,000 ~ 22,000원</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v>1635000</v>
-      </c>
-      <c r="J19" s="6" t="n">
-        <v>359.7</v>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>NH투자증권 02-768-7462, 7467</t>
-        </is>
-      </c>
-      <c r="L19" s="7" t="inlineStr">
+      <c r="L19" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3446,53 +3446,53 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>래블업</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>시스템 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>이에스티</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>그 외 기타 전자부품 제조업</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,600 ~ 12,400원</t>
+          <t>19,000 ~ 22,000원</t>
         </is>
       </c>
       <c r="I20" s="5" t="n">
-        <v>1650000</v>
+        <v>1635000</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>204.6</v>
+        <v>359.7</v>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+          <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr">
@@ -3504,114 +3504,114 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>이에스티</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>그 외 기타 전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>10,600 ~ 12,400원</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>204.6</v>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>에이엘로봇</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>기타 기계 및 장비 제조업</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>정정-변경(수요예측)</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>15,700 ~ 17,600원</t>
         </is>
       </c>
-      <c r="I21" s="5" t="n">
+      <c r="I22" s="5" t="n">
         <v>1800000</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="J22" s="6" t="n">
         <v>316.8</v>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="L21" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>아델</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>18,000 ~ 25,000원</t>
-        </is>
-      </c>
-      <c r="I22" s="10" t="n">
-        <v>1627500</v>
-      </c>
-      <c r="J22" s="11" t="n">
-        <v>406.9</v>
-      </c>
-      <c r="K22" s="9" t="inlineStr">
-        <is>
-          <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
-        </is>
-      </c>
-      <c r="L22" s="12" t="inlineStr">
+      <c r="L22" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3625,12 +3625,12 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>SimwonAmericaCorp.</t>
+          <t>아델</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>자동차 신품 부품 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
@@ -3640,15 +3640,35 @@
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>수요예측 항목 없음(원문 확인)</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr"/>
-      <c r="G23" s="8" t="inlineStr"/>
-      <c r="H23" s="8" t="inlineStr"/>
-      <c r="I23" s="10" t="inlineStr"/>
-      <c r="J23" s="11" t="inlineStr"/>
-      <c r="K23" s="9" t="inlineStr"/>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>18,000 ~ 25,000원</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="n">
+        <v>1627500</v>
+      </c>
+      <c r="J23" s="11" t="n">
+        <v>406.9</v>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -3658,55 +3678,35 @@
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>다비오</t>
+          <t>SimwonAmericaCorp.</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
+          <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>12,300 ~ 16,600원</t>
-        </is>
-      </c>
-      <c r="I24" s="10" t="n">
-        <v>750000</v>
-      </c>
-      <c r="J24" s="11" t="n">
-        <v>124.5</v>
-      </c>
-      <c r="K24" s="9" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
-        </is>
-      </c>
+          <t>수요예측 항목 없음(원문 확인)</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr"/>
+      <c r="G24" s="8" t="inlineStr"/>
+      <c r="H24" s="8" t="inlineStr"/>
+      <c r="I24" s="10" t="inlineStr"/>
+      <c r="J24" s="11" t="inlineStr"/>
+      <c r="K24" s="9" t="inlineStr"/>
       <c r="L24" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -3721,7 +3721,7 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>엔키화이트햇</t>
+          <t>다비오</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -3741,28 +3741,28 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>13,000 ~ 16,500원</t>
+          <t>12,300 ~ 16,600원</t>
         </is>
       </c>
       <c r="I25" s="10" t="n">
-        <v>1258000</v>
+        <v>750000</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>207.6</v>
+        <v>124.5</v>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
+          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr">
@@ -3779,167 +3779,167 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
+          <t>엔키화이트햇</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>13,000 ~ 16,500원</t>
+        </is>
+      </c>
+      <c r="I26" s="10" t="n">
+        <v>1258000</v>
+      </c>
+      <c r="J26" s="11" t="n">
+        <v>207.6</v>
+      </c>
+      <c r="K26" s="9" t="inlineStr">
+        <is>
+          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
+        </is>
+      </c>
+      <c r="L26" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
           <t>영광와이케이엠씨</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>그 외 기타 금속가공업</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="G26" s="8" t="inlineStr">
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>9,400 ~ 11,000원</t>
         </is>
       </c>
-      <c r="I26" s="10" t="n">
+      <c r="I27" s="10" t="n">
         <v>1694840</v>
       </c>
-      <c r="J26" s="11" t="n">
+      <c r="J27" s="11" t="n">
         <v>186.4</v>
       </c>
-      <c r="K26" s="9" t="inlineStr">
+      <c r="K27" s="9" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
         </is>
       </c>
-      <c r="L26" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="L27" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>영광</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>수상 금속 골조 구조재 제조업</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>14,000 ~ 17,000원</t>
         </is>
       </c>
-      <c r="I27" s="5" t="n">
+      <c r="I28" s="5" t="n">
         <v>1695000</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="J28" s="6" t="n">
         <v>288.1</v>
       </c>
-      <c r="K27" s="3" t="inlineStr">
+      <c r="K28" s="3" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L27" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>인텔리빅스</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>7,600 ~ 9,000원</t>
-        </is>
-      </c>
-      <c r="I28" s="10" t="n">
-        <v>1875000</v>
-      </c>
-      <c r="J28" s="11" t="n">
-        <v>168.8</v>
-      </c>
-      <c r="K28" s="9" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
-        </is>
-      </c>
-      <c r="L28" s="12" t="inlineStr">
+      <c r="L28" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3948,172 +3948,172 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>인텔리빅스</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>7,600 ~ 9,000원</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="n">
+        <v>1875000</v>
+      </c>
+      <c r="J29" s="11" t="n">
+        <v>168.8</v>
+      </c>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
+      <c r="L29" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>제논</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="F30" s="8" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>9,700 ~ 12,200원</t>
         </is>
       </c>
-      <c r="I29" s="10" t="n">
+      <c r="I30" s="10" t="n">
         <v>1550000</v>
       </c>
-      <c r="J29" s="11" t="n">
+      <c r="J30" s="11" t="n">
         <v>189.1</v>
       </c>
-      <c r="K29" s="9" t="inlineStr">
+      <c r="K30" s="9" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-8023, 7653, 7850</t>
         </is>
       </c>
-      <c r="L29" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="L30" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>래블업</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>시스템 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>19,000 ~ 22,000원</t>
         </is>
       </c>
-      <c r="I30" s="5" t="n">
+      <c r="I31" s="5" t="n">
         <v>1635000</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="J31" s="6" t="n">
         <v>359.7</v>
       </c>
-      <c r="K30" s="3" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="L30" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>케이엠에프</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>기타 식품 제조업</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-20</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>15,000 ~ 17,800원</t>
-        </is>
-      </c>
-      <c r="I31" s="10" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="J31" s="11" t="n">
-        <v>267</v>
-      </c>
-      <c r="K31" s="9" t="inlineStr">
-        <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
-        </is>
-      </c>
-      <c r="L31" s="12" t="inlineStr">
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4122,22 +4122,22 @@
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>바로팜</t>
+          <t>케이엠에프</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>전자상거래 소매 중개업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
@@ -4147,28 +4147,28 @@
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>16,400 ~ 20,200원</t>
+          <t>15,000 ~ 17,800원</t>
         </is>
       </c>
       <c r="I32" s="10" t="n">
-        <v>1335000</v>
+        <v>1500000</v>
       </c>
       <c r="J32" s="11" t="n">
-        <v>269.7</v>
+        <v>267</v>
       </c>
       <c r="K32" s="9" t="inlineStr">
         <is>
-          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
         </is>
       </c>
       <c r="L32" s="12" t="inlineStr">
@@ -4185,17 +4185,17 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>동원파츠</t>
+          <t>바로팜</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>반도체 제조용 기계 제조업</t>
+          <t>전자상거래 소매 중개업</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -4215,18 +4215,18 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>23,000 ~ 26,500원</t>
+          <t>16,400 ~ 20,200원</t>
         </is>
       </c>
       <c r="I33" s="10" t="n">
-        <v>1522500</v>
+        <v>1335000</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>403.5</v>
+        <v>269.7</v>
       </c>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-6975, 8217, 7651</t>
+          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
       <c r="L33" s="12" t="inlineStr">
@@ -4243,17 +4243,17 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>디티에스</t>
+          <t>동원파츠</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>반도체 제조용 기계 제조업</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
@@ -4263,28 +4263,28 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>17,000 ~ 18,500원</t>
+          <t>23,000 ~ 26,500원</t>
         </is>
       </c>
       <c r="I34" s="10" t="n">
-        <v>1671687</v>
+        <v>1522500</v>
       </c>
       <c r="J34" s="11" t="n">
-        <v>309.3</v>
+        <v>403.5</v>
       </c>
       <c r="K34" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
+          <t>삼성증권 02-2020-6975, 8217, 7651</t>
         </is>
       </c>
       <c r="L34" s="12" t="inlineStr">
@@ -4296,17 +4296,17 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>엠에스바이오</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>그 외 기타 의료용 기기 제조업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
@@ -4321,28 +4321,28 @@
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>6,800 ~ 7,800원</t>
+          <t>17,000 ~ 18,500원</t>
         </is>
       </c>
       <c r="I35" s="10" t="n">
-        <v>2840000</v>
+        <v>1671687</v>
       </c>
       <c r="J35" s="11" t="n">
-        <v>221.5</v>
+        <v>309.3</v>
       </c>
       <c r="K35" s="9" t="inlineStr">
         <is>
-          <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
+          <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
         </is>
       </c>
       <c r="L35" s="12" t="inlineStr">
@@ -4359,17 +4359,17 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>옵토닉스</t>
+          <t>엠에스바이오</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>광학렌즈 및 광학요소 제조업</t>
+          <t>그 외 기타 의료용 기기 제조업</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
@@ -4379,28 +4379,28 @@
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>10,000 ~ 12,000원</t>
+          <t>6,800 ~ 7,800원</t>
         </is>
       </c>
       <c r="I36" s="10" t="n">
-        <v>1572490</v>
+        <v>2840000</v>
       </c>
       <c r="J36" s="11" t="n">
-        <v>188.7</v>
+        <v>221.5</v>
       </c>
       <c r="K36" s="9" t="inlineStr">
         <is>
-          <t>한국투자증권 02-3276-5958, 6269</t>
+          <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
       <c r="L36" s="12" t="inlineStr">
@@ -4412,17 +4412,17 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>넥스아이</t>
+          <t>옵토닉스</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>의학 및 약학 연구개발업</t>
+          <t>광학렌즈 및 광학요소 제조업</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
@@ -4437,28 +4437,28 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>10,500 ~ 13,000원</t>
+          <t>10,000 ~ 12,000원</t>
         </is>
       </c>
       <c r="I37" s="10" t="n">
-        <v>3750000</v>
+        <v>1572490</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>487.5</v>
+        <v>188.7</v>
       </c>
       <c r="K37" s="9" t="inlineStr">
         <is>
-          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
+          <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
       <c r="L37" s="12" t="inlineStr">
@@ -4475,17 +4475,17 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
@@ -4495,28 +4495,28 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>15,000 ~ 18,000원</t>
+          <t>10,500 ~ 13,000원</t>
         </is>
       </c>
       <c r="I38" s="10" t="n">
-        <v>1050000</v>
+        <v>3750000</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>189</v>
+        <v>487.5</v>
       </c>
       <c r="K38" s="9" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-7414, 7375, 7651</t>
+          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
         </is>
       </c>
       <c r="L38" s="12" t="inlineStr">
@@ -4528,17 +4528,17 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>티앤이코리아</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>산업용 송풍기 및 배기장치 제조업</t>
+          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
@@ -4553,28 +4553,28 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>12,600 ~ 15,300원</t>
+          <t>15,000 ~ 18,000원</t>
         </is>
       </c>
       <c r="I39" s="10" t="n">
-        <v>1800000</v>
+        <v>1050000</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>275.4</v>
+        <v>189</v>
       </c>
       <c r="K39" s="9" t="inlineStr">
         <is>
-          <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
+          <t>삼성증권 02-2020-7414, 7375, 7651</t>
         </is>
       </c>
       <c r="L39" s="12" t="inlineStr">
@@ -4586,22 +4586,22 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>티앤이코리아</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>항공기용 부품 제조업</t>
+          <t>산업용 송풍기 및 배기장치 제조업</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
@@ -4611,28 +4611,28 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>4,700 ~ 5,700원</t>
+          <t>12,600 ~ 15,300원</t>
         </is>
       </c>
       <c r="I40" s="10" t="n">
-        <v>3300000</v>
+        <v>1800000</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>188.1</v>
+        <v>275.4</v>
       </c>
       <c r="K40" s="9" t="inlineStr">
         <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
+          <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
         </is>
       </c>
       <c r="L40" s="12" t="inlineStr">
@@ -4649,17 +4649,17 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>래블업</t>
+          <t>하나에어로다이내믹스</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>시스템 소프트웨어 개발 및 공급업</t>
+          <t>항공기용 부품 제조업</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -4669,28 +4669,28 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>19,000 ~ 22,000원</t>
+          <t>4,700 ~ 5,700원</t>
         </is>
       </c>
       <c r="I41" s="10" t="n">
-        <v>1635000</v>
+        <v>3300000</v>
       </c>
       <c r="J41" s="11" t="n">
-        <v>359.7</v>
+        <v>188.1</v>
       </c>
       <c r="K41" s="9" t="inlineStr">
         <is>
-          <t>NH투자증권 02-768-7462, 7467</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
         </is>
       </c>
       <c r="L41" s="12" t="inlineStr">
@@ -4707,17 +4707,17 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>영광</t>
+          <t>래블업</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>수상 금속 골조 구조재 제조업</t>
+          <t>시스템 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
@@ -4737,18 +4737,18 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>14,000 ~ 17,000원</t>
+          <t>19,000 ~ 22,000원</t>
         </is>
       </c>
       <c r="I42" s="10" t="n">
-        <v>1695000</v>
+        <v>1635000</v>
       </c>
       <c r="J42" s="11" t="n">
-        <v>288.1</v>
+        <v>359.7</v>
       </c>
       <c r="K42" s="9" t="inlineStr">
         <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+          <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
       <c r="L42" s="12" t="inlineStr">
@@ -4765,12 +4765,12 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>이에스티</t>
+          <t>영광</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>그 외 기타 전자부품 제조업</t>
+          <t>수상 금속 골조 구조재 제조업</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
@@ -4785,28 +4785,28 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>10,600 ~ 12,400원</t>
+          <t>14,000 ~ 17,000원</t>
         </is>
       </c>
       <c r="I43" s="10" t="n">
-        <v>1650000</v>
+        <v>1695000</v>
       </c>
       <c r="J43" s="11" t="n">
-        <v>204.6</v>
+        <v>288.1</v>
       </c>
       <c r="K43" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
       <c r="L43" s="12" t="inlineStr">
@@ -4823,58 +4823,116 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
+          <t>이에스티</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>그 외 기타 전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>10,600 ~ 12,400원</t>
+        </is>
+      </c>
+      <c r="I44" s="10" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J44" s="11" t="n">
+        <v>204.6</v>
+      </c>
+      <c r="K44" s="9" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+        </is>
+      </c>
+      <c r="L44" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
           <t>에이엘로봇</t>
         </is>
       </c>
-      <c r="C44" s="9" t="inlineStr">
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>기타 기계 및 장비 제조업</t>
         </is>
       </c>
-      <c r="D44" s="9" t="inlineStr">
+      <c r="D45" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E44" s="8" t="inlineStr">
+      <c r="E45" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F44" s="8" t="inlineStr">
+      <c r="F45" s="8" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G44" s="8" t="inlineStr">
+      <c r="G45" s="8" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="H44" s="8" t="inlineStr">
+      <c r="H45" s="8" t="inlineStr">
         <is>
           <t>15,700 ~ 17,600원</t>
         </is>
       </c>
-      <c r="I44" s="10" t="n">
+      <c r="I45" s="10" t="n">
         <v>1800000</v>
       </c>
-      <c r="J44" s="11" t="n">
+      <c r="J45" s="11" t="n">
         <v>316.8</v>
       </c>
-      <c r="K44" s="9" t="inlineStr">
+      <c r="K45" s="9" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="L44" s="12" t="inlineStr">
+      <c r="L45" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L44"/>
+  <autoFilter ref="A1:L45"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -4919,6 +4977,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/수요예측_일정.xlsx
+++ b/수요예측_일정.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체 이력" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'수요예측 일정'!$A$1:$L$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체 이력'!$A$1:$L$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'수요예측 일정'!$A$1:$N$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체 이력'!$A$1:$N$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -491,7 +491,9 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="48" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -552,6 +554,16 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>청약일</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>납입일</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>DART</t>
         </is>
       </c>
@@ -608,7 +620,17 @@
           <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
         </is>
       </c>
-      <c r="L2" s="7" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -666,7 +688,17 @@
           <t>삼성증권 02-2020-8023, 7653, 7850</t>
         </is>
       </c>
-      <c r="L3" s="7" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -724,7 +756,17 @@
           <t>삼성증권 02-2020-6975, 8217, 7651</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -782,7 +824,17 @@
           <t>한국투자증권㈜ 02-3276-5700, 6648</t>
         </is>
       </c>
-      <c r="L5" s="12" t="inlineStr">
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="N5" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -840,7 +892,17 @@
           <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
         </is>
       </c>
-      <c r="L6" s="12" t="inlineStr">
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="N6" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -898,7 +960,17 @@
           <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
-      <c r="L7" s="7" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -956,7 +1028,17 @@
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L8" s="12" t="inlineStr">
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-07</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="N8" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1014,7 +1096,17 @@
           <t>NH투자증권 02-2229-6315, 6829</t>
         </is>
       </c>
-      <c r="L9" s="12" t="inlineStr">
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="N9" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1072,7 +1164,17 @@
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="L10" s="7" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1130,7 +1232,17 @@
           <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
         </is>
       </c>
-      <c r="L11" s="12" t="inlineStr">
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="N11" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1188,7 +1300,17 @@
           <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
-      <c r="L12" s="12" t="inlineStr">
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+      <c r="N12" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1246,7 +1368,17 @@
           <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
         </is>
       </c>
-      <c r="L13" s="12" t="inlineStr">
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N13" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1304,7 +1436,17 @@
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L14" s="12" t="inlineStr">
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N14" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1362,7 +1504,17 @@
           <t>한국투자증권㈜ 02-3276-6384, 5198</t>
         </is>
       </c>
-      <c r="L15" s="7" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1420,7 +1572,17 @@
           <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
         </is>
       </c>
-      <c r="L16" s="7" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1478,7 +1640,17 @@
           <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L17" s="7" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1536,7 +1708,17 @@
           <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
         </is>
       </c>
-      <c r="L18" s="12" t="inlineStr">
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N18" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1594,7 +1776,17 @@
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="L19" s="7" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1652,7 +1844,17 @@
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="L20" s="7" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1710,7 +1912,17 @@
           <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L21" s="12" t="inlineStr">
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="M21" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="N21" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1748,7 +1960,13 @@
       <c r="I22" s="10" t="inlineStr"/>
       <c r="J22" s="11" t="inlineStr"/>
       <c r="K22" s="9" t="inlineStr"/>
-      <c r="L22" s="12" t="inlineStr">
+      <c r="L22" s="8" t="inlineStr"/>
+      <c r="M22" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="N22" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1806,7 +2024,17 @@
           <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
         </is>
       </c>
-      <c r="L23" s="12" t="inlineStr">
+      <c r="L23" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="M23" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="N23" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1864,7 +2092,17 @@
           <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
         </is>
       </c>
-      <c r="L24" s="12" t="inlineStr">
+      <c r="L24" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N24" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1922,7 +2160,17 @@
           <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
         </is>
       </c>
-      <c r="L25" s="12" t="inlineStr">
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="M25" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="N25" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1980,7 +2228,17 @@
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L26" s="7" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2038,7 +2296,17 @@
           <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L27" s="12" t="inlineStr">
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="M27" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="N27" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2096,7 +2364,17 @@
           <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
         </is>
       </c>
-      <c r="L28" s="12" t="inlineStr">
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="N28" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2154,7 +2432,17 @@
           <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
-      <c r="L29" s="12" t="inlineStr">
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M29" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="N29" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2212,7 +2500,17 @@
           <t>삼성증권 02-2020-7414, 7375, 7651</t>
         </is>
       </c>
-      <c r="L30" s="12" t="inlineStr">
+      <c r="L30" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="M30" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="N30" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2270,45 +2568,55 @@
           <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
         </is>
       </c>
-      <c r="L31" s="12" t="inlineStr">
+      <c r="L31" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="M31" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="N31" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L31"/>
+  <autoFilter ref="A1:N31"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2320,7 +2628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2334,7 +2642,9 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="48" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2395,6 +2705,16 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>청약일</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>납입일</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>DART</t>
         </is>
       </c>
@@ -2451,7 +2771,17 @@
           <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
         </is>
       </c>
-      <c r="L2" s="7" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2509,7 +2839,17 @@
           <t>삼성증권 02-2020-8023, 7653, 7850</t>
         </is>
       </c>
-      <c r="L3" s="7" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2567,7 +2907,9 @@
           <t>삼성증권 02-2020-8023, 7653, 7850</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2625,7 +2967,17 @@
           <t>삼성증권 02-2020-6975, 8217, 7651</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2683,7 +3035,17 @@
           <t>한국투자증권㈜ 02-3276-5700, 6648</t>
         </is>
       </c>
-      <c r="L6" s="12" t="inlineStr">
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="N6" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2741,7 +3103,17 @@
           <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
         </is>
       </c>
-      <c r="L7" s="12" t="inlineStr">
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="N7" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2799,7 +3171,17 @@
           <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
-      <c r="L8" s="7" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2857,7 +3239,17 @@
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L9" s="12" t="inlineStr">
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-07</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="N9" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2915,7 +3307,17 @@
           <t>NH투자증권 02-2229-6315, 6829</t>
         </is>
       </c>
-      <c r="L10" s="12" t="inlineStr">
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="N10" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2973,7 +3375,17 @@
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="L11" s="7" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3031,7 +3443,17 @@
           <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
         </is>
       </c>
-      <c r="L12" s="12" t="inlineStr">
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="N12" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3089,7 +3511,17 @@
           <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
-      <c r="L13" s="12" t="inlineStr">
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+      <c r="N13" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3147,7 +3579,17 @@
           <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
         </is>
       </c>
-      <c r="L14" s="12" t="inlineStr">
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N14" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3205,7 +3647,17 @@
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L15" s="12" t="inlineStr">
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M15" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N15" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3263,7 +3715,17 @@
           <t>한국투자증권㈜ 02-3276-6384, 5198</t>
         </is>
       </c>
-      <c r="L16" s="7" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3321,7 +3783,17 @@
           <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
         </is>
       </c>
-      <c r="L17" s="7" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3379,7 +3851,17 @@
           <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L18" s="7" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3437,7 +3919,17 @@
           <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
         </is>
       </c>
-      <c r="L19" s="12" t="inlineStr">
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M19" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N19" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3495,7 +3987,17 @@
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="L20" s="7" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3553,7 +4055,9 @@
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="L21" s="7" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3611,7 +4115,17 @@
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="L22" s="7" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3669,7 +4183,17 @@
           <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L23" s="12" t="inlineStr">
+      <c r="L23" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="M23" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="N23" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3707,7 +4231,13 @@
       <c r="I24" s="10" t="inlineStr"/>
       <c r="J24" s="11" t="inlineStr"/>
       <c r="K24" s="9" t="inlineStr"/>
-      <c r="L24" s="12" t="inlineStr">
+      <c r="L24" s="8" t="inlineStr"/>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="N24" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3765,7 +4295,17 @@
           <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
         </is>
       </c>
-      <c r="L25" s="12" t="inlineStr">
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="M25" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="N25" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3823,7 +4363,17 @@
           <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
         </is>
       </c>
-      <c r="L26" s="12" t="inlineStr">
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M26" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N26" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3881,7 +4431,17 @@
           <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
         </is>
       </c>
-      <c r="L27" s="12" t="inlineStr">
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="M27" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="N27" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3939,7 +4499,17 @@
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L28" s="7" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3997,7 +4567,17 @@
           <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L29" s="12" t="inlineStr">
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="M29" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="N29" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4055,7 +4635,9 @@
           <t>삼성증권 02-2020-8023, 7653, 7850</t>
         </is>
       </c>
-      <c r="L30" s="12" t="inlineStr">
+      <c r="L30" s="8" t="inlineStr"/>
+      <c r="M30" s="8" t="inlineStr"/>
+      <c r="N30" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4113,7 +4695,9 @@
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4171,7 +4755,9 @@
           <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
         </is>
       </c>
-      <c r="L32" s="12" t="inlineStr">
+      <c r="L32" s="8" t="inlineStr"/>
+      <c r="M32" s="8" t="inlineStr"/>
+      <c r="N32" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4229,7 +4815,9 @@
           <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L33" s="12" t="inlineStr">
+      <c r="L33" s="8" t="inlineStr"/>
+      <c r="M33" s="8" t="inlineStr"/>
+      <c r="N33" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4287,7 +4875,9 @@
           <t>삼성증권 02-2020-6975, 8217, 7651</t>
         </is>
       </c>
-      <c r="L34" s="12" t="inlineStr">
+      <c r="L34" s="8" t="inlineStr"/>
+      <c r="M34" s="8" t="inlineStr"/>
+      <c r="N34" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4345,7 +4935,17 @@
           <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
         </is>
       </c>
-      <c r="L35" s="12" t="inlineStr">
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="M35" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="N35" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4403,7 +5003,17 @@
           <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
-      <c r="L36" s="12" t="inlineStr">
+      <c r="L36" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M36" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="N36" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4461,7 +5071,9 @@
           <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
-      <c r="L37" s="12" t="inlineStr">
+      <c r="L37" s="8" t="inlineStr"/>
+      <c r="M37" s="8" t="inlineStr"/>
+      <c r="N37" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4519,7 +5131,9 @@
           <t>한국투자증권㈜ 02-3276-6384, 5198</t>
         </is>
       </c>
-      <c r="L38" s="12" t="inlineStr">
+      <c r="L38" s="8" t="inlineStr"/>
+      <c r="M38" s="8" t="inlineStr"/>
+      <c r="N38" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4577,7 +5191,17 @@
           <t>삼성증권 02-2020-7414, 7375, 7651</t>
         </is>
       </c>
-      <c r="L39" s="12" t="inlineStr">
+      <c r="L39" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="M39" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="N39" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4635,7 +5259,17 @@
           <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
         </is>
       </c>
-      <c r="L40" s="12" t="inlineStr">
+      <c r="L40" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="M40" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="N40" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4693,7 +5327,9 @@
           <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
         </is>
       </c>
-      <c r="L41" s="12" t="inlineStr">
+      <c r="L41" s="8" t="inlineStr"/>
+      <c r="M41" s="8" t="inlineStr"/>
+      <c r="N41" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4751,7 +5387,9 @@
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="L42" s="12" t="inlineStr">
+      <c r="L42" s="8" t="inlineStr"/>
+      <c r="M42" s="8" t="inlineStr"/>
+      <c r="N42" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4809,7 +5447,9 @@
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L43" s="12" t="inlineStr">
+      <c r="L43" s="8" t="inlineStr"/>
+      <c r="M43" s="8" t="inlineStr"/>
+      <c r="N43" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4867,7 +5507,9 @@
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="L44" s="12" t="inlineStr">
+      <c r="L44" s="8" t="inlineStr"/>
+      <c r="M44" s="8" t="inlineStr"/>
+      <c r="N44" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4925,59 +5567,61 @@
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="L45" s="12" t="inlineStr">
+      <c r="L45" s="8" t="inlineStr"/>
+      <c r="M45" s="8" t="inlineStr"/>
+      <c r="N45" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L45"/>
+  <autoFilter ref="A1:N45"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N45" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/수요예측_일정.xlsx
+++ b/수요예측_일정.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체 이력" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'수요예측 일정'!$A$1:$N$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체 이력'!$A$1:$N$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'수요예측 일정'!$A$1:$L$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체 이력'!$A$1:$L$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -491,9 +491,7 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="48" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -554,16 +552,6 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>청약일</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>납입일</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
           <t>DART</t>
         </is>
       </c>
@@ -620,85 +608,65 @@
           <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-24</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-27</t>
-        </is>
-      </c>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>제논</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경(수요예측)</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-20</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>9,700 ~ 12,200원</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>1550000</v>
-      </c>
-      <c r="J3" s="6" t="n">
-        <v>189.1</v>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>삼성증권 02-2020-8023, 7653, 7850</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-24</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-27</t>
-        </is>
-      </c>
-      <c r="N3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>우리투자제1호기업인수목적</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>스팩</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>2,000원 (단일가)</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="n">
+        <v>4875000</v>
+      </c>
+      <c r="J3" s="11" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>우리투자증권 02-6390-3889</t>
+        </is>
+      </c>
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -707,134 +675,114 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>제논</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경(수요예측)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9,700 ~ 12,200원</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>1550000</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>189.1</v>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-8023, 7653, 7850</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>동원파츠</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>반도체 제조용 기계 제조업</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>23,000 ~ 26,500원</t>
         </is>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="I5" s="5" t="n">
         <v>1522500</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="J5" s="6" t="n">
         <v>403.5</v>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-6975, 8217, 7651</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="N4" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>인터엑스</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-04</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>10,000 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I5" s="10" t="n">
-        <v>2250000</v>
-      </c>
-      <c r="J5" s="11" t="n">
-        <v>292.5</v>
-      </c>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5700, 6648</t>
-        </is>
-      </c>
-      <c r="L5" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-09</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-14</t>
-        </is>
-      </c>
-      <c r="N5" s="12" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -843,202 +791,172 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>인터엑스</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>10,000 ~ 13,000원</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>2250000</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5700, 6648</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>유캐스트</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>기타 무선 통신장비 제조업</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>19,000 ~ 23,000원</t>
         </is>
       </c>
-      <c r="I6" s="10" t="n">
+      <c r="I7" s="10" t="n">
         <v>600000</v>
       </c>
-      <c r="J6" s="11" t="n">
+      <c r="J7" s="11" t="n">
         <v>138</v>
       </c>
-      <c r="K6" s="9" t="inlineStr">
+      <c r="K7" s="9" t="inlineStr">
         <is>
           <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
         </is>
       </c>
-      <c r="L6" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-      <c r="N6" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="L7" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>옵토닉스</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>광학렌즈 및 광학요소 제조업</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>10,000 ~ 12,000원</t>
         </is>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="I8" s="5" t="n">
         <v>1572490</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J8" s="6" t="n">
         <v>188.7</v>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>이노보테라퓨틱스</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-02</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>20,000 ~ 24,000원</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="J8" s="11" t="n">
-        <v>396</v>
-      </c>
-      <c r="K8" s="9" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-07</t>
-        </is>
-      </c>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-10</t>
-        </is>
-      </c>
-      <c r="N8" s="12" t="inlineStr">
+      <c r="L8" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1047,202 +965,172 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>이노보테라퓨틱스</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>의학 및 약학 연구개발업</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>20,000 ~ 24,000원</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>396</v>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+        </is>
+      </c>
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>기타 엔지니어링 서비스업</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>2026-11-19</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>2026-11-25</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>11,200 ~ 13,600원</t>
         </is>
       </c>
-      <c r="I9" s="10" t="n">
+      <c r="I10" s="10" t="n">
         <v>1575000</v>
       </c>
-      <c r="J9" s="11" t="n">
+      <c r="J10" s="11" t="n">
         <v>214.2</v>
       </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="K10" s="9" t="inlineStr">
         <is>
           <t>NH투자증권 02-2229-6315, 6829</t>
         </is>
       </c>
-      <c r="L9" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-27</t>
-        </is>
-      </c>
-      <c r="M9" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-02</t>
-        </is>
-      </c>
-      <c r="N9" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="L10" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>이에스티</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>그 외 기타 전자부품 제조업</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>10,600 ~ 12,400원</t>
         </is>
       </c>
-      <c r="I10" s="5" t="n">
+      <c r="I11" s="5" t="n">
         <v>1650000</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J11" s="6" t="n">
         <v>204.6</v>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>에스에프씨</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>그 외 기타 분류 안된 화학제품 제조업</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>31,600 ~ 36,100원</t>
-        </is>
-      </c>
-      <c r="I11" s="10" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J11" s="11" t="n">
-        <v>1353.8</v>
-      </c>
-      <c r="K11" s="9" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
-        </is>
-      </c>
-      <c r="L11" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="M11" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-      <c r="N11" s="12" t="inlineStr">
+      <c r="L11" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1256,12 +1144,12 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>씨아이에스케미칼</t>
+          <t>에스에프씨</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>알루미늄 제련, 정련 및 합금 제조업</t>
+          <t>그 외 기타 분류 안된 화학제품 제조업</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
@@ -1276,41 +1164,31 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>5,400 ~ 6,800원</t>
+          <t>31,600 ~ 36,100원</t>
         </is>
       </c>
       <c r="I12" s="10" t="n">
-        <v>3000000</v>
+        <v>3750000</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>204</v>
+        <v>1353.8</v>
       </c>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
-        </is>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-10</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-15</t>
-        </is>
-      </c>
-      <c r="N12" s="12" t="inlineStr">
+          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
+        </is>
+      </c>
+      <c r="L12" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1319,17 +1197,17 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>제이앤티지</t>
+          <t>씨아이에스케미칼</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>그 외 자동차용 신품 부품 제조업</t>
+          <t>알루미늄 제련, 정련 및 합금 제조업</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -1344,41 +1222,31 @@
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>26,400 ~ 31,900원</t>
+          <t>5,400 ~ 6,800원</t>
         </is>
       </c>
       <c r="I13" s="10" t="n">
-        <v>3182000</v>
+        <v>3000000</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>1015.1</v>
+        <v>204</v>
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
-        </is>
-      </c>
-      <c r="L13" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="M13" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-17</t>
-        </is>
-      </c>
-      <c r="N13" s="12" t="inlineStr">
+          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
+        </is>
+      </c>
+      <c r="L13" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1392,129 +1260,109 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
+          <t>제이앤티지</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>그 외 자동차용 신품 부품 제조업</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>26,400 ~ 31,900원</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="n">
+        <v>3182000</v>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>1015.1</v>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
+        </is>
+      </c>
+      <c r="L14" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
           <t>씨앤엠</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>전동기 및 발전기 제조업</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>10,000 ~ 13,000원</t>
         </is>
       </c>
-      <c r="I14" s="10" t="n">
+      <c r="I15" s="10" t="n">
         <v>2059500</v>
       </c>
-      <c r="J14" s="11" t="n">
+      <c r="J15" s="11" t="n">
         <v>267.7</v>
       </c>
-      <c r="K14" s="9" t="inlineStr">
+      <c r="K15" s="9" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L14" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="M14" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-17</t>
-        </is>
-      </c>
-      <c r="N14" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>넥스아이</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>10,500 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J15" s="6" t="n">
-        <v>487.5</v>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="inlineStr">
+      <c r="L15" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1528,12 +1376,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>항공기용 부품 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1548,41 +1396,31 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,700 ~ 5,700원</t>
+          <t>10,500 ~ 13,000원</t>
         </is>
       </c>
       <c r="I16" s="5" t="n">
-        <v>3300000</v>
+        <v>3750000</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>188.1</v>
+        <v>487.5</v>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="inlineStr">
+          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1591,202 +1429,172 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>하나에어로다이내믹스</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>항공기용 부품 제조업</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>4,700 ~ 5,700원</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>188.1</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>바로팜</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>전자상거래 소매 중개업</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>16,400 ~ 20,200원</t>
         </is>
       </c>
-      <c r="I17" s="5" t="n">
+      <c r="I18" s="5" t="n">
         <v>1335000</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="J18" s="6" t="n">
         <v>269.7</v>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="K18" s="3" t="inlineStr">
         <is>
           <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>엠비디</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>물질 검사, 측정 및 분석기구 제조업</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="N17" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>엠비디</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>물질 검사, 측정 및 분석기구 제조업</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>9,600 ~ 11,700원</t>
         </is>
       </c>
-      <c r="I18" s="10" t="n">
+      <c r="I19" s="10" t="n">
         <v>1500000</v>
       </c>
-      <c r="J18" s="11" t="n">
+      <c r="J19" s="11" t="n">
         <v>175.5</v>
       </c>
-      <c r="K18" s="9" t="inlineStr">
+      <c r="K19" s="9" t="inlineStr">
         <is>
           <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
         </is>
       </c>
-      <c r="L18" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="M18" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-17</t>
-        </is>
-      </c>
-      <c r="N18" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>래블업</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>시스템 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>19,000 ~ 22,000원</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v>1635000</v>
-      </c>
-      <c r="J19" s="6" t="n">
-        <v>359.7</v>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>NH투자증권 02-768-7462, 7467</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="N19" s="7" t="inlineStr">
+      <c r="L19" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1795,134 +1603,114 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>래블업</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>시스템 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>19,000 ~ 22,000원</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>1635000</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>359.7</v>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>NH투자증권 02-768-7462, 7467</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>에이엘로봇</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>기타 기계 및 장비 제조업</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>정정-변경(수요예측)</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>15,700 ~ 17,600원</t>
         </is>
       </c>
-      <c r="I20" s="5" t="n">
+      <c r="I21" s="5" t="n">
         <v>1800000</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="J21" s="6" t="n">
         <v>316.8</v>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="N20" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>아델</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>18,000 ~ 25,000원</t>
-        </is>
-      </c>
-      <c r="I21" s="10" t="n">
-        <v>1627500</v>
-      </c>
-      <c r="J21" s="11" t="n">
-        <v>406.9</v>
-      </c>
-      <c r="K21" s="9" t="inlineStr">
-        <is>
-          <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
-        </is>
-      </c>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-      <c r="M21" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="N21" s="12" t="inlineStr">
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1936,12 +1724,12 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>SimwonAmericaCorp.</t>
+          <t>아델</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>자동차 신품 부품 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
@@ -1951,22 +1739,36 @@
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>수요예측 항목 없음(원문 확인)</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr"/>
-      <c r="G22" s="8" t="inlineStr"/>
-      <c r="H22" s="8" t="inlineStr"/>
-      <c r="I22" s="10" t="inlineStr"/>
-      <c r="J22" s="11" t="inlineStr"/>
-      <c r="K22" s="9" t="inlineStr"/>
-      <c r="L22" s="8" t="inlineStr"/>
-      <c r="M22" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="N22" s="12" t="inlineStr">
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>18,000 ~ 25,000원</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="n">
+        <v>1627500</v>
+      </c>
+      <c r="J22" s="11" t="n">
+        <v>406.9</v>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
+      <c r="L22" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1975,66 +1777,36 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>다비오</t>
+          <t>SimwonAmericaCorp.</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
+          <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>12,300 ~ 16,600원</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="n">
-        <v>750000</v>
-      </c>
-      <c r="J23" s="11" t="n">
-        <v>124.5</v>
-      </c>
-      <c r="K23" s="9" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
-        </is>
-      </c>
-      <c r="L23" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="M23" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="N23" s="12" t="inlineStr">
+          <t>수요예측 항목 없음(원문 확인)</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr"/>
+      <c r="G23" s="8" t="inlineStr"/>
+      <c r="H23" s="8" t="inlineStr"/>
+      <c r="I23" s="10" t="inlineStr"/>
+      <c r="J23" s="11" t="inlineStr"/>
+      <c r="K23" s="9" t="inlineStr"/>
+      <c r="L23" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2048,7 +1820,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>엔키화이트햇</t>
+          <t>다비오</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -2058,7 +1830,7 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
@@ -2068,41 +1840,31 @@
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>13,000 ~ 16,500원</t>
+          <t>12,300 ~ 16,600원</t>
         </is>
       </c>
       <c r="I24" s="10" t="n">
-        <v>1258000</v>
+        <v>750000</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>207.6</v>
+        <v>124.5</v>
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
-          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
-        </is>
-      </c>
-      <c r="L24" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="M24" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-17</t>
-        </is>
-      </c>
-      <c r="N24" s="12" t="inlineStr">
+          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
+        </is>
+      </c>
+      <c r="L24" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2116,197 +1878,167 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
+          <t>엔키화이트햇</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>13,000 ~ 16,500원</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="n">
+        <v>1258000</v>
+      </c>
+      <c r="J25" s="11" t="n">
+        <v>207.6</v>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
+        </is>
+      </c>
+      <c r="L25" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
           <t>영광와이케이엠씨</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>그 외 기타 금속가공업</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>9,400 ~ 11,000원</t>
         </is>
       </c>
-      <c r="I25" s="10" t="n">
+      <c r="I26" s="10" t="n">
         <v>1694840</v>
       </c>
-      <c r="J25" s="11" t="n">
+      <c r="J26" s="11" t="n">
         <v>186.4</v>
       </c>
-      <c r="K25" s="9" t="inlineStr">
+      <c r="K26" s="9" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
         </is>
       </c>
-      <c r="L25" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="M25" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="N25" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="L26" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>영광</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>수상 금속 골조 구조재 제조업</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>14,000 ~ 17,000원</t>
         </is>
       </c>
-      <c r="I26" s="5" t="n">
+      <c r="I27" s="5" t="n">
         <v>1695000</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="J27" s="6" t="n">
         <v>288.1</v>
       </c>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="N26" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>인텔리빅스</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>7,600 ~ 9,000원</t>
-        </is>
-      </c>
-      <c r="I27" s="10" t="n">
-        <v>1875000</v>
-      </c>
-      <c r="J27" s="11" t="n">
-        <v>168.8</v>
-      </c>
-      <c r="K27" s="9" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
-        </is>
-      </c>
-      <c r="L27" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="M27" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="N27" s="12" t="inlineStr">
+      <c r="L27" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2315,17 +2047,17 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>디티에스</t>
+          <t>인텔리빅스</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
@@ -2340,177 +2072,147 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>7,600 ~ 9,000원</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="n">
+        <v>1875000</v>
+      </c>
+      <c r="J28" s="11" t="n">
+        <v>168.8</v>
+      </c>
+      <c r="K28" s="9" t="inlineStr">
+        <is>
+          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
+      <c r="L28" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>17,000 ~ 18,500원</t>
-        </is>
-      </c>
-      <c r="I28" s="10" t="n">
-        <v>1671687</v>
-      </c>
-      <c r="J28" s="11" t="n">
-        <v>309.3</v>
-      </c>
-      <c r="K28" s="9" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
-        </is>
-      </c>
-      <c r="L28" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="M28" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="N28" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>엠에스바이오</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>그 외 기타 의료용 기기 제조업</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>아이엠기업인수목적1호</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>스팩</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t>6,800 ~ 7,800원</t>
-        </is>
-      </c>
-      <c r="I29" s="10" t="n">
-        <v>2840000</v>
-      </c>
-      <c r="J29" s="11" t="n">
-        <v>221.5</v>
-      </c>
-      <c r="K29" s="9" t="inlineStr">
-        <is>
-          <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
-        </is>
-      </c>
-      <c r="L29" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="M29" s="8" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>2,000원 (단일가)</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>아이엠증권 02-2122-9688, 9485</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>한화플러스제6호기업인수목적</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>스팩</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="N29" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>크리에이츠</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="H30" s="8" t="inlineStr">
-        <is>
-          <t>15,000 ~ 18,000원</t>
-        </is>
-      </c>
-      <c r="I30" s="10" t="n">
-        <v>1050000</v>
-      </c>
-      <c r="J30" s="11" t="n">
-        <v>189</v>
-      </c>
-      <c r="K30" s="9" t="inlineStr">
-        <is>
-          <t>삼성증권 02-2020-7414, 7375, 7651</t>
-        </is>
-      </c>
-      <c r="L30" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="M30" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="N30" s="12" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>2,000원 (단일가)</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>한화투자증권㈜ 02-3772-7395, 7398, 7393</t>
+        </is>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2519,104 +2221,271 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>디티에스</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>특수 목적용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>17,000 ~ 18,500원</t>
+        </is>
+      </c>
+      <c r="I31" s="10" t="n">
+        <v>1671687</v>
+      </c>
+      <c r="J31" s="11" t="n">
+        <v>309.3</v>
+      </c>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
+        </is>
+      </c>
+      <c r="L31" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>엠에스바이오</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>그 외 기타 의료용 기기 제조업</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>6,800 ~ 7,800원</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="n">
+        <v>2840000</v>
+      </c>
+      <c r="J32" s="11" t="n">
+        <v>221.5</v>
+      </c>
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
+        </is>
+      </c>
+      <c r="L32" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>크리에이츠</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>15,000 ~ 18,000원</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="n">
+        <v>1050000</v>
+      </c>
+      <c r="J33" s="11" t="n">
+        <v>189</v>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-7414, 7375, 7651</t>
+        </is>
+      </c>
+      <c r="L33" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>티앤이코리아</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>산업용 송풍기 및 배기장치 제조업</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="G31" s="8" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>12,600 ~ 15,300원</t>
         </is>
       </c>
-      <c r="I31" s="10" t="n">
+      <c r="I34" s="10" t="n">
         <v>1800000</v>
       </c>
-      <c r="J31" s="11" t="n">
+      <c r="J34" s="11" t="n">
         <v>275.4</v>
       </c>
-      <c r="K31" s="9" t="inlineStr">
+      <c r="K34" s="9" t="inlineStr">
         <is>
           <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
         </is>
       </c>
-      <c r="L31" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="M31" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="N31" s="12" t="inlineStr">
+      <c r="L34" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N31"/>
+  <autoFilter ref="A1:L34"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2628,7 +2497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2642,9 +2511,7 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="48" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2705,16 +2572,6 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>청약일</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>납입일</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
           <t>DART</t>
         </is>
       </c>
@@ -2771,85 +2628,65 @@
           <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-24</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-27</t>
-        </is>
-      </c>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>제논</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경(수요예측)</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-20</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>9,700 ~ 12,200원</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>1550000</v>
-      </c>
-      <c r="J3" s="6" t="n">
-        <v>189.1</v>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>삼성증권 02-2020-8023, 7653, 7850</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-24</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-27</t>
-        </is>
-      </c>
-      <c r="N3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>우리투자제1호기업인수목적</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>스팩</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>2,000원 (단일가)</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="n">
+        <v>4875000</v>
+      </c>
+      <c r="J3" s="11" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>우리투자증권 02-6390-3889</t>
+        </is>
+      </c>
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2858,7 +2695,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -2878,17 +2715,17 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>정정-변경없음</t>
+          <t>정정-변경(수요예측)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -2907,9 +2744,7 @@
           <t>삼성증권 02-2020-8023, 7653, 7850</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="L4" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2923,129 +2758,109 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>제논</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>9,700 ~ 12,200원</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>1550000</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>189.1</v>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-8023, 7653, 7850</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>동원파츠</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>반도체 제조용 기계 제조업</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>23,000 ~ 26,500원</t>
         </is>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I6" s="5" t="n">
         <v>1522500</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="J6" s="6" t="n">
         <v>403.5</v>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-6975, 8217, 7651</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>인터엑스</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-04</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>10,000 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I6" s="10" t="n">
-        <v>2250000</v>
-      </c>
-      <c r="J6" s="11" t="n">
-        <v>292.5</v>
-      </c>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5700, 6648</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-09</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-14</t>
-        </is>
-      </c>
-      <c r="N6" s="12" t="inlineStr">
+      <c r="L6" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3054,202 +2869,172 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>인터엑스</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>10,000 ~ 13,000원</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>2250000</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5700, 6648</t>
+        </is>
+      </c>
+      <c r="L7" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>유캐스트</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>기타 무선 통신장비 제조업</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>19,000 ~ 23,000원</t>
         </is>
       </c>
-      <c r="I7" s="10" t="n">
+      <c r="I8" s="10" t="n">
         <v>600000</v>
       </c>
-      <c r="J7" s="11" t="n">
+      <c r="J8" s="11" t="n">
         <v>138</v>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="K8" s="9" t="inlineStr">
         <is>
           <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
         </is>
       </c>
-      <c r="L7" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-      <c r="N7" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="L8" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>옵토닉스</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>광학렌즈 및 광학요소 제조업</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>10,000 ~ 12,000원</t>
         </is>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="I9" s="5" t="n">
         <v>1572490</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J9" s="6" t="n">
         <v>188.7</v>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>이노보테라퓨틱스</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-02</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>20,000 ~ 24,000원</t>
-        </is>
-      </c>
-      <c r="I9" s="10" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="J9" s="11" t="n">
-        <v>396</v>
-      </c>
-      <c r="K9" s="9" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
-        </is>
-      </c>
-      <c r="L9" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-07</t>
-        </is>
-      </c>
-      <c r="M9" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-10</t>
-        </is>
-      </c>
-      <c r="N9" s="12" t="inlineStr">
+      <c r="L9" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3258,202 +3043,172 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>이노보테라퓨틱스</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>의학 및 약학 연구개발업</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>20,000 ~ 24,000원</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J10" s="11" t="n">
+        <v>396</v>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+        </is>
+      </c>
+      <c r="L10" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>기타 엔지니어링 서비스업</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>2026-11-19</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>2026-11-25</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>11,200 ~ 13,600원</t>
         </is>
       </c>
-      <c r="I10" s="10" t="n">
+      <c r="I11" s="10" t="n">
         <v>1575000</v>
       </c>
-      <c r="J10" s="11" t="n">
+      <c r="J11" s="11" t="n">
         <v>214.2</v>
       </c>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="K11" s="9" t="inlineStr">
         <is>
           <t>NH투자증권 02-2229-6315, 6829</t>
         </is>
       </c>
-      <c r="L10" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-27</t>
-        </is>
-      </c>
-      <c r="M10" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-02</t>
-        </is>
-      </c>
-      <c r="N10" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="L11" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>이에스티</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>그 외 기타 전자부품 제조업</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>10,600 ~ 12,400원</t>
         </is>
       </c>
-      <c r="I11" s="5" t="n">
+      <c r="I12" s="5" t="n">
         <v>1650000</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J12" s="6" t="n">
         <v>204.6</v>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>에스에프씨</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>그 외 기타 분류 안된 화학제품 제조업</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>31,600 ~ 36,100원</t>
-        </is>
-      </c>
-      <c r="I12" s="10" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J12" s="11" t="n">
-        <v>1353.8</v>
-      </c>
-      <c r="K12" s="9" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
-        </is>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-      <c r="N12" s="12" t="inlineStr">
+      <c r="L12" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3467,12 +3222,12 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>씨아이에스케미칼</t>
+          <t>에스에프씨</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>알루미늄 제련, 정련 및 합금 제조업</t>
+          <t>그 외 기타 분류 안된 화학제품 제조업</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -3487,41 +3242,31 @@
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>5,400 ~ 6,800원</t>
+          <t>31,600 ~ 36,100원</t>
         </is>
       </c>
       <c r="I13" s="10" t="n">
-        <v>3000000</v>
+        <v>3750000</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>204</v>
+        <v>1353.8</v>
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
-        </is>
-      </c>
-      <c r="L13" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-10</t>
-        </is>
-      </c>
-      <c r="M13" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-15</t>
-        </is>
-      </c>
-      <c r="N13" s="12" t="inlineStr">
+          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
+        </is>
+      </c>
+      <c r="L13" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3530,17 +3275,17 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>제이앤티지</t>
+          <t>씨아이에스케미칼</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>그 외 자동차용 신품 부품 제조업</t>
+          <t>알루미늄 제련, 정련 및 합금 제조업</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
@@ -3555,41 +3300,31 @@
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>26,400 ~ 31,900원</t>
+          <t>5,400 ~ 6,800원</t>
         </is>
       </c>
       <c r="I14" s="10" t="n">
-        <v>3182000</v>
+        <v>3000000</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>1015.1</v>
+        <v>204</v>
       </c>
       <c r="K14" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
-        </is>
-      </c>
-      <c r="L14" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="M14" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-17</t>
-        </is>
-      </c>
-      <c r="N14" s="12" t="inlineStr">
+          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
+        </is>
+      </c>
+      <c r="L14" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3603,129 +3338,109 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
+          <t>제이앤티지</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>그 외 자동차용 신품 부품 제조업</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>26,400 ~ 31,900원</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>3182000</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>1015.1</v>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
+        </is>
+      </c>
+      <c r="L15" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
           <t>씨앤엠</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>전동기 및 발전기 제조업</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>10,000 ~ 13,000원</t>
         </is>
       </c>
-      <c r="I15" s="10" t="n">
+      <c r="I16" s="10" t="n">
         <v>2059500</v>
       </c>
-      <c r="J15" s="11" t="n">
+      <c r="J16" s="11" t="n">
         <v>267.7</v>
       </c>
-      <c r="K15" s="9" t="inlineStr">
+      <c r="K16" s="9" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L15" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="M15" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-17</t>
-        </is>
-      </c>
-      <c r="N15" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>넥스아이</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>10,500 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J16" s="6" t="n">
-        <v>487.5</v>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="inlineStr">
+      <c r="L16" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3739,12 +3454,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>항공기용 부품 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -3759,41 +3474,31 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,700 ~ 5,700원</t>
+          <t>10,500 ~ 13,000원</t>
         </is>
       </c>
       <c r="I17" s="5" t="n">
-        <v>3300000</v>
+        <v>3750000</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>188.1</v>
+        <v>487.5</v>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="N17" s="7" t="inlineStr">
+          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3802,202 +3507,172 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>하나에어로다이내믹스</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>항공기용 부품 제조업</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4,700 ~ 5,700원</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>188.1</v>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>바로팜</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>전자상거래 소매 중개업</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>16,400 ~ 20,200원</t>
         </is>
       </c>
-      <c r="I18" s="5" t="n">
+      <c r="I19" s="5" t="n">
         <v>1335000</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="J19" s="6" t="n">
         <v>269.7</v>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>엠비디</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>물질 검사, 측정 및 분석기구 제조업</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="N18" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>엠비디</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>물질 검사, 측정 및 분석기구 제조업</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>9,600 ~ 11,700원</t>
         </is>
       </c>
-      <c r="I19" s="10" t="n">
+      <c r="I20" s="10" t="n">
         <v>1500000</v>
       </c>
-      <c r="J19" s="11" t="n">
+      <c r="J20" s="11" t="n">
         <v>175.5</v>
       </c>
-      <c r="K19" s="9" t="inlineStr">
+      <c r="K20" s="9" t="inlineStr">
         <is>
           <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
         </is>
       </c>
-      <c r="L19" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="M19" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-17</t>
-        </is>
-      </c>
-      <c r="N19" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>래블업</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>시스템 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>19,000 ~ 22,000원</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="n">
-        <v>1635000</v>
-      </c>
-      <c r="J20" s="6" t="n">
-        <v>359.7</v>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>NH투자증권 02-768-7462, 7467</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="N20" s="7" t="inlineStr">
+      <c r="L20" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4006,58 +3681,56 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>래블업</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>시스템 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>이에스티</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>그 외 기타 전자부품 제조업</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,600 ~ 12,400원</t>
+          <t>19,000 ~ 22,000원</t>
         </is>
       </c>
       <c r="I21" s="5" t="n">
-        <v>1650000</v>
+        <v>1635000</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>204.6</v>
+        <v>359.7</v>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="7" t="inlineStr">
+          <t>NH투자증권 02-768-7462, 7467</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4066,134 +3739,114 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>이에스티</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>그 외 기타 전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>10,600 ~ 12,400원</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>204.6</v>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>에이엘로봇</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>기타 기계 및 장비 제조업</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>정정-변경(수요예측)</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>15,700 ~ 17,600원</t>
         </is>
       </c>
-      <c r="I22" s="5" t="n">
+      <c r="I23" s="5" t="n">
         <v>1800000</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="J23" s="6" t="n">
         <v>316.8</v>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>아델</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>18,000 ~ 25,000원</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="n">
-        <v>1627500</v>
-      </c>
-      <c r="J23" s="11" t="n">
-        <v>406.9</v>
-      </c>
-      <c r="K23" s="9" t="inlineStr">
-        <is>
-          <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
-        </is>
-      </c>
-      <c r="L23" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-      <c r="M23" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="N23" s="12" t="inlineStr">
+      <c r="L23" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4207,12 +3860,12 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>SimwonAmericaCorp.</t>
+          <t>아델</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>자동차 신품 부품 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
@@ -4222,22 +3875,36 @@
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>수요예측 항목 없음(원문 확인)</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr"/>
-      <c r="G24" s="8" t="inlineStr"/>
-      <c r="H24" s="8" t="inlineStr"/>
-      <c r="I24" s="10" t="inlineStr"/>
-      <c r="J24" s="11" t="inlineStr"/>
-      <c r="K24" s="9" t="inlineStr"/>
-      <c r="L24" s="8" t="inlineStr"/>
-      <c r="M24" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="N24" s="12" t="inlineStr">
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>18,000 ~ 25,000원</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="n">
+        <v>1627500</v>
+      </c>
+      <c r="J24" s="11" t="n">
+        <v>406.9</v>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
+      <c r="L24" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4246,66 +3913,36 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>다비오</t>
+          <t>SimwonAmericaCorp.</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
+          <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>12,300 ~ 16,600원</t>
-        </is>
-      </c>
-      <c r="I25" s="10" t="n">
-        <v>750000</v>
-      </c>
-      <c r="J25" s="11" t="n">
-        <v>124.5</v>
-      </c>
-      <c r="K25" s="9" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
-        </is>
-      </c>
-      <c r="L25" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="M25" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="N25" s="12" t="inlineStr">
+          <t>수요예측 항목 없음(원문 확인)</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr"/>
+      <c r="G25" s="8" t="inlineStr"/>
+      <c r="H25" s="8" t="inlineStr"/>
+      <c r="I25" s="10" t="inlineStr"/>
+      <c r="J25" s="11" t="inlineStr"/>
+      <c r="K25" s="9" t="inlineStr"/>
+      <c r="L25" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4319,7 +3956,7 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>엔키화이트햇</t>
+          <t>다비오</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
@@ -4329,7 +3966,7 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
@@ -4339,41 +3976,31 @@
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>13,000 ~ 16,500원</t>
+          <t>12,300 ~ 16,600원</t>
         </is>
       </c>
       <c r="I26" s="10" t="n">
-        <v>1258000</v>
+        <v>750000</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>207.6</v>
+        <v>124.5</v>
       </c>
       <c r="K26" s="9" t="inlineStr">
         <is>
-          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
-        </is>
-      </c>
-      <c r="L26" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="M26" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-17</t>
-        </is>
-      </c>
-      <c r="N26" s="12" t="inlineStr">
+          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
+        </is>
+      </c>
+      <c r="L26" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4387,197 +4014,167 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
+          <t>엔키화이트햇</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>13,000 ~ 16,500원</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="n">
+        <v>1258000</v>
+      </c>
+      <c r="J27" s="11" t="n">
+        <v>207.6</v>
+      </c>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
+        </is>
+      </c>
+      <c r="L27" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
           <t>영광와이케이엠씨</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>그 외 기타 금속가공업</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>9,400 ~ 11,000원</t>
         </is>
       </c>
-      <c r="I27" s="10" t="n">
+      <c r="I28" s="10" t="n">
         <v>1694840</v>
       </c>
-      <c r="J27" s="11" t="n">
+      <c r="J28" s="11" t="n">
         <v>186.4</v>
       </c>
-      <c r="K27" s="9" t="inlineStr">
+      <c r="K28" s="9" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
         </is>
       </c>
-      <c r="L27" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="M27" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="N27" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="L28" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>영광</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>수상 금속 골조 구조재 제조업</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>14,000 ~ 17,000원</t>
         </is>
       </c>
-      <c r="I28" s="5" t="n">
+      <c r="I29" s="5" t="n">
         <v>1695000</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="J29" s="6" t="n">
         <v>288.1</v>
       </c>
-      <c r="K28" s="3" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="N28" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>인텔리빅스</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t>7,600 ~ 9,000원</t>
-        </is>
-      </c>
-      <c r="I29" s="10" t="n">
-        <v>1875000</v>
-      </c>
-      <c r="J29" s="11" t="n">
-        <v>168.8</v>
-      </c>
-      <c r="K29" s="9" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
-        </is>
-      </c>
-      <c r="L29" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="M29" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="N29" s="12" t="inlineStr">
+      <c r="L29" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4586,22 +4183,22 @@
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>제논</t>
+          <t>인텔리빅스</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
+          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
@@ -4611,33 +4208,31 @@
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>9,700 ~ 12,200원</t>
+          <t>7,600 ~ 9,000원</t>
         </is>
       </c>
       <c r="I30" s="10" t="n">
-        <v>1550000</v>
+        <v>1875000</v>
       </c>
       <c r="J30" s="11" t="n">
-        <v>189.1</v>
+        <v>168.8</v>
       </c>
       <c r="K30" s="9" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-8023, 7653, 7850</t>
-        </is>
-      </c>
-      <c r="L30" s="8" t="inlineStr"/>
-      <c r="M30" s="8" t="inlineStr"/>
-      <c r="N30" s="12" t="inlineStr">
+          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
+      <c r="L30" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4646,17 +4241,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>래블업</t>
+          <t>아이엠기업인수목적1호</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>시스템 소프트웨어 개발 및 공급업</t>
+          <t>스팩</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -4671,33 +4266,31 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,000 ~ 22,000원</t>
+          <t>2,000원 (단일가)</t>
         </is>
       </c>
       <c r="I31" s="5" t="n">
-        <v>1635000</v>
+        <v>3750000</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>359.7</v>
+        <v>75</v>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>NH투자증권 02-768-7462, 7467</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="7" t="inlineStr">
+          <t>아이엠증권 02-2122-9688, 9485</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4706,22 +4299,22 @@
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>케이엠에프</t>
+          <t>아이엠기업인수목적1호</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>스팩</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
@@ -4731,33 +4324,31 @@
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>15,000 ~ 17,800원</t>
+          <t>2,000원 (단일가)</t>
         </is>
       </c>
       <c r="I32" s="10" t="n">
-        <v>1500000</v>
+        <v>3750000</v>
       </c>
       <c r="J32" s="11" t="n">
-        <v>267</v>
+        <v>75</v>
       </c>
       <c r="K32" s="9" t="inlineStr">
         <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
-        </is>
-      </c>
-      <c r="L32" s="8" t="inlineStr"/>
-      <c r="M32" s="8" t="inlineStr"/>
-      <c r="N32" s="12" t="inlineStr">
+          <t>아이엠증권 02-2122-9688, 9485</t>
+        </is>
+      </c>
+      <c r="L32" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4766,186 +4357,172 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>바로팜</t>
+          <t>제논</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>전자상거래 소매 중개업</t>
+          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>9,700 ~ 12,200원</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="n">
+        <v>1550000</v>
+      </c>
+      <c r="J33" s="11" t="n">
+        <v>189.1</v>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-8023, 7653, 7850</t>
+        </is>
+      </c>
+      <c r="L33" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>한화플러스제6호기업인수목적</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>스팩</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="inlineStr">
-        <is>
-          <t>16,400 ~ 20,200원</t>
-        </is>
-      </c>
-      <c r="I33" s="10" t="n">
-        <v>1335000</v>
-      </c>
-      <c r="J33" s="11" t="n">
-        <v>269.7</v>
-      </c>
-      <c r="K33" s="9" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
-        </is>
-      </c>
-      <c r="L33" s="8" t="inlineStr"/>
-      <c r="M33" s="8" t="inlineStr"/>
-      <c r="N33" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>동원파츠</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>반도체 제조용 기계 제조업</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G34" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="H34" s="8" t="inlineStr">
-        <is>
-          <t>23,000 ~ 26,500원</t>
-        </is>
-      </c>
-      <c r="I34" s="10" t="n">
-        <v>1522500</v>
-      </c>
-      <c r="J34" s="11" t="n">
-        <v>403.5</v>
-      </c>
-      <c r="K34" s="9" t="inlineStr">
-        <is>
-          <t>삼성증권 02-2020-6975, 8217, 7651</t>
-        </is>
-      </c>
-      <c r="L34" s="8" t="inlineStr"/>
-      <c r="M34" s="8" t="inlineStr"/>
-      <c r="N34" s="12" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>2,000원 (단일가)</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="J34" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>한화투자증권㈜ 02-3772-7395, 7398, 7393</t>
+        </is>
+      </c>
+      <c r="L34" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>디티에스</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>특수 목적용 기계 제조업</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>래블업</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>시스템 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="H35" s="8" t="inlineStr">
-        <is>
-          <t>17,000 ~ 18,500원</t>
-        </is>
-      </c>
-      <c r="I35" s="10" t="n">
-        <v>1671687</v>
-      </c>
-      <c r="J35" s="11" t="n">
-        <v>309.3</v>
-      </c>
-      <c r="K35" s="9" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
-        </is>
-      </c>
-      <c r="L35" s="8" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="M35" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="N35" s="12" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>19,000 ~ 22,000원</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>1635000</v>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v>359.7</v>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>NH투자증권 02-768-7462, 7467</t>
+        </is>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4954,17 +4531,17 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>엠에스바이오</t>
+          <t>한화플러스제6호기업인수목적</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>그 외 기타 의료용 기기 제조업</t>
+          <t>스팩</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
@@ -4979,41 +4556,31 @@
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>6,800 ~ 7,800원</t>
+          <t>2,000원 (단일가)</t>
         </is>
       </c>
       <c r="I36" s="10" t="n">
-        <v>2840000</v>
+        <v>4500000</v>
       </c>
       <c r="J36" s="11" t="n">
-        <v>221.5</v>
+        <v>90</v>
       </c>
       <c r="K36" s="9" t="inlineStr">
         <is>
-          <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
-        </is>
-      </c>
-      <c r="L36" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="M36" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="N36" s="12" t="inlineStr">
+          <t>한화투자증권㈜ 02-3772-7395, 7398, 7393</t>
+        </is>
+      </c>
+      <c r="L36" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -5022,17 +4589,17 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>옵토닉스</t>
+          <t>케이엠에프</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>광학렌즈 및 광학요소 제조업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
@@ -5047,33 +4614,31 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>10,000 ~ 12,000원</t>
+          <t>15,000 ~ 17,800원</t>
         </is>
       </c>
       <c r="I37" s="10" t="n">
-        <v>1572490</v>
+        <v>1500000</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>188.7</v>
+        <v>267</v>
       </c>
       <c r="K37" s="9" t="inlineStr">
         <is>
-          <t>한국투자증권 02-3276-5958, 6269</t>
-        </is>
-      </c>
-      <c r="L37" s="8" t="inlineStr"/>
-      <c r="M37" s="8" t="inlineStr"/>
-      <c r="N37" s="12" t="inlineStr">
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
+        </is>
+      </c>
+      <c r="L37" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -5082,22 +4647,22 @@
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>넥스아이</t>
+          <t>바로팜</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>의학 및 약학 연구개발업</t>
+          <t>전자상거래 소매 중개업</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
@@ -5117,23 +4682,21 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>10,500 ~ 13,000원</t>
+          <t>16,400 ~ 20,200원</t>
         </is>
       </c>
       <c r="I38" s="10" t="n">
-        <v>3750000</v>
+        <v>1335000</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>487.5</v>
+        <v>269.7</v>
       </c>
       <c r="K38" s="9" t="inlineStr">
         <is>
-          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
-        </is>
-      </c>
-      <c r="L38" s="8" t="inlineStr"/>
-      <c r="M38" s="8" t="inlineStr"/>
-      <c r="N38" s="12" t="inlineStr">
+          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
+      <c r="L38" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -5142,22 +4705,22 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>동원파츠</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
+          <t>반도체 제조용 기계 제조업</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -5167,41 +4730,31 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>15,000 ~ 18,000원</t>
+          <t>23,000 ~ 26,500원</t>
         </is>
       </c>
       <c r="I39" s="10" t="n">
-        <v>1050000</v>
+        <v>1522500</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>189</v>
+        <v>403.5</v>
       </c>
       <c r="K39" s="9" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-7414, 7375, 7651</t>
-        </is>
-      </c>
-      <c r="L39" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="M39" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="N39" s="12" t="inlineStr">
+          <t>삼성증권 02-2020-6975, 8217, 7651</t>
+        </is>
+      </c>
+      <c r="L39" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -5210,17 +4763,17 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>티앤이코리아</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>산업용 송풍기 및 배기장치 제조업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
@@ -5235,41 +4788,31 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>12,600 ~ 15,300원</t>
+          <t>17,000 ~ 18,500원</t>
         </is>
       </c>
       <c r="I40" s="10" t="n">
-        <v>1800000</v>
+        <v>1671687</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>275.4</v>
+        <v>309.3</v>
       </c>
       <c r="K40" s="9" t="inlineStr">
         <is>
-          <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
-        </is>
-      </c>
-      <c r="L40" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="M40" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="N40" s="12" t="inlineStr">
+          <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
+        </is>
+      </c>
+      <c r="L40" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -5278,22 +4821,22 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>엠에스바이오</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>항공기용 부품 제조업</t>
+          <t>그 외 기타 의료용 기기 제조업</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -5303,33 +4846,31 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>4,700 ~ 5,700원</t>
+          <t>6,800 ~ 7,800원</t>
         </is>
       </c>
       <c r="I41" s="10" t="n">
-        <v>3300000</v>
+        <v>2840000</v>
       </c>
       <c r="J41" s="11" t="n">
-        <v>188.1</v>
+        <v>221.5</v>
       </c>
       <c r="K41" s="9" t="inlineStr">
         <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
-        </is>
-      </c>
-      <c r="L41" s="8" t="inlineStr"/>
-      <c r="M41" s="8" t="inlineStr"/>
-      <c r="N41" s="12" t="inlineStr">
+          <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
+        </is>
+      </c>
+      <c r="L41" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -5338,22 +4879,22 @@
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>래블업</t>
+          <t>옵토닉스</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>시스템 소프트웨어 개발 및 공급업</t>
+          <t>광학렌즈 및 광학요소 제조업</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
@@ -5363,33 +4904,31 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>19,000 ~ 22,000원</t>
+          <t>10,000 ~ 12,000원</t>
         </is>
       </c>
       <c r="I42" s="10" t="n">
-        <v>1635000</v>
+        <v>1572490</v>
       </c>
       <c r="J42" s="11" t="n">
-        <v>359.7</v>
+        <v>188.7</v>
       </c>
       <c r="K42" s="9" t="inlineStr">
         <is>
-          <t>NH투자증권 02-768-7462, 7467</t>
-        </is>
-      </c>
-      <c r="L42" s="8" t="inlineStr"/>
-      <c r="M42" s="8" t="inlineStr"/>
-      <c r="N42" s="12" t="inlineStr">
+          <t>한국투자증권 02-3276-5958, 6269</t>
+        </is>
+      </c>
+      <c r="L42" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -5398,17 +4937,17 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>영광</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>수상 금속 골조 구조재 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
@@ -5423,33 +4962,31 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>14,000 ~ 17,000원</t>
+          <t>10,500 ~ 13,000원</t>
         </is>
       </c>
       <c r="I43" s="10" t="n">
-        <v>1695000</v>
+        <v>3750000</v>
       </c>
       <c r="J43" s="11" t="n">
-        <v>288.1</v>
+        <v>487.5</v>
       </c>
       <c r="K43" s="9" t="inlineStr">
         <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
-        </is>
-      </c>
-      <c r="L43" s="8" t="inlineStr"/>
-      <c r="M43" s="8" t="inlineStr"/>
-      <c r="N43" s="12" t="inlineStr">
+          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
+        </is>
+      </c>
+      <c r="L43" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -5458,22 +4995,22 @@
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>이에스티</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>그 외 기타 전자부품 제조업</t>
+          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
@@ -5483,33 +5020,31 @@
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>10,600 ~ 12,400원</t>
+          <t>15,000 ~ 18,000원</t>
         </is>
       </c>
       <c r="I44" s="10" t="n">
-        <v>1650000</v>
+        <v>1050000</v>
       </c>
       <c r="J44" s="11" t="n">
-        <v>204.6</v>
+        <v>189</v>
       </c>
       <c r="K44" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
-        </is>
-      </c>
-      <c r="L44" s="8" t="inlineStr"/>
-      <c r="M44" s="8" t="inlineStr"/>
-      <c r="N44" s="12" t="inlineStr">
+          <t>삼성증권 02-2020-7414, 7375, 7651</t>
+        </is>
+      </c>
+      <c r="L44" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -5518,22 +5053,22 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>에이엘로봇</t>
+          <t>티앤이코리아</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>기타 기계 및 장비 제조업</t>
+          <t>산업용 송풍기 및 배기장치 제조업</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -5543,85 +5078,378 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>15,700 ~ 17,600원</t>
+          <t>12,600 ~ 15,300원</t>
         </is>
       </c>
       <c r="I45" s="10" t="n">
         <v>1800000</v>
       </c>
       <c r="J45" s="11" t="n">
+        <v>275.4</v>
+      </c>
+      <c r="K45" s="9" t="inlineStr">
+        <is>
+          <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
+        </is>
+      </c>
+      <c r="L45" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>하나에어로다이내믹스</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>항공기용 부품 제조업</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>4,700 ~ 5,700원</t>
+        </is>
+      </c>
+      <c r="I46" s="10" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="J46" s="11" t="n">
+        <v>188.1</v>
+      </c>
+      <c r="K46" s="9" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
+        </is>
+      </c>
+      <c r="L46" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>래블업</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>시스템 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>19,000 ~ 22,000원</t>
+        </is>
+      </c>
+      <c r="I47" s="10" t="n">
+        <v>1635000</v>
+      </c>
+      <c r="J47" s="11" t="n">
+        <v>359.7</v>
+      </c>
+      <c r="K47" s="9" t="inlineStr">
+        <is>
+          <t>NH투자증권 02-768-7462, 7467</t>
+        </is>
+      </c>
+      <c r="L47" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>영광</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>수상 금속 골조 구조재 제조업</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>14,000 ~ 17,000원</t>
+        </is>
+      </c>
+      <c r="I48" s="10" t="n">
+        <v>1695000</v>
+      </c>
+      <c r="J48" s="11" t="n">
+        <v>288.1</v>
+      </c>
+      <c r="K48" s="9" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+        </is>
+      </c>
+      <c r="L48" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>이에스티</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>그 외 기타 전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>10,600 ~ 12,400원</t>
+        </is>
+      </c>
+      <c r="I49" s="10" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J49" s="11" t="n">
+        <v>204.6</v>
+      </c>
+      <c r="K49" s="9" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+        </is>
+      </c>
+      <c r="L49" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>에이엘로봇</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>기타 기계 및 장비 제조업</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>15,700 ~ 17,600원</t>
+        </is>
+      </c>
+      <c r="I50" s="10" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="J50" s="11" t="n">
         <v>316.8</v>
       </c>
-      <c r="K45" s="9" t="inlineStr">
+      <c r="K50" s="9" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="L45" s="8" t="inlineStr"/>
-      <c r="M45" s="8" t="inlineStr"/>
-      <c r="N45" s="12" t="inlineStr">
+      <c r="L50" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N45"/>
+  <autoFilter ref="A1:L50"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/수요예측_일정.xlsx
+++ b/수요예측_일정.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체 이력" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'수요예측 일정'!$A$1:$L$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체 이력'!$A$1:$L$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'수요예측 일정'!$A$1:$O$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체 이력'!$A$1:$O$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -491,7 +491,10 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="48" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -552,6 +555,21 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>청약일</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>납입일</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>상장일</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>DART</t>
         </is>
       </c>
@@ -608,7 +626,18 @@
           <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
         </is>
       </c>
-      <c r="L2" s="7" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -666,7 +695,18 @@
           <t>우리투자증권 02-6390-3889</t>
         </is>
       </c>
-      <c r="L3" s="12" t="inlineStr">
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-07</t>
+        </is>
+      </c>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -724,7 +764,18 @@
           <t>삼성증권 02-2020-8023, 7653, 7850</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -782,7 +833,18 @@
           <t>삼성증권 02-2020-6975, 8217, 7651</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -840,7 +902,18 @@
           <t>한국투자증권㈜ 02-3276-5700, 6648</t>
         </is>
       </c>
-      <c r="L6" s="12" t="inlineStr">
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr"/>
+      <c r="O6" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -898,7 +971,18 @@
           <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
         </is>
       </c>
-      <c r="L7" s="12" t="inlineStr">
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="N7" s="8" t="inlineStr"/>
+      <c r="O7" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -956,7 +1040,18 @@
           <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
-      <c r="L8" s="7" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1014,7 +1109,18 @@
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L9" s="12" t="inlineStr">
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-07</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="N9" s="8" t="inlineStr"/>
+      <c r="O9" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1072,7 +1178,18 @@
           <t>NH투자증권 02-2229-6315, 6829</t>
         </is>
       </c>
-      <c r="L10" s="12" t="inlineStr">
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="N10" s="8" t="inlineStr"/>
+      <c r="O10" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1130,7 +1247,18 @@
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="L11" s="7" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1188,7 +1316,18 @@
           <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
         </is>
       </c>
-      <c r="L12" s="12" t="inlineStr">
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="N12" s="8" t="inlineStr"/>
+      <c r="O12" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1246,7 +1385,18 @@
           <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
-      <c r="L13" s="12" t="inlineStr">
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+      <c r="N13" s="8" t="inlineStr"/>
+      <c r="O13" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1304,7 +1454,18 @@
           <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
         </is>
       </c>
-      <c r="L14" s="12" t="inlineStr">
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N14" s="8" t="inlineStr"/>
+      <c r="O14" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1362,7 +1523,18 @@
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L15" s="12" t="inlineStr">
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M15" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N15" s="8" t="inlineStr"/>
+      <c r="O15" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1420,7 +1592,18 @@
           <t>한국투자증권㈜ 02-3276-6384, 5198</t>
         </is>
       </c>
-      <c r="L16" s="7" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1478,7 +1661,18 @@
           <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
         </is>
       </c>
-      <c r="L17" s="7" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1536,7 +1730,18 @@
           <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L18" s="7" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1594,7 +1799,18 @@
           <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
         </is>
       </c>
-      <c r="L19" s="12" t="inlineStr">
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M19" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N19" s="8" t="inlineStr"/>
+      <c r="O19" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1652,7 +1868,18 @@
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="L20" s="7" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1710,7 +1937,18 @@
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="L21" s="7" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1768,7 +2006,18 @@
           <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L22" s="12" t="inlineStr">
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="M22" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="N22" s="8" t="inlineStr"/>
+      <c r="O22" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1806,7 +2055,14 @@
       <c r="I23" s="10" t="inlineStr"/>
       <c r="J23" s="11" t="inlineStr"/>
       <c r="K23" s="9" t="inlineStr"/>
-      <c r="L23" s="12" t="inlineStr">
+      <c r="L23" s="8" t="inlineStr"/>
+      <c r="M23" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="N23" s="8" t="inlineStr"/>
+      <c r="O23" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1864,7 +2120,18 @@
           <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
         </is>
       </c>
-      <c r="L24" s="12" t="inlineStr">
+      <c r="L24" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="N24" s="8" t="inlineStr"/>
+      <c r="O24" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1922,7 +2189,18 @@
           <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
         </is>
       </c>
-      <c r="L25" s="12" t="inlineStr">
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M25" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N25" s="8" t="inlineStr"/>
+      <c r="O25" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1980,7 +2258,18 @@
           <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
         </is>
       </c>
-      <c r="L26" s="12" t="inlineStr">
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="M26" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="N26" s="8" t="inlineStr"/>
+      <c r="O26" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2038,7 +2327,18 @@
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L27" s="7" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2096,7 +2396,18 @@
           <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L28" s="12" t="inlineStr">
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="N28" s="8" t="inlineStr"/>
+      <c r="O28" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2154,7 +2465,18 @@
           <t>아이엠증권 02-2122-9688, 9485</t>
         </is>
       </c>
-      <c r="L29" s="7" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2212,7 +2534,18 @@
           <t>한화투자증권㈜ 02-3772-7395, 7398, 7393</t>
         </is>
       </c>
-      <c r="L30" s="7" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2270,7 +2603,18 @@
           <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
         </is>
       </c>
-      <c r="L31" s="12" t="inlineStr">
+      <c r="L31" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="M31" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="N31" s="8" t="inlineStr"/>
+      <c r="O31" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2328,7 +2672,18 @@
           <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
-      <c r="L32" s="12" t="inlineStr">
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M32" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="N32" s="8" t="inlineStr"/>
+      <c r="O32" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2386,7 +2741,18 @@
           <t>삼성증권 02-2020-7414, 7375, 7651</t>
         </is>
       </c>
-      <c r="L33" s="12" t="inlineStr">
+      <c r="L33" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="M33" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="N33" s="8" t="inlineStr"/>
+      <c r="O33" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2444,48 +2810,59 @@
           <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
         </is>
       </c>
-      <c r="L34" s="12" t="inlineStr">
+      <c r="L34" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="M34" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="N34" s="8" t="inlineStr"/>
+      <c r="O34" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L34"/>
+  <autoFilter ref="A1:O34"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2497,7 +2874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2511,7 +2888,10 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="48" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2572,6 +2952,21 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>청약일</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>납입일</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>상장일</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>DART</t>
         </is>
       </c>
@@ -2628,7 +3023,18 @@
           <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
         </is>
       </c>
-      <c r="L2" s="7" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2686,7 +3092,18 @@
           <t>우리투자증권 02-6390-3889</t>
         </is>
       </c>
-      <c r="L3" s="12" t="inlineStr">
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-07</t>
+        </is>
+      </c>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2744,7 +3161,18 @@
           <t>삼성증권 02-2020-8023, 7653, 7850</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2802,7 +3230,10 @@
           <t>삼성증권 02-2020-8023, 7653, 7850</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2860,7 +3291,18 @@
           <t>삼성증권 02-2020-6975, 8217, 7651</t>
         </is>
       </c>
-      <c r="L6" s="7" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2918,7 +3360,18 @@
           <t>한국투자증권㈜ 02-3276-5700, 6648</t>
         </is>
       </c>
-      <c r="L7" s="12" t="inlineStr">
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="N7" s="8" t="inlineStr"/>
+      <c r="O7" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2976,7 +3429,18 @@
           <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
         </is>
       </c>
-      <c r="L8" s="12" t="inlineStr">
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr"/>
+      <c r="O8" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3034,7 +3498,18 @@
           <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
-      <c r="L9" s="7" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3092,7 +3567,18 @@
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L10" s="12" t="inlineStr">
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-07</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="N10" s="8" t="inlineStr"/>
+      <c r="O10" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3150,7 +3636,18 @@
           <t>NH투자증권 02-2229-6315, 6829</t>
         </is>
       </c>
-      <c r="L11" s="12" t="inlineStr">
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="N11" s="8" t="inlineStr"/>
+      <c r="O11" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3208,7 +3705,18 @@
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="L12" s="7" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3266,7 +3774,18 @@
           <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
         </is>
       </c>
-      <c r="L13" s="12" t="inlineStr">
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="N13" s="8" t="inlineStr"/>
+      <c r="O13" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3324,7 +3843,18 @@
           <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
-      <c r="L14" s="12" t="inlineStr">
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+      <c r="N14" s="8" t="inlineStr"/>
+      <c r="O14" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3382,7 +3912,18 @@
           <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
         </is>
       </c>
-      <c r="L15" s="12" t="inlineStr">
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M15" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N15" s="8" t="inlineStr"/>
+      <c r="O15" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3440,7 +3981,18 @@
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L16" s="12" t="inlineStr">
+      <c r="L16" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M16" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N16" s="8" t="inlineStr"/>
+      <c r="O16" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3498,7 +4050,18 @@
           <t>한국투자증권㈜ 02-3276-6384, 5198</t>
         </is>
       </c>
-      <c r="L17" s="7" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3556,7 +4119,18 @@
           <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
         </is>
       </c>
-      <c r="L18" s="7" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3614,7 +4188,18 @@
           <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L19" s="7" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3672,7 +4257,18 @@
           <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
         </is>
       </c>
-      <c r="L20" s="12" t="inlineStr">
+      <c r="L20" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M20" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N20" s="8" t="inlineStr"/>
+      <c r="O20" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3730,7 +4326,18 @@
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="L21" s="7" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3788,7 +4395,10 @@
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="L22" s="7" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3846,7 +4456,18 @@
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="L23" s="7" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3904,7 +4525,18 @@
           <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L24" s="12" t="inlineStr">
+      <c r="L24" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="N24" s="8" t="inlineStr"/>
+      <c r="O24" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3942,7 +4574,14 @@
       <c r="I25" s="10" t="inlineStr"/>
       <c r="J25" s="11" t="inlineStr"/>
       <c r="K25" s="9" t="inlineStr"/>
-      <c r="L25" s="12" t="inlineStr">
+      <c r="L25" s="8" t="inlineStr"/>
+      <c r="M25" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="N25" s="8" t="inlineStr"/>
+      <c r="O25" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4000,7 +4639,18 @@
           <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
         </is>
       </c>
-      <c r="L26" s="12" t="inlineStr">
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="M26" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="N26" s="8" t="inlineStr"/>
+      <c r="O26" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4058,7 +4708,18 @@
           <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
         </is>
       </c>
-      <c r="L27" s="12" t="inlineStr">
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M27" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N27" s="8" t="inlineStr"/>
+      <c r="O27" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4116,7 +4777,18 @@
           <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
         </is>
       </c>
-      <c r="L28" s="12" t="inlineStr">
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="N28" s="8" t="inlineStr"/>
+      <c r="O28" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4174,7 +4846,18 @@
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L29" s="7" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4232,7 +4915,18 @@
           <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L30" s="12" t="inlineStr">
+      <c r="L30" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="M30" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="N30" s="8" t="inlineStr"/>
+      <c r="O30" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4290,7 +4984,18 @@
           <t>아이엠증권 02-2122-9688, 9485</t>
         </is>
       </c>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4348,7 +5053,10 @@
           <t>아이엠증권 02-2122-9688, 9485</t>
         </is>
       </c>
-      <c r="L32" s="12" t="inlineStr">
+      <c r="L32" s="8" t="inlineStr"/>
+      <c r="M32" s="8" t="inlineStr"/>
+      <c r="N32" s="8" t="inlineStr"/>
+      <c r="O32" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4406,7 +5114,10 @@
           <t>삼성증권 02-2020-8023, 7653, 7850</t>
         </is>
       </c>
-      <c r="L33" s="12" t="inlineStr">
+      <c r="L33" s="8" t="inlineStr"/>
+      <c r="M33" s="8" t="inlineStr"/>
+      <c r="N33" s="8" t="inlineStr"/>
+      <c r="O33" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4464,7 +5175,18 @@
           <t>한화투자증권㈜ 02-3772-7395, 7398, 7393</t>
         </is>
       </c>
-      <c r="L34" s="7" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4522,7 +5244,10 @@
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="L35" s="7" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4580,7 +5305,10 @@
           <t>한화투자증권㈜ 02-3772-7395, 7398, 7393</t>
         </is>
       </c>
-      <c r="L36" s="12" t="inlineStr">
+      <c r="L36" s="8" t="inlineStr"/>
+      <c r="M36" s="8" t="inlineStr"/>
+      <c r="N36" s="8" t="inlineStr"/>
+      <c r="O36" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4638,7 +5366,10 @@
           <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
         </is>
       </c>
-      <c r="L37" s="12" t="inlineStr">
+      <c r="L37" s="8" t="inlineStr"/>
+      <c r="M37" s="8" t="inlineStr"/>
+      <c r="N37" s="8" t="inlineStr"/>
+      <c r="O37" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4696,7 +5427,10 @@
           <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L38" s="12" t="inlineStr">
+      <c r="L38" s="8" t="inlineStr"/>
+      <c r="M38" s="8" t="inlineStr"/>
+      <c r="N38" s="8" t="inlineStr"/>
+      <c r="O38" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4754,7 +5488,10 @@
           <t>삼성증권 02-2020-6975, 8217, 7651</t>
         </is>
       </c>
-      <c r="L39" s="12" t="inlineStr">
+      <c r="L39" s="8" t="inlineStr"/>
+      <c r="M39" s="8" t="inlineStr"/>
+      <c r="N39" s="8" t="inlineStr"/>
+      <c r="O39" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4812,7 +5549,18 @@
           <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
         </is>
       </c>
-      <c r="L40" s="12" t="inlineStr">
+      <c r="L40" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="M40" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="N40" s="8" t="inlineStr"/>
+      <c r="O40" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4870,7 +5618,18 @@
           <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
-      <c r="L41" s="12" t="inlineStr">
+      <c r="L41" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M41" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="N41" s="8" t="inlineStr"/>
+      <c r="O41" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4928,7 +5687,10 @@
           <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
-      <c r="L42" s="12" t="inlineStr">
+      <c r="L42" s="8" t="inlineStr"/>
+      <c r="M42" s="8" t="inlineStr"/>
+      <c r="N42" s="8" t="inlineStr"/>
+      <c r="O42" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4986,7 +5748,10 @@
           <t>한국투자증권㈜ 02-3276-6384, 5198</t>
         </is>
       </c>
-      <c r="L43" s="12" t="inlineStr">
+      <c r="L43" s="8" t="inlineStr"/>
+      <c r="M43" s="8" t="inlineStr"/>
+      <c r="N43" s="8" t="inlineStr"/>
+      <c r="O43" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -5044,7 +5809,18 @@
           <t>삼성증권 02-2020-7414, 7375, 7651</t>
         </is>
       </c>
-      <c r="L44" s="12" t="inlineStr">
+      <c r="L44" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="M44" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="N44" s="8" t="inlineStr"/>
+      <c r="O44" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -5102,7 +5878,18 @@
           <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
         </is>
       </c>
-      <c r="L45" s="12" t="inlineStr">
+      <c r="L45" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="M45" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="N45" s="8" t="inlineStr"/>
+      <c r="O45" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -5160,7 +5947,10 @@
           <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
         </is>
       </c>
-      <c r="L46" s="12" t="inlineStr">
+      <c r="L46" s="8" t="inlineStr"/>
+      <c r="M46" s="8" t="inlineStr"/>
+      <c r="N46" s="8" t="inlineStr"/>
+      <c r="O46" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -5218,7 +6008,10 @@
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="L47" s="12" t="inlineStr">
+      <c r="L47" s="8" t="inlineStr"/>
+      <c r="M47" s="8" t="inlineStr"/>
+      <c r="N47" s="8" t="inlineStr"/>
+      <c r="O47" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -5276,7 +6069,10 @@
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L48" s="12" t="inlineStr">
+      <c r="L48" s="8" t="inlineStr"/>
+      <c r="M48" s="8" t="inlineStr"/>
+      <c r="N48" s="8" t="inlineStr"/>
+      <c r="O48" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -5334,7 +6130,10 @@
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="L49" s="12" t="inlineStr">
+      <c r="L49" s="8" t="inlineStr"/>
+      <c r="M49" s="8" t="inlineStr"/>
+      <c r="N49" s="8" t="inlineStr"/>
+      <c r="O49" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -5392,64 +6191,67 @@
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="L50" s="12" t="inlineStr">
+      <c r="L50" s="8" t="inlineStr"/>
+      <c r="M50" s="8" t="inlineStr"/>
+      <c r="N50" s="8" t="inlineStr"/>
+      <c r="O50" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L50"/>
+  <autoFilter ref="A1:O50"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/수요예측_일정.xlsx
+++ b/수요예측_일정.xlsx
@@ -1257,7 +1257,11 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
       <c r="O11" s="7" t="inlineStr">
         <is>
           <t>열기</t>
@@ -1878,7 +1882,11 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
       <c r="O20" s="7" t="inlineStr">
         <is>
           <t>열기</t>
@@ -2337,7 +2345,11 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="N27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
       <c r="O27" s="7" t="inlineStr">
         <is>
           <t>열기</t>
@@ -2406,7 +2418,11 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="N28" s="8" t="inlineStr"/>
+      <c r="N28" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="O28" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -2544,7 +2560,11 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="O30" s="7" t="inlineStr">
         <is>
           <t>열기</t>
@@ -3715,7 +3735,11 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
           <t>열기</t>
@@ -4336,7 +4360,11 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
           <t>열기</t>
@@ -4397,7 +4425,11 @@
       </c>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
       <c r="O22" s="7" t="inlineStr">
         <is>
           <t>열기</t>
@@ -4856,7 +4888,11 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="N29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
       <c r="O29" s="7" t="inlineStr">
         <is>
           <t>열기</t>
@@ -4925,7 +4961,11 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="N30" s="8" t="inlineStr"/>
+      <c r="N30" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="O30" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -5185,7 +5225,11 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="N34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="O34" s="7" t="inlineStr">
         <is>
           <t>열기</t>
@@ -5246,7 +5290,11 @@
       </c>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr"/>
-      <c r="N35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
       <c r="O35" s="7" t="inlineStr">
         <is>
           <t>열기</t>
@@ -5307,7 +5355,11 @@
       </c>
       <c r="L36" s="8" t="inlineStr"/>
       <c r="M36" s="8" t="inlineStr"/>
-      <c r="N36" s="8" t="inlineStr"/>
+      <c r="N36" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="O36" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -6010,7 +6062,11 @@
       </c>
       <c r="L47" s="8" t="inlineStr"/>
       <c r="M47" s="8" t="inlineStr"/>
-      <c r="N47" s="8" t="inlineStr"/>
+      <c r="N47" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
       <c r="O47" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -6071,7 +6127,11 @@
       </c>
       <c r="L48" s="8" t="inlineStr"/>
       <c r="M48" s="8" t="inlineStr"/>
-      <c r="N48" s="8" t="inlineStr"/>
+      <c r="N48" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
       <c r="O48" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -6132,7 +6192,11 @@
       </c>
       <c r="L49" s="8" t="inlineStr"/>
       <c r="M49" s="8" t="inlineStr"/>
-      <c r="N49" s="8" t="inlineStr"/>
+      <c r="N49" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
       <c r="O49" s="12" t="inlineStr">
         <is>
           <t>열기</t>

--- a/수요예측_일정.xlsx
+++ b/수요예측_일정.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'수요예측 일정'!$A$1:$O$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체 이력'!$A$1:$O$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체 이력'!$A$1:$O$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2633,7 +2633,11 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="N31" s="8" t="inlineStr"/>
+      <c r="N31" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="O31" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -2702,7 +2706,11 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="N32" s="8" t="inlineStr"/>
+      <c r="N32" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
       <c r="O32" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -2771,7 +2779,11 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="N33" s="8" t="inlineStr"/>
+      <c r="N33" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="O33" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -2840,7 +2852,11 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="N34" s="8" t="inlineStr"/>
+      <c r="N34" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
       <c r="O34" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -2894,7 +2910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:O62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5611,7 +5627,11 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="N40" s="8" t="inlineStr"/>
+      <c r="N40" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="O40" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -5680,7 +5700,11 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="N41" s="8" t="inlineStr"/>
+      <c r="N41" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
       <c r="O41" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -5871,7 +5895,11 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="N44" s="8" t="inlineStr"/>
+      <c r="N44" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="O44" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -5940,7 +5968,11 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="N45" s="8" t="inlineStr"/>
+      <c r="N45" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
       <c r="O45" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -6264,8 +6296,860 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>엠비디</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>물질 검사, 측정 및 분석기구 제조업</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경(수요예측)</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>9,600 ~ 11,700원</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="J51" s="6" t="n">
+        <v>175.5</v>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>한화플러스제6호기업인수목적</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>스팩</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>2,000원 (단일가)</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="J52" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>한화투자증권㈜ 02-3772-7395, 7398, 7393</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="O52" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>아이엠기업인수목적1호</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>스팩</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>2,000원 (단일가)</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="J53" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>아이엠증권 02-2122-9688, 9485</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>크리에이츠</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>15,000 ~ 18,000원</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>1050000</v>
+      </c>
+      <c r="J54" s="6" t="n">
+        <v>189</v>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-7414, 7375, 7651</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="O54" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>인텔리빅스</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경(문의처)</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>7,600 ~ 9,000원</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>1875000</v>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>168.8</v>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="O55" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>다비오</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>[정정제출요구] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경(수요예측)</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>12,300 ~ 16,600원</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>750000</v>
+      </c>
+      <c r="J56" s="6" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>유캐스트</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>기타 무선 통신장비 제조업</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>[정정제출요구] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경(수요예측,밴드)</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>21,000 ~ 26,000원</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>600000</v>
+      </c>
+      <c r="J57" s="6" t="n">
+        <v>156</v>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>바로팜</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>전자상거래 소매 중개업</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경(문의처)</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>16,400 ~ 20,200원</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>1335000</v>
+      </c>
+      <c r="J58" s="6" t="n">
+        <v>269.7</v>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>크리에이츠</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>15,000 ~ 18,000원</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>1050000</v>
+      </c>
+      <c r="J59" s="6" t="n">
+        <v>189</v>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-7414, 7375, 7651</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="O59" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>티앤이코리아</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>산업용 송풍기 및 배기장치 제조업</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경(수요예측)</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>12,600 ~ 15,300원</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="J60" s="6" t="n">
+        <v>275.4</v>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="O60" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>엠비디</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>물질 검사, 측정 및 분석기구 제조업</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경(수요예측,밴드)</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>9,400 ~ 11,500원</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="J61" s="6" t="n">
+        <v>172.5</v>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>래블업</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>시스템 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경(수요예측,밴드)</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>20,000 ~ 23,000원</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>1635000</v>
+      </c>
+      <c r="J62" s="6" t="n">
+        <v>376.1</v>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>NH투자증권 02-768-7462, 7467</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="O62" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O50"/>
+  <autoFilter ref="A1:O62"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -6316,6 +7200,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId61"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/수요예측_일정.xlsx
+++ b/수요예측_일정.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'수요예측 일정'!$A$1:$O$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체 이력'!$A$1:$O$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체 이력'!$A$1:$O$63</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -582,12 +582,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>케이엠에프</t>
+          <t>아델</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -597,43 +597,43 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>정정-변경없음</t>
+          <t>정정-변경(문의처)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>15,000 ~ 17,800원</t>
+          <t>18,000 ~ 25,000원</t>
         </is>
       </c>
       <c r="I2" s="5" t="n">
-        <v>1500000</v>
+        <v>1627500</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>267</v>
+        <v>406.9</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
+          <t>삼성증권 02-2020-8213, 6661</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr"/>
@@ -644,138 +644,138 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>케이엠에프</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>기타 식품 제조업</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>15,000 ~ 17,800원</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="J3" s="6" t="n">
+        <v>267</v>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>우리투자제1호기업인수목적</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>스팩</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>2026-11-25</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>2026-11-26</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>2,000원 (단일가)</t>
         </is>
       </c>
-      <c r="I3" s="10" t="n">
+      <c r="I4" s="10" t="n">
         <v>4875000</v>
       </c>
-      <c r="J3" s="11" t="n">
+      <c r="J4" s="11" t="n">
         <v>97.5</v>
       </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="K4" s="9" t="inlineStr">
         <is>
           <t>우리투자증권 02-6390-3889</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>2026-12-02</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t>2026-12-07</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr"/>
-      <c r="O3" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>제논</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경(수요예측)</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-20</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,700 ~ 12,200원</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>1550000</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>189.1</v>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>삼성증권 02-2020-8023, 7653, 7850</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-24</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-27</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="7" t="inlineStr">
+      <c r="N4" s="8" t="inlineStr"/>
+      <c r="O4" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -784,17 +784,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>동원파츠</t>
+          <t>제논</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>반도체 제조용 기계 제조업</t>
+          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -804,43 +804,43 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>정정-변경없음</t>
+          <t>정정-변경(수요예측)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,000 ~ 26,500원</t>
+          <t>9,700 ~ 12,200원</t>
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>1522500</v>
+        <v>1550000</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>403.5</v>
+        <v>189.1</v>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-6975, 8217, 7651</t>
+          <t>삼성증권 02-2020-8023, 7653, 7850</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr"/>
@@ -851,69 +851,69 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>동원파츠</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>반도체 제조용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>인터엑스</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-04</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>10,000 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I6" s="10" t="n">
-        <v>2250000</v>
-      </c>
-      <c r="J6" s="11" t="n">
-        <v>292.5</v>
-      </c>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5700, 6648</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-09</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-14</t>
-        </is>
-      </c>
-      <c r="N6" s="8" t="inlineStr"/>
-      <c r="O6" s="12" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>23,000 ~ 26,500원</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>1522500</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>403.5</v>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-6975, 8217, 7651</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -922,22 +922,22 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>유캐스트</t>
+          <t>인터엑스</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>기타 무선 통신장비 제조업</t>
+          <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -947,38 +947,38 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>19,000 ~ 23,000원</t>
+          <t>10,000 ~ 13,000원</t>
         </is>
       </c>
       <c r="I7" s="10" t="n">
-        <v>600000</v>
+        <v>2250000</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>138</v>
+        <v>292.5</v>
       </c>
       <c r="K7" s="9" t="inlineStr">
         <is>
-          <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
+          <t>한국투자증권㈜ 02-3276-5700, 6648</t>
         </is>
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="N7" s="8" t="inlineStr"/>
@@ -989,138 +989,138 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>유캐스트</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>기타 무선 통신장비 제조업</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>19,000 ~ 23,000원</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>600000</v>
+      </c>
+      <c r="J8" s="11" t="n">
+        <v>138</v>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr"/>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>옵토닉스</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>광학렌즈 및 광학요소 제조업</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>10,000 ~ 12,000원</t>
         </is>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="I9" s="5" t="n">
         <v>1572490</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J9" s="6" t="n">
         <v>188.7</v>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>2026-11-05</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>이노보테라퓨틱스</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-02</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>20,000 ~ 24,000원</t>
-        </is>
-      </c>
-      <c r="I9" s="10" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="J9" s="11" t="n">
-        <v>396</v>
-      </c>
-      <c r="K9" s="9" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
-        </is>
-      </c>
-      <c r="L9" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-07</t>
-        </is>
-      </c>
-      <c r="M9" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-10</t>
-        </is>
-      </c>
-      <c r="N9" s="8" t="inlineStr"/>
-      <c r="O9" s="12" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1129,17 +1129,17 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>에이엔에이치스트럭쳐</t>
+          <t>이노보테라퓨틱스</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>기타 엔지니어링 서비스업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -1154,38 +1154,38 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>11,200 ~ 13,600원</t>
+          <t>20,000 ~ 24,000원</t>
         </is>
       </c>
       <c r="I10" s="10" t="n">
-        <v>1575000</v>
+        <v>1650000</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>214.2</v>
+        <v>396</v>
       </c>
       <c r="K10" s="9" t="inlineStr">
         <is>
-          <t>NH투자증권 02-2229-6315, 6829</t>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="M10" s="8" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="N10" s="8" t="inlineStr"/>
@@ -1196,142 +1196,142 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>에이엔에이치스트럭쳐</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>기타 엔지니어링 서비스업</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>11,200 ~ 13,600원</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>1575000</v>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>214.2</v>
+      </c>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>NH투자증권 02-2229-6315, 6829</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="N11" s="8" t="inlineStr"/>
+      <c r="O11" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>이에스티</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>그 외 기타 전자부품 제조업</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>10,600 ~ 12,400원</t>
         </is>
       </c>
-      <c r="I11" s="5" t="n">
+      <c r="I12" s="5" t="n">
         <v>1650000</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J12" s="6" t="n">
         <v>204.6</v>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>2026-11-04</t>
         </is>
       </c>
-      <c r="O11" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>에스에프씨</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>그 외 기타 분류 안된 화학제품 제조업</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>31,600 ~ 36,100원</t>
-        </is>
-      </c>
-      <c r="I12" s="10" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J12" s="11" t="n">
-        <v>1353.8</v>
-      </c>
-      <c r="K12" s="9" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
-        </is>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-      <c r="N12" s="8" t="inlineStr"/>
-      <c r="O12" s="12" t="inlineStr">
+      <c r="O12" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>씨아이에스케미칼</t>
+          <t>에스에프씨</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>알루미늄 제련, 정련 및 합금 제조업</t>
+          <t>그 외 기타 분류 안된 화학제품 제조업</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -1365,38 +1365,38 @@
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>5,400 ~ 6,800원</t>
+          <t>31,600 ~ 36,100원</t>
         </is>
       </c>
       <c r="I13" s="10" t="n">
-        <v>3000000</v>
+        <v>3750000</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>204</v>
+        <v>1353.8</v>
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
+          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="M13" s="8" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="N13" s="8" t="inlineStr"/>
@@ -1409,17 +1409,17 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>제이앤티지</t>
+          <t>씨아이에스케미칼</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>그 외 자동차용 신품 부품 제조업</t>
+          <t>알루미늄 제련, 정련 및 합금 제조업</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
@@ -1434,38 +1434,38 @@
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>26,400 ~ 31,900원</t>
+          <t>5,400 ~ 6,800원</t>
         </is>
       </c>
       <c r="I14" s="10" t="n">
-        <v>3182000</v>
+        <v>3000000</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>1015.1</v>
+        <v>204</v>
       </c>
       <c r="K14" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
+          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="N14" s="8" t="inlineStr"/>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>씨앤엠</t>
+          <t>제이앤티지</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>전동기 및 발전기 제조업</t>
+          <t>그 외 자동차용 신품 부품 제조업</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -1513,18 +1513,18 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>10,000 ~ 13,000원</t>
+          <t>26,400 ~ 31,900원</t>
         </is>
       </c>
       <c r="I15" s="10" t="n">
-        <v>2059500</v>
+        <v>3182000</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>267.7</v>
+        <v>1015.1</v>
       </c>
       <c r="K15" s="9" t="inlineStr">
         <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
         </is>
       </c>
       <c r="L15" s="8" t="inlineStr">
@@ -1545,69 +1545,69 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>넥스아이</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>10,500 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J16" s="6" t="n">
-        <v>487.5</v>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>씨앤엠</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>전동기 및 발전기 제조업</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="7" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>10,000 ~ 13,000원</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>2059500</v>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>267.7</v>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+        </is>
+      </c>
+      <c r="L16" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M16" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N16" s="8" t="inlineStr"/>
+      <c r="O16" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1621,12 +1621,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>항공기용 부품 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -1641,38 +1641,38 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>10,500 ~ 13,000원</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>487.5</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
           <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>4,700 ~ 5,700원</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>3300000</v>
-      </c>
-      <c r="J17" s="6" t="n">
-        <v>188.1</v>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr"/>
@@ -1685,17 +1685,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>바로팜</t>
+          <t>하나에어로다이내믹스</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>전자상거래 소매 중개업</t>
+          <t>항공기용 부품 제조업</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1710,38 +1710,38 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,400 ~ 20,200원</t>
+          <t>4,700 ~ 5,700원</t>
         </is>
       </c>
       <c r="I18" s="5" t="n">
-        <v>1335000</v>
+        <v>3300000</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>269.7</v>
+        <v>188.1</v>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr"/>
@@ -1752,142 +1752,138 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>바로팜</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>전자상거래 소매 중개업</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>16,400 ~ 20,200원</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>1335000</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>269.7</v>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>엠비디</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>물질 검사, 측정 및 분석기구 제조업</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>9,600 ~ 11,700원</t>
         </is>
       </c>
-      <c r="I19" s="10" t="n">
+      <c r="I20" s="10" t="n">
         <v>1500000</v>
       </c>
-      <c r="J19" s="11" t="n">
+      <c r="J20" s="11" t="n">
         <v>175.5</v>
       </c>
-      <c r="K19" s="9" t="inlineStr">
+      <c r="K20" s="9" t="inlineStr">
         <is>
           <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
         </is>
       </c>
-      <c r="L19" s="8" t="inlineStr">
+      <c r="L20" s="8" t="inlineStr">
         <is>
           <t>2026-11-12</t>
         </is>
       </c>
-      <c r="M19" s="8" t="inlineStr">
+      <c r="M20" s="8" t="inlineStr">
         <is>
           <t>2026-11-17</t>
         </is>
       </c>
-      <c r="N19" s="8" t="inlineStr"/>
-      <c r="O19" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>래블업</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>시스템 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>19,000 ~ 22,000원</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="n">
-        <v>1635000</v>
-      </c>
-      <c r="J20" s="6" t="n">
-        <v>359.7</v>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>NH투자증권 02-768-7462, 7467</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="O20" s="7" t="inlineStr">
+      <c r="N20" s="8" t="inlineStr"/>
+      <c r="O20" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1896,136 +1892,140 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>래블업</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>시스템 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>19,000 ~ 22,000원</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>1635000</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>359.7</v>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>NH투자증권 02-768-7462, 7467</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>에이엘로봇</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>기타 기계 및 장비 제조업</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>정정-변경(수요예측)</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>15,700 ~ 17,600원</t>
         </is>
       </c>
-      <c r="I21" s="5" t="n">
+      <c r="I22" s="5" t="n">
         <v>1800000</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="J22" s="6" t="n">
         <v>316.8</v>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>2026-11-11</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr"/>
-      <c r="O21" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>아델</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>18,000 ~ 25,000원</t>
-        </is>
-      </c>
-      <c r="I22" s="10" t="n">
-        <v>1627500</v>
-      </c>
-      <c r="J22" s="11" t="n">
-        <v>406.9</v>
-      </c>
-      <c r="K22" s="9" t="inlineStr">
-        <is>
-          <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
-        </is>
-      </c>
-      <c r="L22" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-      <c r="M22" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="N22" s="8" t="inlineStr"/>
-      <c r="O22" s="12" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2910,7 +2910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O62"/>
+  <dimension ref="A1:O63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3015,12 +3015,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>케이엠에프</t>
+          <t>아델</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -3030,43 +3030,43 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>정정-변경없음</t>
+          <t>정정-변경(문의처)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>15,000 ~ 17,800원</t>
+          <t>18,000 ~ 25,000원</t>
         </is>
       </c>
       <c r="I2" s="5" t="n">
-        <v>1500000</v>
+        <v>1627500</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>267</v>
+        <v>406.9</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
+          <t>삼성증권 02-2020-8213, 6661</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr"/>
@@ -3077,138 +3077,138 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>케이엠에프</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>기타 식품 제조업</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>15,000 ~ 17,800원</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="J3" s="6" t="n">
+        <v>267</v>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>우리투자제1호기업인수목적</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>스팩</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>2026-11-25</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>2026-11-26</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>2,000원 (단일가)</t>
         </is>
       </c>
-      <c r="I3" s="10" t="n">
+      <c r="I4" s="10" t="n">
         <v>4875000</v>
       </c>
-      <c r="J3" s="11" t="n">
+      <c r="J4" s="11" t="n">
         <v>97.5</v>
       </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="K4" s="9" t="inlineStr">
         <is>
           <t>우리투자증권 02-6390-3889</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>2026-12-02</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t>2026-12-07</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr"/>
-      <c r="O3" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>제논</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경(수요예측)</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-20</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,700 ~ 12,200원</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>1550000</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>189.1</v>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>삼성증권 02-2020-8023, 7653, 7850</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-24</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-27</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="7" t="inlineStr">
+      <c r="N4" s="8" t="inlineStr"/>
+      <c r="O4" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3217,7 +3217,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -3237,17 +3237,17 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>정정-변경없음</t>
+          <t>정정-변경(수요예측)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -3266,8 +3266,16 @@
           <t>삼성증권 02-2020-8023, 7653, 7850</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="7" t="inlineStr">
         <is>
@@ -3283,12 +3291,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>동원파츠</t>
+          <t>제논</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>반도체 제조용 기계 제조업</t>
+          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -3303,40 +3311,32 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,000 ~ 26,500원</t>
+          <t>9,700 ~ 12,200원</t>
         </is>
       </c>
       <c r="I6" s="5" t="n">
-        <v>1522500</v>
+        <v>1550000</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>403.5</v>
+        <v>189.1</v>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-6975, 8217, 7651</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
+          <t>삼성증권 02-2020-8023, 7653, 7850</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="7" t="inlineStr">
         <is>
@@ -3345,69 +3345,69 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>동원파츠</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>반도체 제조용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>인터엑스</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-04</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>10,000 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I7" s="10" t="n">
-        <v>2250000</v>
-      </c>
-      <c r="J7" s="11" t="n">
-        <v>292.5</v>
-      </c>
-      <c r="K7" s="9" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5700, 6648</t>
-        </is>
-      </c>
-      <c r="L7" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-09</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-14</t>
-        </is>
-      </c>
-      <c r="N7" s="8" t="inlineStr"/>
-      <c r="O7" s="12" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>23,000 ~ 26,500원</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>1522500</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>403.5</v>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-6975, 8217, 7651</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3416,22 +3416,22 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>유캐스트</t>
+          <t>인터엑스</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>기타 무선 통신장비 제조업</t>
+          <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -3441,38 +3441,38 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>19,000 ~ 23,000원</t>
+          <t>10,000 ~ 13,000원</t>
         </is>
       </c>
       <c r="I8" s="10" t="n">
-        <v>600000</v>
+        <v>2250000</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>138</v>
+        <v>292.5</v>
       </c>
       <c r="K8" s="9" t="inlineStr">
         <is>
-          <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
+          <t>한국투자증권㈜ 02-3276-5700, 6648</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="N8" s="8" t="inlineStr"/>
@@ -3483,138 +3483,138 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>유캐스트</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>기타 무선 통신장비 제조업</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>19,000 ~ 23,000원</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>600000</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>138</v>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="N9" s="8" t="inlineStr"/>
+      <c r="O9" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>옵토닉스</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>광학렌즈 및 광학요소 제조업</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>10,000 ~ 12,000원</t>
         </is>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="I10" s="5" t="n">
         <v>1572490</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J10" s="6" t="n">
         <v>188.7</v>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>2026-11-05</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>이노보테라퓨틱스</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-02</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>20,000 ~ 24,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="10" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="J10" s="11" t="n">
-        <v>396</v>
-      </c>
-      <c r="K10" s="9" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
-        </is>
-      </c>
-      <c r="L10" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-07</t>
-        </is>
-      </c>
-      <c r="M10" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-10</t>
-        </is>
-      </c>
-      <c r="N10" s="8" t="inlineStr"/>
-      <c r="O10" s="12" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3623,17 +3623,17 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>에이엔에이치스트럭쳐</t>
+          <t>이노보테라퓨틱스</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>기타 엔지니어링 서비스업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -3648,38 +3648,38 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>11,200 ~ 13,600원</t>
+          <t>20,000 ~ 24,000원</t>
         </is>
       </c>
       <c r="I11" s="10" t="n">
-        <v>1575000</v>
+        <v>1650000</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>214.2</v>
+        <v>396</v>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>NH투자증권 02-2229-6315, 6829</t>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="N11" s="8" t="inlineStr"/>
@@ -3690,142 +3690,142 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>에이엔에이치스트럭쳐</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>기타 엔지니어링 서비스업</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>11,200 ~ 13,600원</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>1575000</v>
+      </c>
+      <c r="J12" s="11" t="n">
+        <v>214.2</v>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>NH투자증권 02-2229-6315, 6829</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="N12" s="8" t="inlineStr"/>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>이에스티</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>그 외 기타 전자부품 제조업</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>10,600 ~ 12,400원</t>
         </is>
       </c>
-      <c r="I12" s="5" t="n">
+      <c r="I13" s="5" t="n">
         <v>1650000</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="J13" s="6" t="n">
         <v>204.6</v>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2026-11-04</t>
         </is>
       </c>
-      <c r="O12" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>에스에프씨</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>그 외 기타 분류 안된 화학제품 제조업</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>31,600 ~ 36,100원</t>
-        </is>
-      </c>
-      <c r="I13" s="10" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J13" s="11" t="n">
-        <v>1353.8</v>
-      </c>
-      <c r="K13" s="9" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
-        </is>
-      </c>
-      <c r="L13" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="M13" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-      <c r="N13" s="8" t="inlineStr"/>
-      <c r="O13" s="12" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3839,12 +3839,12 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>씨아이에스케미칼</t>
+          <t>에스에프씨</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>알루미늄 제련, 정련 및 합금 제조업</t>
+          <t>그 외 기타 분류 안된 화학제품 제조업</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
@@ -3859,38 +3859,38 @@
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>5,400 ~ 6,800원</t>
+          <t>31,600 ~ 36,100원</t>
         </is>
       </c>
       <c r="I14" s="10" t="n">
-        <v>3000000</v>
+        <v>3750000</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>204</v>
+        <v>1353.8</v>
       </c>
       <c r="K14" s="9" t="inlineStr">
         <is>
-          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
+          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
         </is>
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="N14" s="8" t="inlineStr"/>
@@ -3903,17 +3903,17 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>제이앤티지</t>
+          <t>씨아이에스케미칼</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>그 외 자동차용 신품 부품 제조업</t>
+          <t>알루미늄 제련, 정련 및 합금 제조업</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -3928,38 +3928,38 @@
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>26,400 ~ 31,900원</t>
+          <t>5,400 ~ 6,800원</t>
         </is>
       </c>
       <c r="I15" s="10" t="n">
-        <v>3182000</v>
+        <v>3000000</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>1015.1</v>
+        <v>204</v>
       </c>
       <c r="K15" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
+          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="M15" s="8" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="N15" s="8" t="inlineStr"/>
@@ -3977,12 +3977,12 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>씨앤엠</t>
+          <t>제이앤티지</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>전동기 및 발전기 제조업</t>
+          <t>그 외 자동차용 신품 부품 제조업</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -4007,18 +4007,18 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>10,000 ~ 13,000원</t>
+          <t>26,400 ~ 31,900원</t>
         </is>
       </c>
       <c r="I16" s="10" t="n">
-        <v>2059500</v>
+        <v>3182000</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>267.7</v>
+        <v>1015.1</v>
       </c>
       <c r="K16" s="9" t="inlineStr">
         <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
         </is>
       </c>
       <c r="L16" s="8" t="inlineStr">
@@ -4039,69 +4039,69 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>넥스아이</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>10,500 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J17" s="6" t="n">
-        <v>487.5</v>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>씨앤엠</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>전동기 및 발전기 제조업</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
-      <c r="O17" s="7" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>10,000 ~ 13,000원</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="n">
+        <v>2059500</v>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>267.7</v>
+      </c>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+        </is>
+      </c>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N17" s="8" t="inlineStr"/>
+      <c r="O17" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4115,12 +4115,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>항공기용 부품 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -4135,38 +4135,38 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>10,500 ~ 13,000원</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>487.5</v>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
           <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>4,700 ~ 5,700원</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>3300000</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>188.1</v>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr"/>
@@ -4179,17 +4179,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>바로팜</t>
+          <t>하나에어로다이내믹스</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>전자상거래 소매 중개업</t>
+          <t>항공기용 부품 제조업</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -4204,38 +4204,38 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,400 ~ 20,200원</t>
+          <t>4,700 ~ 5,700원</t>
         </is>
       </c>
       <c r="I19" s="5" t="n">
-        <v>1335000</v>
+        <v>3300000</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>269.7</v>
+        <v>188.1</v>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr"/>
@@ -4246,142 +4246,138 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>바로팜</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>전자상거래 소매 중개업</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>16,400 ~ 20,200원</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>1335000</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>269.7</v>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>엠비디</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>물질 검사, 측정 및 분석기구 제조업</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>9,600 ~ 11,700원</t>
         </is>
       </c>
-      <c r="I20" s="10" t="n">
+      <c r="I21" s="10" t="n">
         <v>1500000</v>
       </c>
-      <c r="J20" s="11" t="n">
+      <c r="J21" s="11" t="n">
         <v>175.5</v>
       </c>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="K21" s="9" t="inlineStr">
         <is>
           <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
         </is>
       </c>
-      <c r="L20" s="8" t="inlineStr">
+      <c r="L21" s="8" t="inlineStr">
         <is>
           <t>2026-11-12</t>
         </is>
       </c>
-      <c r="M20" s="8" t="inlineStr">
+      <c r="M21" s="8" t="inlineStr">
         <is>
           <t>2026-11-17</t>
         </is>
       </c>
-      <c r="N20" s="8" t="inlineStr"/>
-      <c r="O20" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>래블업</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>시스템 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>19,000 ~ 22,000원</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="n">
-        <v>1635000</v>
-      </c>
-      <c r="J21" s="6" t="n">
-        <v>359.7</v>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>NH투자증권 02-768-7462, 7467</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="O21" s="7" t="inlineStr">
+      <c r="N21" s="8" t="inlineStr"/>
+      <c r="O21" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4390,60 +4386,68 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>래블업</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>시스템 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>이에스티</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>그 외 기타 전자부품 제조업</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,600 ~ 12,400원</t>
+          <t>19,000 ~ 22,000원</t>
         </is>
       </c>
       <c r="I22" s="5" t="n">
-        <v>1650000</v>
+        <v>1635000</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>204.6</v>
+        <v>359.7</v>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>NH투자증권 02-768-7462, 7467</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="O22" s="7" t="inlineStr">
@@ -4455,136 +4459,132 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>이에스티</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>그 외 기타 전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>10,600 ~ 12,400원</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>204.6</v>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>에이엘로봇</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>기타 기계 및 장비 제조업</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>정정-변경(수요예측)</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>15,700 ~ 17,600원</t>
         </is>
       </c>
-      <c r="I23" s="5" t="n">
+      <c r="I24" s="5" t="n">
         <v>1800000</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="J24" s="6" t="n">
         <v>316.8</v>
       </c>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="K24" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>2026-11-11</t>
         </is>
       </c>
-      <c r="N23" s="2" t="inlineStr"/>
-      <c r="O23" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>아델</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>18,000 ~ 25,000원</t>
-        </is>
-      </c>
-      <c r="I24" s="10" t="n">
-        <v>1627500</v>
-      </c>
-      <c r="J24" s="11" t="n">
-        <v>406.9</v>
-      </c>
-      <c r="K24" s="9" t="inlineStr">
-        <is>
-          <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
-        </is>
-      </c>
-      <c r="L24" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-      <c r="M24" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="N24" s="8" t="inlineStr"/>
-      <c r="O24" s="12" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>SimwonAmericaCorp.</t>
+          <t>아델</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>자동차 신품 부품 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
@@ -4613,19 +4613,43 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>수요예측 항목 없음(원문 확인)</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr"/>
-      <c r="G25" s="8" t="inlineStr"/>
-      <c r="H25" s="8" t="inlineStr"/>
-      <c r="I25" s="10" t="inlineStr"/>
-      <c r="J25" s="11" t="inlineStr"/>
-      <c r="K25" s="9" t="inlineStr"/>
-      <c r="L25" s="8" t="inlineStr"/>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>18,000 ~ 25,000원</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="n">
+        <v>1627500</v>
+      </c>
+      <c r="J25" s="11" t="n">
+        <v>406.9</v>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr"/>
@@ -4638,63 +4662,39 @@
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>다비오</t>
+          <t>SimwonAmericaCorp.</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
+          <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>12,300 ~ 16,600원</t>
-        </is>
-      </c>
-      <c r="I26" s="10" t="n">
-        <v>750000</v>
-      </c>
-      <c r="J26" s="11" t="n">
-        <v>124.5</v>
-      </c>
-      <c r="K26" s="9" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
-        </is>
-      </c>
-      <c r="L26" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
+          <t>수요예측 항목 없음(원문 확인)</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr"/>
+      <c r="G26" s="8" t="inlineStr"/>
+      <c r="H26" s="8" t="inlineStr"/>
+      <c r="I26" s="10" t="inlineStr"/>
+      <c r="J26" s="11" t="inlineStr"/>
+      <c r="K26" s="9" t="inlineStr"/>
+      <c r="L26" s="8" t="inlineStr"/>
       <c r="M26" s="8" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="N26" s="8" t="inlineStr"/>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>엔키화이트햇</t>
+          <t>다비오</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -4732,38 +4732,38 @@
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>13,000 ~ 16,500원</t>
+          <t>12,300 ~ 16,600원</t>
         </is>
       </c>
       <c r="I27" s="10" t="n">
-        <v>1258000</v>
+        <v>750000</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>207.6</v>
+        <v>124.5</v>
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
+          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
         </is>
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="M27" s="8" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="N27" s="8" t="inlineStr"/>
@@ -4781,12 +4781,12 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>영광와이케이엠씨</t>
+          <t>엔키화이트햇</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>그 외 기타 금속가공업</t>
+          <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
@@ -4801,38 +4801,38 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>9,400 ~ 11,000원</t>
+          <t>13,000 ~ 16,500원</t>
         </is>
       </c>
       <c r="I28" s="10" t="n">
-        <v>1694840</v>
+        <v>1258000</v>
       </c>
       <c r="J28" s="11" t="n">
-        <v>186.4</v>
+        <v>207.6</v>
       </c>
       <c r="K28" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
+          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
         </is>
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="M28" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="N28" s="8" t="inlineStr"/>
@@ -4843,276 +4843,284 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>영광와이케이엠씨</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>그 외 기타 금속가공업</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>9,400 ~ 11,000원</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="n">
+        <v>1694840</v>
+      </c>
+      <c r="J29" s="11" t="n">
+        <v>186.4</v>
+      </c>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
+        </is>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="M29" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="N29" s="8" t="inlineStr"/>
+      <c r="O29" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>영광</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>수상 금속 골조 구조재 제조업</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>14,000 ~ 17,000원</t>
         </is>
       </c>
-      <c r="I29" s="5" t="n">
+      <c r="I30" s="5" t="n">
         <v>1695000</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="J30" s="6" t="n">
         <v>288.1</v>
       </c>
-      <c r="K29" s="3" t="inlineStr">
+      <c r="K30" s="3" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="O29" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="O30" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>인텔리빅스</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>7,600 ~ 9,000원</t>
         </is>
       </c>
-      <c r="I30" s="10" t="n">
+      <c r="I31" s="10" t="n">
         <v>1875000</v>
       </c>
-      <c r="J30" s="11" t="n">
+      <c r="J31" s="11" t="n">
         <v>168.8</v>
       </c>
-      <c r="K30" s="9" t="inlineStr">
+      <c r="K31" s="9" t="inlineStr">
         <is>
           <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L30" s="8" t="inlineStr">
+      <c r="L31" s="8" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="M30" s="8" t="inlineStr">
+      <c r="M31" s="8" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="N30" s="8" t="inlineStr">
+      <c r="N31" s="8" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="O30" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="O31" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>아이엠기업인수목적1호</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>스팩</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>2,000원 (단일가)</t>
         </is>
       </c>
-      <c r="I31" s="5" t="n">
+      <c r="I32" s="5" t="n">
         <v>3750000</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="J32" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="K31" s="3" t="inlineStr">
+      <c r="K32" s="3" t="inlineStr">
         <is>
           <t>아이엠증권 02-2122-9688, 9485</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N31" s="2" t="inlineStr"/>
-      <c r="O31" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>아이엠기업인수목적1호</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>스팩</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="H32" s="8" t="inlineStr">
-        <is>
-          <t>2,000원 (단일가)</t>
-        </is>
-      </c>
-      <c r="I32" s="10" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J32" s="11" t="n">
-        <v>75</v>
-      </c>
-      <c r="K32" s="9" t="inlineStr">
-        <is>
-          <t>아이엠증권 02-2122-9688, 9485</t>
-        </is>
-      </c>
-      <c r="L32" s="8" t="inlineStr"/>
-      <c r="M32" s="8" t="inlineStr"/>
-      <c r="N32" s="8" t="inlineStr"/>
-      <c r="O32" s="12" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -5121,22 +5129,22 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>제논</t>
+          <t>아이엠기업인수목적1호</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
+          <t>스팩</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -5146,28 +5154,28 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>9,700 ~ 12,200원</t>
+          <t>2,000원 (단일가)</t>
         </is>
       </c>
       <c r="I33" s="10" t="n">
-        <v>1550000</v>
+        <v>3750000</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>189.1</v>
+        <v>75</v>
       </c>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-8023, 7653, 7850</t>
+          <t>아이엠증권 02-2122-9688, 9485</t>
         </is>
       </c>
       <c r="L33" s="8" t="inlineStr"/>
@@ -5180,73 +5188,61 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>한화플러스제6호기업인수목적</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>스팩</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>2,000원 (단일가)</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="J34" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>한화투자증권㈜ 02-3772-7395, 7398, 7393</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>제논</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="O34" s="7" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>9,700 ~ 12,200원</t>
+        </is>
+      </c>
+      <c r="I34" s="10" t="n">
+        <v>1550000</v>
+      </c>
+      <c r="J34" s="11" t="n">
+        <v>189.1</v>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-8023, 7653, 7850</t>
+        </is>
+      </c>
+      <c r="L34" s="8" t="inlineStr"/>
+      <c r="M34" s="8" t="inlineStr"/>
+      <c r="N34" s="8" t="inlineStr"/>
+      <c r="O34" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -5255,128 +5251,136 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>한화플러스제6호기업인수목적</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>스팩</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>2,000원 (단일가)</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>한화투자증권㈜ 02-3772-7395, 7398, 7393</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="O35" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>래블업</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>시스템 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>19,000 ~ 22,000원</t>
         </is>
       </c>
-      <c r="I35" s="5" t="n">
+      <c r="I36" s="5" t="n">
         <v>1635000</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="J36" s="6" t="n">
         <v>359.7</v>
       </c>
-      <c r="K35" s="3" t="inlineStr">
+      <c r="K36" s="3" t="inlineStr">
         <is>
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr"/>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="O35" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>한화플러스제6호기업인수목적</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>스팩</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="H36" s="8" t="inlineStr">
-        <is>
-          <t>2,000원 (단일가)</t>
-        </is>
-      </c>
-      <c r="I36" s="10" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="J36" s="11" t="n">
-        <v>90</v>
-      </c>
-      <c r="K36" s="9" t="inlineStr">
-        <is>
-          <t>한화투자증권㈜ 02-3772-7395, 7398, 7393</t>
-        </is>
-      </c>
-      <c r="L36" s="8" t="inlineStr"/>
-      <c r="M36" s="8" t="inlineStr"/>
-      <c r="N36" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="O36" s="12" t="inlineStr">
+      <c r="O36" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -5385,22 +5389,22 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>케이엠에프</t>
+          <t>한화플러스제6호기업인수목적</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>스팩</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -5410,33 +5414,37 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>15,000 ~ 17,800원</t>
+          <t>2,000원 (단일가)</t>
         </is>
       </c>
       <c r="I37" s="10" t="n">
-        <v>1500000</v>
+        <v>4500000</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>267</v>
+        <v>90</v>
       </c>
       <c r="K37" s="9" t="inlineStr">
         <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
+          <t>한화투자증권㈜ 02-3772-7395, 7398, 7393</t>
         </is>
       </c>
       <c r="L37" s="8" t="inlineStr"/>
       <c r="M37" s="8" t="inlineStr"/>
-      <c r="N37" s="8" t="inlineStr"/>
+      <c r="N37" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="O37" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -5446,22 +5454,22 @@
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>바로팜</t>
+          <t>케이엠에프</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>전자상거래 소매 중개업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
@@ -5471,28 +5479,28 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>16,400 ~ 20,200원</t>
+          <t>15,000 ~ 17,800원</t>
         </is>
       </c>
       <c r="I38" s="10" t="n">
-        <v>1335000</v>
+        <v>1500000</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>269.7</v>
+        <v>267</v>
       </c>
       <c r="K38" s="9" t="inlineStr">
         <is>
-          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
         </is>
       </c>
       <c r="L38" s="8" t="inlineStr"/>
@@ -5512,17 +5520,17 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>동원파츠</t>
+          <t>바로팜</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>반도체 제조용 기계 제조업</t>
+          <t>전자상거래 소매 중개업</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -5542,18 +5550,18 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>23,000 ~ 26,500원</t>
+          <t>16,400 ~ 20,200원</t>
         </is>
       </c>
       <c r="I39" s="10" t="n">
-        <v>1522500</v>
+        <v>1335000</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>403.5</v>
+        <v>269.7</v>
       </c>
       <c r="K39" s="9" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-6975, 8217, 7651</t>
+          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
       <c r="L39" s="8" t="inlineStr"/>
@@ -5573,17 +5581,17 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>디티에스</t>
+          <t>동원파츠</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>반도체 제조용 기계 제조업</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
@@ -5593,45 +5601,33 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>17,000 ~ 18,500원</t>
+          <t>23,000 ~ 26,500원</t>
         </is>
       </c>
       <c r="I40" s="10" t="n">
-        <v>1671687</v>
+        <v>1522500</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>309.3</v>
+        <v>403.5</v>
       </c>
       <c r="K40" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
-        </is>
-      </c>
-      <c r="L40" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="M40" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="N40" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
+          <t>삼성증권 02-2020-6975, 8217, 7651</t>
+        </is>
+      </c>
+      <c r="L40" s="8" t="inlineStr"/>
+      <c r="M40" s="8" t="inlineStr"/>
+      <c r="N40" s="8" t="inlineStr"/>
       <c r="O40" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -5641,17 +5637,17 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>엠에스바이오</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>그 외 기타 의료용 기기 제조업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
@@ -5666,43 +5662,43 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>6,800 ~ 7,800원</t>
+          <t>17,000 ~ 18,500원</t>
         </is>
       </c>
       <c r="I41" s="10" t="n">
-        <v>2840000</v>
+        <v>1671687</v>
       </c>
       <c r="J41" s="11" t="n">
-        <v>221.5</v>
+        <v>309.3</v>
       </c>
       <c r="K41" s="9" t="inlineStr">
         <is>
-          <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
+          <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
         </is>
       </c>
       <c r="L41" s="8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="M41" s="8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="N41" s="8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="O41" s="12" t="inlineStr">
@@ -5719,17 +5715,17 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>옵토닉스</t>
+          <t>엠에스바이오</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>광학렌즈 및 광학요소 제조업</t>
+          <t>그 외 기타 의료용 기기 제조업</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
@@ -5739,33 +5735,45 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>10,000 ~ 12,000원</t>
+          <t>6,800 ~ 7,800원</t>
         </is>
       </c>
       <c r="I42" s="10" t="n">
-        <v>1572490</v>
+        <v>2840000</v>
       </c>
       <c r="J42" s="11" t="n">
-        <v>188.7</v>
+        <v>221.5</v>
       </c>
       <c r="K42" s="9" t="inlineStr">
         <is>
-          <t>한국투자증권 02-3276-5958, 6269</t>
-        </is>
-      </c>
-      <c r="L42" s="8" t="inlineStr"/>
-      <c r="M42" s="8" t="inlineStr"/>
-      <c r="N42" s="8" t="inlineStr"/>
+          <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
+        </is>
+      </c>
+      <c r="L42" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M42" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="N42" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
       <c r="O42" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -5775,17 +5783,17 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>넥스아이</t>
+          <t>옵토닉스</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>의학 및 약학 연구개발업</t>
+          <t>광학렌즈 및 광학요소 제조업</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
@@ -5800,28 +5808,28 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>10,500 ~ 13,000원</t>
+          <t>10,000 ~ 12,000원</t>
         </is>
       </c>
       <c r="I43" s="10" t="n">
-        <v>3750000</v>
+        <v>1572490</v>
       </c>
       <c r="J43" s="11" t="n">
-        <v>487.5</v>
+        <v>188.7</v>
       </c>
       <c r="K43" s="9" t="inlineStr">
         <is>
-          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
+          <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
       <c r="L43" s="8" t="inlineStr"/>
@@ -5841,17 +5849,17 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
@@ -5861,45 +5869,33 @@
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>15,000 ~ 18,000원</t>
+          <t>10,500 ~ 13,000원</t>
         </is>
       </c>
       <c r="I44" s="10" t="n">
-        <v>1050000</v>
+        <v>3750000</v>
       </c>
       <c r="J44" s="11" t="n">
-        <v>189</v>
+        <v>487.5</v>
       </c>
       <c r="K44" s="9" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-7414, 7375, 7651</t>
-        </is>
-      </c>
-      <c r="L44" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="M44" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="N44" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
+          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
+        </is>
+      </c>
+      <c r="L44" s="8" t="inlineStr"/>
+      <c r="M44" s="8" t="inlineStr"/>
+      <c r="N44" s="8" t="inlineStr"/>
       <c r="O44" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -5909,17 +5905,17 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>티앤이코리아</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>산업용 송풍기 및 배기장치 제조업</t>
+          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
@@ -5934,28 +5930,28 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>12,600 ~ 15,300원</t>
+          <t>15,000 ~ 18,000원</t>
         </is>
       </c>
       <c r="I45" s="10" t="n">
-        <v>1800000</v>
+        <v>1050000</v>
       </c>
       <c r="J45" s="11" t="n">
-        <v>275.4</v>
+        <v>189</v>
       </c>
       <c r="K45" s="9" t="inlineStr">
         <is>
-          <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
+          <t>삼성증권 02-2020-7414, 7375, 7651</t>
         </is>
       </c>
       <c r="L45" s="8" t="inlineStr">
@@ -5970,7 +5966,7 @@
       </c>
       <c r="N45" s="8" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="O45" s="12" t="inlineStr">
@@ -5982,22 +5978,22 @@
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>티앤이코리아</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>항공기용 부품 제조업</t>
+          <t>산업용 송풍기 및 배기장치 제조업</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
@@ -6007,33 +6003,45 @@
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>4,700 ~ 5,700원</t>
+          <t>12,600 ~ 15,300원</t>
         </is>
       </c>
       <c r="I46" s="10" t="n">
-        <v>3300000</v>
+        <v>1800000</v>
       </c>
       <c r="J46" s="11" t="n">
-        <v>188.1</v>
+        <v>275.4</v>
       </c>
       <c r="K46" s="9" t="inlineStr">
         <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
-        </is>
-      </c>
-      <c r="L46" s="8" t="inlineStr"/>
-      <c r="M46" s="8" t="inlineStr"/>
-      <c r="N46" s="8" t="inlineStr"/>
+          <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
+        </is>
+      </c>
+      <c r="L46" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="M46" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="N46" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
       <c r="O46" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -6048,17 +6056,17 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>래블업</t>
+          <t>하나에어로다이내믹스</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>시스템 소프트웨어 개발 및 공급업</t>
+          <t>항공기용 부품 제조업</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -6068,37 +6076,33 @@
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>19,000 ~ 22,000원</t>
+          <t>4,700 ~ 5,700원</t>
         </is>
       </c>
       <c r="I47" s="10" t="n">
-        <v>1635000</v>
+        <v>3300000</v>
       </c>
       <c r="J47" s="11" t="n">
-        <v>359.7</v>
+        <v>188.1</v>
       </c>
       <c r="K47" s="9" t="inlineStr">
         <is>
-          <t>NH투자증권 02-768-7462, 7467</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
         </is>
       </c>
       <c r="L47" s="8" t="inlineStr"/>
       <c r="M47" s="8" t="inlineStr"/>
-      <c r="N47" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
+      <c r="N47" s="8" t="inlineStr"/>
       <c r="O47" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -6113,17 +6117,17 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>영광</t>
+          <t>래블업</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>수상 금속 골조 구조재 제조업</t>
+          <t>시스템 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
@@ -6143,25 +6147,25 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>14,000 ~ 17,000원</t>
+          <t>19,000 ~ 22,000원</t>
         </is>
       </c>
       <c r="I48" s="10" t="n">
-        <v>1695000</v>
+        <v>1635000</v>
       </c>
       <c r="J48" s="11" t="n">
-        <v>288.1</v>
+        <v>359.7</v>
       </c>
       <c r="K48" s="9" t="inlineStr">
         <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+          <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
       <c r="L48" s="8" t="inlineStr"/>
       <c r="M48" s="8" t="inlineStr"/>
       <c r="N48" s="8" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="O48" s="12" t="inlineStr">
@@ -6178,12 +6182,12 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>이에스티</t>
+          <t>영광</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>그 외 기타 전자부품 제조업</t>
+          <t>수상 금속 골조 구조재 제조업</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
@@ -6198,35 +6202,35 @@
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>10,600 ~ 12,400원</t>
+          <t>14,000 ~ 17,000원</t>
         </is>
       </c>
       <c r="I49" s="10" t="n">
-        <v>1650000</v>
+        <v>1695000</v>
       </c>
       <c r="J49" s="11" t="n">
-        <v>204.6</v>
+        <v>288.1</v>
       </c>
       <c r="K49" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
       <c r="L49" s="8" t="inlineStr"/>
       <c r="M49" s="8" t="inlineStr"/>
       <c r="N49" s="8" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="O49" s="12" t="inlineStr">
@@ -6243,12 +6247,12 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>에이엘로봇</t>
+          <t>이에스티</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>기타 기계 및 장비 제조업</t>
+          <t>그 외 기타 전자부품 제조업</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
@@ -6263,33 +6267,37 @@
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>15,700 ~ 17,600원</t>
+          <t>10,600 ~ 12,400원</t>
         </is>
       </c>
       <c r="I50" s="10" t="n">
-        <v>1800000</v>
+        <v>1650000</v>
       </c>
       <c r="J50" s="11" t="n">
-        <v>316.8</v>
+        <v>204.6</v>
       </c>
       <c r="K50" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
+          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
       <c r="L50" s="8" t="inlineStr"/>
       <c r="M50" s="8" t="inlineStr"/>
-      <c r="N50" s="8" t="inlineStr"/>
+      <c r="N50" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
       <c r="O50" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -6297,69 +6305,61 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>엠비디</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>물질 검사, 측정 및 분석기구 제조업</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경(수요예측)</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>9,600 ~ 11,700원</t>
-        </is>
-      </c>
-      <c r="I51" s="5" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="J51" s="6" t="n">
-        <v>175.5</v>
-      </c>
-      <c r="K51" s="3" t="inlineStr">
-        <is>
-          <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr"/>
-      <c r="O51" s="7" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>에이엘로봇</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>기타 기계 및 장비 제조업</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>15,700 ~ 17,600원</t>
+        </is>
+      </c>
+      <c r="I51" s="10" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="J51" s="11" t="n">
+        <v>316.8</v>
+      </c>
+      <c r="K51" s="9" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
+        </is>
+      </c>
+      <c r="L51" s="8" t="inlineStr"/>
+      <c r="M51" s="8" t="inlineStr"/>
+      <c r="N51" s="8" t="inlineStr"/>
+      <c r="O51" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -6368,70 +6368,66 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>한화플러스제6호기업인수목적</t>
+          <t>엠비디</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>스팩</t>
+          <t>물질 검사, 측정 및 분석기구 제조업</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>정정-변경없음</t>
+          <t>정정-변경(수요예측)</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>2,000원 (단일가)</t>
+          <t>9,600 ~ 11,700원</t>
         </is>
       </c>
       <c r="I52" s="5" t="n">
-        <v>4500000</v>
+        <v>1500000</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>90</v>
+        <v>175.5</v>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>한화투자증권㈜ 02-3772-7395, 7398, 7393</t>
+          <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="7" t="inlineStr">
         <is>
           <t>열기</t>
@@ -6446,7 +6442,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>아이엠기업인수목적1호</t>
+          <t>한화플러스제6호기업인수목적</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -6466,41 +6462,45 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>2,000원 (단일가)</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="J53" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>한화투자증권㈜ 02-3772-7395, 7398, 7393</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>2,000원 (단일가)</t>
-        </is>
-      </c>
-      <c r="I53" s="5" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J53" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="K53" s="3" t="inlineStr">
-        <is>
-          <t>아이엠증권 02-2122-9688, 9485</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr"/>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="O53" s="7" t="inlineStr">
         <is>
           <t>열기</t>
@@ -6515,17 +6515,17 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>아이엠기업인수목적1호</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
+          <t>스팩</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -6535,45 +6535,41 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15,000 ~ 18,000원</t>
+          <t>2,000원 (단일가)</t>
         </is>
       </c>
       <c r="I54" s="5" t="n">
-        <v>1050000</v>
+        <v>3750000</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-7414, 7375, 7651</t>
+          <t>아이엠증권 02-2122-9688, 9485</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="7" t="inlineStr">
         <is>
           <t>열기</t>
@@ -6583,27 +6579,27 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>인텔리빅스</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
+          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>정정-변경(문의처)</t>
+          <t>정정-변경없음</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -6618,28 +6614,28 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>7,600 ~ 9,000원</t>
+          <t>15,000 ~ 18,000원</t>
         </is>
       </c>
       <c r="I55" s="5" t="n">
-        <v>1875000</v>
+        <v>1050000</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>168.8</v>
+        <v>189</v>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085</t>
+          <t>삼성증권 02-2020-7414, 7375, 7651</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6656,66 +6652,70 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>다비오</t>
+          <t>인텔리빅스</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
+          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>[정정제출요구] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>정정-변경(수요예측)</t>
+          <t>정정-변경(문의처)</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>12,300 ~ 16,600원</t>
+          <t>7,600 ~ 9,000원</t>
         </is>
       </c>
       <c r="I56" s="5" t="n">
-        <v>750000</v>
+        <v>1875000</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>124.5</v>
+        <v>168.8</v>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
+          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="O56" s="7" t="inlineStr">
         <is>
           <t>열기</t>
@@ -6725,17 +6725,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>유캐스트</t>
+          <t>다비오</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>기타 무선 통신장비 제조업</t>
+          <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>정정-변경(수요예측,밴드)</t>
+          <t>정정-변경(수요예측)</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -6760,18 +6760,18 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>21,000 ~ 26,000원</t>
+          <t>12,300 ~ 16,600원</t>
         </is>
       </c>
       <c r="I57" s="5" t="n">
-        <v>600000</v>
+        <v>750000</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>156</v>
+        <v>124.5</v>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
+          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
@@ -6794,63 +6794,63 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>바로팜</t>
+          <t>유캐스트</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>전자상거래 소매 중개업</t>
+          <t>기타 무선 통신장비 제조업</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[정정제출요구] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>정정-변경(문의처)</t>
+          <t>정정-변경(수요예측,밴드)</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>21,000 ~ 26,000원</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>600000</v>
+      </c>
+      <c r="J58" s="6" t="n">
+        <v>156</v>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
           <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>16,400 ~ 20,200원</t>
-        </is>
-      </c>
-      <c r="I58" s="5" t="n">
-        <v>1335000</v>
-      </c>
-      <c r="J58" s="6" t="n">
-        <v>269.7</v>
-      </c>
-      <c r="K58" s="3" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr"/>
@@ -6863,17 +6863,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>바로팜</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
+          <t>전자상거래 소매 중개업</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -6883,50 +6883,46 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>정정-변경없음</t>
+          <t>정정-변경(문의처)</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>15,000 ~ 18,000원</t>
+          <t>16,400 ~ 20,200원</t>
         </is>
       </c>
       <c r="I59" s="5" t="n">
-        <v>1050000</v>
+        <v>1335000</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>189</v>
+        <v>269.7</v>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-7414, 7375, 7651</t>
+          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="7" t="inlineStr">
         <is>
           <t>열기</t>
@@ -6936,17 +6932,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>티앤이코리아</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>산업용 송풍기 및 배기장치 제조업</t>
+          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -6956,33 +6952,33 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>정정-변경(수요예측)</t>
+          <t>정정-변경없음</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>12,600 ~ 15,300원</t>
+          <t>15,000 ~ 18,000원</t>
         </is>
       </c>
       <c r="I60" s="5" t="n">
-        <v>1800000</v>
+        <v>1050000</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>275.4</v>
+        <v>189</v>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
+          <t>삼성증권 02-2020-7414, 7375, 7651</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -6997,7 +6993,7 @@
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="O60" s="7" t="inlineStr">
@@ -7009,17 +7005,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>엠비디</t>
+          <t>티앤이코리아</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>물질 검사, 측정 및 분석기구 제조업</t>
+          <t>산업용 송풍기 및 배기장치 제조업</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -7029,46 +7025,50 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>정정-변경(수요예측,밴드)</t>
+          <t>정정-변경(수요예측)</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>9,400 ~ 11,500원</t>
+          <t>12,600 ~ 15,300원</t>
         </is>
       </c>
       <c r="I61" s="5" t="n">
-        <v>1500000</v>
+        <v>1800000</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>172.5</v>
+        <v>275.4</v>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
+          <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr"/>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
       <c r="O61" s="7" t="inlineStr">
         <is>
           <t>열기</t>
@@ -7078,78 +7078,147 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>엠비디</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>물질 검사, 측정 및 분석기구 제조업</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경(수요예측,밴드)</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>9,400 ~ 11,500원</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="J62" s="6" t="n">
+        <v>172.5</v>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>래블업</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>시스템 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="E63" s="4" t="inlineStr">
         <is>
           <t>정정-변경(수요예측,밴드)</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>20,000 ~ 23,000원</t>
         </is>
       </c>
-      <c r="I62" s="5" t="n">
+      <c r="I63" s="5" t="n">
         <v>1635000</v>
       </c>
-      <c r="J62" s="6" t="n">
+      <c r="J63" s="6" t="n">
         <v>376.1</v>
       </c>
-      <c r="K62" s="3" t="inlineStr">
+      <c r="K63" s="3" t="inlineStr">
         <is>
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="L62" s="2" t="inlineStr">
+      <c r="L63" s="2" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="M62" s="2" t="inlineStr">
+      <c r="M63" s="2" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="N62" s="2" t="inlineStr">
+      <c r="N63" s="2" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="O62" s="7" t="inlineStr">
+      <c r="O63" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O62"/>
+  <autoFilter ref="A1:O63"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -7212,6 +7281,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId62"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/수요예측_일정.xlsx
+++ b/수요예측_일정.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'수요예측 일정'!$A$1:$O$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체 이력'!$A$1:$O$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체 이력'!$A$1:$O$65</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -582,12 +582,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>아델</t>
+          <t>케이엠에프</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>의학 및 약학 연구개발업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -597,43 +597,43 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>정정-변경(문의처)</t>
+          <t>정정-변경없음</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>18,000 ~ 25,000원</t>
+          <t>15,000 ~ 17,800원</t>
         </is>
       </c>
       <c r="I2" s="5" t="n">
-        <v>1627500</v>
+        <v>1500000</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>406.9</v>
+        <v>267</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-8213, 6661</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799 / 아이비케이투자증권㈜ 02-6915-5337, 5338, 5799</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr"/>
@@ -651,12 +651,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>케이엠에프</t>
+          <t>엔키화이트햇</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -666,43 +666,43 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>정정-변경없음</t>
+          <t>정정-변경(수요예측)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>15,000 ~ 17,800원</t>
+          <t>13,000 ~ 16,500원</t>
         </is>
       </c>
       <c r="I3" s="5" t="n">
-        <v>1500000</v>
+        <v>1258000</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>267</v>
+        <v>207.6</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
+          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr"/>
@@ -713,138 +713,138 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>아델</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>의학 및 약학 연구개발업</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경(문의처)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>18,000 ~ 25,000원</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>1627500</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>406.9</v>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-8213, 6661</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>우리투자제1호기업인수목적</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>스팩</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>2026-11-25</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>2026-11-26</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>2,000원 (단일가)</t>
         </is>
       </c>
-      <c r="I4" s="10" t="n">
+      <c r="I5" s="10" t="n">
         <v>4875000</v>
       </c>
-      <c r="J4" s="11" t="n">
+      <c r="J5" s="11" t="n">
         <v>97.5</v>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K5" s="9" t="inlineStr">
         <is>
           <t>우리투자증권 02-6390-3889</t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr">
+      <c r="L5" s="8" t="inlineStr">
         <is>
           <t>2026-12-02</t>
         </is>
       </c>
-      <c r="M4" s="8" t="inlineStr">
+      <c r="M5" s="8" t="inlineStr">
         <is>
           <t>2026-12-07</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr"/>
-      <c r="O4" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>제논</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경(수요예측)</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-20</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>9,700 ~ 12,200원</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>1550000</v>
-      </c>
-      <c r="J5" s="6" t="n">
-        <v>189.1</v>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>삼성증권 02-2020-8023, 7653, 7850</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-24</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-27</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="7" t="inlineStr">
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -853,17 +853,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>동원파츠</t>
+          <t>제논</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>반도체 제조용 기계 제조업</t>
+          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -873,43 +873,43 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>정정-변경없음</t>
+          <t>정정-변경(수요예측)</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,000 ~ 26,500원</t>
+          <t>9,700 ~ 12,200원</t>
         </is>
       </c>
       <c r="I6" s="5" t="n">
-        <v>1522500</v>
+        <v>1550000</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>403.5</v>
+        <v>189.1</v>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-6975, 8217, 7651</t>
+          <t>삼성증권 02-2020-8023, 7653, 7850</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr"/>
@@ -920,69 +920,69 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>동원파츠</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>반도체 제조용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>인터엑스</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-04</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>10,000 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I7" s="10" t="n">
-        <v>2250000</v>
-      </c>
-      <c r="J7" s="11" t="n">
-        <v>292.5</v>
-      </c>
-      <c r="K7" s="9" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5700, 6648</t>
-        </is>
-      </c>
-      <c r="L7" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-09</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-14</t>
-        </is>
-      </c>
-      <c r="N7" s="8" t="inlineStr"/>
-      <c r="O7" s="12" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>23,000 ~ 26,500원</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>1522500</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>403.5</v>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-6975, 8217, 7651</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -991,22 +991,22 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>유캐스트</t>
+          <t>인터엑스</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>기타 무선 통신장비 제조업</t>
+          <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>19,000 ~ 23,000원</t>
+          <t>10,000 ~ 13,000원</t>
         </is>
       </c>
       <c r="I8" s="10" t="n">
-        <v>600000</v>
+        <v>2250000</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>138</v>
+        <v>292.5</v>
       </c>
       <c r="K8" s="9" t="inlineStr">
         <is>
-          <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
+          <t>한국투자증권㈜ 02-3276-5700, 6648</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="N8" s="8" t="inlineStr"/>
@@ -1058,138 +1058,138 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>유캐스트</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>기타 무선 통신장비 제조업</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>19,000 ~ 23,000원</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>600000</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>138</v>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="N9" s="8" t="inlineStr"/>
+      <c r="O9" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>옵토닉스</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>광학렌즈 및 광학요소 제조업</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>10,000 ~ 12,000원</t>
         </is>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="I10" s="5" t="n">
         <v>1572490</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J10" s="6" t="n">
         <v>188.7</v>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>2026-11-05</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>이노보테라퓨틱스</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-02</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>20,000 ~ 24,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="10" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="J10" s="11" t="n">
-        <v>396</v>
-      </c>
-      <c r="K10" s="9" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
-        </is>
-      </c>
-      <c r="L10" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-07</t>
-        </is>
-      </c>
-      <c r="M10" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-10</t>
-        </is>
-      </c>
-      <c r="N10" s="8" t="inlineStr"/>
-      <c r="O10" s="12" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1198,17 +1198,17 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>에이엔에이치스트럭쳐</t>
+          <t>이노보테라퓨틱스</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>기타 엔지니어링 서비스업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -1223,38 +1223,38 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>11,200 ~ 13,600원</t>
+          <t>20,000 ~ 24,000원</t>
         </is>
       </c>
       <c r="I11" s="10" t="n">
-        <v>1575000</v>
+        <v>1650000</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>214.2</v>
+        <v>396</v>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>NH투자증권 02-2229-6315, 6829</t>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="N11" s="8" t="inlineStr"/>
@@ -1265,142 +1265,142 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>에이엔에이치스트럭쳐</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>기타 엔지니어링 서비스업</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>11,200 ~ 13,600원</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>1575000</v>
+      </c>
+      <c r="J12" s="11" t="n">
+        <v>214.2</v>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>NH투자증권 02-2229-6315, 6829</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="N12" s="8" t="inlineStr"/>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>이에스티</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>그 외 기타 전자부품 제조업</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>10,600 ~ 12,400원</t>
         </is>
       </c>
-      <c r="I12" s="5" t="n">
+      <c r="I13" s="5" t="n">
         <v>1650000</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="J13" s="6" t="n">
         <v>204.6</v>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2026-11-04</t>
         </is>
       </c>
-      <c r="O12" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>에스에프씨</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>그 외 기타 분류 안된 화학제품 제조업</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>31,600 ~ 36,100원</t>
-        </is>
-      </c>
-      <c r="I13" s="10" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J13" s="11" t="n">
-        <v>1353.8</v>
-      </c>
-      <c r="K13" s="9" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
-        </is>
-      </c>
-      <c r="L13" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="M13" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-      <c r="N13" s="8" t="inlineStr"/>
-      <c r="O13" s="12" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>씨아이에스케미칼</t>
+          <t>에스에프씨</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>알루미늄 제련, 정련 및 합금 제조업</t>
+          <t>그 외 기타 분류 안된 화학제품 제조업</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
@@ -1434,38 +1434,38 @@
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>5,400 ~ 6,800원</t>
+          <t>31,600 ~ 36,100원</t>
         </is>
       </c>
       <c r="I14" s="10" t="n">
-        <v>3000000</v>
+        <v>3750000</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>204</v>
+        <v>1353.8</v>
       </c>
       <c r="K14" s="9" t="inlineStr">
         <is>
-          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
+          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
         </is>
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="N14" s="8" t="inlineStr"/>
@@ -1478,17 +1478,17 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>제이앤티지</t>
+          <t>씨아이에스케미칼</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>그 외 자동차용 신품 부품 제조업</t>
+          <t>알루미늄 제련, 정련 및 합금 제조업</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -1503,38 +1503,38 @@
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>26,400 ~ 31,900원</t>
+          <t>5,400 ~ 6,800원</t>
         </is>
       </c>
       <c r="I15" s="10" t="n">
-        <v>3182000</v>
+        <v>3000000</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>1015.1</v>
+        <v>204</v>
       </c>
       <c r="K15" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
+          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="M15" s="8" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="N15" s="8" t="inlineStr"/>
@@ -1552,12 +1552,12 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>씨앤엠</t>
+          <t>제이앤티지</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>전동기 및 발전기 제조업</t>
+          <t>그 외 자동차용 신품 부품 제조업</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -1582,18 +1582,18 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>10,000 ~ 13,000원</t>
+          <t>26,400 ~ 31,900원</t>
         </is>
       </c>
       <c r="I16" s="10" t="n">
-        <v>2059500</v>
+        <v>3182000</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>267.7</v>
+        <v>1015.1</v>
       </c>
       <c r="K16" s="9" t="inlineStr">
         <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
         </is>
       </c>
       <c r="L16" s="8" t="inlineStr">
@@ -1614,69 +1614,69 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>넥스아이</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>10,500 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J17" s="6" t="n">
-        <v>487.5</v>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>씨앤엠</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>전동기 및 발전기 제조업</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
-      <c r="O17" s="7" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>10,000 ~ 13,000원</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="n">
+        <v>2059500</v>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>267.7</v>
+      </c>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+        </is>
+      </c>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N17" s="8" t="inlineStr"/>
+      <c r="O17" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1690,12 +1690,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>항공기용 부품 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1710,38 +1710,38 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>10,500 ~ 13,000원</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>487.5</v>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
           <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>4,700 ~ 5,700원</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>3300000</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>188.1</v>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr"/>
@@ -1754,17 +1754,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>바로팜</t>
+          <t>하나에어로다이내믹스</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>전자상거래 소매 중개업</t>
+          <t>항공기용 부품 제조업</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1779,38 +1779,38 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,400 ~ 20,200원</t>
+          <t>4,700 ~ 5,700원</t>
         </is>
       </c>
       <c r="I19" s="5" t="n">
-        <v>1335000</v>
+        <v>3300000</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>269.7</v>
+        <v>188.1</v>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr"/>
@@ -1821,142 +1821,138 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>바로팜</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>전자상거래 소매 중개업</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>16,400 ~ 20,200원</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>1335000</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>269.7</v>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>엠비디</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>물질 검사, 측정 및 분석기구 제조업</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>9,600 ~ 11,700원</t>
         </is>
       </c>
-      <c r="I20" s="10" t="n">
+      <c r="I21" s="10" t="n">
         <v>1500000</v>
       </c>
-      <c r="J20" s="11" t="n">
+      <c r="J21" s="11" t="n">
         <v>175.5</v>
       </c>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="K21" s="9" t="inlineStr">
         <is>
           <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
         </is>
       </c>
-      <c r="L20" s="8" t="inlineStr">
+      <c r="L21" s="8" t="inlineStr">
         <is>
           <t>2026-11-12</t>
         </is>
       </c>
-      <c r="M20" s="8" t="inlineStr">
+      <c r="M21" s="8" t="inlineStr">
         <is>
           <t>2026-11-17</t>
         </is>
       </c>
-      <c r="N20" s="8" t="inlineStr"/>
-      <c r="O20" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>래블업</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>시스템 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>19,000 ~ 22,000원</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="n">
-        <v>1635000</v>
-      </c>
-      <c r="J21" s="6" t="n">
-        <v>359.7</v>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>NH투자증권 02-768-7462, 7467</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="O21" s="7" t="inlineStr">
+      <c r="N21" s="8" t="inlineStr"/>
+      <c r="O21" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1965,112 +1961,140 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>래블업</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>시스템 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>19,000 ~ 22,000원</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>1635000</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>359.7</v>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>NH투자증권 02-768-7462, 7467</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>에이엘로봇</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>기타 기계 및 장비 제조업</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>정정-변경(수요예측)</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>15,700 ~ 17,600원</t>
         </is>
       </c>
-      <c r="I22" s="5" t="n">
+      <c r="I23" s="5" t="n">
         <v>1800000</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="J23" s="6" t="n">
         <v>316.8</v>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>2026-11-11</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>SimwonAmericaCorp.</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>자동차 신품 부품 제조업</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>수요예측 항목 없음(원문 확인)</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr"/>
-      <c r="G23" s="8" t="inlineStr"/>
-      <c r="H23" s="8" t="inlineStr"/>
-      <c r="I23" s="10" t="inlineStr"/>
-      <c r="J23" s="11" t="inlineStr"/>
-      <c r="K23" s="9" t="inlineStr"/>
-      <c r="L23" s="8" t="inlineStr"/>
-      <c r="M23" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="N23" s="8" t="inlineStr"/>
-      <c r="O23" s="12" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2079,63 +2103,39 @@
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>다비오</t>
+          <t>SimwonAmericaCorp.</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
+          <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>12,300 ~ 16,600원</t>
-        </is>
-      </c>
-      <c r="I24" s="10" t="n">
-        <v>750000</v>
-      </c>
-      <c r="J24" s="11" t="n">
-        <v>124.5</v>
-      </c>
-      <c r="K24" s="9" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
-        </is>
-      </c>
-      <c r="L24" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
+          <t>수요예측 항목 없음(원문 확인)</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr"/>
+      <c r="G24" s="8" t="inlineStr"/>
+      <c r="H24" s="8" t="inlineStr"/>
+      <c r="I24" s="10" t="inlineStr"/>
+      <c r="J24" s="11" t="inlineStr"/>
+      <c r="K24" s="9" t="inlineStr"/>
+      <c r="L24" s="8" t="inlineStr"/>
       <c r="M24" s="8" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr"/>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>엔키화이트햇</t>
+          <t>다비오</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -2173,38 +2173,38 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>13,000 ~ 16,500원</t>
+          <t>12,300 ~ 16,600원</t>
         </is>
       </c>
       <c r="I25" s="10" t="n">
-        <v>1258000</v>
+        <v>750000</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>207.6</v>
+        <v>124.5</v>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
+          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
         </is>
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr"/>
@@ -2910,7 +2910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O63"/>
+  <dimension ref="A1:O65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3015,12 +3015,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>아델</t>
+          <t>케이엠에프</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>의학 및 약학 연구개발업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -3030,43 +3030,43 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>정정-변경(문의처)</t>
+          <t>정정-변경없음</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>18,000 ~ 25,000원</t>
+          <t>15,000 ~ 17,800원</t>
         </is>
       </c>
       <c r="I2" s="5" t="n">
-        <v>1627500</v>
+        <v>1500000</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>406.9</v>
+        <v>267</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-8213, 6661</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799 / 아이비케이투자증권㈜ 02-6915-5337, 5338, 5799</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr"/>
@@ -3084,12 +3084,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>케이엠에프</t>
+          <t>엔키화이트햇</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -3099,43 +3099,43 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>정정-변경없음</t>
+          <t>정정-변경(수요예측)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>15,000 ~ 17,800원</t>
+          <t>13,000 ~ 16,500원</t>
         </is>
       </c>
       <c r="I3" s="5" t="n">
-        <v>1500000</v>
+        <v>1258000</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>267</v>
+        <v>207.6</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
+          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr"/>
@@ -3146,69 +3146,69 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>우리투자제1호기업인수목적</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>스팩</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-25</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>아델</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>의학 및 약학 연구개발업</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경(문의처)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>18,000 ~ 25,000원</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>1627500</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>406.9</v>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-8213, 6661</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>2026-11-26</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>2,000원 (단일가)</t>
-        </is>
-      </c>
-      <c r="I4" s="10" t="n">
-        <v>4875000</v>
-      </c>
-      <c r="J4" s="11" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="K4" s="9" t="inlineStr">
-        <is>
-          <t>우리투자증권 02-6390-3889</t>
-        </is>
-      </c>
-      <c r="L4" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-02</t>
-        </is>
-      </c>
-      <c r="M4" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-07</t>
-        </is>
-      </c>
-      <c r="N4" s="8" t="inlineStr"/>
-      <c r="O4" s="12" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3217,17 +3217,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>제논</t>
+          <t>케이엠에프</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>정정-변경(수요예측)</t>
+          <t>정정-변경없음</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3252,18 +3252,18 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,700 ~ 12,200원</t>
+          <t>15,000 ~ 17,800원</t>
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>1550000</v>
+        <v>1500000</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>189.1</v>
+        <v>267</v>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-8023, 7653, 7850</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -3284,61 +3284,69 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>제논</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,700 ~ 12,200원</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>1550000</v>
-      </c>
-      <c r="J6" s="6" t="n">
-        <v>189.1</v>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>삼성증권 02-2020-8023, 7653, 7850</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>우리투자제1호기업인수목적</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>스팩</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>2,000원 (단일가)</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>4875000</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>우리투자증권 02-6390-3889</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-07</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr"/>
+      <c r="O6" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3347,17 +3355,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>동원파츠</t>
+          <t>제논</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>반도체 제조용 기계 제조업</t>
+          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -3367,43 +3375,43 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>정정-변경없음</t>
+          <t>정정-변경(수요예측)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,000 ~ 26,500원</t>
+          <t>9,700 ~ 12,200원</t>
         </is>
       </c>
       <c r="I7" s="5" t="n">
-        <v>1522500</v>
+        <v>1550000</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>403.5</v>
+        <v>189.1</v>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-6975, 8217, 7651</t>
+          <t>삼성증권 02-2020-8023, 7653, 7850</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr"/>
@@ -3414,207 +3422,199 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>제논</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>9,700 ~ 12,200원</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>1550000</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>189.1</v>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-8023, 7653, 7850</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>동원파츠</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>반도체 제조용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>23,000 ~ 26,500원</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>1522500</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>403.5</v>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-6975, 8217, 7651</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>인터엑스</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>2026-11-30</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>2026-12-04</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>10,000 ~ 13,000원</t>
         </is>
       </c>
-      <c r="I8" s="10" t="n">
+      <c r="I10" s="10" t="n">
         <v>2250000</v>
       </c>
-      <c r="J8" s="11" t="n">
+      <c r="J10" s="11" t="n">
         <v>292.5</v>
       </c>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="K10" s="9" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5700, 6648</t>
         </is>
       </c>
-      <c r="L8" s="8" t="inlineStr">
+      <c r="L10" s="8" t="inlineStr">
         <is>
           <t>2026-12-09</t>
         </is>
       </c>
-      <c r="M8" s="8" t="inlineStr">
+      <c r="M10" s="8" t="inlineStr">
         <is>
           <t>2026-12-14</t>
         </is>
       </c>
-      <c r="N8" s="8" t="inlineStr"/>
-      <c r="O8" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>유캐스트</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>기타 무선 통신장비 제조업</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>19,000 ~ 23,000원</t>
-        </is>
-      </c>
-      <c r="I9" s="10" t="n">
-        <v>600000</v>
-      </c>
-      <c r="J9" s="11" t="n">
-        <v>138</v>
-      </c>
-      <c r="K9" s="9" t="inlineStr">
-        <is>
-          <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
-        </is>
-      </c>
-      <c r="L9" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="M9" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-      <c r="N9" s="8" t="inlineStr"/>
-      <c r="O9" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>옵토닉스</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>광학렌즈 및 광학요소 제조업</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,000 ~ 12,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>1572490</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>188.7</v>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>한국투자증권 02-3276-5958, 6269</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="7" t="inlineStr">
+      <c r="N10" s="8" t="inlineStr"/>
+      <c r="O10" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3628,17 +3628,17 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>이노보테라퓨틱스</t>
+          <t>유캐스트</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>의학 및 약학 연구개발업</t>
+          <t>기타 무선 통신장비 제조업</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -3648,38 +3648,38 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>20,000 ~ 24,000원</t>
+          <t>19,000 ~ 23,000원</t>
         </is>
       </c>
       <c r="I11" s="10" t="n">
-        <v>1650000</v>
+        <v>600000</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>396</v>
+        <v>138</v>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+          <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="N11" s="8" t="inlineStr"/>
@@ -3690,142 +3690,138 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>에이엔에이치스트럭쳐</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>기타 엔지니어링 서비스업</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>옵토닉스</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>광학렌즈 및 광학요소 제조업</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>10,000 ~ 12,000원</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>1572490</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>188.7</v>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>한국투자증권 02-3276-5958, 6269</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>이노보테라퓨틱스</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>의학 및 약학 연구개발업</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-19</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-25</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>11,200 ~ 13,600원</t>
-        </is>
-      </c>
-      <c r="I12" s="10" t="n">
-        <v>1575000</v>
-      </c>
-      <c r="J12" s="11" t="n">
-        <v>214.2</v>
-      </c>
-      <c r="K12" s="9" t="inlineStr">
-        <is>
-          <t>NH투자증권 02-2229-6315, 6829</t>
-        </is>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-27</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>2026-12-02</t>
         </is>
       </c>
-      <c r="N12" s="8" t="inlineStr"/>
-      <c r="O12" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>이에스티</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>그 외 기타 전자부품 제조업</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,600 ~ 12,400원</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="n">
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>20,000 ~ 24,000원</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="n">
         <v>1650000</v>
       </c>
-      <c r="J13" s="6" t="n">
-        <v>204.6</v>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="O13" s="7" t="inlineStr">
+      <c r="J13" s="11" t="n">
+        <v>396</v>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-07</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="N13" s="8" t="inlineStr"/>
+      <c r="O13" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3834,17 +3830,17 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>에스에프씨</t>
+          <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>그 외 기타 분류 안된 화학제품 제조업</t>
+          <t>기타 엔지니어링 서비스업</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
@@ -3859,38 +3855,38 @@
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>31,600 ~ 36,100원</t>
+          <t>11,200 ~ 13,600원</t>
         </is>
       </c>
       <c r="I14" s="10" t="n">
-        <v>3750000</v>
+        <v>1575000</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>1353.8</v>
+        <v>214.2</v>
       </c>
       <c r="K14" s="9" t="inlineStr">
         <is>
-          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
+          <t>NH투자증권 02-2229-6315, 6829</t>
         </is>
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="N14" s="8" t="inlineStr"/>
@@ -3901,69 +3897,73 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>씨아이에스케미칼</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>알루미늄 제련, 정련 및 합금 제조업</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-04</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>5,400 ~ 6,800원</t>
-        </is>
-      </c>
-      <c r="I15" s="10" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="J15" s="11" t="n">
-        <v>204</v>
-      </c>
-      <c r="K15" s="9" t="inlineStr">
-        <is>
-          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
-        </is>
-      </c>
-      <c r="L15" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-10</t>
-        </is>
-      </c>
-      <c r="M15" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-15</t>
-        </is>
-      </c>
-      <c r="N15" s="8" t="inlineStr"/>
-      <c r="O15" s="12" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>이에스티</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>그 외 기타 전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>10,600 ~ 12,400원</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>204.6</v>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="O15" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3972,17 +3972,17 @@
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>제이앤티지</t>
+          <t>에스에프씨</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>그 외 자동차용 신품 부품 제조업</t>
+          <t>그 외 기타 분류 안된 화학제품 제조업</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -3997,38 +3997,38 @@
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>26,400 ~ 31,900원</t>
+          <t>31,600 ~ 36,100원</t>
         </is>
       </c>
       <c r="I16" s="10" t="n">
-        <v>3182000</v>
+        <v>3750000</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>1015.1</v>
+        <v>1353.8</v>
       </c>
       <c r="K16" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
+          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
         </is>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="M16" s="8" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="N16" s="8" t="inlineStr"/>
@@ -4041,17 +4041,17 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>씨앤엠</t>
+          <t>씨아이에스케미칼</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>전동기 및 발전기 제조업</t>
+          <t>알루미늄 제련, 정련 및 합금 제조업</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -4066,38 +4066,38 @@
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>10,000 ~ 13,000원</t>
+          <t>5,400 ~ 6,800원</t>
         </is>
       </c>
       <c r="I17" s="10" t="n">
-        <v>2059500</v>
+        <v>3000000</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>267.7</v>
+        <v>204</v>
       </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="M17" s="8" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="N17" s="8" t="inlineStr"/>
@@ -4108,138 +4108,138 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>넥스아이</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>10,500 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>487.5</v>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>제이앤티지</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>그 외 자동차용 신품 부품 제조업</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="7" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>26,400 ~ 31,900원</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="n">
+        <v>3182000</v>
+      </c>
+      <c r="J18" s="11" t="n">
+        <v>1015.1</v>
+      </c>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
+        </is>
+      </c>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N18" s="8" t="inlineStr"/>
+      <c r="O18" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>하나에어로다이내믹스</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>항공기용 부품 제조업</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>4,700 ~ 5,700원</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v>3300000</v>
-      </c>
-      <c r="J19" s="6" t="n">
-        <v>188.1</v>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="7" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>씨앤엠</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>전동기 및 발전기 제조업</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>10,000 ~ 13,000원</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="n">
+        <v>2059500</v>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>267.7</v>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+        </is>
+      </c>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M19" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N19" s="8" t="inlineStr"/>
+      <c r="O19" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4248,17 +4248,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>바로팜</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>전자상거래 소매 중개업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -4283,28 +4283,28 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,400 ~ 20,200원</t>
+          <t>10,500 ~ 13,000원</t>
         </is>
       </c>
       <c r="I20" s="5" t="n">
-        <v>1335000</v>
+        <v>3750000</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>269.7</v>
+        <v>487.5</v>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
+          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr"/>
@@ -4315,69 +4315,69 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>엠비디</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>물질 검사, 측정 및 분석기구 제조업</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>하나에어로다이내믹스</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>항공기용 부품 제조업</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>9,600 ~ 11,700원</t>
-        </is>
-      </c>
-      <c r="I21" s="10" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="J21" s="11" t="n">
-        <v>175.5</v>
-      </c>
-      <c r="K21" s="9" t="inlineStr">
-        <is>
-          <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
-        </is>
-      </c>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="M21" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-17</t>
-        </is>
-      </c>
-      <c r="N21" s="8" t="inlineStr"/>
-      <c r="O21" s="12" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>4,700 ~ 5,700원</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>188.1</v>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4386,17 +4386,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>래블업</t>
+          <t>바로팜</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>시스템 소프트웨어 개발 및 공급업</t>
+          <t>전자상거래 소매 중개업</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -4411,45 +4411,41 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,000 ~ 22,000원</t>
+          <t>16,400 ~ 20,200원</t>
         </is>
       </c>
       <c r="I22" s="5" t="n">
-        <v>1635000</v>
+        <v>1335000</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>359.7</v>
+        <v>269.7</v>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>NH투자증권 02-768-7462, 7467</t>
+          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="7" t="inlineStr">
         <is>
           <t>열기</t>
@@ -4457,65 +4453,69 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>이에스티</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>그 외 기타 전자부품 제조업</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>엠비디</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>물질 검사, 측정 및 분석기구 제조업</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>10,600 ~ 12,400원</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>204.6</v>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="O23" s="7" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>9,600 ~ 11,700원</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="J23" s="11" t="n">
+        <v>175.5</v>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
+        </is>
+      </c>
+      <c r="L23" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M23" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N23" s="8" t="inlineStr"/>
+      <c r="O23" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4524,181 +4524,205 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>래블업</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>시스템 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>19,000 ~ 22,000원</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>1635000</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>359.7</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>NH투자증권 02-768-7462, 7467</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="O24" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>이에스티</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>그 외 기타 전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>10,600 ~ 12,400원</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>204.6</v>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>에이엘로봇</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>기타 기계 및 장비 제조업</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>정정-변경(수요예측)</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>15,700 ~ 17,600원</t>
         </is>
       </c>
-      <c r="I24" s="5" t="n">
+      <c r="I26" s="5" t="n">
         <v>1800000</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="J26" s="6" t="n">
         <v>316.8</v>
       </c>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>2026-11-11</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>아델</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>18,000 ~ 25,000원</t>
-        </is>
-      </c>
-      <c r="I25" s="10" t="n">
-        <v>1627500</v>
-      </c>
-      <c r="J25" s="11" t="n">
-        <v>406.9</v>
-      </c>
-      <c r="K25" s="9" t="inlineStr">
-        <is>
-          <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
-        </is>
-      </c>
-      <c r="L25" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-      <c r="M25" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="N25" s="8" t="inlineStr"/>
-      <c r="O25" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>SimwonAmericaCorp.</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>자동차 신품 부품 제조업</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>수요예측 항목 없음(원문 확인)</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr"/>
-      <c r="G26" s="8" t="inlineStr"/>
-      <c r="H26" s="8" t="inlineStr"/>
-      <c r="I26" s="10" t="inlineStr"/>
-      <c r="J26" s="11" t="inlineStr"/>
-      <c r="K26" s="9" t="inlineStr"/>
-      <c r="L26" s="8" t="inlineStr"/>
-      <c r="M26" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="N26" s="8" t="inlineStr"/>
-      <c r="O26" s="12" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4707,22 +4731,22 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>다비오</t>
+          <t>아델</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -4732,38 +4756,38 @@
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>12,300 ~ 16,600원</t>
+          <t>18,000 ~ 25,000원</t>
         </is>
       </c>
       <c r="I27" s="10" t="n">
-        <v>750000</v>
+        <v>1627500</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>124.5</v>
+        <v>406.9</v>
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
+          <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="M27" s="8" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="N27" s="8" t="inlineStr"/>
@@ -4776,17 +4800,17 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>엔키화이트햇</t>
+          <t>SimwonAmericaCorp.</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
+          <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
@@ -4796,43 +4820,19 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
+          <t>수요예측 항목 없음(원문 확인)</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr"/>
+      <c r="G28" s="8" t="inlineStr"/>
+      <c r="H28" s="8" t="inlineStr"/>
+      <c r="I28" s="10" t="inlineStr"/>
+      <c r="J28" s="11" t="inlineStr"/>
+      <c r="K28" s="9" t="inlineStr"/>
+      <c r="L28" s="8" t="inlineStr"/>
+      <c r="M28" s="8" t="inlineStr">
         <is>
           <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>13,000 ~ 16,500원</t>
-        </is>
-      </c>
-      <c r="I28" s="10" t="n">
-        <v>1258000</v>
-      </c>
-      <c r="J28" s="11" t="n">
-        <v>207.6</v>
-      </c>
-      <c r="K28" s="9" t="inlineStr">
-        <is>
-          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
-        </is>
-      </c>
-      <c r="L28" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="M28" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-17</t>
         </is>
       </c>
       <c r="N28" s="8" t="inlineStr"/>
@@ -4850,17 +4850,17 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>영광와이케이엠씨</t>
+          <t>다비오</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>그 외 기타 금속가공업</t>
+          <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -4870,38 +4870,38 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>9,400 ~ 11,000원</t>
+          <t>12,300 ~ 16,600원</t>
         </is>
       </c>
       <c r="I29" s="10" t="n">
-        <v>1694840</v>
+        <v>750000</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>186.4</v>
+        <v>124.5</v>
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
+          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
         </is>
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="N29" s="8" t="inlineStr"/>
@@ -4912,73 +4912,69 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>영광</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>수상 금속 골조 구조재 제조업</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>14,000 ~ 17,000원</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>1695000</v>
-      </c>
-      <c r="J30" s="6" t="n">
-        <v>288.1</v>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="O30" s="7" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>엔키화이트햇</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>13,000 ~ 16,500원</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="n">
+        <v>1258000</v>
+      </c>
+      <c r="J30" s="11" t="n">
+        <v>207.6</v>
+      </c>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
+        </is>
+      </c>
+      <c r="L30" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M30" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N30" s="8" t="inlineStr"/>
+      <c r="O30" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4992,17 +4988,17 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>인텔리빅스</t>
+          <t>영광와이케이엠씨</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
+          <t>그 외 기타 금속가공업</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -5012,45 +5008,41 @@
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>7,600 ~ 9,000원</t>
+          <t>9,400 ~ 11,000원</t>
         </is>
       </c>
       <c r="I31" s="10" t="n">
-        <v>1875000</v>
+        <v>1694840</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>168.8</v>
+        <v>186.4</v>
       </c>
       <c r="K31" s="9" t="inlineStr">
         <is>
-          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
+          <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
         </is>
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="M31" s="8" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="N31" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="N31" s="8" t="inlineStr"/>
       <c r="O31" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -5065,12 +5057,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>아이엠기업인수목적1호</t>
+          <t>영광</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>스팩</t>
+          <t>수상 금속 골조 구조재 제조업</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -5085,41 +5077,45 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,000원 (단일가)</t>
+          <t>14,000 ~ 17,000원</t>
         </is>
       </c>
       <c r="I32" s="5" t="n">
-        <v>3750000</v>
+        <v>1695000</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>75</v>
+        <v>288.1</v>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>아이엠증권 02-2122-9688, 9485</t>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
       <c r="O32" s="7" t="inlineStr">
         <is>
           <t>열기</t>
@@ -5134,379 +5130,395 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
+          <t>인텔리빅스</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>7,600 ~ 9,000원</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="n">
+        <v>1875000</v>
+      </c>
+      <c r="J33" s="11" t="n">
+        <v>168.8</v>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
+      <c r="L33" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="M33" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="N33" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="O33" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>아이엠기업인수목적1호</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>스팩</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>2,000원 (단일가)</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="J34" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>아이엠증권 02-2122-9688, 9485</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>아이엠기업인수목적1호</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>스팩</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="F35" s="8" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="G35" s="8" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr">
+      <c r="H35" s="8" t="inlineStr">
         <is>
           <t>2,000원 (단일가)</t>
         </is>
       </c>
-      <c r="I33" s="10" t="n">
+      <c r="I35" s="10" t="n">
         <v>3750000</v>
       </c>
-      <c r="J33" s="11" t="n">
+      <c r="J35" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="K33" s="9" t="inlineStr">
+      <c r="K35" s="9" t="inlineStr">
         <is>
           <t>아이엠증권 02-2122-9688, 9485</t>
         </is>
       </c>
-      <c r="L33" s="8" t="inlineStr"/>
-      <c r="M33" s="8" t="inlineStr"/>
-      <c r="N33" s="8" t="inlineStr"/>
-      <c r="O33" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="L35" s="8" t="inlineStr"/>
+      <c r="M35" s="8" t="inlineStr"/>
+      <c r="N35" s="8" t="inlineStr"/>
+      <c r="O35" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>제논</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="D36" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="G34" s="8" t="inlineStr">
+      <c r="G36" s="8" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr">
+      <c r="H36" s="8" t="inlineStr">
         <is>
           <t>9,700 ~ 12,200원</t>
         </is>
       </c>
-      <c r="I34" s="10" t="n">
+      <c r="I36" s="10" t="n">
         <v>1550000</v>
       </c>
-      <c r="J34" s="11" t="n">
+      <c r="J36" s="11" t="n">
         <v>189.1</v>
       </c>
-      <c r="K34" s="9" t="inlineStr">
+      <c r="K36" s="9" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-8023, 7653, 7850</t>
         </is>
       </c>
-      <c r="L34" s="8" t="inlineStr"/>
-      <c r="M34" s="8" t="inlineStr"/>
-      <c r="N34" s="8" t="inlineStr"/>
-      <c r="O34" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="L36" s="8" t="inlineStr"/>
+      <c r="M36" s="8" t="inlineStr"/>
+      <c r="N36" s="8" t="inlineStr"/>
+      <c r="O36" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>한화플러스제6호기업인수목적</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>스팩</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>2,000원 (단일가)</t>
         </is>
       </c>
-      <c r="I35" s="5" t="n">
+      <c r="I37" s="5" t="n">
         <v>4500000</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="J37" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="K35" s="3" t="inlineStr">
+      <c r="K37" s="3" t="inlineStr">
         <is>
           <t>한화투자증권㈜ 02-3772-7395, 7398, 7393</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="O35" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="O37" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>래블업</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>시스템 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>19,000 ~ 22,000원</t>
         </is>
       </c>
-      <c r="I36" s="5" t="n">
+      <c r="I38" s="5" t="n">
         <v>1635000</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="J38" s="6" t="n">
         <v>359.7</v>
       </c>
-      <c r="K36" s="3" t="inlineStr">
+      <c r="K38" s="3" t="inlineStr">
         <is>
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="O36" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>한화플러스제6호기업인수목적</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>스팩</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="H37" s="8" t="inlineStr">
-        <is>
-          <t>2,000원 (단일가)</t>
-        </is>
-      </c>
-      <c r="I37" s="10" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="J37" s="11" t="n">
-        <v>90</v>
-      </c>
-      <c r="K37" s="9" t="inlineStr">
-        <is>
-          <t>한화투자증권㈜ 02-3772-7395, 7398, 7393</t>
-        </is>
-      </c>
-      <c r="L37" s="8" t="inlineStr"/>
-      <c r="M37" s="8" t="inlineStr"/>
-      <c r="N37" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="O37" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>케이엠에프</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>기타 식품 제조업</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-20</t>
-        </is>
-      </c>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t>15,000 ~ 17,800원</t>
-        </is>
-      </c>
-      <c r="I38" s="10" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="J38" s="11" t="n">
-        <v>267</v>
-      </c>
-      <c r="K38" s="9" t="inlineStr">
-        <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
-        </is>
-      </c>
-      <c r="L38" s="8" t="inlineStr"/>
-      <c r="M38" s="8" t="inlineStr"/>
-      <c r="N38" s="8" t="inlineStr"/>
-      <c r="O38" s="12" t="inlineStr">
+      <c r="O38" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -5515,17 +5527,17 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>바로팜</t>
+          <t>한화플러스제6호기업인수목적</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>전자상거래 소매 중개업</t>
+          <t>스팩</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
@@ -5540,33 +5552,37 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>16,400 ~ 20,200원</t>
+          <t>2,000원 (단일가)</t>
         </is>
       </c>
       <c r="I39" s="10" t="n">
-        <v>1335000</v>
+        <v>4500000</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>269.7</v>
+        <v>90</v>
       </c>
       <c r="K39" s="9" t="inlineStr">
         <is>
-          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
+          <t>한화투자증권㈜ 02-3772-7395, 7398, 7393</t>
         </is>
       </c>
       <c r="L39" s="8" t="inlineStr"/>
       <c r="M39" s="8" t="inlineStr"/>
-      <c r="N39" s="8" t="inlineStr"/>
+      <c r="N39" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="O39" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -5576,17 +5592,17 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>동원파츠</t>
+          <t>케이엠에프</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>반도체 제조용 기계 제조업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
@@ -5601,28 +5617,28 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>23,000 ~ 26,500원</t>
+          <t>15,000 ~ 17,800원</t>
         </is>
       </c>
       <c r="I40" s="10" t="n">
-        <v>1522500</v>
+        <v>1500000</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>403.5</v>
+        <v>267</v>
       </c>
       <c r="K40" s="9" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-6975, 8217, 7651</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
         </is>
       </c>
       <c r="L40" s="8" t="inlineStr"/>
@@ -5642,12 +5658,12 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>디티에스</t>
+          <t>바로팜</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>전자상거래 소매 중개업</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
@@ -5662,45 +5678,33 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>17,000 ~ 18,500원</t>
+          <t>16,400 ~ 20,200원</t>
         </is>
       </c>
       <c r="I41" s="10" t="n">
-        <v>1671687</v>
+        <v>1335000</v>
       </c>
       <c r="J41" s="11" t="n">
-        <v>309.3</v>
+        <v>269.7</v>
       </c>
       <c r="K41" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
-        </is>
-      </c>
-      <c r="L41" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="M41" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="N41" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
+          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
+      <c r="L41" s="8" t="inlineStr"/>
+      <c r="M41" s="8" t="inlineStr"/>
+      <c r="N41" s="8" t="inlineStr"/>
       <c r="O41" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -5710,22 +5714,22 @@
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>엠에스바이오</t>
+          <t>동원파츠</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>그 외 기타 의료용 기기 제조업</t>
+          <t>반도체 제조용 기계 제조업</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
@@ -5735,45 +5739,33 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>6,800 ~ 7,800원</t>
+          <t>23,000 ~ 26,500원</t>
         </is>
       </c>
       <c r="I42" s="10" t="n">
-        <v>2840000</v>
+        <v>1522500</v>
       </c>
       <c r="J42" s="11" t="n">
-        <v>221.5</v>
+        <v>403.5</v>
       </c>
       <c r="K42" s="9" t="inlineStr">
         <is>
-          <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
-        </is>
-      </c>
-      <c r="L42" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="M42" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="N42" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
+          <t>삼성증권 02-2020-6975, 8217, 7651</t>
+        </is>
+      </c>
+      <c r="L42" s="8" t="inlineStr"/>
+      <c r="M42" s="8" t="inlineStr"/>
+      <c r="N42" s="8" t="inlineStr"/>
       <c r="O42" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -5783,22 +5775,22 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>옵토닉스</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>광학렌즈 및 광학요소 제조업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -5808,33 +5800,45 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>10,000 ~ 12,000원</t>
+          <t>17,000 ~ 18,500원</t>
         </is>
       </c>
       <c r="I43" s="10" t="n">
-        <v>1572490</v>
+        <v>1671687</v>
       </c>
       <c r="J43" s="11" t="n">
-        <v>188.7</v>
+        <v>309.3</v>
       </c>
       <c r="K43" s="9" t="inlineStr">
         <is>
-          <t>한국투자증권 02-3276-5958, 6269</t>
-        </is>
-      </c>
-      <c r="L43" s="8" t="inlineStr"/>
-      <c r="M43" s="8" t="inlineStr"/>
-      <c r="N43" s="8" t="inlineStr"/>
+          <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
+        </is>
+      </c>
+      <c r="L43" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="M43" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="N43" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="O43" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -5844,58 +5848,70 @@
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>엠에스바이오</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>그 외 기타 의료용 기기 제조업</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>넥스아이</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F44" s="8" t="inlineStr">
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>6,800 ~ 7,800원</t>
+        </is>
+      </c>
+      <c r="I44" s="10" t="n">
+        <v>2840000</v>
+      </c>
+      <c r="J44" s="11" t="n">
+        <v>221.5</v>
+      </c>
+      <c r="K44" s="9" t="inlineStr">
+        <is>
+          <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
+        </is>
+      </c>
+      <c r="L44" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M44" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="N44" s="8" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="G44" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="H44" s="8" t="inlineStr">
-        <is>
-          <t>10,500 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I44" s="10" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J44" s="11" t="n">
-        <v>487.5</v>
-      </c>
-      <c r="K44" s="9" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
-        </is>
-      </c>
-      <c r="L44" s="8" t="inlineStr"/>
-      <c r="M44" s="8" t="inlineStr"/>
-      <c r="N44" s="8" t="inlineStr"/>
       <c r="O44" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -5905,22 +5921,22 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>옵토닉스</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
+          <t>광학렌즈 및 광학요소 제조업</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -5930,45 +5946,33 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>15,000 ~ 18,000원</t>
+          <t>10,000 ~ 12,000원</t>
         </is>
       </c>
       <c r="I45" s="10" t="n">
-        <v>1050000</v>
+        <v>1572490</v>
       </c>
       <c r="J45" s="11" t="n">
-        <v>189</v>
+        <v>188.7</v>
       </c>
       <c r="K45" s="9" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-7414, 7375, 7651</t>
-        </is>
-      </c>
-      <c r="L45" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="M45" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="N45" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
+          <t>한국투자증권 02-3276-5958, 6269</t>
+        </is>
+      </c>
+      <c r="L45" s="8" t="inlineStr"/>
+      <c r="M45" s="8" t="inlineStr"/>
+      <c r="N45" s="8" t="inlineStr"/>
       <c r="O45" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -5978,22 +5982,22 @@
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>티앤이코리아</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>산업용 송풍기 및 배기장치 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
@@ -6003,45 +6007,33 @@
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>12,600 ~ 15,300원</t>
+          <t>10,500 ~ 13,000원</t>
         </is>
       </c>
       <c r="I46" s="10" t="n">
-        <v>1800000</v>
+        <v>3750000</v>
       </c>
       <c r="J46" s="11" t="n">
-        <v>275.4</v>
+        <v>487.5</v>
       </c>
       <c r="K46" s="9" t="inlineStr">
         <is>
-          <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
-        </is>
-      </c>
-      <c r="L46" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="M46" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="N46" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
+          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
+        </is>
+      </c>
+      <c r="L46" s="8" t="inlineStr"/>
+      <c r="M46" s="8" t="inlineStr"/>
+      <c r="N46" s="8" t="inlineStr"/>
       <c r="O46" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -6051,22 +6043,22 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>항공기용 부품 제조업</t>
+          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -6076,33 +6068,45 @@
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>4,700 ~ 5,700원</t>
+          <t>15,000 ~ 18,000원</t>
         </is>
       </c>
       <c r="I47" s="10" t="n">
-        <v>3300000</v>
+        <v>1050000</v>
       </c>
       <c r="J47" s="11" t="n">
-        <v>188.1</v>
+        <v>189</v>
       </c>
       <c r="K47" s="9" t="inlineStr">
         <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
-        </is>
-      </c>
-      <c r="L47" s="8" t="inlineStr"/>
-      <c r="M47" s="8" t="inlineStr"/>
-      <c r="N47" s="8" t="inlineStr"/>
+          <t>삼성증권 02-2020-7414, 7375, 7651</t>
+        </is>
+      </c>
+      <c r="L47" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="M47" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="N47" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="O47" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -6112,17 +6116,17 @@
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>래블업</t>
+          <t>티앤이코리아</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>시스템 소프트웨어 개발 및 공급업</t>
+          <t>산업용 송풍기 및 배기장치 제조업</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
@@ -6137,35 +6141,43 @@
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>19,000 ~ 22,000원</t>
+          <t>12,600 ~ 15,300원</t>
         </is>
       </c>
       <c r="I48" s="10" t="n">
-        <v>1635000</v>
+        <v>1800000</v>
       </c>
       <c r="J48" s="11" t="n">
-        <v>359.7</v>
+        <v>275.4</v>
       </c>
       <c r="K48" s="9" t="inlineStr">
         <is>
-          <t>NH투자증권 02-768-7462, 7467</t>
-        </is>
-      </c>
-      <c r="L48" s="8" t="inlineStr"/>
-      <c r="M48" s="8" t="inlineStr"/>
+          <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
+        </is>
+      </c>
+      <c r="L48" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="M48" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="N48" s="8" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="O48" s="12" t="inlineStr">
@@ -6182,12 +6194,12 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>영광</t>
+          <t>하나에어로다이내믹스</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>수상 금속 골조 구조재 제조업</t>
+          <t>항공기용 부품 제조업</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
@@ -6202,37 +6214,33 @@
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>14,000 ~ 17,000원</t>
+          <t>4,700 ~ 5,700원</t>
         </is>
       </c>
       <c r="I49" s="10" t="n">
-        <v>1695000</v>
+        <v>3300000</v>
       </c>
       <c r="J49" s="11" t="n">
-        <v>288.1</v>
+        <v>188.1</v>
       </c>
       <c r="K49" s="9" t="inlineStr">
         <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
         </is>
       </c>
       <c r="L49" s="8" t="inlineStr"/>
       <c r="M49" s="8" t="inlineStr"/>
-      <c r="N49" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
+      <c r="N49" s="8" t="inlineStr"/>
       <c r="O49" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -6247,17 +6255,17 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>이에스티</t>
+          <t>래블업</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>그 외 기타 전자부품 제조업</t>
+          <t>시스템 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
@@ -6267,35 +6275,35 @@
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>10,600 ~ 12,400원</t>
+          <t>19,000 ~ 22,000원</t>
         </is>
       </c>
       <c r="I50" s="10" t="n">
-        <v>1650000</v>
+        <v>1635000</v>
       </c>
       <c r="J50" s="11" t="n">
-        <v>204.6</v>
+        <v>359.7</v>
       </c>
       <c r="K50" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+          <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
       <c r="L50" s="8" t="inlineStr"/>
       <c r="M50" s="8" t="inlineStr"/>
       <c r="N50" s="8" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="O50" s="12" t="inlineStr">
@@ -6312,12 +6320,12 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>에이엘로봇</t>
+          <t>영광</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>기타 기계 및 장비 제조업</t>
+          <t>수상 금속 골조 구조재 제조업</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
@@ -6332,33 +6340,37 @@
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>15,700 ~ 17,600원</t>
+          <t>14,000 ~ 17,000원</t>
         </is>
       </c>
       <c r="I51" s="10" t="n">
-        <v>1800000</v>
+        <v>1695000</v>
       </c>
       <c r="J51" s="11" t="n">
-        <v>316.8</v>
+        <v>288.1</v>
       </c>
       <c r="K51" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
       <c r="L51" s="8" t="inlineStr"/>
       <c r="M51" s="8" t="inlineStr"/>
-      <c r="N51" s="8" t="inlineStr"/>
+      <c r="N51" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
       <c r="O51" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -6366,142 +6378,126 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>엠비디</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>물질 검사, 측정 및 분석기구 제조업</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경(수요예측)</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>9,600 ~ 11,700원</t>
-        </is>
-      </c>
-      <c r="I52" s="5" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="J52" s="6" t="n">
-        <v>175.5</v>
-      </c>
-      <c r="K52" s="3" t="inlineStr">
-        <is>
-          <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr"/>
-      <c r="O52" s="7" t="inlineStr">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>이에스티</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>그 외 기타 전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>10,600 ~ 12,400원</t>
+        </is>
+      </c>
+      <c r="I52" s="10" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J52" s="11" t="n">
+        <v>204.6</v>
+      </c>
+      <c r="K52" s="9" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+        </is>
+      </c>
+      <c r="L52" s="8" t="inlineStr"/>
+      <c r="M52" s="8" t="inlineStr"/>
+      <c r="N52" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="O52" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>한화플러스제6호기업인수목적</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>스팩</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>에이엘로봇</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>기타 기계 및 장비 제조업</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>2,000원 (단일가)</t>
-        </is>
-      </c>
-      <c r="I53" s="5" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="J53" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="K53" s="3" t="inlineStr">
-        <is>
-          <t>한화투자증권㈜ 02-3772-7395, 7398, 7393</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="O53" s="7" t="inlineStr">
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t>15,700 ~ 17,600원</t>
+        </is>
+      </c>
+      <c r="I53" s="10" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="J53" s="11" t="n">
+        <v>316.8</v>
+      </c>
+      <c r="K53" s="9" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
+        </is>
+      </c>
+      <c r="L53" s="8" t="inlineStr"/>
+      <c r="M53" s="8" t="inlineStr"/>
+      <c r="N53" s="8" t="inlineStr"/>
+      <c r="O53" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -6510,63 +6506,63 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>아이엠기업인수목적1호</t>
+          <t>엠비디</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>스팩</t>
+          <t>물질 검사, 측정 및 분석기구 제조업</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>정정-변경없음</t>
+          <t>정정-변경(수요예측)</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2,000원 (단일가)</t>
+          <t>9,600 ~ 11,700원</t>
         </is>
       </c>
       <c r="I54" s="5" t="n">
-        <v>3750000</v>
+        <v>1500000</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>75</v>
+        <v>175.5</v>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>아이엠증권 02-2122-9688, 9485</t>
+          <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr"/>
@@ -6584,17 +6580,17 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>한화플러스제6호기업인수목적</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
+          <t>스팩</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -6604,28 +6600,28 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>15,000 ~ 18,000원</t>
+          <t>2,000원 (단일가)</t>
         </is>
       </c>
       <c r="I55" s="5" t="n">
-        <v>1050000</v>
+        <v>4500000</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>189</v>
+        <v>90</v>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-7414, 7375, 7651</t>
+          <t>한화투자증권㈜ 02-3772-7395, 7398, 7393</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
@@ -6652,17 +6648,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>인텔리빅스</t>
+          <t>아이엠기업인수목적1호</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
+          <t>스팩</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -6672,50 +6668,46 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>정정-변경(문의처)</t>
+          <t>정정-변경없음</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>7,600 ~ 9,000원</t>
+          <t>2,000원 (단일가)</t>
         </is>
       </c>
       <c r="I56" s="5" t="n">
-        <v>1875000</v>
+        <v>3750000</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>168.8</v>
+        <v>75</v>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085</t>
+          <t>아이엠증권 02-2122-9688, 9485</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="7" t="inlineStr">
         <is>
           <t>열기</t>
@@ -6725,66 +6717,70 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>다비오</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
+          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>[정정제출요구] 증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>정정-변경(수요예측)</t>
+          <t>정정-변경없음</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>12,300 ~ 16,600원</t>
+          <t>15,000 ~ 18,000원</t>
         </is>
       </c>
       <c r="I57" s="5" t="n">
-        <v>750000</v>
+        <v>1050000</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>124.5</v>
+        <v>189</v>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
+          <t>삼성증권 02-2020-7414, 7375, 7651</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr"/>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
           <t>열기</t>
@@ -6794,66 +6790,70 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>유캐스트</t>
+          <t>인텔리빅스</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>기타 무선 통신장비 제조업</t>
+          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>[정정제출요구] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>정정-변경(수요예측,밴드)</t>
+          <t>정정-변경(문의처)</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>21,000 ~ 26,000원</t>
+          <t>7,600 ~ 9,000원</t>
         </is>
       </c>
       <c r="I58" s="5" t="n">
-        <v>600000</v>
+        <v>1875000</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>156</v>
+        <v>168.8</v>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
+          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="O58" s="7" t="inlineStr">
         <is>
           <t>열기</t>
@@ -6863,63 +6863,63 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>바로팜</t>
+          <t>다비오</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>전자상거래 소매 중개업</t>
+          <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[정정제출요구] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>정정-변경(문의처)</t>
+          <t>정정-변경(수요예측)</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>12,300 ~ 16,600원</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>750000</v>
+      </c>
+      <c r="J59" s="6" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
           <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>16,400 ~ 20,200원</t>
-        </is>
-      </c>
-      <c r="I59" s="5" t="n">
-        <v>1335000</v>
-      </c>
-      <c r="J59" s="6" t="n">
-        <v>269.7</v>
-      </c>
-      <c r="K59" s="3" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr"/>
@@ -6932,70 +6932,66 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>유캐스트</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
+          <t>기타 무선 통신장비 제조업</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[정정제출요구] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>정정-변경없음</t>
+          <t>정정-변경(수요예측,밴드)</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>15,000 ~ 18,000원</t>
+          <t>21,000 ~ 26,000원</t>
         </is>
       </c>
       <c r="I60" s="5" t="n">
-        <v>1050000</v>
+        <v>600000</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>189</v>
+        <v>156</v>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-7414, 7375, 7651</t>
+          <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="7" t="inlineStr">
         <is>
           <t>열기</t>
@@ -7005,17 +7001,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>티앤이코리아</t>
+          <t>바로팜</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>산업용 송풍기 및 배기장치 제조업</t>
+          <t>전자상거래 소매 중개업</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -7025,50 +7021,46 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>정정-변경(수요예측)</t>
+          <t>정정-변경(문의처)</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>12,600 ~ 15,300원</t>
+          <t>16,400 ~ 20,200원</t>
         </is>
       </c>
       <c r="I61" s="5" t="n">
-        <v>1800000</v>
+        <v>1335000</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>275.4</v>
+        <v>269.7</v>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
+          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="7" t="inlineStr">
         <is>
           <t>열기</t>
@@ -7078,17 +7070,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>엠비디</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>물질 검사, 측정 및 분석기구 제조업</t>
+          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -7098,46 +7090,50 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>정정-변경(수요예측,밴드)</t>
+          <t>정정-변경없음</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>9,400 ~ 11,500원</t>
+          <t>15,000 ~ 18,000원</t>
         </is>
       </c>
       <c r="I62" s="5" t="n">
-        <v>1500000</v>
+        <v>1050000</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>172.5</v>
+        <v>189</v>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
+          <t>삼성증권 02-2020-7414, 7375, 7651</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr"/>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="O62" s="7" t="inlineStr">
         <is>
           <t>열기</t>
@@ -7147,78 +7143,220 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>티앤이코리아</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>산업용 송풍기 및 배기장치 제조업</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경(수요예측)</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>12,600 ~ 15,300원</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="J63" s="6" t="n">
+        <v>275.4</v>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="O63" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>엠비디</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>물질 검사, 측정 및 분석기구 제조업</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경(수요예측,밴드)</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>9,400 ~ 11,500원</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="J64" s="6" t="n">
+        <v>172.5</v>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>래블업</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>시스템 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
+      <c r="E65" s="4" t="inlineStr">
         <is>
           <t>정정-변경(수요예측,밴드)</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>20,000 ~ 23,000원</t>
         </is>
       </c>
-      <c r="I63" s="5" t="n">
+      <c r="I65" s="5" t="n">
         <v>1635000</v>
       </c>
-      <c r="J63" s="6" t="n">
+      <c r="J65" s="6" t="n">
         <v>376.1</v>
       </c>
-      <c r="K63" s="3" t="inlineStr">
+      <c r="K65" s="3" t="inlineStr">
         <is>
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="L63" s="2" t="inlineStr">
+      <c r="L65" s="2" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="M63" s="2" t="inlineStr">
+      <c r="M65" s="2" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="N63" s="2" t="inlineStr">
+      <c r="N65" s="2" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="O63" s="7" t="inlineStr">
+      <c r="O65" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O63"/>
+  <autoFilter ref="A1:O65"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -7282,6 +7420,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId64"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/수요예측_일정.xlsx
+++ b/수요예측_일정.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체 이력" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'수요예측 일정'!$A$1:$O$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체 이력'!$A$1:$O$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'수요예측 일정'!$A$1:$O$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체 이력'!$A$1:$O$66</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -79,6 +79,21 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -95,21 +110,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -577,273 +577,273 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>KTE</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>배전반 및 전기 자동제어반 제조업</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>19,000 ~ 23,000원</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>2112000</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>485.8</v>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>NH투자증권 02-768-7462, 7467</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>케이엠에프</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>기타 식품 제조업</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>2026-11-16</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>15,000 ~ 17,800원</t>
         </is>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I3" s="10" t="n">
         <v>1500000</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="J3" s="11" t="n">
         <v>267</v>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K3" s="8" t="inlineStr">
         <is>
           <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799 / 아이비케이투자증권㈜ 02-6915-5337, 5338, 5799</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L3" s="7" t="inlineStr">
         <is>
           <t>2026-11-24</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M3" s="7" t="inlineStr">
         <is>
           <t>2026-11-27</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="N3" s="7" t="inlineStr"/>
+      <c r="O3" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>엔키화이트햇</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>정정-변경(수요예측)</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>2026-11-26</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>13,000 ~ 16,500원</t>
         </is>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="I4" s="10" t="n">
         <v>1258000</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="J4" s="11" t="n">
         <v>207.6</v>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L4" s="7" t="inlineStr">
         <is>
           <t>2026-12-01</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M4" s="7" t="inlineStr">
         <is>
           <t>2026-12-04</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="N4" s="7" t="inlineStr"/>
+      <c r="O4" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>아델</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>정정-변경(문의처)</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>2026-11-12</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>2026-11-18</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>18,000 ~ 25,000원</t>
         </is>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="I5" s="10" t="n">
         <v>1627500</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="J5" s="11" t="n">
         <v>406.9</v>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-8213, 6661</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>2026-11-23</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>2026-11-26</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>우리투자제1호기업인수목적</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>스팩</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-25</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>2,000원 (단일가)</t>
-        </is>
-      </c>
-      <c r="I5" s="10" t="n">
-        <v>4875000</v>
-      </c>
-      <c r="J5" s="11" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>우리투자증권 02-6390-3889</t>
-        </is>
-      </c>
-      <c r="L5" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-02</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-07</t>
-        </is>
-      </c>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="7" t="inlineStr"/>
       <c r="O5" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -858,269 +858,269 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>우리투자제1호기업인수목적</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>스팩</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,000원 (단일가)</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>4875000</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>우리투자증권 02-6390-3889</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-07</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
           <t>제논</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>정정-변경(수요예측)</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>2026-11-16</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>9,700 ~ 12,200원</t>
         </is>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="I7" s="10" t="n">
         <v>1550000</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="J7" s="11" t="n">
         <v>189.1</v>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-8023, 7653, 7850</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>2026-11-24</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>2026-11-27</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="N7" s="7" t="inlineStr"/>
+      <c r="O7" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>동원파츠</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>반도체 제조용 기계 제조업</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>23,000 ~ 26,500원</t>
         </is>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="I8" s="10" t="n">
         <v>1522500</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J8" s="11" t="n">
         <v>403.5</v>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-6975, 8217, 7651</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L8" s="7" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M8" s="7" t="inlineStr">
         <is>
           <t>2026-11-05</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="N8" s="7" t="inlineStr"/>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>인터엑스</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>2026-11-30</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>2026-12-04</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>10,000 ~ 13,000원</t>
         </is>
       </c>
-      <c r="I8" s="10" t="n">
+      <c r="I9" s="4" t="n">
         <v>2250000</v>
       </c>
-      <c r="J8" s="11" t="n">
+      <c r="J9" s="5" t="n">
         <v>292.5</v>
       </c>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5700, 6648</t>
         </is>
       </c>
-      <c r="L8" s="8" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>2026-12-09</t>
         </is>
       </c>
-      <c r="M8" s="8" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>2026-12-14</t>
         </is>
       </c>
-      <c r="N8" s="8" t="inlineStr"/>
-      <c r="O8" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>유캐스트</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>기타 무선 통신장비 제조업</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>19,000 ~ 23,000원</t>
-        </is>
-      </c>
-      <c r="I9" s="10" t="n">
-        <v>600000</v>
-      </c>
-      <c r="J9" s="11" t="n">
-        <v>138</v>
-      </c>
-      <c r="K9" s="9" t="inlineStr">
-        <is>
-          <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
-        </is>
-      </c>
-      <c r="L9" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="M9" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-      <c r="N9" s="8" t="inlineStr"/>
-      <c r="O9" s="12" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1134,200 +1134,200 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>유캐스트</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>기타 무선 통신장비 제조업</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>19,000 ~ 23,000원</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>600000</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>138</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
           <t>옵토닉스</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>광학렌즈 및 광학요소 제조업</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>10,000 ~ 12,000원</t>
         </is>
       </c>
-      <c r="I10" s="5" t="n">
+      <c r="I11" s="10" t="n">
         <v>1572490</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J11" s="11" t="n">
         <v>188.7</v>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="K11" s="8" t="inlineStr">
         <is>
           <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L11" s="7" t="inlineStr">
         <is>
           <t>2026-11-05</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M11" s="7" t="inlineStr">
         <is>
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="N11" s="7" t="inlineStr"/>
+      <c r="O11" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>이노보테라퓨틱스</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>2026-11-26</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2026-12-02</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>20,000 ~ 24,000원</t>
         </is>
       </c>
-      <c r="I11" s="10" t="n">
+      <c r="I12" s="4" t="n">
         <v>1650000</v>
       </c>
-      <c r="J11" s="11" t="n">
+      <c r="J12" s="5" t="n">
         <v>396</v>
       </c>
-      <c r="K11" s="9" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L11" s="8" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>2026-12-07</t>
         </is>
       </c>
-      <c r="M11" s="8" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>2026-12-10</t>
         </is>
       </c>
-      <c r="N11" s="8" t="inlineStr"/>
-      <c r="O11" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>에이엔에이치스트럭쳐</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>기타 엔지니어링 서비스업</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-19</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-25</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>11,200 ~ 13,600원</t>
-        </is>
-      </c>
-      <c r="I12" s="10" t="n">
-        <v>1575000</v>
-      </c>
-      <c r="J12" s="11" t="n">
-        <v>214.2</v>
-      </c>
-      <c r="K12" s="9" t="inlineStr">
-        <is>
-          <t>NH투자증권 02-2229-6315, 6829</t>
-        </is>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-27</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-02</t>
-        </is>
-      </c>
-      <c r="N12" s="8" t="inlineStr"/>
-      <c r="O12" s="12" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1341,342 +1341,342 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>에이엔에이치스트럭쳐</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>기타 엔지니어링 서비스업</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11,200 ~ 13,600원</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>1575000</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>214.2</v>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>NH투자증권 02-2229-6315, 6829</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
           <t>이에스티</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>그 외 기타 전자부품 제조업</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>10,600 ~ 12,400원</t>
         </is>
       </c>
-      <c r="I13" s="5" t="n">
+      <c r="I14" s="10" t="n">
         <v>1650000</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="J14" s="11" t="n">
         <v>204.6</v>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="L14" s="7" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="M14" s="7" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N14" s="7" t="inlineStr">
         <is>
           <t>2026-11-04</t>
         </is>
       </c>
-      <c r="O13" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>에스에프씨</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>그 외 기타 분류 안된 화학제품 제조업</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>31,600 ~ 36,100원</t>
         </is>
       </c>
-      <c r="I14" s="10" t="n">
+      <c r="I15" s="4" t="n">
         <v>3750000</v>
       </c>
-      <c r="J14" s="11" t="n">
+      <c r="J15" s="5" t="n">
         <v>1353.8</v>
       </c>
-      <c r="K14" s="9" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
         </is>
       </c>
-      <c r="L14" s="8" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>2026-11-18</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>2026-11-23</t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr"/>
-      <c r="O14" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>씨아이에스케미칼</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>알루미늄 제련, 정련 및 합금 제조업</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>2026-11-30</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2026-12-04</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>5,400 ~ 6,800원</t>
         </is>
       </c>
-      <c r="I15" s="10" t="n">
+      <c r="I16" s="4" t="n">
         <v>3000000</v>
       </c>
-      <c r="J15" s="11" t="n">
+      <c r="J16" s="5" t="n">
         <v>204</v>
       </c>
-      <c r="K15" s="9" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
-      <c r="L15" s="8" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>2026-12-10</t>
         </is>
       </c>
-      <c r="M15" s="8" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>2026-12-15</t>
         </is>
       </c>
-      <c r="N15" s="8" t="inlineStr"/>
-      <c r="O15" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>제이앤티지</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>그 외 자동차용 신품 부품 제조업</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>26,400 ~ 31,900원</t>
         </is>
       </c>
-      <c r="I16" s="10" t="n">
+      <c r="I17" s="4" t="n">
         <v>3182000</v>
       </c>
-      <c r="J16" s="11" t="n">
+      <c r="J17" s="5" t="n">
         <v>1015.1</v>
       </c>
-      <c r="K16" s="9" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
         </is>
       </c>
-      <c r="L16" s="8" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>2026-11-12</t>
         </is>
       </c>
-      <c r="M16" s="8" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>2026-11-17</t>
         </is>
       </c>
-      <c r="N16" s="8" t="inlineStr"/>
-      <c r="O16" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>씨앤엠</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>전동기 및 발전기 제조업</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>10,000 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I17" s="10" t="n">
-        <v>2059500</v>
-      </c>
-      <c r="J17" s="11" t="n">
-        <v>267.7</v>
-      </c>
-      <c r="K17" s="9" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
-        </is>
-      </c>
-      <c r="L17" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="M17" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-17</t>
-        </is>
-      </c>
-      <c r="N17" s="8" t="inlineStr"/>
-      <c r="O17" s="12" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1690,268 +1690,268 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
+          <t>씨앤엠</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>전동기 및 발전기 제조업</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>10,000 ~ 13,000원</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>2059500</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>267.7</v>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
           <t>넥스아이</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>10,500 ~ 13,000원</t>
         </is>
       </c>
-      <c r="I18" s="5" t="n">
+      <c r="I19" s="10" t="n">
         <v>3750000</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="J19" s="11" t="n">
         <v>487.5</v>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K19" s="8" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-6384, 5198</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="N19" s="7" t="inlineStr"/>
+      <c r="O19" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>하나에어로다이내믹스</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>항공기용 부품 제조업</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>4,700 ~ 5,700원</t>
         </is>
       </c>
-      <c r="I19" s="5" t="n">
+      <c r="I20" s="10" t="n">
         <v>3300000</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="J20" s="11" t="n">
         <v>188.1</v>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="K20" s="8" t="inlineStr">
         <is>
           <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="L20" s="7" t="inlineStr">
         <is>
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="M20" s="7" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="N20" s="7" t="inlineStr"/>
+      <c r="O20" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>바로팜</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>전자상거래 소매 중개업</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G21" s="7" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>16,400 ~ 20,200원</t>
         </is>
       </c>
-      <c r="I20" s="5" t="n">
+      <c r="I21" s="10" t="n">
         <v>1335000</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="J21" s="11" t="n">
         <v>269.7</v>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K21" s="8" t="inlineStr">
         <is>
           <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr">
         <is>
           <t>2026-11-05</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>엠비디</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>물질 검사, 측정 및 분석기구 제조업</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>9,600 ~ 11,700원</t>
-        </is>
-      </c>
-      <c r="I21" s="10" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="J21" s="11" t="n">
-        <v>175.5</v>
-      </c>
-      <c r="K21" s="9" t="inlineStr">
-        <is>
-          <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
-        </is>
-      </c>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="M21" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-17</t>
-        </is>
-      </c>
-      <c r="N21" s="8" t="inlineStr"/>
+      <c r="N21" s="7" t="inlineStr"/>
       <c r="O21" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -1961,323 +1961,323 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>엠비디</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>물질 검사, 측정 및 분석기구 제조업</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>9,600 ~ 11,700원</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>175.5</v>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>래블업</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>시스템 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>19,000 ~ 22,000원</t>
         </is>
       </c>
-      <c r="I22" s="5" t="n">
+      <c r="I23" s="10" t="n">
         <v>1635000</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="J23" s="11" t="n">
         <v>359.7</v>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="K23" s="8" t="inlineStr">
         <is>
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="L23" s="7" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="N23" s="7" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="O22" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="O23" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>에이엘로봇</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>기타 기계 및 장비 제조업</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>정정-변경(수요예측)</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>15,700 ~ 17,600원</t>
         </is>
       </c>
-      <c r="I23" s="5" t="n">
+      <c r="I24" s="10" t="n">
         <v>1800000</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="J24" s="11" t="n">
         <v>316.8</v>
       </c>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="K24" s="8" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="L24" s="7" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="M24" s="7" t="inlineStr">
         <is>
           <t>2026-11-11</t>
         </is>
       </c>
-      <c r="N23" s="2" t="inlineStr"/>
-      <c r="O23" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="N24" s="7" t="inlineStr"/>
+      <c r="O24" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>SimwonAmericaCorp.</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>수요예측 항목 없음(원문 확인)</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr"/>
-      <c r="G24" s="8" t="inlineStr"/>
-      <c r="H24" s="8" t="inlineStr"/>
-      <c r="I24" s="10" t="inlineStr"/>
-      <c r="J24" s="11" t="inlineStr"/>
-      <c r="K24" s="9" t="inlineStr"/>
-      <c r="L24" s="8" t="inlineStr"/>
-      <c r="M24" s="8" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="N24" s="8" t="inlineStr"/>
-      <c r="O24" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>다비오</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>12,300 ~ 16,600원</t>
         </is>
       </c>
-      <c r="I25" s="10" t="n">
+      <c r="I26" s="4" t="n">
         <v>750000</v>
       </c>
-      <c r="J25" s="11" t="n">
+      <c r="J26" s="5" t="n">
         <v>124.5</v>
       </c>
-      <c r="K25" s="9" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
         </is>
       </c>
-      <c r="L25" s="8" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="M25" s="8" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>
       </c>
-      <c r="N25" s="8" t="inlineStr"/>
-      <c r="O25" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>영광와이케이엠씨</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>그 외 기타 금속가공업</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>9,400 ~ 11,000원</t>
-        </is>
-      </c>
-      <c r="I26" s="10" t="n">
-        <v>1694840</v>
-      </c>
-      <c r="J26" s="11" t="n">
-        <v>186.4</v>
-      </c>
-      <c r="K26" s="9" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
-        </is>
-      </c>
-      <c r="L26" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="M26" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="N26" s="8" t="inlineStr"/>
-      <c r="O26" s="12" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2291,136 +2291,132 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
+          <t>영광와이케이엠씨</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>그 외 기타 금속가공업</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>9,400 ~ 11,000원</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>1694840</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>186.4</v>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
           <t>영광</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>수상 금속 골조 구조재 제조업</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>14,000 ~ 17,000원</t>
         </is>
       </c>
-      <c r="I27" s="5" t="n">
+      <c r="I28" s="10" t="n">
         <v>1695000</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="J28" s="11" t="n">
         <v>288.1</v>
       </c>
-      <c r="K27" s="3" t="inlineStr">
+      <c r="K28" s="8" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="L28" s="7" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="M28" s="7" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="N28" s="7" t="inlineStr">
         <is>
           <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="O27" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>인텔리빅스</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>7,600 ~ 9,000원</t>
-        </is>
-      </c>
-      <c r="I28" s="10" t="n">
-        <v>1875000</v>
-      </c>
-      <c r="J28" s="11" t="n">
-        <v>168.8</v>
-      </c>
-      <c r="K28" s="9" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
-        </is>
-      </c>
-      <c r="L28" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="M28" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="N28" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
         </is>
       </c>
       <c r="O28" s="12" t="inlineStr">
@@ -2437,434 +2433,507 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
+          <t>인텔리빅스</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>7,600 ~ 9,000원</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>1875000</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>168.8</v>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="O29" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
           <t>아이엠기업인수목적1호</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>스팩</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>2,000원 (단일가)</t>
         </is>
       </c>
-      <c r="I29" s="5" t="n">
+      <c r="I30" s="10" t="n">
         <v>3750000</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="J30" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="K29" s="3" t="inlineStr">
+      <c r="K30" s="8" t="inlineStr">
         <is>
           <t>아이엠증권 02-2122-9688, 9485</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="L30" s="7" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="M30" s="7" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N29" s="2" t="inlineStr"/>
-      <c r="O29" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="N30" s="7" t="inlineStr"/>
+      <c r="O30" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>한화플러스제6호기업인수목적</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>스팩</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>2,000원 (단일가)</t>
         </is>
       </c>
-      <c r="I30" s="5" t="n">
+      <c r="I31" s="10" t="n">
         <v>4500000</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="J31" s="11" t="n">
         <v>90</v>
       </c>
-      <c r="K30" s="3" t="inlineStr">
+      <c r="K31" s="8" t="inlineStr">
         <is>
           <t>한화투자증권㈜ 02-3772-7395, 7398, 7393</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="M31" s="7" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="N31" s="7" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="O30" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="O31" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>디티에스</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="G31" s="8" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>17,000 ~ 18,500원</t>
         </is>
       </c>
-      <c r="I31" s="10" t="n">
+      <c r="I32" s="4" t="n">
         <v>1671687</v>
       </c>
-      <c r="J31" s="11" t="n">
+      <c r="J32" s="5" t="n">
         <v>309.3</v>
       </c>
-      <c r="K31" s="9" t="inlineStr">
+      <c r="K32" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
         </is>
       </c>
-      <c r="L31" s="8" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="M31" s="8" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="N31" s="8" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="O31" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="O32" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>엠에스바이오</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>그 외 기타 의료용 기기 제조업</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F32" s="8" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="G32" s="8" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>6,800 ~ 7,800원</t>
         </is>
       </c>
-      <c r="I32" s="10" t="n">
+      <c r="I33" s="4" t="n">
         <v>2840000</v>
       </c>
-      <c r="J32" s="11" t="n">
+      <c r="J33" s="5" t="n">
         <v>221.5</v>
       </c>
-      <c r="K32" s="9" t="inlineStr">
+      <c r="K33" s="3" t="inlineStr">
         <is>
           <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
-      <c r="L32" s="8" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="M32" s="8" t="inlineStr">
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="N32" s="8" t="inlineStr">
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="O32" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="O33" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>크리에이츠</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>15,000 ~ 18,000원</t>
         </is>
       </c>
-      <c r="I33" s="10" t="n">
+      <c r="I34" s="4" t="n">
         <v>1050000</v>
       </c>
-      <c r="J33" s="11" t="n">
+      <c r="J34" s="5" t="n">
         <v>189</v>
       </c>
-      <c r="K33" s="9" t="inlineStr">
+      <c r="K34" s="3" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-7414, 7375, 7651</t>
         </is>
       </c>
-      <c r="L33" s="8" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="M33" s="8" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="N33" s="8" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="O33" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="O34" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>티앤이코리아</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>산업용 송풍기 및 배기장치 제조업</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="G34" s="8" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>12,600 ~ 15,300원</t>
         </is>
       </c>
-      <c r="I34" s="10" t="n">
+      <c r="I35" s="4" t="n">
         <v>1800000</v>
       </c>
-      <c r="J34" s="11" t="n">
+      <c r="J35" s="5" t="n">
         <v>275.4</v>
       </c>
-      <c r="K34" s="9" t="inlineStr">
+      <c r="K35" s="3" t="inlineStr">
         <is>
           <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
         </is>
       </c>
-      <c r="L34" s="8" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="M34" s="8" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="N34" s="8" t="inlineStr">
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="O34" s="12" t="inlineStr">
+      <c r="O35" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O34"/>
+  <autoFilter ref="A1:O35"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -2899,6 +2968,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2910,7 +2980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O65"/>
+  <dimension ref="A1:O66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3010,342 +3080,342 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>KTE</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>배전반 및 전기 자동제어반 제조업</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>19,000 ~ 23,000원</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>2112000</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>485.8</v>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>NH투자증권 02-768-7462, 7467</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>케이엠에프</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>기타 식품 제조업</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>2026-11-16</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>15,000 ~ 17,800원</t>
         </is>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I3" s="10" t="n">
         <v>1500000</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="J3" s="11" t="n">
         <v>267</v>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K3" s="8" t="inlineStr">
         <is>
           <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799 / 아이비케이투자증권㈜ 02-6915-5337, 5338, 5799</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L3" s="7" t="inlineStr">
         <is>
           <t>2026-11-24</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M3" s="7" t="inlineStr">
         <is>
           <t>2026-11-27</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="N3" s="7" t="inlineStr"/>
+      <c r="O3" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>엔키화이트햇</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>정정-변경(수요예측)</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>2026-11-26</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>13,000 ~ 16,500원</t>
         </is>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="I4" s="10" t="n">
         <v>1258000</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="J4" s="11" t="n">
         <v>207.6</v>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L4" s="7" t="inlineStr">
         <is>
           <t>2026-12-01</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M4" s="7" t="inlineStr">
         <is>
           <t>2026-12-04</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="N4" s="7" t="inlineStr"/>
+      <c r="O4" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>아델</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>정정-변경(문의처)</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>2026-11-12</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>2026-11-18</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>18,000 ~ 25,000원</t>
         </is>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="I5" s="10" t="n">
         <v>1627500</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="J5" s="11" t="n">
         <v>406.9</v>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-8213, 6661</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>2026-11-23</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>2026-11-26</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr"/>
+      <c r="O5" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>케이엠에프</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>기타 식품 제조업</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>2026-11-16</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>15,000 ~ 17,800원</t>
         </is>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I6" s="10" t="n">
         <v>1500000</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="J6" s="11" t="n">
         <v>267</v>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K6" s="8" t="inlineStr">
         <is>
           <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L6" s="7" t="inlineStr">
         <is>
           <t>2026-11-24</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M6" s="7" t="inlineStr">
         <is>
           <t>2026-11-27</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>우리투자제1호기업인수목적</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>스팩</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-25</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>2,000원 (단일가)</t>
-        </is>
-      </c>
-      <c r="I6" s="10" t="n">
-        <v>4875000</v>
-      </c>
-      <c r="J6" s="11" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>우리투자증권 02-6390-3889</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-02</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-07</t>
-        </is>
-      </c>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="7" t="inlineStr"/>
       <c r="O6" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -3360,330 +3430,330 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>우리투자제1호기업인수목적</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>스팩</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,000원 (단일가)</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>4875000</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>우리투자증권 02-6390-3889</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-07</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
           <t>제논</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>정정-변경(수요예측)</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>2026-11-16</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>9,700 ~ 12,200원</t>
         </is>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="I8" s="10" t="n">
         <v>1550000</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J8" s="11" t="n">
         <v>189.1</v>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-8023, 7653, 7850</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L8" s="7" t="inlineStr">
         <is>
           <t>2026-11-24</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M8" s="7" t="inlineStr">
         <is>
           <t>2026-11-27</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="N8" s="7" t="inlineStr"/>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>제논</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>9,700 ~ 12,200원</t>
         </is>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="I9" s="10" t="n">
         <v>1550000</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J9" s="11" t="n">
         <v>189.1</v>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K9" s="8" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-8023, 7653, 7850</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="L9" s="7" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
+      <c r="N9" s="7" t="inlineStr"/>
+      <c r="O9" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>동원파츠</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>반도체 제조용 기계 제조업</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>23,000 ~ 26,500원</t>
         </is>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="I10" s="10" t="n">
         <v>1522500</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J10" s="11" t="n">
         <v>403.5</v>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K10" s="8" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-6975, 8217, 7651</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L10" s="7" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M10" s="7" t="inlineStr">
         <is>
           <t>2026-11-05</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="N10" s="7" t="inlineStr"/>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>인터엑스</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>2026-11-30</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>2026-12-04</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>10,000 ~ 13,000원</t>
         </is>
       </c>
-      <c r="I10" s="10" t="n">
+      <c r="I11" s="4" t="n">
         <v>2250000</v>
       </c>
-      <c r="J10" s="11" t="n">
+      <c r="J11" s="5" t="n">
         <v>292.5</v>
       </c>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5700, 6648</t>
         </is>
       </c>
-      <c r="L10" s="8" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>2026-12-09</t>
         </is>
       </c>
-      <c r="M10" s="8" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>2026-12-14</t>
         </is>
       </c>
-      <c r="N10" s="8" t="inlineStr"/>
-      <c r="O10" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>유캐스트</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>기타 무선 통신장비 제조업</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>19,000 ~ 23,000원</t>
-        </is>
-      </c>
-      <c r="I11" s="10" t="n">
-        <v>600000</v>
-      </c>
-      <c r="J11" s="11" t="n">
-        <v>138</v>
-      </c>
-      <c r="K11" s="9" t="inlineStr">
-        <is>
-          <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
-        </is>
-      </c>
-      <c r="L11" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="M11" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-      <c r="N11" s="8" t="inlineStr"/>
-      <c r="O11" s="12" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3697,200 +3767,200 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>유캐스트</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>기타 무선 통신장비 제조업</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>19,000 ~ 23,000원</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>600000</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>138</v>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
           <t>옵토닉스</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>광학렌즈 및 광학요소 제조업</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>10,000 ~ 12,000원</t>
         </is>
       </c>
-      <c r="I12" s="5" t="n">
+      <c r="I13" s="10" t="n">
         <v>1572490</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="J13" s="11" t="n">
         <v>188.7</v>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K13" s="8" t="inlineStr">
         <is>
           <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L13" s="7" t="inlineStr">
         <is>
           <t>2026-11-05</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="N13" s="7" t="inlineStr"/>
+      <c r="O13" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>이노보테라퓨틱스</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>2026-11-26</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>2026-12-02</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>20,000 ~ 24,000원</t>
         </is>
       </c>
-      <c r="I13" s="10" t="n">
+      <c r="I14" s="4" t="n">
         <v>1650000</v>
       </c>
-      <c r="J13" s="11" t="n">
+      <c r="J14" s="5" t="n">
         <v>396</v>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L13" s="8" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>2026-12-07</t>
         </is>
       </c>
-      <c r="M13" s="8" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>2026-12-10</t>
         </is>
       </c>
-      <c r="N13" s="8" t="inlineStr"/>
-      <c r="O13" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>에이엔에이치스트럭쳐</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>기타 엔지니어링 서비스업</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-19</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-25</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>11,200 ~ 13,600원</t>
-        </is>
-      </c>
-      <c r="I14" s="10" t="n">
-        <v>1575000</v>
-      </c>
-      <c r="J14" s="11" t="n">
-        <v>214.2</v>
-      </c>
-      <c r="K14" s="9" t="inlineStr">
-        <is>
-          <t>NH투자증권 02-2229-6315, 6829</t>
-        </is>
-      </c>
-      <c r="L14" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-27</t>
-        </is>
-      </c>
-      <c r="M14" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-02</t>
-        </is>
-      </c>
-      <c r="N14" s="8" t="inlineStr"/>
-      <c r="O14" s="12" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3904,342 +3974,342 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>에이엔에이치스트럭쳐</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>기타 엔지니어링 서비스업</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>11,200 ~ 13,600원</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>1575000</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>214.2</v>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>NH투자증권 02-2229-6315, 6829</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
           <t>이에스티</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>그 외 기타 전자부품 제조업</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>10,600 ~ 12,400원</t>
         </is>
       </c>
-      <c r="I15" s="5" t="n">
+      <c r="I16" s="10" t="n">
         <v>1650000</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="J16" s="11" t="n">
         <v>204.6</v>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K16" s="8" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="L16" s="7" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N16" s="7" t="inlineStr">
         <is>
           <t>2026-11-04</t>
         </is>
       </c>
-      <c r="O15" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>에스에프씨</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>그 외 기타 분류 안된 화학제품 제조업</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>31,600 ~ 36,100원</t>
         </is>
       </c>
-      <c r="I16" s="10" t="n">
+      <c r="I17" s="4" t="n">
         <v>3750000</v>
       </c>
-      <c r="J16" s="11" t="n">
+      <c r="J17" s="5" t="n">
         <v>1353.8</v>
       </c>
-      <c r="K16" s="9" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
         </is>
       </c>
-      <c r="L16" s="8" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>2026-11-18</t>
         </is>
       </c>
-      <c r="M16" s="8" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>2026-11-23</t>
         </is>
       </c>
-      <c r="N16" s="8" t="inlineStr"/>
-      <c r="O16" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>씨아이에스케미칼</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>알루미늄 제련, 정련 및 합금 제조업</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>2026-11-30</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>2026-12-04</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>5,400 ~ 6,800원</t>
         </is>
       </c>
-      <c r="I17" s="10" t="n">
+      <c r="I18" s="4" t="n">
         <v>3000000</v>
       </c>
-      <c r="J17" s="11" t="n">
+      <c r="J18" s="5" t="n">
         <v>204</v>
       </c>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="K18" s="3" t="inlineStr">
         <is>
           <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
-      <c r="L17" s="8" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>2026-12-10</t>
         </is>
       </c>
-      <c r="M17" s="8" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>2026-12-15</t>
         </is>
       </c>
-      <c r="N17" s="8" t="inlineStr"/>
-      <c r="O17" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>제이앤티지</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>그 외 자동차용 신품 부품 제조업</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>26,400 ~ 31,900원</t>
         </is>
       </c>
-      <c r="I18" s="10" t="n">
+      <c r="I19" s="4" t="n">
         <v>3182000</v>
       </c>
-      <c r="J18" s="11" t="n">
+      <c r="J19" s="5" t="n">
         <v>1015.1</v>
       </c>
-      <c r="K18" s="9" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
         </is>
       </c>
-      <c r="L18" s="8" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>2026-11-12</t>
         </is>
       </c>
-      <c r="M18" s="8" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>2026-11-17</t>
         </is>
       </c>
-      <c r="N18" s="8" t="inlineStr"/>
-      <c r="O18" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>씨앤엠</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>전동기 및 발전기 제조업</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>10,000 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I19" s="10" t="n">
-        <v>2059500</v>
-      </c>
-      <c r="J19" s="11" t="n">
-        <v>267.7</v>
-      </c>
-      <c r="K19" s="9" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
-        </is>
-      </c>
-      <c r="L19" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="M19" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-17</t>
-        </is>
-      </c>
-      <c r="N19" s="8" t="inlineStr"/>
-      <c r="O19" s="12" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4253,268 +4323,268 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
+          <t>씨앤엠</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>전동기 및 발전기 제조업</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>10,000 ~ 13,000원</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>2059500</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>267.7</v>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
           <t>넥스아이</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G21" s="7" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>10,500 ~ 13,000원</t>
         </is>
       </c>
-      <c r="I20" s="5" t="n">
+      <c r="I21" s="10" t="n">
         <v>3750000</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="J21" s="11" t="n">
         <v>487.5</v>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K21" s="8" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-6384, 5198</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="N21" s="7" t="inlineStr"/>
+      <c r="O21" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>하나에어로다이내믹스</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>항공기용 부품 제조업</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>4,700 ~ 5,700원</t>
         </is>
       </c>
-      <c r="I21" s="5" t="n">
+      <c r="I22" s="10" t="n">
         <v>3300000</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="J22" s="11" t="n">
         <v>188.1</v>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="K22" s="8" t="inlineStr">
         <is>
           <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="L22" s="7" t="inlineStr">
         <is>
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="M22" s="7" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr"/>
-      <c r="O21" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="N22" s="7" t="inlineStr"/>
+      <c r="O22" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>바로팜</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>전자상거래 소매 중개업</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>16,400 ~ 20,200원</t>
         </is>
       </c>
-      <c r="I22" s="5" t="n">
+      <c r="I23" s="10" t="n">
         <v>1335000</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="J23" s="11" t="n">
         <v>269.7</v>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="K23" s="8" t="inlineStr">
         <is>
           <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="L23" s="7" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr">
         <is>
           <t>2026-11-05</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>엠비디</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>물질 검사, 측정 및 분석기구 제조업</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>9,600 ~ 11,700원</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="J23" s="11" t="n">
-        <v>175.5</v>
-      </c>
-      <c r="K23" s="9" t="inlineStr">
-        <is>
-          <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
-        </is>
-      </c>
-      <c r="L23" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="M23" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-17</t>
-        </is>
-      </c>
-      <c r="N23" s="8" t="inlineStr"/>
+      <c r="N23" s="7" t="inlineStr"/>
       <c r="O23" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -4524,526 +4594,526 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>엠비디</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>물질 검사, 측정 및 분석기구 제조업</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>9,600 ~ 11,700원</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>175.5</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>래블업</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>시스템 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>19,000 ~ 22,000원</t>
         </is>
       </c>
-      <c r="I24" s="5" t="n">
+      <c r="I25" s="10" t="n">
         <v>1635000</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="J25" s="11" t="n">
         <v>359.7</v>
       </c>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="K25" s="8" t="inlineStr">
         <is>
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="L25" s="7" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="N25" s="7" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="O24" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="O25" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>이에스티</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>그 외 기타 전자부품 제조업</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>10,600 ~ 12,400원</t>
         </is>
       </c>
-      <c r="I25" s="5" t="n">
+      <c r="I26" s="10" t="n">
         <v>1650000</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="J26" s="11" t="n">
         <v>204.6</v>
       </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="K26" s="8" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="L26" s="7" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr"/>
+      <c r="N26" s="7" t="inlineStr">
         <is>
           <t>2026-11-04</t>
         </is>
       </c>
-      <c r="O25" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="O26" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>에이엘로봇</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>기타 기계 및 장비 제조업</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>정정-변경(수요예측)</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>15,700 ~ 17,600원</t>
         </is>
       </c>
-      <c r="I26" s="5" t="n">
+      <c r="I27" s="10" t="n">
         <v>1800000</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="J27" s="11" t="n">
         <v>316.8</v>
       </c>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="K27" s="8" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="L27" s="7" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="M27" s="7" t="inlineStr">
         <is>
           <t>2026-11-11</t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="N27" s="7" t="inlineStr"/>
+      <c r="O27" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>아델</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>2026-11-12</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>2026-11-18</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>18,000 ~ 25,000원</t>
         </is>
       </c>
-      <c r="I27" s="10" t="n">
+      <c r="I28" s="4" t="n">
         <v>1627500</v>
       </c>
-      <c r="J27" s="11" t="n">
+      <c r="J28" s="5" t="n">
         <v>406.9</v>
       </c>
-      <c r="K27" s="9" t="inlineStr">
+      <c r="K28" s="3" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L27" s="8" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>2026-11-23</t>
         </is>
       </c>
-      <c r="M27" s="8" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>2026-11-26</t>
         </is>
       </c>
-      <c r="N27" s="8" t="inlineStr"/>
-      <c r="O27" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>SimwonAmericaCorp.</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>수요예측 항목 없음(원문 확인)</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr"/>
-      <c r="G28" s="8" t="inlineStr"/>
-      <c r="H28" s="8" t="inlineStr"/>
-      <c r="I28" s="10" t="inlineStr"/>
-      <c r="J28" s="11" t="inlineStr"/>
-      <c r="K28" s="9" t="inlineStr"/>
-      <c r="L28" s="8" t="inlineStr"/>
-      <c r="M28" s="8" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="4" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="3" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="N28" s="8" t="inlineStr"/>
-      <c r="O28" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>다비오</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>12,300 ~ 16,600원</t>
         </is>
       </c>
-      <c r="I29" s="10" t="n">
+      <c r="I30" s="4" t="n">
         <v>750000</v>
       </c>
-      <c r="J29" s="11" t="n">
+      <c r="J30" s="5" t="n">
         <v>124.5</v>
       </c>
-      <c r="K29" s="9" t="inlineStr">
+      <c r="K30" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
         </is>
       </c>
-      <c r="L29" s="8" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="M29" s="8" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>
       </c>
-      <c r="N29" s="8" t="inlineStr"/>
-      <c r="O29" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>엔키화이트햇</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>13,000 ~ 16,500원</t>
         </is>
       </c>
-      <c r="I30" s="10" t="n">
+      <c r="I31" s="4" t="n">
         <v>1258000</v>
       </c>
-      <c r="J30" s="11" t="n">
+      <c r="J31" s="5" t="n">
         <v>207.6</v>
       </c>
-      <c r="K30" s="9" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
         </is>
       </c>
-      <c r="L30" s="8" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>2026-11-12</t>
         </is>
       </c>
-      <c r="M30" s="8" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>2026-11-17</t>
         </is>
       </c>
-      <c r="N30" s="8" t="inlineStr"/>
-      <c r="O30" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>영광와이케이엠씨</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>그 외 기타 금속가공업</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>9,400 ~ 11,000원</t>
-        </is>
-      </c>
-      <c r="I31" s="10" t="n">
-        <v>1694840</v>
-      </c>
-      <c r="J31" s="11" t="n">
-        <v>186.4</v>
-      </c>
-      <c r="K31" s="9" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
-        </is>
-      </c>
-      <c r="L31" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="M31" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="N31" s="8" t="inlineStr"/>
-      <c r="O31" s="12" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -5057,136 +5127,132 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
+          <t>영광와이케이엠씨</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>그 외 기타 금속가공업</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>9,400 ~ 11,000원</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>1694840</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>186.4</v>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
           <t>영광</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>수상 금속 골조 구조재 제조업</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>14,000 ~ 17,000원</t>
         </is>
       </c>
-      <c r="I32" s="5" t="n">
+      <c r="I33" s="10" t="n">
         <v>1695000</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="J33" s="11" t="n">
         <v>288.1</v>
       </c>
-      <c r="K32" s="3" t="inlineStr">
+      <c r="K33" s="8" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="L33" s="7" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="M33" s="7" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="N33" s="7" t="inlineStr">
         <is>
           <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="O32" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>인텔리빅스</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="inlineStr">
-        <is>
-          <t>7,600 ~ 9,000원</t>
-        </is>
-      </c>
-      <c r="I33" s="10" t="n">
-        <v>1875000</v>
-      </c>
-      <c r="J33" s="11" t="n">
-        <v>168.8</v>
-      </c>
-      <c r="K33" s="9" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
-        </is>
-      </c>
-      <c r="L33" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="M33" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="N33" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
         </is>
       </c>
       <c r="O33" s="12" t="inlineStr">
@@ -5203,104 +5269,108 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
+          <t>인텔리빅스</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>7,600 ~ 9,000원</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>1875000</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>168.8</v>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="O34" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
           <t>아이엠기업인수목적1호</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>스팩</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>2,000원 (단일가)</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J34" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>아이엠증권 02-2122-9688, 9485</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
-      <c r="O34" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>아이엠기업인수목적1호</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>스팩</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="H35" s="8" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>2,000원 (단일가)</t>
         </is>
@@ -5311,14 +5381,22 @@
       <c r="J35" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="K35" s="9" t="inlineStr">
+      <c r="K35" s="8" t="inlineStr">
         <is>
           <t>아이엠증권 02-2122-9688, 9485</t>
         </is>
       </c>
-      <c r="L35" s="8" t="inlineStr"/>
-      <c r="M35" s="8" t="inlineStr"/>
-      <c r="N35" s="8" t="inlineStr"/>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="M35" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N35" s="7" t="inlineStr"/>
       <c r="O35" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -5326,61 +5404,61 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>제논</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>아이엠기업인수목적1호</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>스팩</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="H36" s="8" t="inlineStr">
-        <is>
-          <t>9,700 ~ 12,200원</t>
-        </is>
-      </c>
-      <c r="I36" s="10" t="n">
-        <v>1550000</v>
-      </c>
-      <c r="J36" s="11" t="n">
-        <v>189.1</v>
-      </c>
-      <c r="K36" s="9" t="inlineStr">
-        <is>
-          <t>삼성증권 02-2020-8023, 7653, 7850</t>
-        </is>
-      </c>
-      <c r="L36" s="8" t="inlineStr"/>
-      <c r="M36" s="8" t="inlineStr"/>
-      <c r="N36" s="8" t="inlineStr"/>
-      <c r="O36" s="12" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>2,000원 (단일가)</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>아이엠증권 02-2122-9688, 9485</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -5394,1110 +5472,1110 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
+          <t>제논</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>9,700 ~ 12,200원</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>1550000</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>189.1</v>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-8023, 7653, 7850</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
           <t>한화플러스제6호기업인수목적</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>스팩</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E38" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G38" s="7" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H38" s="7" t="inlineStr">
         <is>
           <t>2,000원 (단일가)</t>
         </is>
       </c>
-      <c r="I37" s="5" t="n">
+      <c r="I38" s="10" t="n">
         <v>4500000</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="J38" s="11" t="n">
         <v>90</v>
       </c>
-      <c r="K37" s="3" t="inlineStr">
+      <c r="K38" s="8" t="inlineStr">
         <is>
           <t>한화투자증권㈜ 02-3772-7395, 7398, 7393</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="L38" s="7" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
+      <c r="M38" s="7" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="N38" s="7" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="O37" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="O38" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>래블업</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>시스템 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E39" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>19,000 ~ 22,000원</t>
         </is>
       </c>
-      <c r="I38" s="5" t="n">
+      <c r="I39" s="10" t="n">
         <v>1635000</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="J39" s="11" t="n">
         <v>359.7</v>
       </c>
-      <c r="K38" s="3" t="inlineStr">
+      <c r="K39" s="8" t="inlineStr">
         <is>
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="L39" s="7" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr"/>
+      <c r="N39" s="7" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="O38" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="O39" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>한화플러스제6호기업인수목적</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>스팩</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="G39" s="8" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="H39" s="8" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>2,000원 (단일가)</t>
         </is>
       </c>
-      <c r="I39" s="10" t="n">
+      <c r="I40" s="4" t="n">
         <v>4500000</v>
       </c>
-      <c r="J39" s="11" t="n">
+      <c r="J40" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="K39" s="9" t="inlineStr">
+      <c r="K40" s="3" t="inlineStr">
         <is>
           <t>한화투자증권㈜ 02-3772-7395, 7398, 7393</t>
         </is>
       </c>
-      <c r="L39" s="8" t="inlineStr"/>
-      <c r="M39" s="8" t="inlineStr"/>
-      <c r="N39" s="8" t="inlineStr">
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="O39" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="O40" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>케이엠에프</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>기타 식품 제조업</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>2026-11-16</t>
         </is>
       </c>
-      <c r="G40" s="8" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
       </c>
-      <c r="H40" s="8" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>15,000 ~ 17,800원</t>
         </is>
       </c>
-      <c r="I40" s="10" t="n">
+      <c r="I41" s="4" t="n">
         <v>1500000</v>
       </c>
-      <c r="J40" s="11" t="n">
+      <c r="J41" s="5" t="n">
         <v>267</v>
       </c>
-      <c r="K40" s="9" t="inlineStr">
+      <c r="K41" s="3" t="inlineStr">
         <is>
           <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
         </is>
       </c>
-      <c r="L40" s="8" t="inlineStr"/>
-      <c r="M40" s="8" t="inlineStr"/>
-      <c r="N40" s="8" t="inlineStr"/>
-      <c r="O40" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>바로팜</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>전자상거래 소매 중개업</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="G41" s="8" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="H41" s="8" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>16,400 ~ 20,200원</t>
         </is>
       </c>
-      <c r="I41" s="10" t="n">
+      <c r="I42" s="4" t="n">
         <v>1335000</v>
       </c>
-      <c r="J41" s="11" t="n">
+      <c r="J42" s="5" t="n">
         <v>269.7</v>
       </c>
-      <c r="K41" s="9" t="inlineStr">
+      <c r="K42" s="3" t="inlineStr">
         <is>
           <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L41" s="8" t="inlineStr"/>
-      <c r="M41" s="8" t="inlineStr"/>
-      <c r="N41" s="8" t="inlineStr"/>
-      <c r="O41" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>동원파츠</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>반도체 제조용 기계 제조업</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="G42" s="8" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="H42" s="8" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>23,000 ~ 26,500원</t>
         </is>
       </c>
-      <c r="I42" s="10" t="n">
+      <c r="I43" s="4" t="n">
         <v>1522500</v>
       </c>
-      <c r="J42" s="11" t="n">
+      <c r="J43" s="5" t="n">
         <v>403.5</v>
       </c>
-      <c r="K42" s="9" t="inlineStr">
+      <c r="K43" s="3" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-6975, 8217, 7651</t>
         </is>
       </c>
-      <c r="L42" s="8" t="inlineStr"/>
-      <c r="M42" s="8" t="inlineStr"/>
-      <c r="N42" s="8" t="inlineStr"/>
-      <c r="O42" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>디티에스</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
-      <c r="D43" s="9" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F43" s="8" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="G43" s="8" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="H43" s="8" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>17,000 ~ 18,500원</t>
         </is>
       </c>
-      <c r="I43" s="10" t="n">
+      <c r="I44" s="4" t="n">
         <v>1671687</v>
       </c>
-      <c r="J43" s="11" t="n">
+      <c r="J44" s="5" t="n">
         <v>309.3</v>
       </c>
-      <c r="K43" s="9" t="inlineStr">
+      <c r="K44" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
         </is>
       </c>
-      <c r="L43" s="8" t="inlineStr">
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="M43" s="8" t="inlineStr">
+      <c r="M44" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="N43" s="8" t="inlineStr">
+      <c r="N44" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="O43" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="O44" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>엠에스바이오</t>
         </is>
       </c>
-      <c r="C44" s="9" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>그 외 기타 의료용 기기 제조업</t>
         </is>
       </c>
-      <c r="D44" s="9" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E44" s="8" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F44" s="8" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="G44" s="8" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="H44" s="8" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>6,800 ~ 7,800원</t>
         </is>
       </c>
-      <c r="I44" s="10" t="n">
+      <c r="I45" s="4" t="n">
         <v>2840000</v>
       </c>
-      <c r="J44" s="11" t="n">
+      <c r="J45" s="5" t="n">
         <v>221.5</v>
       </c>
-      <c r="K44" s="9" t="inlineStr">
+      <c r="K45" s="3" t="inlineStr">
         <is>
           <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
-      <c r="L44" s="8" t="inlineStr">
+      <c r="L45" s="2" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="M44" s="8" t="inlineStr">
+      <c r="M45" s="2" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="N44" s="8" t="inlineStr">
+      <c r="N45" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="O44" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="O45" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>옵토닉스</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>광학렌즈 및 광학요소 제조업</t>
         </is>
       </c>
-      <c r="D45" s="9" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E45" s="8" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F45" s="8" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="G45" s="8" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="H45" s="8" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>10,000 ~ 12,000원</t>
         </is>
       </c>
-      <c r="I45" s="10" t="n">
+      <c r="I46" s="4" t="n">
         <v>1572490</v>
       </c>
-      <c r="J45" s="11" t="n">
+      <c r="J46" s="5" t="n">
         <v>188.7</v>
       </c>
-      <c r="K45" s="9" t="inlineStr">
+      <c r="K46" s="3" t="inlineStr">
         <is>
           <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
-      <c r="L45" s="8" t="inlineStr"/>
-      <c r="M45" s="8" t="inlineStr"/>
-      <c r="N45" s="8" t="inlineStr"/>
-      <c r="O45" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>넥스아이</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
-      <c r="D46" s="9" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E46" s="8" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F46" s="8" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="G46" s="8" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="H46" s="8" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>10,500 ~ 13,000원</t>
         </is>
       </c>
-      <c r="I46" s="10" t="n">
+      <c r="I47" s="4" t="n">
         <v>3750000</v>
       </c>
-      <c r="J46" s="11" t="n">
+      <c r="J47" s="5" t="n">
         <v>487.5</v>
       </c>
-      <c r="K46" s="9" t="inlineStr">
+      <c r="K47" s="3" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-6384, 5198</t>
         </is>
       </c>
-      <c r="L46" s="8" t="inlineStr"/>
-      <c r="M46" s="8" t="inlineStr"/>
-      <c r="N46" s="8" t="inlineStr"/>
-      <c r="O46" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>크리에이츠</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
         </is>
       </c>
-      <c r="D47" s="9" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E47" s="8" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F47" s="8" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="G47" s="8" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H47" s="8" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>15,000 ~ 18,000원</t>
         </is>
       </c>
-      <c r="I47" s="10" t="n">
+      <c r="I48" s="4" t="n">
         <v>1050000</v>
       </c>
-      <c r="J47" s="11" t="n">
+      <c r="J48" s="5" t="n">
         <v>189</v>
       </c>
-      <c r="K47" s="9" t="inlineStr">
+      <c r="K48" s="3" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-7414, 7375, 7651</t>
         </is>
       </c>
-      <c r="L47" s="8" t="inlineStr">
+      <c r="L48" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="M47" s="8" t="inlineStr">
+      <c r="M48" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="N47" s="8" t="inlineStr">
+      <c r="N48" s="2" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="O47" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="O48" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>티앤이코리아</t>
         </is>
       </c>
-      <c r="C48" s="9" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>산업용 송풍기 및 배기장치 제조업</t>
         </is>
       </c>
-      <c r="D48" s="9" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F48" s="8" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="G48" s="8" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="H48" s="8" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>12,600 ~ 15,300원</t>
         </is>
       </c>
-      <c r="I48" s="10" t="n">
+      <c r="I49" s="4" t="n">
         <v>1800000</v>
       </c>
-      <c r="J48" s="11" t="n">
+      <c r="J49" s="5" t="n">
         <v>275.4</v>
       </c>
-      <c r="K48" s="9" t="inlineStr">
+      <c r="K49" s="3" t="inlineStr">
         <is>
           <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
         </is>
       </c>
-      <c r="L48" s="8" t="inlineStr">
+      <c r="L49" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="M48" s="8" t="inlineStr">
+      <c r="M49" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="N48" s="8" t="inlineStr">
+      <c r="N49" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="O48" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="O49" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>하나에어로다이내믹스</t>
         </is>
       </c>
-      <c r="C49" s="9" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>항공기용 부품 제조업</t>
         </is>
       </c>
-      <c r="D49" s="9" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E49" s="8" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F49" s="8" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="G49" s="8" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="H49" s="8" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>4,700 ~ 5,700원</t>
         </is>
       </c>
-      <c r="I49" s="10" t="n">
+      <c r="I50" s="4" t="n">
         <v>3300000</v>
       </c>
-      <c r="J49" s="11" t="n">
+      <c r="J50" s="5" t="n">
         <v>188.1</v>
       </c>
-      <c r="K49" s="9" t="inlineStr">
+      <c r="K50" s="3" t="inlineStr">
         <is>
           <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
         </is>
       </c>
-      <c r="L49" s="8" t="inlineStr"/>
-      <c r="M49" s="8" t="inlineStr"/>
-      <c r="N49" s="8" t="inlineStr"/>
-      <c r="O49" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>래블업</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>시스템 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D50" s="9" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E50" s="8" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F50" s="8" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="G50" s="8" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H50" s="8" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>19,000 ~ 22,000원</t>
         </is>
       </c>
-      <c r="I50" s="10" t="n">
+      <c r="I51" s="4" t="n">
         <v>1635000</v>
       </c>
-      <c r="J50" s="11" t="n">
+      <c r="J51" s="5" t="n">
         <v>359.7</v>
       </c>
-      <c r="K50" s="9" t="inlineStr">
+      <c r="K51" s="3" t="inlineStr">
         <is>
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="L50" s="8" t="inlineStr"/>
-      <c r="M50" s="8" t="inlineStr"/>
-      <c r="N50" s="8" t="inlineStr">
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="O50" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="O51" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>영광</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>수상 금속 골조 구조재 제조업</t>
         </is>
       </c>
-      <c r="D51" s="9" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E51" s="8" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F51" s="8" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="G51" s="8" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H51" s="8" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>14,000 ~ 17,000원</t>
         </is>
       </c>
-      <c r="I51" s="10" t="n">
+      <c r="I52" s="4" t="n">
         <v>1695000</v>
       </c>
-      <c r="J51" s="11" t="n">
+      <c r="J52" s="5" t="n">
         <v>288.1</v>
       </c>
-      <c r="K51" s="9" t="inlineStr">
+      <c r="K52" s="3" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L51" s="8" t="inlineStr"/>
-      <c r="M51" s="8" t="inlineStr"/>
-      <c r="N51" s="8" t="inlineStr">
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="O51" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="O52" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>이에스티</t>
         </is>
       </c>
-      <c r="C52" s="9" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>그 외 기타 전자부품 제조업</t>
         </is>
       </c>
-      <c r="D52" s="9" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E52" s="8" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F52" s="8" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="G52" s="8" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="H52" s="8" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>10,600 ~ 12,400원</t>
         </is>
       </c>
-      <c r="I52" s="10" t="n">
+      <c r="I53" s="4" t="n">
         <v>1650000</v>
       </c>
-      <c r="J52" s="11" t="n">
+      <c r="J53" s="5" t="n">
         <v>204.6</v>
       </c>
-      <c r="K52" s="9" t="inlineStr">
+      <c r="K53" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="L52" s="8" t="inlineStr"/>
-      <c r="M52" s="8" t="inlineStr"/>
-      <c r="N52" s="8" t="inlineStr">
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
         <is>
           <t>2026-11-04</t>
         </is>
       </c>
-      <c r="O52" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>에이엘로봇</t>
-        </is>
-      </c>
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>기타 기계 및 장비 제조업</t>
-        </is>
-      </c>
-      <c r="D53" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F53" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G53" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="H53" s="8" t="inlineStr">
-        <is>
-          <t>15,700 ~ 17,600원</t>
-        </is>
-      </c>
-      <c r="I53" s="10" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="J53" s="11" t="n">
-        <v>316.8</v>
-      </c>
-      <c r="K53" s="9" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
-        </is>
-      </c>
-      <c r="L53" s="8" t="inlineStr"/>
-      <c r="M53" s="8" t="inlineStr"/>
-      <c r="N53" s="8" t="inlineStr"/>
-      <c r="O53" s="12" t="inlineStr">
+      <c r="O53" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -6506,857 +6584,918 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>에이엘로봇</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>기타 기계 및 장비 제조업</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>15,700 ~ 17,600원</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>316.8</v>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>엠비디</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>물질 검사, 측정 및 분석기구 제조업</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D55" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="E55" s="9" t="inlineStr">
         <is>
           <t>정정-변경(수요예측)</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="7" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G55" s="7" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="7" t="inlineStr">
         <is>
           <t>9,600 ~ 11,700원</t>
         </is>
       </c>
-      <c r="I54" s="5" t="n">
+      <c r="I55" s="10" t="n">
         <v>1500000</v>
       </c>
-      <c r="J54" s="6" t="n">
+      <c r="J55" s="11" t="n">
         <v>175.5</v>
       </c>
-      <c r="K54" s="3" t="inlineStr">
+      <c r="K55" s="8" t="inlineStr">
         <is>
           <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr">
+      <c r="L55" s="7" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="M54" s="2" t="inlineStr">
+      <c r="M55" s="7" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="N54" s="2" t="inlineStr"/>
-      <c r="O54" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="N55" s="7" t="inlineStr"/>
+      <c r="O55" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>한화플러스제6호기업인수목적</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>스팩</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D56" s="8" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
+      <c r="E56" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="7" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G56" s="7" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="7" t="inlineStr">
         <is>
           <t>2,000원 (단일가)</t>
         </is>
       </c>
-      <c r="I55" s="5" t="n">
+      <c r="I56" s="10" t="n">
         <v>4500000</v>
       </c>
-      <c r="J55" s="6" t="n">
+      <c r="J56" s="11" t="n">
         <v>90</v>
       </c>
-      <c r="K55" s="3" t="inlineStr">
+      <c r="K56" s="8" t="inlineStr">
         <is>
           <t>한화투자증권㈜ 02-3772-7395, 7398, 7393</t>
         </is>
       </c>
-      <c r="L55" s="2" t="inlineStr">
+      <c r="L56" s="7" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="M55" s="2" t="inlineStr">
+      <c r="M56" s="7" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="N55" s="2" t="inlineStr">
+      <c r="N56" s="7" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="O55" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="O56" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>아이엠기업인수목적1호</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>스팩</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D57" s="8" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="E57" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="7" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G57" s="7" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H57" s="7" t="inlineStr">
         <is>
           <t>2,000원 (단일가)</t>
         </is>
       </c>
-      <c r="I56" s="5" t="n">
+      <c r="I57" s="10" t="n">
         <v>3750000</v>
       </c>
-      <c r="J56" s="6" t="n">
+      <c r="J57" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="K56" s="3" t="inlineStr">
+      <c r="K57" s="8" t="inlineStr">
         <is>
           <t>아이엠증권 02-2122-9688, 9485</t>
         </is>
       </c>
-      <c r="L56" s="2" t="inlineStr">
+      <c r="L57" s="7" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="M56" s="2" t="inlineStr">
+      <c r="M57" s="7" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N56" s="2" t="inlineStr"/>
-      <c r="O56" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="N57" s="7" t="inlineStr"/>
+      <c r="O57" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>크리에이츠</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D58" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="E58" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="7" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G58" s="7" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="7" t="inlineStr">
         <is>
           <t>15,000 ~ 18,000원</t>
         </is>
       </c>
-      <c r="I57" s="5" t="n">
+      <c r="I58" s="10" t="n">
         <v>1050000</v>
       </c>
-      <c r="J57" s="6" t="n">
+      <c r="J58" s="11" t="n">
         <v>189</v>
       </c>
-      <c r="K57" s="3" t="inlineStr">
+      <c r="K58" s="8" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-7414, 7375, 7651</t>
         </is>
       </c>
-      <c r="L57" s="2" t="inlineStr">
+      <c r="L58" s="7" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="M57" s="2" t="inlineStr">
+      <c r="M58" s="7" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="N57" s="2" t="inlineStr">
+      <c r="N58" s="7" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="O57" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="O58" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>인텔리빅스</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C59" s="8" t="inlineStr">
         <is>
           <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D59" s="8" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="E59" s="9" t="inlineStr">
         <is>
           <t>정정-변경(문의처)</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="7" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G59" s="7" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="7" t="inlineStr">
         <is>
           <t>7,600 ~ 9,000원</t>
         </is>
       </c>
-      <c r="I58" s="5" t="n">
+      <c r="I59" s="10" t="n">
         <v>1875000</v>
       </c>
-      <c r="J58" s="6" t="n">
+      <c r="J59" s="11" t="n">
         <v>168.8</v>
       </c>
-      <c r="K58" s="3" t="inlineStr">
+      <c r="K59" s="8" t="inlineStr">
         <is>
           <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085</t>
         </is>
       </c>
-      <c r="L58" s="2" t="inlineStr">
+      <c r="L59" s="7" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="M58" s="2" t="inlineStr">
+      <c r="M59" s="7" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="N58" s="2" t="inlineStr">
+      <c r="N59" s="7" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="O58" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="O59" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>다비오</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D60" s="8" t="inlineStr">
         <is>
           <t>[정정제출요구] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="E60" s="9" t="inlineStr">
         <is>
           <t>정정-변경(수요예측)</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="7" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G60" s="7" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H60" s="7" t="inlineStr">
         <is>
           <t>12,300 ~ 16,600원</t>
         </is>
       </c>
-      <c r="I59" s="5" t="n">
+      <c r="I60" s="10" t="n">
         <v>750000</v>
       </c>
-      <c r="J59" s="6" t="n">
+      <c r="J60" s="11" t="n">
         <v>124.5</v>
       </c>
-      <c r="K59" s="3" t="inlineStr">
+      <c r="K60" s="8" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
         </is>
       </c>
-      <c r="L59" s="2" t="inlineStr">
+      <c r="L60" s="7" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="M59" s="2" t="inlineStr">
+      <c r="M60" s="7" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="N59" s="2" t="inlineStr"/>
-      <c r="O59" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="N60" s="7" t="inlineStr"/>
+      <c r="O60" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
         <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>유캐스트</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C61" s="8" t="inlineStr">
         <is>
           <t>기타 무선 통신장비 제조업</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D61" s="8" t="inlineStr">
         <is>
           <t>[정정제출요구] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="E61" s="9" t="inlineStr">
         <is>
           <t>정정-변경(수요예측,밴드)</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="7" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G61" s="7" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H61" s="7" t="inlineStr">
         <is>
           <t>21,000 ~ 26,000원</t>
         </is>
       </c>
-      <c r="I60" s="5" t="n">
+      <c r="I61" s="10" t="n">
         <v>600000</v>
       </c>
-      <c r="J60" s="6" t="n">
+      <c r="J61" s="11" t="n">
         <v>156</v>
       </c>
-      <c r="K60" s="3" t="inlineStr">
+      <c r="K61" s="8" t="inlineStr">
         <is>
           <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
         </is>
       </c>
-      <c r="L60" s="2" t="inlineStr">
+      <c r="L61" s="7" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="M60" s="2" t="inlineStr">
+      <c r="M61" s="7" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="N60" s="2" t="inlineStr"/>
-      <c r="O60" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="N61" s="7" t="inlineStr"/>
+      <c r="O61" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>바로팜</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>전자상거래 소매 중개업</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D62" s="8" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
+      <c r="E62" s="9" t="inlineStr">
         <is>
           <t>정정-변경(문의처)</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="7" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G62" s="7" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H62" s="7" t="inlineStr">
         <is>
           <t>16,400 ~ 20,200원</t>
         </is>
       </c>
-      <c r="I61" s="5" t="n">
+      <c r="I62" s="10" t="n">
         <v>1335000</v>
       </c>
-      <c r="J61" s="6" t="n">
+      <c r="J62" s="11" t="n">
         <v>269.7</v>
       </c>
-      <c r="K61" s="3" t="inlineStr">
+      <c r="K62" s="8" t="inlineStr">
         <is>
           <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805</t>
         </is>
       </c>
-      <c r="L61" s="2" t="inlineStr">
+      <c r="L62" s="7" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="M61" s="2" t="inlineStr">
+      <c r="M62" s="7" t="inlineStr">
         <is>
           <t>2026-11-05</t>
         </is>
       </c>
-      <c r="N61" s="2" t="inlineStr"/>
-      <c r="O61" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="N62" s="7" t="inlineStr"/>
+      <c r="O62" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>크리에이츠</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D63" s="8" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="E63" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="7" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G63" s="7" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H63" s="7" t="inlineStr">
         <is>
           <t>15,000 ~ 18,000원</t>
         </is>
       </c>
-      <c r="I62" s="5" t="n">
+      <c r="I63" s="10" t="n">
         <v>1050000</v>
       </c>
-      <c r="J62" s="6" t="n">
+      <c r="J63" s="11" t="n">
         <v>189</v>
       </c>
-      <c r="K62" s="3" t="inlineStr">
+      <c r="K63" s="8" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-7414, 7375, 7651</t>
         </is>
       </c>
-      <c r="L62" s="2" t="inlineStr">
+      <c r="L63" s="7" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="M62" s="2" t="inlineStr">
+      <c r="M63" s="7" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="N62" s="2" t="inlineStr">
+      <c r="N63" s="7" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="O62" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="O63" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>티앤이코리아</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C64" s="8" t="inlineStr">
         <is>
           <t>산업용 송풍기 및 배기장치 제조업</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D64" s="8" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
+      <c r="E64" s="9" t="inlineStr">
         <is>
           <t>정정-변경(수요예측)</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="7" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G64" s="7" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H64" s="7" t="inlineStr">
         <is>
           <t>12,600 ~ 15,300원</t>
         </is>
       </c>
-      <c r="I63" s="5" t="n">
+      <c r="I64" s="10" t="n">
         <v>1800000</v>
       </c>
-      <c r="J63" s="6" t="n">
+      <c r="J64" s="11" t="n">
         <v>275.4</v>
       </c>
-      <c r="K63" s="3" t="inlineStr">
+      <c r="K64" s="8" t="inlineStr">
         <is>
           <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
         </is>
       </c>
-      <c r="L63" s="2" t="inlineStr">
+      <c r="L64" s="7" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="M63" s="2" t="inlineStr">
+      <c r="M64" s="7" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="N63" s="2" t="inlineStr">
+      <c r="N64" s="7" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="O63" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="O64" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>엠비디</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C65" s="8" t="inlineStr">
         <is>
           <t>물질 검사, 측정 및 분석기구 제조업</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D65" s="8" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
+      <c r="E65" s="9" t="inlineStr">
         <is>
           <t>정정-변경(수요예측,밴드)</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="7" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G65" s="7" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H65" s="7" t="inlineStr">
         <is>
           <t>9,400 ~ 11,500원</t>
         </is>
       </c>
-      <c r="I64" s="5" t="n">
+      <c r="I65" s="10" t="n">
         <v>1500000</v>
       </c>
-      <c r="J64" s="6" t="n">
+      <c r="J65" s="11" t="n">
         <v>172.5</v>
       </c>
-      <c r="K64" s="3" t="inlineStr">
+      <c r="K65" s="8" t="inlineStr">
         <is>
           <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
         </is>
       </c>
-      <c r="L64" s="2" t="inlineStr">
+      <c r="L65" s="7" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="M64" s="2" t="inlineStr">
+      <c r="M65" s="7" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="N64" s="2" t="inlineStr"/>
-      <c r="O64" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="N65" s="7" t="inlineStr"/>
+      <c r="O65" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B66" s="7" t="inlineStr">
         <is>
           <t>래블업</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C66" s="8" t="inlineStr">
         <is>
           <t>시스템 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D66" s="8" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="E66" s="9" t="inlineStr">
         <is>
           <t>정정-변경(수요예측,밴드)</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="7" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G66" s="7" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H66" s="7" t="inlineStr">
         <is>
           <t>20,000 ~ 23,000원</t>
         </is>
       </c>
-      <c r="I65" s="5" t="n">
+      <c r="I66" s="10" t="n">
         <v>1635000</v>
       </c>
-      <c r="J65" s="6" t="n">
+      <c r="J66" s="11" t="n">
         <v>376.1</v>
       </c>
-      <c r="K65" s="3" t="inlineStr">
+      <c r="K66" s="8" t="inlineStr">
         <is>
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="L65" s="2" t="inlineStr">
+      <c r="L66" s="7" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="M65" s="2" t="inlineStr">
+      <c r="M66" s="7" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="N65" s="2" t="inlineStr">
+      <c r="N66" s="7" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="O65" s="7" t="inlineStr">
+      <c r="O66" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O65"/>
+  <autoFilter ref="A1:O66"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -7422,6 +7561,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId65"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/수요예측_일정.xlsx
+++ b/수요예측_일정.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체 이력" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'수요예측 일정'!$A$1:$O$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체 이력'!$A$1:$O$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'수요예측 일정'!$A$1:$O$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체 이력'!$A$1:$O$68</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -582,12 +582,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>KTE</t>
+          <t>신영해피투모로우제12호기업인수목적</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>배전반 및 전기 자동제어반 제조업</t>
+          <t>스팩</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -602,38 +602,38 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>19,000 ~ 23,000원</t>
+          <t>2,000원 (단일가)</t>
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>2112000</v>
+        <v>4687500</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>485.8</v>
+        <v>93.8</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>NH투자증권 02-768-7462, 7467</t>
+          <t>신영증권㈜ 02-2004-9554, 9230, 9403</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr"/>
@@ -644,138 +644,138 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>케이엠에프</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>기타 식품 제조업</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-20</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>15,000 ~ 17,800원</t>
-        </is>
-      </c>
-      <c r="I3" s="10" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="J3" s="11" t="n">
-        <v>267</v>
-      </c>
-      <c r="K3" s="8" t="inlineStr">
-        <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799 / 아이비케이투자증권㈜ 02-6915-5337, 5338, 5799</t>
-        </is>
-      </c>
-      <c r="L3" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-24</t>
-        </is>
-      </c>
-      <c r="M3" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-27</t>
-        </is>
-      </c>
-      <c r="N3" s="7" t="inlineStr"/>
-      <c r="O3" s="12" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>데스틴파워</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>전동기, 발전기 및 전기 변환장치 제조업</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>8,000 ~ 11,000원</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5958, 6269</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>엔키화이트햇</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>정정-변경(수요예측)</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-20</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>13,000 ~ 16,500원</t>
-        </is>
-      </c>
-      <c r="I4" s="10" t="n">
-        <v>1258000</v>
-      </c>
-      <c r="J4" s="11" t="n">
-        <v>207.6</v>
-      </c>
-      <c r="K4" s="8" t="inlineStr">
-        <is>
-          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
-        </is>
-      </c>
-      <c r="L4" s="7" t="inlineStr">
-        <is>
-          <t>2026-12-01</t>
-        </is>
-      </c>
-      <c r="M4" s="7" t="inlineStr">
-        <is>
-          <t>2026-12-04</t>
-        </is>
-      </c>
-      <c r="N4" s="7" t="inlineStr"/>
-      <c r="O4" s="12" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>KTE</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>배전반 및 전기 자동제어반 제조업</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>19,000 ~ 23,000원</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>2112000</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>485.8</v>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>NH투자증권 02-768-7462, 7467</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -789,12 +789,12 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>아델</t>
+          <t>케이엠에프</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>의학 및 약학 연구개발업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -804,43 +804,43 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>정정-변경(문의처)</t>
+          <t>정정-변경없음</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>18,000 ~ 25,000원</t>
+          <t>15,000 ~ 17,800원</t>
         </is>
       </c>
       <c r="I5" s="10" t="n">
-        <v>1627500</v>
+        <v>1500000</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>406.9</v>
+        <v>267</v>
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-8213, 6661</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799 / 아이비케이투자증권㈜ 02-6915-5337, 5338, 5799</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr"/>
@@ -851,69 +851,69 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>우리투자제1호기업인수목적</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>스팩</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-25</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>엔키화이트햇</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>정정-변경(수요예측)</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>2026-11-26</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,000원 (단일가)</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>4875000</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>우리투자증권 02-6390-3889</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-02</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-07</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="6" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>13,000 ~ 16,500원</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>1258000</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>207.6</v>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr"/>
+      <c r="O6" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -922,17 +922,17 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>제논</t>
+          <t>아델</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -942,43 +942,43 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>정정-변경(수요예측)</t>
+          <t>정정-변경(문의처)</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>9,700 ~ 12,200원</t>
+          <t>18,000 ~ 25,000원</t>
         </is>
       </c>
       <c r="I7" s="10" t="n">
-        <v>1550000</v>
+        <v>1627500</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>189.1</v>
+        <v>406.9</v>
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-8023, 7653, 7850</t>
+          <t>삼성증권 02-2020-8213, 6661</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr"/>
@@ -989,276 +989,276 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>우리투자제1호기업인수목적</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>스팩</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2,000원 (단일가)</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>4875000</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>우리투자증권 02-6390-3889</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-07</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>제논</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>정정-변경(수요예측)</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>9,700 ~ 12,200원</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>1550000</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>189.1</v>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-8023, 7653, 7850</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr"/>
+      <c r="O9" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>동원파츠</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>반도체 제조용 기계 제조업</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>23,000 ~ 26,500원</t>
         </is>
       </c>
-      <c r="I8" s="10" t="n">
+      <c r="I10" s="10" t="n">
         <v>1522500</v>
       </c>
-      <c r="J8" s="11" t="n">
+      <c r="J10" s="11" t="n">
         <v>403.5</v>
       </c>
-      <c r="K8" s="8" t="inlineStr">
+      <c r="K10" s="8" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-6975, 8217, 7651</t>
         </is>
       </c>
-      <c r="L8" s="7" t="inlineStr">
+      <c r="L10" s="7" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="M8" s="7" t="inlineStr">
+      <c r="M10" s="7" t="inlineStr">
         <is>
           <t>2026-11-05</t>
         </is>
       </c>
-      <c r="N8" s="7" t="inlineStr"/>
-      <c r="O8" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="N10" s="7" t="inlineStr"/>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>인터엑스</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>2026-11-30</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>2026-12-04</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>10,000 ~ 13,000원</t>
         </is>
       </c>
-      <c r="I9" s="4" t="n">
+      <c r="I11" s="4" t="n">
         <v>2250000</v>
       </c>
-      <c r="J9" s="5" t="n">
+      <c r="J11" s="5" t="n">
         <v>292.5</v>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5700, 6648</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>2026-12-09</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>2026-12-14</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>유캐스트</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>기타 무선 통신장비 제조업</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19,000 ~ 23,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>600000</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>138</v>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>옵토닉스</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>광학렌즈 및 광학요소 제조업</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>10,000 ~ 12,000원</t>
-        </is>
-      </c>
-      <c r="I11" s="10" t="n">
-        <v>1572490</v>
-      </c>
-      <c r="J11" s="11" t="n">
-        <v>188.7</v>
-      </c>
-      <c r="K11" s="8" t="inlineStr">
-        <is>
-          <t>한국투자증권 02-3276-5958, 6269</t>
-        </is>
-      </c>
-      <c r="L11" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="M11" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="inlineStr"/>
-      <c r="O11" s="12" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1272,17 +1272,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>이노보테라퓨틱스</t>
+          <t>유캐스트</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>의학 및 약학 연구개발업</t>
+          <t>기타 무선 통신장비 제조업</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1292,38 +1292,38 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,000 ~ 24,000원</t>
+          <t>19,000 ~ 23,000원</t>
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1650000</v>
+        <v>600000</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>396</v>
+        <v>138</v>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+          <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr"/>
@@ -1334,142 +1334,138 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>에이엔에이치스트럭쳐</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>기타 엔지니어링 서비스업</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>옵토닉스</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>광학렌즈 및 광학요소 제조업</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>10,000 ~ 12,000원</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>1572490</v>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>188.7</v>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>한국투자증권 02-3276-5958, 6269</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr"/>
+      <c r="O13" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>이노보테라퓨틱스</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>의학 및 약학 연구개발업</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-19</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-25</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>11,200 ~ 13,600원</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>1575000</v>
-      </c>
-      <c r="J13" s="5" t="n">
-        <v>214.2</v>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>NH투자증권 02-2229-6315, 6829</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-27</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>2026-12-02</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr"/>
-      <c r="O13" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>이에스티</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>그 외 기타 전자부품 제조업</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>10,600 ~ 12,400원</t>
-        </is>
-      </c>
-      <c r="I14" s="10" t="n">
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>20,000 ~ 24,000원</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="n">
         <v>1650000</v>
       </c>
-      <c r="J14" s="11" t="n">
-        <v>204.6</v>
-      </c>
-      <c r="K14" s="8" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
-        </is>
-      </c>
-      <c r="L14" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="M14" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="N14" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="O14" s="12" t="inlineStr">
+      <c r="J14" s="5" t="n">
+        <v>396</v>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-07</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1478,17 +1474,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>에스에프씨</t>
+          <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>그 외 기타 분류 안된 화학제품 제조업</t>
+          <t>기타 엔지니어링 서비스업</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1503,38 +1499,38 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,600 ~ 36,100원</t>
+          <t>11,200 ~ 13,600원</t>
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>3750000</v>
+        <v>1575000</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>1353.8</v>
+        <v>214.2</v>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
+          <t>NH투자증권 02-2229-6315, 6829</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr"/>
@@ -1545,69 +1541,73 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>씨아이에스케미칼</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>알루미늄 제련, 정련 및 합금 제조업</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-04</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,400 ~ 6,800원</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>204</v>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-10</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-15</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="6" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>이에스티</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>그 외 기타 전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>10,600 ~ 12,400원</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>204.6</v>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="O16" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1616,17 +1616,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>제이앤티지</t>
+          <t>에스에프씨</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>그 외 자동차용 신품 부품 제조업</t>
+          <t>그 외 기타 분류 안된 화학제품 제조업</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -1641,38 +1641,38 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,400 ~ 31,900원</t>
+          <t>31,600 ~ 36,100원</t>
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3182000</v>
+        <v>3750000</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>1015.1</v>
+        <v>1353.8</v>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
+          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr"/>
@@ -1685,17 +1685,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>씨앤엠</t>
+          <t>씨아이에스케미칼</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>전동기 및 발전기 제조업</t>
+          <t>알루미늄 제련, 정련 및 합금 제조업</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1710,38 +1710,38 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,000 ~ 13,000원</t>
+          <t>5,400 ~ 6,800원</t>
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2059500</v>
+        <v>3000000</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>267.7</v>
+        <v>204</v>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr"/>
@@ -1752,138 +1752,138 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>넥스아이</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>10,500 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I19" s="10" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J19" s="11" t="n">
-        <v>487.5</v>
-      </c>
-      <c r="K19" s="8" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
-        </is>
-      </c>
-      <c r="L19" s="7" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>제이앤티지</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>그 외 자동차용 신품 부품 제조업</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="N19" s="7" t="inlineStr"/>
-      <c r="O19" s="12" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>26,400 ~ 31,900원</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>3182000</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>1015.1</v>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>하나에어로다이내믹스</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>항공기용 부품 제조업</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>4,700 ~ 5,700원</t>
-        </is>
-      </c>
-      <c r="I20" s="10" t="n">
-        <v>3300000</v>
-      </c>
-      <c r="J20" s="11" t="n">
-        <v>188.1</v>
-      </c>
-      <c r="K20" s="8" t="inlineStr">
-        <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
-        </is>
-      </c>
-      <c r="L20" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="M20" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="N20" s="7" t="inlineStr"/>
-      <c r="O20" s="12" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>씨앤엠</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>전동기 및 발전기 제조업</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>10,000 ~ 13,000원</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>2059500</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>267.7</v>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1892,17 +1892,17 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>바로팜</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>전자상거래 소매 중개업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -1927,28 +1927,28 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>16,400 ~ 20,200원</t>
+          <t>10,500 ~ 13,000원</t>
         </is>
       </c>
       <c r="I21" s="10" t="n">
-        <v>1335000</v>
+        <v>3750000</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>269.7</v>
+        <v>487.5</v>
       </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
+          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="N21" s="7" t="inlineStr"/>
@@ -1959,69 +1959,69 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>엠비디</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>물질 검사, 측정 및 분석기구 제조업</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>하나에어로다이내믹스</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>항공기용 부품 제조업</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>9,600 ~ 11,700원</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="J22" s="5" t="n">
-        <v>175.5</v>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-17</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="6" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>4,700 ~ 5,700원</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="J22" s="11" t="n">
+        <v>188.1</v>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr"/>
+      <c r="O22" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2030,254 +2030,278 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>바로팜</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>전자상거래 소매 중개업</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>16,400 ~ 20,200원</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="n">
+        <v>1335000</v>
+      </c>
+      <c r="J23" s="11" t="n">
+        <v>269.7</v>
+      </c>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr"/>
+      <c r="O23" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>엠비디</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>물질 검사, 측정 및 분석기구 제조업</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>9,600 ~ 11,700원</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>175.5</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>래블업</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>시스템 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>19,000 ~ 22,000원</t>
         </is>
       </c>
-      <c r="I23" s="10" t="n">
+      <c r="I25" s="10" t="n">
         <v>1635000</v>
       </c>
-      <c r="J23" s="11" t="n">
+      <c r="J25" s="11" t="n">
         <v>359.7</v>
       </c>
-      <c r="K23" s="8" t="inlineStr">
+      <c r="K25" s="8" t="inlineStr">
         <is>
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="L23" s="7" t="inlineStr">
+      <c r="L25" s="7" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="M23" s="7" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="N23" s="7" t="inlineStr">
+      <c r="N25" s="7" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="O23" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="O25" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>에이엘로봇</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>기타 기계 및 장비 제조업</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>정정-변경(수요예측)</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>15,700 ~ 17,600원</t>
         </is>
       </c>
-      <c r="I24" s="10" t="n">
+      <c r="I26" s="10" t="n">
         <v>1800000</v>
       </c>
-      <c r="J24" s="11" t="n">
+      <c r="J26" s="11" t="n">
         <v>316.8</v>
       </c>
-      <c r="K24" s="8" t="inlineStr">
+      <c r="K26" s="8" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="L24" s="7" t="inlineStr">
+      <c r="L26" s="7" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="M24" s="7" t="inlineStr">
+      <c r="M26" s="7" t="inlineStr">
         <is>
           <t>2026-11-11</t>
         </is>
       </c>
-      <c r="N24" s="7" t="inlineStr"/>
-      <c r="O24" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>SimwonAmericaCorp.</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>자동차 신품 부품 제조업</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>수요예측 항목 없음(원문 확인)</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="4" t="inlineStr"/>
-      <c r="J25" s="5" t="inlineStr"/>
-      <c r="K25" s="3" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
-      <c r="O25" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>다비오</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>12,300 ~ 16,600원</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>750000</v>
-      </c>
-      <c r="J26" s="5" t="n">
-        <v>124.5</v>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="6" t="inlineStr">
+      <c r="N26" s="7" t="inlineStr"/>
+      <c r="O26" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2286,17 +2310,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>영광와이케이엠씨</t>
+          <t>SimwonAmericaCorp.</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>그 외 기타 금속가공업</t>
+          <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -2306,40 +2330,16 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>9,400 ~ 11,000원</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>1694840</v>
-      </c>
-      <c r="J27" s="5" t="n">
-        <v>186.4</v>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
+          <t>수요예측 항목 없음(원문 확인)</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="3" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
           <t>2026-11-09</t>
@@ -2353,73 +2353,69 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>영광</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>수상 금속 골조 구조재 제조업</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>다비오</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>14,000 ~ 17,000원</t>
-        </is>
-      </c>
-      <c r="I28" s="10" t="n">
-        <v>1695000</v>
-      </c>
-      <c r="J28" s="11" t="n">
-        <v>288.1</v>
-      </c>
-      <c r="K28" s="8" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
-        </is>
-      </c>
-      <c r="L28" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="M28" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="N28" s="7" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="O28" s="12" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>12,300 ~ 16,600원</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>750000</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2433,17 +2429,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>인텔리빅스</t>
+          <t>영광와이케이엠씨</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
+          <t>그 외 기타 금속가공업</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2453,45 +2449,41 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,600 ~ 9,000원</t>
+          <t>9,400 ~ 11,000원</t>
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1875000</v>
+        <v>1694840</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>168.8</v>
+        <v>186.4</v>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
+          <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="6" t="inlineStr">
         <is>
           <t>열기</t>
@@ -2506,281 +2498,281 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
+          <t>영광</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>수상 금속 골조 구조재 제조업</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>14,000 ~ 17,000원</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="n">
+        <v>1695000</v>
+      </c>
+      <c r="J30" s="11" t="n">
+        <v>288.1</v>
+      </c>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+        </is>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="O30" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>인텔리빅스</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>7,600 ~ 9,000원</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>1875000</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>168.8</v>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="O31" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
           <t>아이엠기업인수목적1호</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>스팩</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>2,000원 (단일가)</t>
         </is>
       </c>
-      <c r="I30" s="10" t="n">
+      <c r="I32" s="10" t="n">
         <v>3750000</v>
       </c>
-      <c r="J30" s="11" t="n">
+      <c r="J32" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="K30" s="8" t="inlineStr">
+      <c r="K32" s="8" t="inlineStr">
         <is>
           <t>아이엠증권 02-2122-9688, 9485</t>
         </is>
       </c>
-      <c r="L30" s="7" t="inlineStr">
+      <c r="L32" s="7" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="M30" s="7" t="inlineStr">
+      <c r="M32" s="7" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N30" s="7" t="inlineStr"/>
-      <c r="O30" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="N32" s="7" t="inlineStr"/>
+      <c r="O32" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>한화플러스제6호기업인수목적</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>스팩</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>2,000원 (단일가)</t>
         </is>
       </c>
-      <c r="I31" s="10" t="n">
+      <c r="I33" s="10" t="n">
         <v>4500000</v>
       </c>
-      <c r="J31" s="11" t="n">
+      <c r="J33" s="11" t="n">
         <v>90</v>
       </c>
-      <c r="K31" s="8" t="inlineStr">
+      <c r="K33" s="8" t="inlineStr">
         <is>
           <t>한화투자증권㈜ 02-3772-7395, 7398, 7393</t>
         </is>
       </c>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="L33" s="7" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="M31" s="7" t="inlineStr">
+      <c r="M33" s="7" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="N31" s="7" t="inlineStr">
+      <c r="N33" s="7" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="O31" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>디티에스</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>특수 목적용 기계 제조업</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>17,000 ~ 18,500원</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="n">
-        <v>1671687</v>
-      </c>
-      <c r="J32" s="5" t="n">
-        <v>309.3</v>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="O32" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>엠에스바이오</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>그 외 기타 의료용 기기 제조업</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>6,800 ~ 7,800원</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>2840000</v>
-      </c>
-      <c r="J33" s="5" t="n">
-        <v>221.5</v>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="O33" s="6" t="inlineStr">
+      <c r="O33" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2789,17 +2781,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -2814,43 +2806,43 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>17,000 ~ 18,500원</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>1671687</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>309.3</v>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>15,000 ~ 18,000원</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="n">
-        <v>1050000</v>
-      </c>
-      <c r="J34" s="5" t="n">
-        <v>189</v>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>삼성증권 02-2020-7414, 7375, 7651</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
         </is>
       </c>
       <c r="O34" s="6" t="inlineStr">
@@ -2862,78 +2854,224 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>엠에스바이오</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>그 외 기타 의료용 기기 제조업</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>6,800 ~ 7,800원</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>2840000</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>221.5</v>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="O35" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>크리에이츠</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>15,000 ~ 18,000원</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>1050000</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>189</v>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-7414, 7375, 7651</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="O36" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>티앤이코리아</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>산업용 송풍기 및 배기장치 제조업</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>12,600 ~ 15,300원</t>
         </is>
       </c>
-      <c r="I35" s="4" t="n">
+      <c r="I37" s="4" t="n">
         <v>1800000</v>
       </c>
-      <c r="J35" s="5" t="n">
+      <c r="J37" s="5" t="n">
         <v>275.4</v>
       </c>
-      <c r="K35" s="3" t="inlineStr">
+      <c r="K37" s="3" t="inlineStr">
         <is>
           <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="O35" s="6" t="inlineStr">
+      <c r="O37" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O35"/>
+  <autoFilter ref="A1:O37"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -2969,6 +3107,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2980,7 +3120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O66"/>
+  <dimension ref="A1:O68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3085,12 +3225,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>KTE</t>
+          <t>신영해피투모로우제12호기업인수목적</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>배전반 및 전기 자동제어반 제조업</t>
+          <t>스팩</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -3105,38 +3245,38 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>19,000 ~ 23,000원</t>
+          <t>2,000원 (단일가)</t>
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>2112000</v>
+        <v>4687500</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>485.8</v>
+        <v>93.8</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>NH투자증권 02-768-7462, 7467</t>
+          <t>신영증권㈜ 02-2004-9554, 9230, 9403</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr"/>
@@ -3147,138 +3287,138 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>케이엠에프</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>기타 식품 제조업</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-20</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>15,000 ~ 17,800원</t>
-        </is>
-      </c>
-      <c r="I3" s="10" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="J3" s="11" t="n">
-        <v>267</v>
-      </c>
-      <c r="K3" s="8" t="inlineStr">
-        <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799 / 아이비케이투자증권㈜ 02-6915-5337, 5338, 5799</t>
-        </is>
-      </c>
-      <c r="L3" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-24</t>
-        </is>
-      </c>
-      <c r="M3" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-27</t>
-        </is>
-      </c>
-      <c r="N3" s="7" t="inlineStr"/>
-      <c r="O3" s="12" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>데스틴파워</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>전동기, 발전기 및 전기 변환장치 제조업</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>8,000 ~ 11,000원</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5958, 6269</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>엔키화이트햇</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>정정-변경(수요예측)</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-20</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>13,000 ~ 16,500원</t>
-        </is>
-      </c>
-      <c r="I4" s="10" t="n">
-        <v>1258000</v>
-      </c>
-      <c r="J4" s="11" t="n">
-        <v>207.6</v>
-      </c>
-      <c r="K4" s="8" t="inlineStr">
-        <is>
-          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
-        </is>
-      </c>
-      <c r="L4" s="7" t="inlineStr">
-        <is>
-          <t>2026-12-01</t>
-        </is>
-      </c>
-      <c r="M4" s="7" t="inlineStr">
-        <is>
-          <t>2026-12-04</t>
-        </is>
-      </c>
-      <c r="N4" s="7" t="inlineStr"/>
-      <c r="O4" s="12" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>KTE</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>배전반 및 전기 자동제어반 제조업</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>19,000 ~ 23,000원</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>2112000</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>485.8</v>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>NH투자증권 02-768-7462, 7467</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3292,12 +3432,12 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>아델</t>
+          <t>케이엠에프</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>의학 및 약학 연구개발업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -3307,43 +3447,43 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>정정-변경(문의처)</t>
+          <t>정정-변경없음</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>18,000 ~ 25,000원</t>
+          <t>15,000 ~ 17,800원</t>
         </is>
       </c>
       <c r="I5" s="10" t="n">
-        <v>1627500</v>
+        <v>1500000</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>406.9</v>
+        <v>267</v>
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-8213, 6661</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799 / 아이비케이투자증권㈜ 02-6915-5337, 5338, 5799</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr"/>
@@ -3361,12 +3501,12 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>케이엠에프</t>
+          <t>엔키화이트햇</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -3376,43 +3516,43 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>정정-변경없음</t>
+          <t>정정-변경(수요예측)</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>15,000 ~ 17,800원</t>
+          <t>13,000 ~ 16,500원</t>
         </is>
       </c>
       <c r="I6" s="10" t="n">
-        <v>1500000</v>
+        <v>1258000</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>267</v>
+        <v>207.6</v>
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
+          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="N6" s="7" t="inlineStr"/>
@@ -3423,69 +3563,69 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>우리투자제1호기업인수목적</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>스팩</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-25</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>아델</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>의학 및 약학 연구개발업</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>정정-변경(문의처)</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>18,000 ~ 25,000원</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>1627500</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>406.9</v>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-8213, 6661</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>2026-11-26</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,000원 (단일가)</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>4875000</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>우리투자증권 02-6390-3889</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-02</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-07</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="6" t="inlineStr">
+      <c r="N7" s="7" t="inlineStr"/>
+      <c r="O7" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3494,17 +3634,17 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>제논</t>
+          <t>케이엠에프</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -3514,7 +3654,7 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>정정-변경(수요예측)</t>
+          <t>정정-변경없음</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -3529,18 +3669,18 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>9,700 ~ 12,200원</t>
+          <t>15,000 ~ 17,800원</t>
         </is>
       </c>
       <c r="I8" s="10" t="n">
-        <v>1550000</v>
+        <v>1500000</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>189.1</v>
+        <v>267</v>
       </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-8023, 7653, 7850</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -3561,61 +3701,69 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>제논</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>9,700 ~ 12,200원</t>
-        </is>
-      </c>
-      <c r="I9" s="10" t="n">
-        <v>1550000</v>
-      </c>
-      <c r="J9" s="11" t="n">
-        <v>189.1</v>
-      </c>
-      <c r="K9" s="8" t="inlineStr">
-        <is>
-          <t>삼성증권 02-2020-8023, 7653, 7850</t>
-        </is>
-      </c>
-      <c r="L9" s="7" t="inlineStr"/>
-      <c r="M9" s="7" t="inlineStr"/>
-      <c r="N9" s="7" t="inlineStr"/>
-      <c r="O9" s="12" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>우리투자제1호기업인수목적</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>스팩</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2,000원 (단일가)</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>4875000</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>우리투자증권 02-6390-3889</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-07</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3624,17 +3772,17 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>동원파츠</t>
+          <t>제논</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>반도체 제조용 기계 제조업</t>
+          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -3644,43 +3792,43 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>정정-변경없음</t>
+          <t>정정-변경(수요예측)</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>23,000 ~ 26,500원</t>
+          <t>9,700 ~ 12,200원</t>
         </is>
       </c>
       <c r="I10" s="10" t="n">
-        <v>1522500</v>
+        <v>1550000</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>403.5</v>
+        <v>189.1</v>
       </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-6975, 8217, 7651</t>
+          <t>삼성증권 02-2020-8023, 7653, 7850</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr"/>
@@ -3691,207 +3839,199 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>제논</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>9,700 ~ 12,200원</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>1550000</v>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>189.1</v>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-8023, 7653, 7850</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr"/>
+      <c r="N11" s="7" t="inlineStr"/>
+      <c r="O11" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>동원파츠</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>반도체 제조용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>23,000 ~ 26,500원</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>1522500</v>
+      </c>
+      <c r="J12" s="11" t="n">
+        <v>403.5</v>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-6975, 8217, 7651</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="inlineStr"/>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>인터엑스</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>2026-11-30</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>2026-12-04</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>10,000 ~ 13,000원</t>
         </is>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="I13" s="4" t="n">
         <v>2250000</v>
       </c>
-      <c r="J11" s="5" t="n">
+      <c r="J13" s="5" t="n">
         <v>292.5</v>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5700, 6648</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>2026-12-09</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>2026-12-14</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>유캐스트</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>기타 무선 통신장비 제조업</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>19,000 ~ 23,000원</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>600000</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>138</v>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>옵토닉스</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>광학렌즈 및 광학요소 제조업</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>10,000 ~ 12,000원</t>
-        </is>
-      </c>
-      <c r="I13" s="10" t="n">
-        <v>1572490</v>
-      </c>
-      <c r="J13" s="11" t="n">
-        <v>188.7</v>
-      </c>
-      <c r="K13" s="8" t="inlineStr">
-        <is>
-          <t>한국투자증권 02-3276-5958, 6269</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="M13" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="inlineStr"/>
-      <c r="O13" s="12" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3905,17 +4045,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>이노보테라퓨틱스</t>
+          <t>유캐스트</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>의학 및 약학 연구개발업</t>
+          <t>기타 무선 통신장비 제조업</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -3925,38 +4065,38 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,000 ~ 24,000원</t>
+          <t>19,000 ~ 23,000원</t>
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1650000</v>
+        <v>600000</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>396</v>
+        <v>138</v>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+          <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr"/>
@@ -3967,142 +4107,138 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>에이엔에이치스트럭쳐</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>기타 엔지니어링 서비스업</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>옵토닉스</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>광학렌즈 및 광학요소 제조업</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>10,000 ~ 12,000원</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>1572490</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>188.7</v>
+      </c>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>한국투자증권 02-3276-5958, 6269</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr"/>
+      <c r="O15" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>이노보테라퓨틱스</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>의학 및 약학 연구개발업</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-19</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-25</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>11,200 ~ 13,600원</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>1575000</v>
-      </c>
-      <c r="J15" s="5" t="n">
-        <v>214.2</v>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>NH투자증권 02-2229-6315, 6829</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-27</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2026-12-02</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr"/>
-      <c r="O15" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>이에스티</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>그 외 기타 전자부품 제조업</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>10,600 ~ 12,400원</t>
-        </is>
-      </c>
-      <c r="I16" s="10" t="n">
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>20,000 ~ 24,000원</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="n">
         <v>1650000</v>
       </c>
-      <c r="J16" s="11" t="n">
-        <v>204.6</v>
-      </c>
-      <c r="K16" s="8" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="M16" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="O16" s="12" t="inlineStr">
+      <c r="J16" s="5" t="n">
+        <v>396</v>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-07</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4111,17 +4247,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>에스에프씨</t>
+          <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>그 외 기타 분류 안된 화학제품 제조업</t>
+          <t>기타 엔지니어링 서비스업</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -4136,38 +4272,38 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,600 ~ 36,100원</t>
+          <t>11,200 ~ 13,600원</t>
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3750000</v>
+        <v>1575000</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>1353.8</v>
+        <v>214.2</v>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
+          <t>NH투자증권 02-2229-6315, 6829</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr"/>
@@ -4178,69 +4314,73 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>씨아이에스케미칼</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>알루미늄 제련, 정련 및 합금 제조업</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-04</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,400 ~ 6,800원</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="J18" s="5" t="n">
-        <v>204</v>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-10</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-15</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="6" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>이에스티</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>그 외 기타 전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>10,600 ~ 12,400원</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J18" s="11" t="n">
+        <v>204.6</v>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="O18" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4249,17 +4389,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>제이앤티지</t>
+          <t>에스에프씨</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>그 외 자동차용 신품 부품 제조업</t>
+          <t>그 외 기타 분류 안된 화학제품 제조업</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -4274,38 +4414,38 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,400 ~ 31,900원</t>
+          <t>31,600 ~ 36,100원</t>
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3182000</v>
+        <v>3750000</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>1015.1</v>
+        <v>1353.8</v>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
+          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr"/>
@@ -4318,17 +4458,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>씨앤엠</t>
+          <t>씨아이에스케미칼</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>전동기 및 발전기 제조업</t>
+          <t>알루미늄 제련, 정련 및 합금 제조업</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -4343,38 +4483,38 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,000 ~ 13,000원</t>
+          <t>5,400 ~ 6,800원</t>
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2059500</v>
+        <v>3000000</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>267.7</v>
+        <v>204</v>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr"/>
@@ -4385,138 +4525,138 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>넥스아이</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>10,500 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I21" s="10" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J21" s="11" t="n">
-        <v>487.5</v>
-      </c>
-      <c r="K21" s="8" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>제이앤티지</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>그 외 자동차용 신품 부품 제조업</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="inlineStr"/>
-      <c r="O21" s="12" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>26,400 ~ 31,900원</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>3182000</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>1015.1</v>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>하나에어로다이내믹스</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>항공기용 부품 제조업</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>4,700 ~ 5,700원</t>
-        </is>
-      </c>
-      <c r="I22" s="10" t="n">
-        <v>3300000</v>
-      </c>
-      <c r="J22" s="11" t="n">
-        <v>188.1</v>
-      </c>
-      <c r="K22" s="8" t="inlineStr">
-        <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
-        </is>
-      </c>
-      <c r="L22" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="M22" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="inlineStr"/>
-      <c r="O22" s="12" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>씨앤엠</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>전동기 및 발전기 제조업</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>10,000 ~ 13,000원</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>2059500</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>267.7</v>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4525,17 +4665,17 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>바로팜</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>전자상거래 소매 중개업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -4560,28 +4700,28 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>16,400 ~ 20,200원</t>
+          <t>10,500 ~ 13,000원</t>
         </is>
       </c>
       <c r="I23" s="10" t="n">
-        <v>1335000</v>
+        <v>3750000</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>269.7</v>
+        <v>487.5</v>
       </c>
       <c r="K23" s="8" t="inlineStr">
         <is>
-          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
+          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="N23" s="7" t="inlineStr"/>
@@ -4592,69 +4732,69 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>엠비디</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>물질 검사, 측정 및 분석기구 제조업</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>하나에어로다이내믹스</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>항공기용 부품 제조업</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>9,600 ~ 11,700원</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="J24" s="5" t="n">
-        <v>175.5</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-17</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="6" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>4,700 ~ 5,700원</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="J24" s="11" t="n">
+        <v>188.1</v>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="inlineStr"/>
+      <c r="O24" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4663,17 +4803,17 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>래블업</t>
+          <t>바로팜</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>시스템 소프트웨어 개발 및 공급업</t>
+          <t>전자상거래 소매 중개업</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -4688,45 +4828,41 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>19,000 ~ 22,000원</t>
+          <t>16,400 ~ 20,200원</t>
         </is>
       </c>
       <c r="I25" s="10" t="n">
-        <v>1635000</v>
+        <v>1335000</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>359.7</v>
+        <v>269.7</v>
       </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
-          <t>NH투자증권 02-768-7462, 7467</t>
+          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="N25" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="inlineStr"/>
       <c r="O25" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -4734,65 +4870,69 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>이에스티</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>그 외 기타 전자부품 제조업</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>엠비디</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>물질 검사, 측정 및 분석기구 제조업</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>10,600 ~ 12,400원</t>
-        </is>
-      </c>
-      <c r="I26" s="10" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="J26" s="11" t="n">
-        <v>204.6</v>
-      </c>
-      <c r="K26" s="8" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
-        </is>
-      </c>
-      <c r="L26" s="7" t="inlineStr"/>
-      <c r="M26" s="7" t="inlineStr"/>
-      <c r="N26" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="O26" s="12" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>9,600 ~ 11,700원</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>175.5</v>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4801,181 +4941,205 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>래블업</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>시스템 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>19,000 ~ 22,000원</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="n">
+        <v>1635000</v>
+      </c>
+      <c r="J27" s="11" t="n">
+        <v>359.7</v>
+      </c>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>NH투자증권 02-768-7462, 7467</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="O27" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>이에스티</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>그 외 기타 전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>10,600 ~ 12,400원</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J28" s="11" t="n">
+        <v>204.6</v>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+        </is>
+      </c>
+      <c r="L28" s="7" t="inlineStr"/>
+      <c r="M28" s="7" t="inlineStr"/>
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="O28" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>에이엘로봇</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>기타 기계 및 장비 제조업</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>정정-변경(수요예측)</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>15,700 ~ 17,600원</t>
         </is>
       </c>
-      <c r="I27" s="10" t="n">
+      <c r="I29" s="10" t="n">
         <v>1800000</v>
       </c>
-      <c r="J27" s="11" t="n">
+      <c r="J29" s="11" t="n">
         <v>316.8</v>
       </c>
-      <c r="K27" s="8" t="inlineStr">
+      <c r="K29" s="8" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="L27" s="7" t="inlineStr">
+      <c r="L29" s="7" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="M27" s="7" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr">
         <is>
           <t>2026-11-11</t>
         </is>
       </c>
-      <c r="N27" s="7" t="inlineStr"/>
-      <c r="O27" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>아델</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>18,000 ~ 25,000원</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="n">
-        <v>1627500</v>
-      </c>
-      <c r="J28" s="5" t="n">
-        <v>406.9</v>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>SimwonAmericaCorp.</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>자동차 신품 부품 제조업</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>수요예측 항목 없음(원문 확인)</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="4" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="3" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
-      <c r="O29" s="6" t="inlineStr">
+      <c r="N29" s="7" t="inlineStr"/>
+      <c r="O29" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4984,22 +5148,22 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>다비오</t>
+          <t>아델</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -5009,38 +5173,38 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,300 ~ 16,600원</t>
+          <t>18,000 ~ 25,000원</t>
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>750000</v>
+        <v>1627500</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>124.5</v>
+        <v>406.9</v>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
+          <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr"/>
@@ -5053,17 +5217,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>엔키화이트햇</t>
+          <t>SimwonAmericaCorp.</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
+          <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -5073,43 +5237,19 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+          <t>수요예측 항목 없음(원문 확인)</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="4" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>13,000 ~ 16,500원</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>1258000</v>
-      </c>
-      <c r="J31" s="5" t="n">
-        <v>207.6</v>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-17</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr"/>
@@ -5127,17 +5267,17 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>영광와이케이엠씨</t>
+          <t>다비오</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>그 외 기타 금속가공업</t>
+          <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -5147,38 +5287,38 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,400 ~ 11,000원</t>
+          <t>12,300 ~ 16,600원</t>
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>1694840</v>
+        <v>750000</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>186.4</v>
+        <v>124.5</v>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
+          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr"/>
@@ -5189,73 +5329,69 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>영광</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>수상 금속 골조 구조재 제조업</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>14,000 ~ 17,000원</t>
-        </is>
-      </c>
-      <c r="I33" s="10" t="n">
-        <v>1695000</v>
-      </c>
-      <c r="J33" s="11" t="n">
-        <v>288.1</v>
-      </c>
-      <c r="K33" s="8" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
-        </is>
-      </c>
-      <c r="L33" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="M33" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="N33" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="O33" s="12" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>엔키화이트햇</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>13,000 ~ 16,500원</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>1258000</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>207.6</v>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -5269,17 +5405,17 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>인텔리빅스</t>
+          <t>영광와이케이엠씨</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
+          <t>그 외 기타 금속가공업</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -5289,45 +5425,41 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,600 ~ 9,000원</t>
+          <t>9,400 ~ 11,000원</t>
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1875000</v>
+        <v>1694840</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>168.8</v>
+        <v>186.4</v>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
+          <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="6" t="inlineStr">
         <is>
           <t>열기</t>
@@ -5342,12 +5474,12 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>아이엠기업인수목적1호</t>
+          <t>영광</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>스팩</t>
+          <t>수상 금속 골조 구조재 제조업</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -5362,41 +5494,45 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>2,000원 (단일가)</t>
+          <t>14,000 ~ 17,000원</t>
         </is>
       </c>
       <c r="I35" s="10" t="n">
-        <v>3750000</v>
+        <v>1695000</v>
       </c>
       <c r="J35" s="11" t="n">
-        <v>75</v>
+        <v>288.1</v>
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>아이엠증권 02-2122-9688, 9485</t>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N35" s="7" t="inlineStr"/>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="N35" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
       <c r="O35" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -5411,379 +5547,395 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
+          <t>인텔리빅스</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>7,600 ~ 9,000원</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>1875000</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>168.8</v>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="O36" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
           <t>아이엠기업인수목적1호</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>스팩</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>2,000원 (단일가)</t>
+        </is>
+      </c>
+      <c r="I37" s="10" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="J37" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="K37" s="8" t="inlineStr">
+        <is>
+          <t>아이엠증권 02-2122-9688, 9485</t>
+        </is>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="inlineStr"/>
+      <c r="O37" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>아이엠기업인수목적1호</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>스팩</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>2,000원 (단일가)</t>
         </is>
       </c>
-      <c r="I36" s="4" t="n">
+      <c r="I38" s="4" t="n">
         <v>3750000</v>
       </c>
-      <c r="J36" s="5" t="n">
+      <c r="J38" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="K36" s="3" t="inlineStr">
+      <c r="K38" s="3" t="inlineStr">
         <is>
           <t>아이엠증권 02-2122-9688, 9485</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="inlineStr"/>
-      <c r="O36" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>제논</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>9,700 ~ 12,200원</t>
         </is>
       </c>
-      <c r="I37" s="4" t="n">
+      <c r="I39" s="4" t="n">
         <v>1550000</v>
       </c>
-      <c r="J37" s="5" t="n">
+      <c r="J39" s="5" t="n">
         <v>189.1</v>
       </c>
-      <c r="K37" s="3" t="inlineStr">
+      <c r="K39" s="3" t="inlineStr">
         <is>
           <t>삼성증권 02-2020-8023, 7653, 7850</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="2" t="inlineStr"/>
-      <c r="O37" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="6" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>한화플러스제6호기업인수목적</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>스팩</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E38" s="9" t="inlineStr">
+      <c r="E40" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="G38" s="7" t="inlineStr">
+      <c r="G40" s="7" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="H38" s="7" t="inlineStr">
+      <c r="H40" s="7" t="inlineStr">
         <is>
           <t>2,000원 (단일가)</t>
         </is>
       </c>
-      <c r="I38" s="10" t="n">
+      <c r="I40" s="10" t="n">
         <v>4500000</v>
       </c>
-      <c r="J38" s="11" t="n">
+      <c r="J40" s="11" t="n">
         <v>90</v>
       </c>
-      <c r="K38" s="8" t="inlineStr">
+      <c r="K40" s="8" t="inlineStr">
         <is>
           <t>한화투자증권㈜ 02-3772-7395, 7398, 7393</t>
         </is>
       </c>
-      <c r="L38" s="7" t="inlineStr">
+      <c r="L40" s="7" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="M38" s="7" t="inlineStr">
+      <c r="M40" s="7" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="N38" s="7" t="inlineStr">
+      <c r="N40" s="7" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="O38" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="O40" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>래블업</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>시스템 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr">
+      <c r="E41" s="9" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="H41" s="7" t="inlineStr">
         <is>
           <t>19,000 ~ 22,000원</t>
         </is>
       </c>
-      <c r="I39" s="10" t="n">
+      <c r="I41" s="10" t="n">
         <v>1635000</v>
       </c>
-      <c r="J39" s="11" t="n">
+      <c r="J41" s="11" t="n">
         <v>359.7</v>
       </c>
-      <c r="K39" s="8" t="inlineStr">
+      <c r="K41" s="8" t="inlineStr">
         <is>
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="L39" s="7" t="inlineStr"/>
-      <c r="M39" s="7" t="inlineStr"/>
-      <c r="N39" s="7" t="inlineStr">
+      <c r="L41" s="7" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr"/>
+      <c r="N41" s="7" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="O39" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>한화플러스제6호기업인수목적</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>스팩</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>2,000원 (단일가)</t>
-        </is>
-      </c>
-      <c r="I40" s="4" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="J40" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t>한화투자증권㈜ 02-3772-7395, 7398, 7393</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr"/>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="O40" s="6" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>케이엠에프</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>기타 식품 제조업</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-20</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>15,000 ~ 17,800원</t>
-        </is>
-      </c>
-      <c r="I41" s="4" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="J41" s="5" t="n">
-        <v>267</v>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr"/>
-      <c r="N41" s="2" t="inlineStr"/>
-      <c r="O41" s="6" t="inlineStr">
+      <c r="O41" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -5792,17 +5944,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>바로팜</t>
+          <t>한화플러스제6호기업인수목적</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>전자상거래 소매 중개업</t>
+          <t>스팩</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -5817,33 +5969,37 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>16,400 ~ 20,200원</t>
+          <t>2,000원 (단일가)</t>
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>1335000</v>
+        <v>4500000</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>269.7</v>
+        <v>90</v>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
+          <t>한화투자증권㈜ 02-3772-7395, 7398, 7393</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr"/>
-      <c r="N42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="O42" s="6" t="inlineStr">
         <is>
           <t>열기</t>
@@ -5853,17 +6009,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>동원파츠</t>
+          <t>케이엠에프</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>반도체 제조용 기계 제조업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -5878,28 +6034,28 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>23,000 ~ 26,500원</t>
+          <t>15,000 ~ 17,800원</t>
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>1522500</v>
+        <v>1500000</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>403.5</v>
+        <v>267</v>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-6975, 8217, 7651</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr"/>
@@ -5919,12 +6075,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>디티에스</t>
+          <t>바로팜</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>전자상거래 소매 중개업</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -5939,45 +6095,33 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>17,000 ~ 18,500원</t>
+          <t>16,400 ~ 20,200원</t>
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>1671687</v>
+        <v>1335000</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>309.3</v>
+        <v>269.7</v>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
+          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="6" t="inlineStr">
         <is>
           <t>열기</t>
@@ -5987,22 +6131,22 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>엠에스바이오</t>
+          <t>동원파츠</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>그 외 기타 의료용 기기 제조업</t>
+          <t>반도체 제조용 기계 제조업</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -6012,45 +6156,33 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>6,800 ~ 7,800원</t>
+          <t>23,000 ~ 26,500원</t>
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>2840000</v>
+        <v>1522500</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>221.5</v>
+        <v>403.5</v>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
+          <t>삼성증권 02-2020-6975, 8217, 7651</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="6" t="inlineStr">
         <is>
           <t>열기</t>
@@ -6060,22 +6192,22 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>옵토닉스</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>광학렌즈 및 광학요소 제조업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -6085,33 +6217,45 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>10,000 ~ 12,000원</t>
+          <t>17,000 ~ 18,500원</t>
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>1572490</v>
+        <v>1671687</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>188.7</v>
+        <v>309.3</v>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>한국투자증권 02-3276-5958, 6269</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr"/>
-      <c r="N46" s="2" t="inlineStr"/>
+          <t>대신증권㈜ 02-769-2426, 02-769-2333</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="O46" s="6" t="inlineStr">
         <is>
           <t>열기</t>
@@ -6121,58 +6265,70 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>엠에스바이오</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>그 외 기타 의료용 기기 제조업</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>넥스아이</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>6,800 ~ 7,800원</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>2840000</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>221.5</v>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>KB증권㈜ 02-6114-0904, 0995 / KB증권㈜ 02-6114-1543</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>10,500 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I47" s="4" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J47" s="5" t="n">
-        <v>487.5</v>
-      </c>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr"/>
-      <c r="M47" s="2" t="inlineStr"/>
-      <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="6" t="inlineStr">
         <is>
           <t>열기</t>
@@ -6182,22 +6338,22 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>옵토닉스</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
+          <t>광학렌즈 및 광학요소 제조업</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -6207,45 +6363,33 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>15,000 ~ 18,000원</t>
+          <t>10,000 ~ 12,000원</t>
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>1050000</v>
+        <v>1572490</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>189</v>
+        <v>188.7</v>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-7414, 7375, 7651</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
+          <t>한국투자증권 02-3276-5958, 6269</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="6" t="inlineStr">
         <is>
           <t>열기</t>
@@ -6255,22 +6399,22 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>티앤이코리아</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>산업용 송풍기 및 배기장치 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -6280,45 +6424,33 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>12,600 ~ 15,300원</t>
+          <t>10,500 ~ 13,000원</t>
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>1800000</v>
+        <v>3750000</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>275.4</v>
+        <v>487.5</v>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
+          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="6" t="inlineStr">
         <is>
           <t>열기</t>
@@ -6328,22 +6460,22 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>항공기용 부품 제조업</t>
+          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -6353,33 +6485,45 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>4,700 ~ 5,700원</t>
+          <t>15,000 ~ 18,000원</t>
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>3300000</v>
+        <v>1050000</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>188.1</v>
+        <v>189</v>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="2" t="inlineStr"/>
-      <c r="N50" s="2" t="inlineStr"/>
+          <t>삼성증권 02-2020-7414, 7375, 7651</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="O50" s="6" t="inlineStr">
         <is>
           <t>열기</t>
@@ -6389,17 +6533,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>래블업</t>
+          <t>티앤이코리아</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>시스템 소프트웨어 개발 및 공급업</t>
+          <t>산업용 송풍기 및 배기장치 제조업</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -6414,35 +6558,43 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>19,000 ~ 22,000원</t>
+          <t>12,600 ~ 15,300원</t>
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>1635000</v>
+        <v>1800000</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>359.7</v>
+        <v>275.4</v>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>NH투자증권 02-768-7462, 7467</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr"/>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="O51" s="6" t="inlineStr">
@@ -6459,12 +6611,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>영광</t>
+          <t>하나에어로다이내믹스</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>수상 금속 골조 구조재 제조업</t>
+          <t>항공기용 부품 제조업</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -6479,37 +6631,33 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14,000 ~ 17,000원</t>
+          <t>4,700 ~ 5,700원</t>
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>1695000</v>
+        <v>3300000</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>288.1</v>
+        <v>188.1</v>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr"/>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
+      <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="6" t="inlineStr">
         <is>
           <t>열기</t>
@@ -6524,17 +6672,17 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>이에스티</t>
+          <t>래블업</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>그 외 기타 전자부품 제조업</t>
+          <t>시스템 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -6544,35 +6692,35 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>10,600 ~ 12,400원</t>
+          <t>19,000 ~ 22,000원</t>
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>1650000</v>
+        <v>1635000</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>204.6</v>
+        <v>359.7</v>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+          <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="O53" s="6" t="inlineStr">
@@ -6589,12 +6737,12 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>에이엘로봇</t>
+          <t>영광</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>기타 기계 및 장비 제조업</t>
+          <t>수상 금속 골조 구조재 제조업</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -6609,33 +6757,37 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15,700 ~ 17,600원</t>
+          <t>14,000 ~ 17,000원</t>
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>1800000</v>
+        <v>1695000</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>316.8</v>
+        <v>288.1</v>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr"/>
-      <c r="N54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
       <c r="O54" s="6" t="inlineStr">
         <is>
           <t>열기</t>
@@ -6643,142 +6795,126 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>엠비디</t>
-        </is>
-      </c>
-      <c r="C55" s="8" t="inlineStr">
-        <is>
-          <t>물질 검사, 측정 및 분석기구 제조업</t>
-        </is>
-      </c>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E55" s="9" t="inlineStr">
-        <is>
-          <t>정정-변경(수요예측)</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="H55" s="7" t="inlineStr">
-        <is>
-          <t>9,600 ~ 11,700원</t>
-        </is>
-      </c>
-      <c r="I55" s="10" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="J55" s="11" t="n">
-        <v>175.5</v>
-      </c>
-      <c r="K55" s="8" t="inlineStr">
-        <is>
-          <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
-        </is>
-      </c>
-      <c r="L55" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="M55" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="N55" s="7" t="inlineStr"/>
-      <c r="O55" s="12" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>이에스티</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>그 외 기타 전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>10,600 ~ 12,400원</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>204.6</v>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="O55" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>한화플러스제6호기업인수목적</t>
-        </is>
-      </c>
-      <c r="C56" s="8" t="inlineStr">
-        <is>
-          <t>스팩</t>
-        </is>
-      </c>
-      <c r="D56" s="8" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>에이엘로봇</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>기타 기계 및 장비 제조업</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E56" s="9" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F56" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="G56" s="7" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="H56" s="7" t="inlineStr">
-        <is>
-          <t>2,000원 (단일가)</t>
-        </is>
-      </c>
-      <c r="I56" s="10" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="J56" s="11" t="n">
-        <v>90</v>
-      </c>
-      <c r="K56" s="8" t="inlineStr">
-        <is>
-          <t>한화투자증권㈜ 02-3772-7395, 7398, 7393</t>
-        </is>
-      </c>
-      <c r="L56" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="M56" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="N56" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="O56" s="12" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>15,700 ~ 17,600원</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>316.8</v>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="6" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -6787,63 +6923,63 @@
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>아이엠기업인수목적1호</t>
+          <t>엠비디</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>스팩</t>
+          <t>물질 검사, 측정 및 분석기구 제조업</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>정정-변경없음</t>
+          <t>정정-변경(수요예측)</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>2,000원 (단일가)</t>
+          <t>9,600 ~ 11,700원</t>
         </is>
       </c>
       <c r="I57" s="10" t="n">
-        <v>3750000</v>
+        <v>1500000</v>
       </c>
       <c r="J57" s="11" t="n">
-        <v>75</v>
+        <v>175.5</v>
       </c>
       <c r="K57" s="8" t="inlineStr">
         <is>
-          <t>아이엠증권 02-2122-9688, 9485</t>
+          <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="N57" s="7" t="inlineStr"/>
@@ -6861,17 +6997,17 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>한화플러스제6호기업인수목적</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
+          <t>스팩</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
@@ -6881,28 +7017,28 @@
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>15,000 ~ 18,000원</t>
+          <t>2,000원 (단일가)</t>
         </is>
       </c>
       <c r="I58" s="10" t="n">
-        <v>1050000</v>
+        <v>4500000</v>
       </c>
       <c r="J58" s="11" t="n">
-        <v>189</v>
+        <v>90</v>
       </c>
       <c r="K58" s="8" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-7414, 7375, 7651</t>
+          <t>한화투자증권㈜ 02-3772-7395, 7398, 7393</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
@@ -6929,17 +7065,17 @@
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>인텔리빅스</t>
+          <t>아이엠기업인수목적1호</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
+          <t>스팩</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
@@ -6949,50 +7085,46 @@
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>정정-변경(문의처)</t>
+          <t>정정-변경없음</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>7,600 ~ 9,000원</t>
+          <t>2,000원 (단일가)</t>
         </is>
       </c>
       <c r="I59" s="10" t="n">
-        <v>1875000</v>
+        <v>3750000</v>
       </c>
       <c r="J59" s="11" t="n">
-        <v>168.8</v>
+        <v>75</v>
       </c>
       <c r="K59" s="8" t="inlineStr">
         <is>
-          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085</t>
+          <t>아이엠증권 02-2122-9688, 9485</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="N59" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N59" s="7" t="inlineStr"/>
       <c r="O59" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -7002,66 +7134,70 @@
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>다비오</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
+          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>[정정제출요구] 증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>정정-변경(수요예측)</t>
+          <t>정정-변경없음</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>12,300 ~ 16,600원</t>
+          <t>15,000 ~ 18,000원</t>
         </is>
       </c>
       <c r="I60" s="10" t="n">
-        <v>750000</v>
+        <v>1050000</v>
       </c>
       <c r="J60" s="11" t="n">
-        <v>124.5</v>
+        <v>189</v>
       </c>
       <c r="K60" s="8" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
+          <t>삼성증권 02-2020-7414, 7375, 7651</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="N60" s="7" t="inlineStr"/>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="N60" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="O60" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -7071,66 +7207,70 @@
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>유캐스트</t>
+          <t>인텔리빅스</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>기타 무선 통신장비 제조업</t>
+          <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>[정정제출요구] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>정정-변경(수요예측,밴드)</t>
+          <t>정정-변경(문의처)</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>21,000 ~ 26,000원</t>
+          <t>7,600 ~ 9,000원</t>
         </is>
       </c>
       <c r="I61" s="10" t="n">
-        <v>600000</v>
+        <v>1875000</v>
       </c>
       <c r="J61" s="11" t="n">
-        <v>156</v>
+        <v>168.8</v>
       </c>
       <c r="K61" s="8" t="inlineStr">
         <is>
-          <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
+          <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="N61" s="7" t="inlineStr"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="N61" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="O61" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -7140,63 +7280,63 @@
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>바로팜</t>
+          <t>다비오</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>전자상거래 소매 중개업</t>
+          <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[정정제출요구] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>정정-변경(문의처)</t>
+          <t>정정-변경(수요예측)</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>12,300 ~ 16,600원</t>
+        </is>
+      </c>
+      <c r="I62" s="10" t="n">
+        <v>750000</v>
+      </c>
+      <c r="J62" s="11" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="K62" s="8" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
+        </is>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M62" s="7" t="inlineStr">
+        <is>
           <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G62" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="H62" s="7" t="inlineStr">
-        <is>
-          <t>16,400 ~ 20,200원</t>
-        </is>
-      </c>
-      <c r="I62" s="10" t="n">
-        <v>1335000</v>
-      </c>
-      <c r="J62" s="11" t="n">
-        <v>269.7</v>
-      </c>
-      <c r="K62" s="8" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805</t>
-        </is>
-      </c>
-      <c r="L62" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="M62" s="7" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
         </is>
       </c>
       <c r="N62" s="7" t="inlineStr"/>
@@ -7209,70 +7349,66 @@
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>유캐스트</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
+          <t>기타 무선 통신장비 제조업</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[정정제출요구] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>정정-변경없음</t>
+          <t>정정-변경(수요예측,밴드)</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>15,000 ~ 18,000원</t>
+          <t>21,000 ~ 26,000원</t>
         </is>
       </c>
       <c r="I63" s="10" t="n">
-        <v>1050000</v>
+        <v>600000</v>
       </c>
       <c r="J63" s="11" t="n">
-        <v>189</v>
+        <v>156</v>
       </c>
       <c r="K63" s="8" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-7414, 7375, 7651</t>
+          <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="N63" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="N63" s="7" t="inlineStr"/>
       <c r="O63" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -7282,17 +7418,17 @@
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>티앤이코리아</t>
+          <t>바로팜</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>산업용 송풍기 및 배기장치 제조업</t>
+          <t>전자상거래 소매 중개업</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
@@ -7302,50 +7438,46 @@
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>정정-변경(수요예측)</t>
+          <t>정정-변경(문의처)</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>12,600 ~ 15,300원</t>
+          <t>16,400 ~ 20,200원</t>
         </is>
       </c>
       <c r="I64" s="10" t="n">
-        <v>1800000</v>
+        <v>1335000</v>
       </c>
       <c r="J64" s="11" t="n">
-        <v>275.4</v>
+        <v>269.7</v>
       </c>
       <c r="K64" s="8" t="inlineStr">
         <is>
-          <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
+          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="N64" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="N64" s="7" t="inlineStr"/>
       <c r="O64" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -7355,17 +7487,17 @@
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>엠비디</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>물질 검사, 측정 및 분석기구 제조업</t>
+          <t>그 외 기타 달리 분류되지 않은 제품 제조업</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
@@ -7375,46 +7507,50 @@
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>정정-변경(수요예측,밴드)</t>
+          <t>정정-변경없음</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>9,400 ~ 11,500원</t>
+          <t>15,000 ~ 18,000원</t>
         </is>
       </c>
       <c r="I65" s="10" t="n">
-        <v>1500000</v>
+        <v>1050000</v>
       </c>
       <c r="J65" s="11" t="n">
-        <v>172.5</v>
+        <v>189</v>
       </c>
       <c r="K65" s="8" t="inlineStr">
         <is>
-          <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
+          <t>삼성증권 02-2020-7414, 7375, 7651</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="N65" s="7" t="inlineStr"/>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="N65" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="O65" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -7424,78 +7560,220 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>티앤이코리아</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>산업용 송풍기 및 배기장치 제조업</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>정정-변경(수요예측)</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>12,600 ~ 15,300원</t>
+        </is>
+      </c>
+      <c r="I66" s="10" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="J66" s="11" t="n">
+        <v>275.4</v>
+      </c>
+      <c r="K66" s="8" t="inlineStr">
+        <is>
+          <t>신한투자증권㈜ 02-3772-2073, 4168, 4161, 3131</t>
+        </is>
+      </c>
+      <c r="L66" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="M66" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="N66" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="O66" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>엠비디</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>물질 검사, 측정 및 분석기구 제조업</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>정정-변경(수요예측,밴드)</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>9,400 ~ 11,500원</t>
+        </is>
+      </c>
+      <c r="I67" s="10" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="J67" s="11" t="n">
+        <v>172.5</v>
+      </c>
+      <c r="K67" s="8" t="inlineStr">
+        <is>
+          <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
+        </is>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="M67" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="N67" s="7" t="inlineStr"/>
+      <c r="O67" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B68" s="7" t="inlineStr">
         <is>
           <t>래블업</t>
         </is>
       </c>
-      <c r="C66" s="8" t="inlineStr">
+      <c r="C68" s="8" t="inlineStr">
         <is>
           <t>시스템 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D66" s="8" t="inlineStr">
+      <c r="D68" s="8" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E66" s="9" t="inlineStr">
+      <c r="E68" s="9" t="inlineStr">
         <is>
           <t>정정-변경(수요예측,밴드)</t>
         </is>
       </c>
-      <c r="F66" s="7" t="inlineStr">
+      <c r="F68" s="7" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="G66" s="7" t="inlineStr">
+      <c r="G68" s="7" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="H66" s="7" t="inlineStr">
+      <c r="H68" s="7" t="inlineStr">
         <is>
           <t>20,000 ~ 23,000원</t>
         </is>
       </c>
-      <c r="I66" s="10" t="n">
+      <c r="I68" s="10" t="n">
         <v>1635000</v>
       </c>
-      <c r="J66" s="11" t="n">
+      <c r="J68" s="11" t="n">
         <v>376.1</v>
       </c>
-      <c r="K66" s="8" t="inlineStr">
+      <c r="K68" s="8" t="inlineStr">
         <is>
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="L66" s="7" t="inlineStr">
+      <c r="L68" s="7" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="M66" s="7" t="inlineStr">
+      <c r="M68" s="7" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="N66" s="7" t="inlineStr">
+      <c r="N68" s="7" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="O66" s="12" t="inlineStr">
+      <c r="O68" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O66"/>
+  <autoFilter ref="A1:O68"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -7562,6 +7840,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="rId67"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/수요예측_일정.xlsx
+++ b/수요예측_일정.xlsx
@@ -2698,7 +2698,11 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N32" s="7" t="inlineStr"/>
+      <c r="N32" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
       <c r="O32" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -5674,7 +5678,11 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N37" s="7" t="inlineStr"/>
+      <c r="N37" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
       <c r="O37" s="12" t="inlineStr">
         <is>
           <t>열기</t>
@@ -5735,7 +5743,11 @@
       </c>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
       <c r="O38" s="6" t="inlineStr">
         <is>
           <t>열기</t>
@@ -7124,7 +7136,11 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N59" s="7" t="inlineStr"/>
+      <c r="N59" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
       <c r="O59" s="12" t="inlineStr">
         <is>
           <t>열기</t>

--- a/수요예측_일정.xlsx
+++ b/수요예측_일정.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'수요예측 일정'!$A$1:$O$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체 이력'!$A$1:$O$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체 이력'!$A$1:$O$70</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -582,12 +582,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>에이엘로봇</t>
+          <t>영광와이케이엠씨</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>기타 기계 및 장비 제조업</t>
+          <t>그 외 기타 금속가공업</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -602,38 +602,38 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>15,700 ~ 17,600원</t>
+          <t>9,400 ~ 11,000원</t>
         </is>
       </c>
       <c r="I2" s="5" t="n">
-        <v>1800000</v>
+        <v>1694840</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>316.8</v>
+        <v>186.4</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
+          <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr"/>
@@ -644,69 +644,69 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>에이엘로봇</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>기타 기계 및 장비 제조업</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>신영해피투모로우제12호기업인수목적</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>스팩</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-19</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-20</t>
-        </is>
-      </c>
-      <c r="H3" s="8" t="inlineStr">
-        <is>
-          <t>2,000원 (단일가)</t>
-        </is>
-      </c>
-      <c r="I3" s="10" t="n">
-        <v>4687500</v>
-      </c>
-      <c r="J3" s="11" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="K3" s="9" t="inlineStr">
-        <is>
-          <t>신영증권㈜ 02-2004-9554, 9230, 9403</t>
-        </is>
-      </c>
-      <c r="L3" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-24</t>
-        </is>
-      </c>
-      <c r="M3" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-27</t>
-        </is>
-      </c>
-      <c r="N3" s="8" t="inlineStr"/>
-      <c r="O3" s="12" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>15,700 ~ 17,600원</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="J3" s="6" t="n">
+        <v>316.8</v>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -720,12 +720,12 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>데스틴파워</t>
+          <t>신영해피투모로우제12호기업인수목적</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>전동기, 발전기 및 전기 변환장치 제조업</t>
+          <t>스팩</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
@@ -740,38 +740,38 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>8,000 ~ 11,000원</t>
+          <t>2,000원 (단일가)</t>
         </is>
       </c>
       <c r="I4" s="10" t="n">
-        <v>1650000</v>
+        <v>4687500</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>181.5</v>
+        <v>93.8</v>
       </c>
       <c r="K4" s="9" t="inlineStr">
         <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6269</t>
+          <t>신영증권㈜ 02-2004-9554, 9230, 9403</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="N4" s="8" t="inlineStr"/>
@@ -789,12 +789,12 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>KTE</t>
+          <t>데스틴파워</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>배전반 및 전기 자동제어반 제조업</t>
+          <t>전동기, 발전기 및 전기 변환장치 제조업</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
@@ -819,18 +819,18 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>19,000 ~ 23,000원</t>
+          <t>8,000 ~ 11,000원</t>
         </is>
       </c>
       <c r="I5" s="10" t="n">
-        <v>2112000</v>
+        <v>1650000</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>485.8</v>
+        <v>181.5</v>
       </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
-          <t>NH투자증권 02-768-7462, 7467</t>
+          <t>한국투자증권㈜ 02-3276-5958, 6269</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
@@ -851,69 +851,69 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>케이엠에프</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>기타 식품 제조업</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-20</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>15,000 ~ 17,800원</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="J6" s="6" t="n">
-        <v>267</v>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799 / 아이비케이투자증권㈜ 02-6915-5337, 5338, 5799</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-24</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-27</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>KTE</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>배전반 및 전기 자동제어반 제조업</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>19,000 ~ 23,000원</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>2112000</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>485.8</v>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>NH투자증권 02-768-7462, 7467</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr"/>
+      <c r="O6" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -927,12 +927,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>엔키화이트햇</t>
+          <t>케이엠에프</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -942,43 +942,43 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>정정-변경(수요예측)</t>
+          <t>정정-변경없음</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>2026-11-20</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,000 ~ 16,500원</t>
+          <t>15,000 ~ 17,800원</t>
         </is>
       </c>
       <c r="I7" s="5" t="n">
-        <v>1258000</v>
+        <v>1500000</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>207.6</v>
+        <v>267</v>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799 / 아이비케이투자증권㈜ 02-6915-5337, 5338, 5799</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr"/>
@@ -996,12 +996,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>아델</t>
+          <t>엔키화이트햇</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>의학 및 약학 연구개발업</t>
+          <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1011,43 +1011,43 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>정정-변경(문의처)</t>
+          <t>정정-변경(수요예측)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,000 ~ 25,000원</t>
+          <t>13,000 ~ 16,500원</t>
         </is>
       </c>
       <c r="I8" s="5" t="n">
-        <v>1627500</v>
+        <v>1258000</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>406.9</v>
+        <v>207.6</v>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-8213, 6661</t>
+          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr"/>
@@ -1058,138 +1058,138 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>아델</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>의학 및 약학 연구개발업</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경(문의처)</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>18,000 ~ 25,000원</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>1627500</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>406.9</v>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-8213, 6661</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>우리투자제1호기업인수목적</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>스팩</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>2026-11-25</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>2026-11-26</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>2,000원 (단일가)</t>
         </is>
       </c>
-      <c r="I9" s="10" t="n">
+      <c r="I10" s="10" t="n">
         <v>4875000</v>
       </c>
-      <c r="J9" s="11" t="n">
+      <c r="J10" s="11" t="n">
         <v>97.5</v>
       </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="K10" s="9" t="inlineStr">
         <is>
           <t>우리투자증권 02-6390-3889</t>
         </is>
       </c>
-      <c r="L9" s="8" t="inlineStr">
+      <c r="L10" s="8" t="inlineStr">
         <is>
           <t>2026-12-02</t>
         </is>
       </c>
-      <c r="M9" s="8" t="inlineStr">
+      <c r="M10" s="8" t="inlineStr">
         <is>
           <t>2026-12-07</t>
         </is>
       </c>
-      <c r="N9" s="8" t="inlineStr"/>
-      <c r="O9" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>제논</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경(수요예측)</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-20</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,700 ~ 12,200원</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>1550000</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>189.1</v>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>삼성증권 02-2020-8023, 7653, 7850</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-24</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-27</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="7" t="inlineStr">
+      <c r="N10" s="8" t="inlineStr"/>
+      <c r="O10" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1198,17 +1198,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>동원파츠</t>
+          <t>제논</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>반도체 제조용 기계 제조업</t>
+          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1218,43 +1218,43 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>정정-변경없음</t>
+          <t>정정-변경(수요예측)</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,000 ~ 26,500원</t>
+          <t>9,700 ~ 12,200원</t>
         </is>
       </c>
       <c r="I11" s="5" t="n">
-        <v>1522500</v>
+        <v>1550000</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>403.5</v>
+        <v>189.1</v>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-6975, 8217, 7651</t>
+          <t>삼성증권 02-2020-8023, 7653, 7850</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr"/>
@@ -1265,69 +1265,69 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>동원파츠</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>반도체 제조용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>인터엑스</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-04</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>10,000 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I12" s="10" t="n">
-        <v>2250000</v>
-      </c>
-      <c r="J12" s="11" t="n">
-        <v>292.5</v>
-      </c>
-      <c r="K12" s="9" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5700, 6648</t>
-        </is>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-09</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-14</t>
-        </is>
-      </c>
-      <c r="N12" s="8" t="inlineStr"/>
-      <c r="O12" s="12" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>23,000 ~ 26,500원</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>1522500</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>403.5</v>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-6975, 8217, 7651</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1336,22 +1336,22 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>유캐스트</t>
+          <t>인터엑스</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>기타 무선 통신장비 제조업</t>
+          <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -1361,38 +1361,38 @@
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>19,000 ~ 23,000원</t>
+          <t>10,000 ~ 13,000원</t>
         </is>
       </c>
       <c r="I13" s="10" t="n">
-        <v>600000</v>
+        <v>2250000</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>138</v>
+        <v>292.5</v>
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
+          <t>한국투자증권㈜ 02-3276-5700, 6648</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="M13" s="8" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="N13" s="8" t="inlineStr"/>
@@ -1403,138 +1403,138 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>유캐스트</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>기타 무선 통신장비 제조업</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>19,000 ~ 23,000원</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="n">
+        <v>600000</v>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>138</v>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
+        </is>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="N14" s="8" t="inlineStr"/>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>옵토닉스</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>광학렌즈 및 광학요소 제조업</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>10,000 ~ 12,000원</t>
         </is>
       </c>
-      <c r="I14" s="5" t="n">
+      <c r="I15" s="5" t="n">
         <v>1572490</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="J15" s="6" t="n">
         <v>188.7</v>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>2026-11-05</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>이노보테라퓨틱스</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-02</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>20,000 ~ 24,000원</t>
-        </is>
-      </c>
-      <c r="I15" s="10" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="J15" s="11" t="n">
-        <v>396</v>
-      </c>
-      <c r="K15" s="9" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
-        </is>
-      </c>
-      <c r="L15" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-07</t>
-        </is>
-      </c>
-      <c r="M15" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-10</t>
-        </is>
-      </c>
-      <c r="N15" s="8" t="inlineStr"/>
-      <c r="O15" s="12" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1543,17 +1543,17 @@
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>에이엔에이치스트럭쳐</t>
+          <t>이노보테라퓨틱스</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>기타 엔지니어링 서비스업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -1568,38 +1568,38 @@
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>11,200 ~ 13,600원</t>
+          <t>20,000 ~ 24,000원</t>
         </is>
       </c>
       <c r="I16" s="10" t="n">
-        <v>1575000</v>
+        <v>1650000</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>214.2</v>
+        <v>396</v>
       </c>
       <c r="K16" s="9" t="inlineStr">
         <is>
-          <t>NH투자증권 02-2229-6315, 6829</t>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="M16" s="8" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="N16" s="8" t="inlineStr"/>
@@ -1610,142 +1610,142 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>에이엔에이치스트럭쳐</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>기타 엔지니어링 서비스업</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>11,200 ~ 13,600원</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="n">
+        <v>1575000</v>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>214.2</v>
+      </c>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>NH투자증권 02-2229-6315, 6829</t>
+        </is>
+      </c>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="N17" s="8" t="inlineStr"/>
+      <c r="O17" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>이에스티</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>그 외 기타 전자부품 제조업</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>10,600 ~ 12,400원</t>
         </is>
       </c>
-      <c r="I17" s="5" t="n">
+      <c r="I18" s="5" t="n">
         <v>1650000</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="J18" s="6" t="n">
         <v>204.6</v>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="K18" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>2026-11-04</t>
         </is>
       </c>
-      <c r="O17" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>에스에프씨</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>그 외 기타 분류 안된 화학제품 제조업</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>31,600 ~ 36,100원</t>
-        </is>
-      </c>
-      <c r="I18" s="10" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J18" s="11" t="n">
-        <v>1353.8</v>
-      </c>
-      <c r="K18" s="9" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
-        </is>
-      </c>
-      <c r="L18" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="M18" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-      <c r="N18" s="8" t="inlineStr"/>
-      <c r="O18" s="12" t="inlineStr">
+      <c r="O18" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>씨아이에스케미칼</t>
+          <t>에스에프씨</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>알루미늄 제련, 정련 및 합금 제조업</t>
+          <t>그 외 기타 분류 안된 화학제품 제조업</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
@@ -1779,38 +1779,38 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>5,400 ~ 6,800원</t>
+          <t>31,600 ~ 36,100원</t>
         </is>
       </c>
       <c r="I19" s="10" t="n">
-        <v>3000000</v>
+        <v>3750000</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>204</v>
+        <v>1353.8</v>
       </c>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
+          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
         </is>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="N19" s="8" t="inlineStr"/>
@@ -1823,17 +1823,17 @@
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>제이앤티지</t>
+          <t>씨아이에스케미칼</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>그 외 자동차용 신품 부품 제조업</t>
+          <t>알루미늄 제련, 정련 및 합금 제조업</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
@@ -1848,38 +1848,38 @@
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>26,400 ~ 31,900원</t>
+          <t>5,400 ~ 6,800원</t>
         </is>
       </c>
       <c r="I20" s="10" t="n">
-        <v>3182000</v>
+        <v>3000000</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>1015.1</v>
+        <v>204</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
+          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="M20" s="8" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="N20" s="8" t="inlineStr"/>
@@ -1897,12 +1897,12 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>씨앤엠</t>
+          <t>제이앤티지</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>전동기 및 발전기 제조업</t>
+          <t>그 외 자동차용 신품 부품 제조업</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
@@ -1927,18 +1927,18 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>10,000 ~ 13,000원</t>
+          <t>26,400 ~ 31,900원</t>
         </is>
       </c>
       <c r="I21" s="10" t="n">
-        <v>2059500</v>
+        <v>3182000</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>267.7</v>
+        <v>1015.1</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
         </is>
       </c>
       <c r="L21" s="8" t="inlineStr">
@@ -1959,69 +1959,69 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>넥스아이</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>10,500 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J22" s="6" t="n">
-        <v>487.5</v>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>씨앤엠</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>전동기 및 발전기 제조업</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="7" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>10,000 ~ 13,000원</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="n">
+        <v>2059500</v>
+      </c>
+      <c r="J22" s="11" t="n">
+        <v>267.7</v>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+        </is>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M22" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N22" s="8" t="inlineStr"/>
+      <c r="O22" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2035,12 +2035,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>항공기용 부품 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -2055,38 +2055,38 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>10,500 ~ 13,000원</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>487.5</v>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
           <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>4,700 ~ 5,700원</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="n">
-        <v>3300000</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>188.1</v>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr"/>
@@ -2099,17 +2099,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>바로팜</t>
+          <t>하나에어로다이내믹스</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>전자상거래 소매 중개업</t>
+          <t>항공기용 부품 제조업</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -2124,38 +2124,38 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,400 ~ 20,200원</t>
+          <t>4,700 ~ 5,700원</t>
         </is>
       </c>
       <c r="I24" s="5" t="n">
-        <v>1335000</v>
+        <v>3300000</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>269.7</v>
+        <v>188.1</v>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr"/>
@@ -2166,187 +2166,211 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>바로팜</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>전자상거래 소매 중개업</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>16,400 ~ 20,200원</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>1335000</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>269.7</v>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>엠비디</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>물질 검사, 측정 및 분석기구 제조업</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>9,600 ~ 11,700원</t>
         </is>
       </c>
-      <c r="I25" s="10" t="n">
+      <c r="I26" s="10" t="n">
         <v>1500000</v>
       </c>
-      <c r="J25" s="11" t="n">
+      <c r="J26" s="11" t="n">
         <v>175.5</v>
       </c>
-      <c r="K25" s="9" t="inlineStr">
+      <c r="K26" s="9" t="inlineStr">
         <is>
           <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
         </is>
       </c>
-      <c r="L25" s="8" t="inlineStr">
+      <c r="L26" s="8" t="inlineStr">
         <is>
           <t>2026-11-12</t>
         </is>
       </c>
-      <c r="M25" s="8" t="inlineStr">
+      <c r="M26" s="8" t="inlineStr">
         <is>
           <t>2026-11-17</t>
         </is>
       </c>
-      <c r="N25" s="8" t="inlineStr"/>
-      <c r="O25" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="N26" s="8" t="inlineStr"/>
+      <c r="O26" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>래블업</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>시스템 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>19,000 ~ 22,000원</t>
         </is>
       </c>
-      <c r="I26" s="5" t="n">
+      <c r="I27" s="5" t="n">
         <v>1635000</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="J27" s="6" t="n">
         <v>359.7</v>
       </c>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>NH투자증권 02-768-7462, 7467</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="O26" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>SimwonAmericaCorp.</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>자동차 신품 부품 제조업</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>수요예측 항목 없음(원문 확인)</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="inlineStr"/>
-      <c r="G27" s="8" t="inlineStr"/>
-      <c r="H27" s="8" t="inlineStr"/>
-      <c r="I27" s="10" t="inlineStr"/>
-      <c r="J27" s="11" t="inlineStr"/>
-      <c r="K27" s="9" t="inlineStr"/>
-      <c r="L27" s="8" t="inlineStr"/>
-      <c r="M27" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="N27" s="8" t="inlineStr"/>
-      <c r="O27" s="12" t="inlineStr">
+      <c r="O27" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -2355,63 +2379,39 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>다비오</t>
+          <t>SimwonAmericaCorp.</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
+          <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>12,300 ~ 16,600원</t>
-        </is>
-      </c>
-      <c r="I28" s="10" t="n">
-        <v>750000</v>
-      </c>
-      <c r="J28" s="11" t="n">
-        <v>124.5</v>
-      </c>
-      <c r="K28" s="9" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
-        </is>
-      </c>
-      <c r="L28" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
+          <t>수요예측 항목 없음(원문 확인)</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr"/>
+      <c r="G28" s="8" t="inlineStr"/>
+      <c r="H28" s="8" t="inlineStr"/>
+      <c r="I28" s="10" t="inlineStr"/>
+      <c r="J28" s="11" t="inlineStr"/>
+      <c r="K28" s="9" t="inlineStr"/>
+      <c r="L28" s="8" t="inlineStr"/>
       <c r="M28" s="8" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="N28" s="8" t="inlineStr"/>
@@ -2429,17 +2429,17 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>영광와이케이엠씨</t>
+          <t>다비오</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>그 외 기타 금속가공업</t>
+          <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -2449,38 +2449,38 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>9,400 ~ 11,000원</t>
+          <t>12,300 ~ 16,600원</t>
         </is>
       </c>
       <c r="I29" s="10" t="n">
-        <v>1694840</v>
+        <v>750000</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>186.4</v>
+        <v>124.5</v>
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
+          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
         </is>
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="N29" s="8" t="inlineStr"/>
@@ -3124,7 +3124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O69"/>
+  <dimension ref="A1:O70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>에이엘로봇</t>
+          <t>영광와이케이엠씨</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>기타 기계 및 장비 제조업</t>
+          <t>그 외 기타 금속가공업</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -3249,38 +3249,38 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>15,700 ~ 17,600원</t>
+          <t>9,400 ~ 11,000원</t>
         </is>
       </c>
       <c r="I2" s="5" t="n">
-        <v>1800000</v>
+        <v>1694840</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>316.8</v>
+        <v>186.4</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
+          <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr"/>
@@ -3291,69 +3291,69 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>에이엘로봇</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>기타 기계 및 장비 제조업</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>신영해피투모로우제12호기업인수목적</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>스팩</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-19</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-20</t>
-        </is>
-      </c>
-      <c r="H3" s="8" t="inlineStr">
-        <is>
-          <t>2,000원 (단일가)</t>
-        </is>
-      </c>
-      <c r="I3" s="10" t="n">
-        <v>4687500</v>
-      </c>
-      <c r="J3" s="11" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="K3" s="9" t="inlineStr">
-        <is>
-          <t>신영증권㈜ 02-2004-9554, 9230, 9403</t>
-        </is>
-      </c>
-      <c r="L3" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-24</t>
-        </is>
-      </c>
-      <c r="M3" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-27</t>
-        </is>
-      </c>
-      <c r="N3" s="8" t="inlineStr"/>
-      <c r="O3" s="12" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>15,700 ~ 17,600원</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="J3" s="6" t="n">
+        <v>316.8</v>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>데스틴파워</t>
+          <t>신영해피투모로우제12호기업인수목적</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>전동기, 발전기 및 전기 변환장치 제조업</t>
+          <t>스팩</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
@@ -3387,38 +3387,38 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>8,000 ~ 11,000원</t>
+          <t>2,000원 (단일가)</t>
         </is>
       </c>
       <c r="I4" s="10" t="n">
-        <v>1650000</v>
+        <v>4687500</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>181.5</v>
+        <v>93.8</v>
       </c>
       <c r="K4" s="9" t="inlineStr">
         <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6269</t>
+          <t>신영증권㈜ 02-2004-9554, 9230, 9403</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="N4" s="8" t="inlineStr"/>
@@ -3436,12 +3436,12 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>KTE</t>
+          <t>데스틴파워</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>배전반 및 전기 자동제어반 제조업</t>
+          <t>전동기, 발전기 및 전기 변환장치 제조업</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
@@ -3466,18 +3466,18 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>19,000 ~ 23,000원</t>
+          <t>8,000 ~ 11,000원</t>
         </is>
       </c>
       <c r="I5" s="10" t="n">
-        <v>2112000</v>
+        <v>1650000</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>485.8</v>
+        <v>181.5</v>
       </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
-          <t>NH투자증권 02-768-7462, 7467</t>
+          <t>한국투자증권㈜ 02-3276-5958, 6269</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
@@ -3498,69 +3498,69 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>케이엠에프</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>기타 식품 제조업</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-20</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>15,000 ~ 17,800원</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="J6" s="6" t="n">
-        <v>267</v>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799 / 아이비케이투자증권㈜ 02-6915-5337, 5338, 5799</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-24</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-27</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>KTE</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>배전반 및 전기 자동제어반 제조업</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>19,000 ~ 23,000원</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>2112000</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>485.8</v>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>NH투자증권 02-768-7462, 7467</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr"/>
+      <c r="O6" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>엔키화이트햇</t>
+          <t>케이엠에프</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -3589,43 +3589,43 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>정정-변경(수요예측)</t>
+          <t>정정-변경없음</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>2026-11-20</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,000 ~ 16,500원</t>
+          <t>15,000 ~ 17,800원</t>
         </is>
       </c>
       <c r="I7" s="5" t="n">
-        <v>1258000</v>
+        <v>1500000</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>207.6</v>
+        <v>267</v>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799 / 아이비케이투자증권㈜ 02-6915-5337, 5338, 5799</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr"/>
@@ -3643,12 +3643,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>아델</t>
+          <t>엔키화이트햇</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>의학 및 약학 연구개발업</t>
+          <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -3658,43 +3658,43 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>정정-변경(문의처)</t>
+          <t>정정-변경(수요예측)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,000 ~ 25,000원</t>
+          <t>13,000 ~ 16,500원</t>
         </is>
       </c>
       <c r="I8" s="5" t="n">
-        <v>1627500</v>
+        <v>1258000</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>406.9</v>
+        <v>207.6</v>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-8213, 6661</t>
+          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>케이엠에프</t>
+          <t>아델</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -3727,43 +3727,43 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>정정-변경없음</t>
+          <t>정정-변경(문의처)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,000 ~ 17,800원</t>
+          <t>18,000 ~ 25,000원</t>
         </is>
       </c>
       <c r="I9" s="5" t="n">
-        <v>1500000</v>
+        <v>1627500</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>267</v>
+        <v>406.9</v>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
+          <t>삼성증권 02-2020-8213, 6661</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr"/>
@@ -3774,138 +3774,138 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>케이엠에프</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>기타 식품 제조업</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15,000 ~ 17,800원</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>267</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5338, 02-6915-5799</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>우리투자제1호기업인수목적</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>스팩</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>2026-11-25</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>2026-11-26</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>2,000원 (단일가)</t>
         </is>
       </c>
-      <c r="I10" s="10" t="n">
+      <c r="I11" s="10" t="n">
         <v>4875000</v>
       </c>
-      <c r="J10" s="11" t="n">
+      <c r="J11" s="11" t="n">
         <v>97.5</v>
       </c>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="K11" s="9" t="inlineStr">
         <is>
           <t>우리투자증권 02-6390-3889</t>
         </is>
       </c>
-      <c r="L10" s="8" t="inlineStr">
+      <c r="L11" s="8" t="inlineStr">
         <is>
           <t>2026-12-02</t>
         </is>
       </c>
-      <c r="M10" s="8" t="inlineStr">
+      <c r="M11" s="8" t="inlineStr">
         <is>
           <t>2026-12-07</t>
         </is>
       </c>
-      <c r="N10" s="8" t="inlineStr"/>
-      <c r="O10" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>제논</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경(수요예측)</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-20</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>9,700 ~ 12,200원</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>1550000</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>189.1</v>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>삼성증권 02-2020-8023, 7653, 7850</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-24</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-27</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="7" t="inlineStr">
+      <c r="N11" s="8" t="inlineStr"/>
+      <c r="O11" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -3914,7 +3914,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -3934,17 +3934,17 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>정정-변경없음</t>
+          <t>정정-변경(수요예측)</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -3963,8 +3963,16 @@
           <t>삼성증권 02-2020-8023, 7653, 7850</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="7" t="inlineStr">
         <is>
@@ -3980,12 +3988,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>동원파츠</t>
+          <t>제논</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>반도체 제조용 기계 제조업</t>
+          <t>컴퓨터시스템 통합 자문, 구축 및 관리업</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -4000,40 +4008,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,000 ~ 26,500원</t>
+          <t>9,700 ~ 12,200원</t>
         </is>
       </c>
       <c r="I13" s="5" t="n">
-        <v>1522500</v>
+        <v>1550000</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>403.5</v>
+        <v>189.1</v>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>삼성증권 02-2020-6975, 8217, 7651</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
+          <t>삼성증권 02-2020-8023, 7653, 7850</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="7" t="inlineStr">
         <is>
@@ -4042,69 +4042,69 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>동원파츠</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>반도체 제조용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>인터엑스</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-04</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>10,000 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I14" s="10" t="n">
-        <v>2250000</v>
-      </c>
-      <c r="J14" s="11" t="n">
-        <v>292.5</v>
-      </c>
-      <c r="K14" s="9" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5700, 6648</t>
-        </is>
-      </c>
-      <c r="L14" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-09</t>
-        </is>
-      </c>
-      <c r="M14" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-14</t>
-        </is>
-      </c>
-      <c r="N14" s="8" t="inlineStr"/>
-      <c r="O14" s="12" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>23,000 ~ 26,500원</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>1522500</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>403.5</v>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-6975, 8217, 7651</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4113,22 +4113,22 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>유캐스트</t>
+          <t>인터엑스</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>기타 무선 통신장비 제조업</t>
+          <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -4138,38 +4138,38 @@
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>19,000 ~ 23,000원</t>
+          <t>10,000 ~ 13,000원</t>
         </is>
       </c>
       <c r="I15" s="10" t="n">
-        <v>600000</v>
+        <v>2250000</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>138</v>
+        <v>292.5</v>
       </c>
       <c r="K15" s="9" t="inlineStr">
         <is>
-          <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
+          <t>한국투자증권㈜ 02-3276-5700, 6648</t>
         </is>
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="M15" s="8" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="N15" s="8" t="inlineStr"/>
@@ -4180,138 +4180,138 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>유캐스트</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>기타 무선 통신장비 제조업</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>19,000 ~ 23,000원</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>600000</v>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>138</v>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>유진투자증권㈜ 02-368-6353, 6349, 6397, 6398, 6352</t>
+        </is>
+      </c>
+      <c r="L16" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="M16" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="N16" s="8" t="inlineStr"/>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>옵토닉스</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>광학렌즈 및 광학요소 제조업</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>10,000 ~ 12,000원</t>
         </is>
       </c>
-      <c r="I16" s="5" t="n">
+      <c r="I17" s="5" t="n">
         <v>1572490</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="J17" s="6" t="n">
         <v>188.7</v>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>한국투자증권 02-3276-5958, 6269</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>2026-11-05</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>이노보테라퓨틱스</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-02</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>20,000 ~ 24,000원</t>
-        </is>
-      </c>
-      <c r="I17" s="10" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="J17" s="11" t="n">
-        <v>396</v>
-      </c>
-      <c r="K17" s="9" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
-        </is>
-      </c>
-      <c r="L17" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-07</t>
-        </is>
-      </c>
-      <c r="M17" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-10</t>
-        </is>
-      </c>
-      <c r="N17" s="8" t="inlineStr"/>
-      <c r="O17" s="12" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4320,17 +4320,17 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>에이엔에이치스트럭쳐</t>
+          <t>이노보테라퓨틱스</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>기타 엔지니어링 서비스업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
@@ -4345,38 +4345,38 @@
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>11,200 ~ 13,600원</t>
+          <t>20,000 ~ 24,000원</t>
         </is>
       </c>
       <c r="I18" s="10" t="n">
-        <v>1575000</v>
+        <v>1650000</v>
       </c>
       <c r="J18" s="11" t="n">
-        <v>214.2</v>
+        <v>396</v>
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>NH투자증권 02-2229-6315, 6829</t>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="M18" s="8" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr"/>
@@ -4387,142 +4387,142 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>에이엔에이치스트럭쳐</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>기타 엔지니어링 서비스업</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>11,200 ~ 13,600원</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="n">
+        <v>1575000</v>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>214.2</v>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>NH투자증권 02-2229-6315, 6829</t>
+        </is>
+      </c>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="M19" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="N19" s="8" t="inlineStr"/>
+      <c r="O19" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>이에스티</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>그 외 기타 전자부품 제조업</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>10,600 ~ 12,400원</t>
         </is>
       </c>
-      <c r="I19" s="5" t="n">
+      <c r="I20" s="5" t="n">
         <v>1650000</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="J20" s="6" t="n">
         <v>204.6</v>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>2026-11-04</t>
         </is>
       </c>
-      <c r="O19" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>에스에프씨</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>그 외 기타 분류 안된 화학제품 제조업</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>31,600 ~ 36,100원</t>
-        </is>
-      </c>
-      <c r="I20" s="10" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J20" s="11" t="n">
-        <v>1353.8</v>
-      </c>
-      <c r="K20" s="9" t="inlineStr">
-        <is>
-          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
-        </is>
-      </c>
-      <c r="L20" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="M20" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-      <c r="N20" s="8" t="inlineStr"/>
-      <c r="O20" s="12" t="inlineStr">
+      <c r="O20" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4536,12 +4536,12 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>씨아이에스케미칼</t>
+          <t>에스에프씨</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>알루미늄 제련, 정련 및 합금 제조업</t>
+          <t>그 외 기타 분류 안된 화학제품 제조업</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
@@ -4556,38 +4556,38 @@
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>5,400 ~ 6,800원</t>
+          <t>31,600 ~ 36,100원</t>
         </is>
       </c>
       <c r="I21" s="10" t="n">
-        <v>3000000</v>
+        <v>3750000</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>204</v>
+        <v>1353.8</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
+          <t>미래에셋증권㈜ 02-3774-7160, 7071, 7147 / 한국투자증권㈜ 02-3276-4626</t>
         </is>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="N21" s="8" t="inlineStr"/>
@@ -4600,17 +4600,17 @@
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>제이앤티지</t>
+          <t>씨아이에스케미칼</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>그 외 자동차용 신품 부품 제조업</t>
+          <t>알루미늄 제련, 정련 및 합금 제조업</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
@@ -4625,38 +4625,38 @@
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>26,400 ~ 31,900원</t>
+          <t>5,400 ~ 6,800원</t>
         </is>
       </c>
       <c r="I22" s="10" t="n">
-        <v>3182000</v>
+        <v>3000000</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>1015.1</v>
+        <v>204</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
+          <t>KB증권㈜ 02-6114-0972, 1671 / KB증권㈜ 02-6114-1543</t>
         </is>
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="N22" s="8" t="inlineStr"/>
@@ -4674,12 +4674,12 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>씨앤엠</t>
+          <t>제이앤티지</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>전동기 및 발전기 제조업</t>
+          <t>그 외 자동차용 신품 부품 제조업</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
@@ -4704,18 +4704,18 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>10,000 ~ 13,000원</t>
+          <t>26,400 ~ 31,900원</t>
         </is>
       </c>
       <c r="I23" s="10" t="n">
-        <v>2059500</v>
+        <v>3182000</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>267.7</v>
+        <v>1015.1</v>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+          <t>대신증권㈜ 02-769-2723, 02-769-2293</t>
         </is>
       </c>
       <c r="L23" s="8" t="inlineStr">
@@ -4736,69 +4736,69 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>넥스아이</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>10,500 ~ 13,000원</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>487.5</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>씨앤엠</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>전동기 및 발전기 제조업</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="7" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>10,000 ~ 13,000원</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="n">
+        <v>2059500</v>
+      </c>
+      <c r="J24" s="11" t="n">
+        <v>267.7</v>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-5958, 6917</t>
+        </is>
+      </c>
+      <c r="L24" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="N24" s="8" t="inlineStr"/>
+      <c r="O24" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -4812,12 +4812,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>항공기용 부품 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -4832,38 +4832,38 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>10,500 ~ 13,000원</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>487.5</v>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>한국투자증권㈜ 02-3276-6384, 5198</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
           <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>4,700 ~ 5,700원</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="n">
-        <v>3300000</v>
-      </c>
-      <c r="J25" s="6" t="n">
-        <v>188.1</v>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr"/>
@@ -4876,17 +4876,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>바로팜</t>
+          <t>하나에어로다이내믹스</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>전자상거래 소매 중개업</t>
+          <t>항공기용 부품 제조업</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -4901,38 +4901,38 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,400 ~ 20,200원</t>
+          <t>4,700 ~ 5,700원</t>
         </is>
       </c>
       <c r="I26" s="5" t="n">
-        <v>1335000</v>
+        <v>3300000</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>269.7</v>
+        <v>188.1</v>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
+          <t>아이비케이투자증권㈜ 02-6915-5337, 02-6915-5794, 02-6915-5361</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr"/>
@@ -4943,142 +4943,138 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>바로팜</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>전자상거래 소매 중개업</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>16,400 ~ 20,200원</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>1335000</v>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>269.7</v>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>미래에셋증권㈜ 02-3774-7017, 7151, 6805 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>엠비디</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>물질 검사, 측정 및 분석기구 제조업</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>9,600 ~ 11,700원</t>
         </is>
       </c>
-      <c r="I27" s="10" t="n">
+      <c r="I28" s="10" t="n">
         <v>1500000</v>
       </c>
-      <c r="J27" s="11" t="n">
+      <c r="J28" s="11" t="n">
         <v>175.5</v>
       </c>
-      <c r="K27" s="9" t="inlineStr">
+      <c r="K28" s="9" t="inlineStr">
         <is>
           <t>하나증권㈜ 02-3771-3482, 3278, 3499, 3120</t>
         </is>
       </c>
-      <c r="L27" s="8" t="inlineStr">
+      <c r="L28" s="8" t="inlineStr">
         <is>
           <t>2026-11-12</t>
         </is>
       </c>
-      <c r="M27" s="8" t="inlineStr">
+      <c r="M28" s="8" t="inlineStr">
         <is>
           <t>2026-11-17</t>
         </is>
       </c>
-      <c r="N27" s="8" t="inlineStr"/>
-      <c r="O27" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>래블업</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>시스템 소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>19,000 ~ 22,000원</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="n">
-        <v>1635000</v>
-      </c>
-      <c r="J28" s="6" t="n">
-        <v>359.7</v>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>NH투자증권 02-768-7462, 7467</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="O28" s="7" t="inlineStr">
+      <c r="N28" s="8" t="inlineStr"/>
+      <c r="O28" s="12" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -5087,60 +5083,68 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>래블업</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>시스템 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>이에스티</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>그 외 기타 전자부품 제조업</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>정정-변경없음</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,600 ~ 12,400원</t>
+          <t>19,000 ~ 22,000원</t>
         </is>
       </c>
       <c r="I29" s="5" t="n">
-        <v>1650000</v>
+        <v>1635000</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>204.6</v>
+        <v>359.7</v>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>NH투자증권 02-768-7462, 7467</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="O29" s="7" t="inlineStr">
@@ -5152,136 +5156,132 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>이에스티</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>그 외 기타 전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>[기재정정] 증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>정정-변경없음</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>10,600 ~ 12,400원</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>204.6</v>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2963, 02-769-2961</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="O30" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>에이엘로봇</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>기타 기계 및 장비 제조업</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>정정-변경(수요예측)</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>15,700 ~ 17,600원</t>
         </is>
       </c>
-      <c r="I30" s="5" t="n">
+      <c r="I31" s="5" t="n">
         <v>1800000</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="J31" s="6" t="n">
         <v>316.8</v>
       </c>
-      <c r="K30" s="3" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>대신증권㈜ 02-769-2429, 02-769-2053</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>2026-11-11</t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr"/>
-      <c r="O30" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>아델</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>의학 및 약학 연구개발업</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>18,000 ~ 25,000원</t>
-        </is>
-      </c>
-      <c r="I31" s="10" t="n">
-        <v>1627500</v>
-      </c>
-      <c r="J31" s="11" t="n">
-        <v>406.9</v>
-      </c>
-      <c r="K31" s="9" t="inlineStr">
-        <is>
-          <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
-        </is>
-      </c>
-      <c r="L31" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-      <c r="M31" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="N31" s="8" t="inlineStr"/>
-      <c r="O31" s="12" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="7" t="inlineStr">
         <is>
           <t>열기</t>
         </is>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>SimwonAmericaCorp.</t>
+          <t>아델</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>자동차 신품 부품 제조업</t>
+          <t>의학 및 약학 연구개발업</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
@@ -5310,19 +5310,43 @@
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>수요예측 항목 없음(원문 확인)</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr"/>
-      <c r="G32" s="8" t="inlineStr"/>
-      <c r="H32" s="8" t="inlineStr"/>
-      <c r="I32" s="10" t="inlineStr"/>
-      <c r="J32" s="11" t="inlineStr"/>
-      <c r="K32" s="9" t="inlineStr"/>
-      <c r="L32" s="8" t="inlineStr"/>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>18,000 ~ 25,000원</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="n">
+        <v>1627500</v>
+      </c>
+      <c r="J32" s="11" t="n">
+        <v>406.9</v>
+      </c>
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>삼성증권 02-2020-8213, 6661 / 미래에셋증권㈜ 02-3774-3775</t>
+        </is>
+      </c>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
       <c r="M32" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="N32" s="8" t="inlineStr"/>
@@ -5335,63 +5359,39 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>다비오</t>
+          <t>SimwonAmericaCorp.</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>응용 소프트웨어 개발 및 공급업</t>
+          <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
+          <t>증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="inlineStr">
-        <is>
-          <t>12,300 ~ 16,600원</t>
-        </is>
-      </c>
-      <c r="I33" s="10" t="n">
-        <v>750000</v>
-      </c>
-      <c r="J33" s="11" t="n">
-        <v>124.5</v>
-      </c>
-      <c r="K33" s="9" t="inlineStr">
-        <is>
-          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
-        </is>
-      </c>
-      <c r="L33" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
+          <t>수요예측 항목 없음(원문 확인)</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr"/>
+      <c r="G33" s="8" t="inlineStr"/>
+      <c r="H33" s="8" t="inlineStr"/>
+      <c r="I33" s="10" t="inlineStr"/>
+      <c r="J33" s="11" t="inlineStr"/>
+      <c r="K33" s="9" t="inlineStr"/>
+      <c r="L33" s="8" t="inlineStr"/>
       <c r="M33" s="8" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="N33" s="8" t="inlineStr"/>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>엔키화이트햇</t>
+          <t>다비오</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>증권신고서(지분증권)</t>
+          <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
@@ -5429,38 +5429,38 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>13,000 ~ 16,500원</t>
+          <t>12,300 ~ 16,600원</t>
         </is>
       </c>
       <c r="I34" s="10" t="n">
-        <v>1258000</v>
+        <v>750000</v>
       </c>
       <c r="J34" s="11" t="n">
-        <v>207.6</v>
+        <v>124.5</v>
       </c>
       <c r="K34" s="9" t="inlineStr">
         <is>
-          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
+          <t>대신증권㈜ 02-769-2752, 02-769-2294</t>
         </is>
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="M34" s="8" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="N34" s="8" t="inlineStr"/>
@@ -5478,12 +5478,12 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>영광와이케이엠씨</t>
+          <t>엔키화이트햇</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>그 외 기타 금속가공업</t>
+          <t>응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
@@ -5498,38 +5498,38 @@
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>9,400 ~ 11,000원</t>
+          <t>13,000 ~ 16,500원</t>
         </is>
       </c>
       <c r="I35" s="10" t="n">
-        <v>1694840</v>
+        <v>1258000</v>
       </c>
       <c r="J35" s="11" t="n">
-        <v>186.4</v>
+        <v>207.6</v>
       </c>
       <c r="K35" s="9" t="inlineStr">
         <is>
-          <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
+          <t>신영증권㈜ 02-2004-9554, 9414, 9230</t>
         </is>
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="M35" s="8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="N35" s="8" t="inlineStr"/>
@@ -5540,284 +5540,288 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>영광와이케이엠씨</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>그 외 기타 금속가공업</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>증권신고서(지분증권)</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>9,400 ~ 11,000원</t>
+        </is>
+      </c>
+      <c r="I36" s="10" t="n">
+        <v>1694840</v>
+      </c>
+      <c r="J36" s="11" t="n">
+        <v>186.4</v>
+      </c>
+      <c r="K36" s="9" t="inlineStr">
+        <is>
+          <t>대신증권㈜ 02-769-2743, 02-769-2741</t>
+        </is>
+      </c>
+      <c r="L36" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="M36" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="N36" s="8" t="inlineStr"/>
+      <c r="O36" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>영광</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>수상 금속 골조 구조재 제조업</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>14,000 ~ 17,000원</t>
         </is>
       </c>
-      <c r="I36" s="5" t="n">
+      <c r="I37" s="5" t="n">
         <v>1695000</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="J37" s="6" t="n">
         <v>288.1</v>
       </c>
-      <c r="K36" s="3" t="inlineStr">
+      <c r="K37" s="3" t="inlineStr">
         <is>
           <t>한국투자증권㈜ 02-3276-5958, 6917</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="O36" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="O37" s="7" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>인텔리빅스</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>시스템ㆍ응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
+      <c r="F38" s="8" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="G37" s="8" t="inlineStr">
+      <c r="G38" s="8" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H37" s="8" t="inlineStr">
+      <c r="H38" s="8" t="inlineStr">
         <is>
           <t>7,600 ~ 9,000원</t>
         </is>
       </c>
-      <c r="I37" s="10" t="n">
+      <c r="I38" s="10" t="n">
         <v>1875000</v>
       </c>
-      <c r="J37" s="11" t="n">
+      <c r="J38" s="11" t="n">
         <v>168.8</v>
       </c>
-      <c r="K37" s="9" t="inlineStr">
+      <c r="K38" s="9" t="inlineStr">
         <is>
           <t>미래에셋증권㈜ 02-3774-7147, 3921, 6085 / 미래에셋증권㈜ 02-3774-3775</t>
         </is>
       </c>
-      <c r="L37" s="8" t="inlineStr">
+      <c r="L38" s="8" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="M37" s="8" t="inlineStr">
+      <c r="M38" s="8" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="N37" s="8" t="inlineStr">
+      <c r="N38" s="8" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="O37" s="12" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="O38" s="12" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>아이엠기업인수목적1호</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>스팩</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>[기재정정] 증권신고서(지분증권)</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>정정-변경없음</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>2,000원 (단일가)</t>
         </is>
       </c>
-      <c r="I38" s="5" t="n">
+      <c r="I39" s="5" t="n">
         <v>3750000</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="J39" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="K38" s="3" t="inlineStr">
+      <c r="K39" s="3" t="inlineStr">
         <is>
           <t>아이엠증권 02-2122-9688, 9485</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="L39" s="2" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="M39" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t>2026-11-04</t>
         </is>
       </c>
-      <c r="O38" s="7" t="inlineStr">
-        <is>
-          <t>열기</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>아이엠기업인수목적1호</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>스팩</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>[기재정정] 증권신고서(지분증권)</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="H39" s="8" t="inlineStr">
-        <is>
-          <t>2,000원 (단일가)</t>
-        </is>
-      </c>
-      <c r="I39" s="10" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="J39" s="11" t="n">
-        <v>75</v>
-      </c>
-      <c r="K39" s="9" t="inlineStr">
-        <is>
-          <t>아이엠증권 02-212